--- a/config/testdata/testdata.xlsx
+++ b/config/testdata/testdata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20412"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mobile_Apps\config\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC07D15-0D61-4C3D-9EBD-0905638E7CC5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CD63B1-6FA7-4EC4-A969-44F4EA656634}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Happy_Path_Patient_Web_and_MR" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="1231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="1234">
   <si>
     <t>KEY</t>
   </si>
@@ -3738,20 +3738,28 @@
     <t>NEW_EMAIL</t>
   </si>
   <si>
-    <t>RubenmtbtbPatient@mmh-demo.com</t>
-  </si>
-  <si>
-    <t>joe;PatBtb;joePat12@mmh-demo.com;Manage@123;2001;Male;African</t>
-  </si>
-  <si>
-    <t>joePat12@mmh-demo.com</t>
+    <t>uatbtb;SelfRegPatient;AutoBtbSelfRegpat@mmh-demo.com;Manage@123;2002;Male;African</t>
+  </si>
+  <si>
+    <t>BTB_NEW_PATIENT_DETAILS</t>
+  </si>
+  <si>
+    <t>AutoBtbSelfRegpat76@mmh-demo.c</t>
+  </si>
+  <si>
+    <t>Automation1_Loc1;Pacifen 10mg Tab;48 Hours;GP2WHITE</t>
+  </si>
+  <si>
+    <t>https://v2webhotfix.mmh-demo.com/</t>
+  </si>
+  <si>
+    <t>16 May 2024;Consult In Surgery;GP2WHITE;Automation1_Loc1;16 May 2024 10:11:36 PM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="27">
     <font>
       <sz val="11"/>
@@ -4567,11 +4575,11 @@
   <dimension ref="A1:W1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="69.5703125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="161.42578125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="161.140625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" width="102.28515625" collapsed="true"/>
-    <col min="5" max="23" customWidth="true" width="8.85546875" collapsed="true"/>
+    <col min="1" max="1" width="69.5703125" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="161.42578125" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="161.140625" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="102.28515625" customWidth="1" collapsed="1"/>
+    <col min="5" max="23" width="8.85546875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="13.5" customHeight="1">
@@ -4612,7 +4620,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="66" t="s">
-        <v>4</v>
+        <v>1232</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>5</v>
@@ -8786,7 +8794,7 @@
         <v>228</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>229</v>
+        <v>1233</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>1182</v>
@@ -15217,9 +15225,9 @@
   <dimension ref="A1:V1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="54.140625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="81.0" collapsed="true"/>
-    <col min="3" max="22" customWidth="true" width="8.7109375" collapsed="true"/>
+    <col min="1" max="1" width="54.140625" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="81" customWidth="1" collapsed="1"/>
+    <col min="3" max="22" width="8.7109375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -24700,13 +24708,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C1000"/>
+  <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="87.7109375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="158.28515625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="41.0" collapsed="true"/>
-    <col min="4" max="26" customWidth="true" width="8.7109375" collapsed="true"/>
+    <col min="1" max="1" width="87.7109375" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="158.28515625" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="41" customWidth="1" collapsed="1"/>
+    <col min="4" max="26" width="8.7109375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -24765,11 +24773,9 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7"/>
       <c r="B7" s="41" t="s">
         <v>456</v>
       </c>
-      <c r="C7"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="42" t="s">
@@ -24778,7 +24784,6 @@
       <c r="B8" s="14" t="s">
         <v>458</v>
       </c>
-      <c r="C8"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="29" t="s">
@@ -24787,7 +24792,6 @@
       <c r="B9" s="29" t="s">
         <v>460</v>
       </c>
-      <c r="C9"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="29" t="s">
@@ -24796,7 +24800,6 @@
       <c r="B10" s="29" t="s">
         <v>462</v>
       </c>
-      <c r="C10"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="29" t="s">
@@ -24805,7 +24808,6 @@
       <c r="B11" s="29" t="s">
         <v>464</v>
       </c>
-      <c r="C11"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="29" t="s">
@@ -24814,7 +24816,6 @@
       <c r="B12" s="29" t="s">
         <v>466</v>
       </c>
-      <c r="C12"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="14" t="s">
@@ -24823,7 +24824,6 @@
       <c r="B13" s="14" t="s">
         <v>460</v>
       </c>
-      <c r="C13"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
@@ -24832,7 +24832,6 @@
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C14"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="14" t="s">
@@ -24841,7 +24840,6 @@
       <c r="B15" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C15"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="14" t="s">
@@ -24850,7 +24848,6 @@
       <c r="B16" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C16"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="14" t="s">
@@ -24859,7 +24856,6 @@
       <c r="B17" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C17"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="14" t="s">
@@ -24868,7 +24864,6 @@
       <c r="B18" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="C18"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="14" t="s">
@@ -24877,7 +24872,6 @@
       <c r="B19" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="C19"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="14" t="s">
@@ -24886,7 +24880,6 @@
       <c r="B20" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C20"/>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1">
       <c r="A21" s="14" t="s">
@@ -24895,7 +24888,6 @@
       <c r="B21" s="14" t="s">
         <v>473</v>
       </c>
-      <c r="C21"/>
     </row>
     <row r="22" spans="1:2" ht="15.75" customHeight="1">
       <c r="A22" s="14" t="s">
@@ -24904,7 +24896,6 @@
       <c r="B22" s="14" t="s">
         <v>475</v>
       </c>
-      <c r="C22"/>
     </row>
     <row r="23" spans="1:2" ht="15.75" customHeight="1">
       <c r="A23" s="14" t="s">
@@ -24913,7 +24904,6 @@
       <c r="B23" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="C23"/>
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1">
       <c r="A24" s="14" t="s">
@@ -24922,7 +24912,6 @@
       <c r="B24" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="C24"/>
     </row>
     <row r="25" spans="1:2" ht="15.75" customHeight="1">
       <c r="A25" s="14" t="s">
@@ -24931,7 +24920,6 @@
       <c r="B25" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C25"/>
     </row>
     <row r="26" spans="1:2" ht="15.75" customHeight="1">
       <c r="A26" s="14" t="s">
@@ -24940,7 +24928,6 @@
       <c r="B26" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="C26"/>
     </row>
     <row r="27" spans="1:2" ht="15.75" customHeight="1">
       <c r="A27" s="14" t="s">
@@ -24949,7 +24936,6 @@
       <c r="B27" s="14" t="s">
         <v>452</v>
       </c>
-      <c r="C27"/>
     </row>
     <row r="28" spans="1:2" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
@@ -24958,7 +24944,6 @@
       <c r="B28" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C28"/>
     </row>
     <row r="29" spans="1:2" ht="15.75" customHeight="1">
       <c r="A29" s="14" t="s">
@@ -24967,25 +24952,14 @@
       <c r="B29" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="C29"/>
-    </row>
-    <row r="30" spans="1:2" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-    </row>
+    </row>
+    <row r="30" spans="1:2" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="31" spans="1:2" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A31"/>
       <c r="B31" s="57" t="s">
         <v>684</v>
       </c>
-      <c r="C31"/>
-    </row>
-    <row r="32" spans="1:2" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A32"/>
-      <c r="B32"/>
-      <c r="C32"/>
-    </row>
+    </row>
+    <row r="32" spans="1:2" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A33" s="35" t="s">
         <v>528</v>
@@ -24997,11 +24971,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A34"/>
-      <c r="B34"/>
-      <c r="C34"/>
-    </row>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A35" s="35" t="s">
         <v>687</v>
@@ -25046,11 +25016,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A39"/>
-      <c r="B39"/>
-      <c r="C39"/>
-    </row>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A40" s="35" t="s">
         <v>695</v>
@@ -25084,11 +25050,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A43"/>
-      <c r="B43"/>
-      <c r="C43"/>
-    </row>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="44" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A44" s="35" t="s">
         <v>703</v>
@@ -25111,11 +25073,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A46"/>
-      <c r="B46"/>
-      <c r="C46"/>
-    </row>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="47" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A47" s="35" t="s">
         <v>707</v>
@@ -25127,11 +25085,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A48"/>
-      <c r="B48"/>
-      <c r="C48"/>
-    </row>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="49" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A49" s="23" t="s">
         <v>710</v>
@@ -25154,23 +25108,13 @@
         <v>714</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A51"/>
-      <c r="B51"/>
-      <c r="C51"/>
-    </row>
+    <row r="51" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="52" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A52"/>
       <c r="B52" s="43" t="s">
         <v>481</v>
       </c>
-      <c r="C52"/>
-    </row>
-    <row r="53" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A53"/>
-      <c r="B53"/>
-      <c r="C53"/>
-    </row>
+    </row>
+    <row r="53" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="54" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A54" s="44" t="s">
         <v>482</v>
@@ -25336,17 +25280,11 @@
         <v>523</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A69"/>
-      <c r="B69"/>
-      <c r="C69"/>
-    </row>
+    <row r="69" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="70" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A70"/>
       <c r="B70" s="43" t="s">
         <v>524</v>
       </c>
-      <c r="C70"/>
     </row>
     <row r="71" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A71" s="35" t="s">
@@ -25414,11 +25352,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A77"/>
-      <c r="B77"/>
-      <c r="C77"/>
-    </row>
+    <row r="77" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="78" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A78" s="1" t="s">
         <v>88</v>
@@ -25441,11 +25375,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A80"/>
-      <c r="B80"/>
-      <c r="C80"/>
-    </row>
+    <row r="80" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="81" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A81" s="23" t="s">
         <v>70</v>
@@ -25468,11 +25398,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A83"/>
-      <c r="B83"/>
-      <c r="C83"/>
-    </row>
+    <row r="83" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="84" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A84" s="35" t="s">
         <v>100</v>
@@ -25495,11 +25421,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A86"/>
-      <c r="B86"/>
-      <c r="C86"/>
-    </row>
+    <row r="86" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="87" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A87" s="35" t="s">
         <v>79</v>
@@ -25522,17 +25444,11 @@
         <v>549</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A89"/>
-      <c r="B89"/>
-      <c r="C89"/>
-    </row>
+    <row r="89" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="90" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A90"/>
       <c r="B90" s="68" t="s">
         <v>1194</v>
       </c>
-      <c r="C90"/>
     </row>
     <row r="91" spans="1:3" ht="15.75" customHeight="1">
       <c r="A91" t="s">
@@ -25545,11 +25461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A92"/>
-      <c r="B92"/>
-      <c r="C92"/>
-    </row>
+    <row r="92" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="93" spans="1:3" ht="15.75" customHeight="1">
       <c r="A93" t="s">
         <v>1196</v>
@@ -25572,11 +25484,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A95"/>
-      <c r="B95"/>
-      <c r="C95"/>
-    </row>
+    <row r="95" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="96" spans="1:3" ht="15.75" customHeight="1">
       <c r="A96" t="s">
         <v>1204</v>
@@ -25599,11 +25507,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A98"/>
-      <c r="B98"/>
-      <c r="C98"/>
-    </row>
+    <row r="98" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="99" spans="1:3" ht="15.75" customHeight="1">
       <c r="A99" t="s">
         <v>1205</v>
@@ -25637,11 +25541,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A102"/>
-      <c r="B102"/>
-      <c r="C102"/>
-    </row>
+    <row r="102" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="103" spans="1:3" ht="15.75" customHeight="1">
       <c r="A103" t="s">
         <v>1218</v>
@@ -25653,11 +25553,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A104"/>
-      <c r="B104"/>
-      <c r="C104"/>
-    </row>
+    <row r="104" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="105" spans="1:3" ht="15.75" customHeight="1">
       <c r="A105" t="s">
         <v>1214</v>
@@ -25674,7 +25570,7 @@
         <v>1216</v>
       </c>
       <c r="B106" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C106" t="s">
         <v>1217</v>
@@ -25702,11 +25598,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A109"/>
-      <c r="B109"/>
-      <c r="C109"/>
-    </row>
+    <row r="109" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="110" spans="1:3" ht="15.75" customHeight="1">
       <c r="A110" t="s">
         <v>1221</v>
@@ -25714,7 +25606,6 @@
       <c r="B110" t="s">
         <v>1222</v>
       </c>
-      <c r="C110"/>
     </row>
     <row r="111" spans="1:3" ht="15.75" customHeight="1">
       <c r="A111" t="s">
@@ -25723,7 +25614,6 @@
       <c r="B111" t="s">
         <v>1223</v>
       </c>
-      <c r="C111"/>
     </row>
     <row r="112" spans="1:3" ht="15.75" customHeight="1">
       <c r="A112" t="s">
@@ -25732,13 +25622,8 @@
       <c r="B112" s="70" t="s">
         <v>1226</v>
       </c>
-      <c r="C112"/>
-    </row>
-    <row r="113" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A113"/>
-      <c r="B113"/>
-      <c r="C113"/>
-    </row>
+    </row>
+    <row r="113" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="114" spans="1:3" ht="15.75" customHeight="1">
       <c r="A114" t="s">
         <v>1227</v>
@@ -25751,4435 +25636,898 @@
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A115"/>
-      <c r="B115"/>
-      <c r="C115"/>
-    </row>
-    <row r="116" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A116"/>
-      <c r="B116"/>
-      <c r="C116"/>
-    </row>
-    <row r="117" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A117"/>
-      <c r="B117"/>
-      <c r="C117"/>
-    </row>
-    <row r="118" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A118"/>
-      <c r="B118"/>
-      <c r="C118"/>
-    </row>
-    <row r="119" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A119"/>
-      <c r="B119"/>
-      <c r="C119"/>
-    </row>
-    <row r="120" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A120"/>
-      <c r="B120"/>
-      <c r="C120"/>
-    </row>
-    <row r="121" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A121"/>
-      <c r="B121"/>
-      <c r="C121"/>
-    </row>
-    <row r="122" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A122"/>
-      <c r="B122"/>
-      <c r="C122"/>
-    </row>
-    <row r="123" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A123"/>
-      <c r="B123"/>
-      <c r="C123"/>
-    </row>
-    <row r="124" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A124"/>
-      <c r="B124"/>
-      <c r="C124"/>
-    </row>
-    <row r="125" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A125"/>
-      <c r="B125"/>
-      <c r="C125"/>
-    </row>
-    <row r="126" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A126"/>
-      <c r="B126"/>
-      <c r="C126"/>
-    </row>
-    <row r="127" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A127"/>
-      <c r="B127"/>
-      <c r="C127"/>
-    </row>
-    <row r="128" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A128"/>
-      <c r="B128"/>
-      <c r="C128"/>
-    </row>
-    <row r="129" ht="15.75" customHeight="1">
-      <c r="A129"/>
-      <c r="B129"/>
-      <c r="C129"/>
-    </row>
-    <row r="130" ht="15.75" customHeight="1">
-      <c r="A130"/>
-      <c r="B130"/>
-      <c r="C130"/>
-    </row>
-    <row r="131" ht="15.75" customHeight="1">
-      <c r="A131"/>
-      <c r="B131"/>
-      <c r="C131"/>
-    </row>
-    <row r="132" ht="15.75" customHeight="1">
-      <c r="A132"/>
-      <c r="B132"/>
-      <c r="C132"/>
-    </row>
-    <row r="133" ht="15.75" customHeight="1">
-      <c r="A133"/>
-      <c r="B133"/>
-      <c r="C133"/>
-    </row>
-    <row r="134" ht="15.75" customHeight="1">
-      <c r="A134"/>
-      <c r="B134"/>
-      <c r="C134"/>
-    </row>
-    <row r="135" ht="15.75" customHeight="1">
-      <c r="A135"/>
-      <c r="B135"/>
-      <c r="C135"/>
-    </row>
-    <row r="136" ht="15.75" customHeight="1">
-      <c r="A136"/>
-      <c r="B136"/>
-      <c r="C136"/>
-    </row>
-    <row r="137" ht="15.75" customHeight="1">
-      <c r="A137"/>
-      <c r="B137"/>
-      <c r="C137"/>
-    </row>
-    <row r="138" ht="15.75" customHeight="1">
-      <c r="A138"/>
-      <c r="B138"/>
-      <c r="C138"/>
-    </row>
-    <row r="139" ht="15.75" customHeight="1">
-      <c r="A139"/>
-      <c r="B139"/>
-      <c r="C139"/>
-    </row>
-    <row r="140" ht="15.75" customHeight="1">
-      <c r="A140"/>
-      <c r="B140"/>
-      <c r="C140"/>
-    </row>
-    <row r="141" ht="15.75" customHeight="1">
-      <c r="A141"/>
-      <c r="B141"/>
-      <c r="C141"/>
-    </row>
-    <row r="142" ht="15.75" customHeight="1">
-      <c r="A142"/>
-      <c r="B142"/>
-      <c r="C142"/>
-    </row>
-    <row r="143" ht="15.75" customHeight="1">
-      <c r="A143"/>
-      <c r="B143"/>
-      <c r="C143"/>
-    </row>
-    <row r="144" ht="15.75" customHeight="1">
-      <c r="A144"/>
-      <c r="B144"/>
-      <c r="C144"/>
-    </row>
-    <row r="145" ht="15.75" customHeight="1">
-      <c r="A145"/>
-      <c r="B145"/>
-      <c r="C145"/>
-    </row>
-    <row r="146" ht="15.75" customHeight="1">
-      <c r="A146"/>
-      <c r="B146"/>
-      <c r="C146"/>
-    </row>
-    <row r="147" ht="15.75" customHeight="1">
-      <c r="A147"/>
-      <c r="B147"/>
-      <c r="C147"/>
-    </row>
-    <row r="148" ht="15.75" customHeight="1">
-      <c r="A148"/>
-      <c r="B148"/>
-      <c r="C148"/>
-    </row>
-    <row r="149" ht="15.75" customHeight="1">
-      <c r="A149"/>
-      <c r="B149"/>
-      <c r="C149"/>
-    </row>
-    <row r="150" ht="15.75" customHeight="1">
-      <c r="A150"/>
-      <c r="B150"/>
-      <c r="C150"/>
-    </row>
-    <row r="151" ht="15.75" customHeight="1">
-      <c r="A151"/>
-      <c r="B151"/>
-      <c r="C151"/>
-    </row>
-    <row r="152" ht="15.75" customHeight="1">
-      <c r="A152"/>
-      <c r="B152"/>
-      <c r="C152"/>
-    </row>
-    <row r="153" ht="15.75" customHeight="1">
-      <c r="A153"/>
-      <c r="B153"/>
-      <c r="C153"/>
-    </row>
-    <row r="154" ht="15.75" customHeight="1">
-      <c r="A154"/>
-      <c r="B154"/>
-      <c r="C154"/>
-    </row>
-    <row r="155" ht="15.75" customHeight="1">
-      <c r="A155"/>
-      <c r="B155"/>
-      <c r="C155"/>
-    </row>
-    <row r="156" ht="15.75" customHeight="1">
-      <c r="A156"/>
-      <c r="B156"/>
-      <c r="C156"/>
-    </row>
-    <row r="157" ht="15.75" customHeight="1">
-      <c r="A157"/>
-      <c r="B157"/>
-      <c r="C157"/>
-    </row>
-    <row r="158" ht="15.75" customHeight="1">
-      <c r="A158"/>
-      <c r="B158"/>
-      <c r="C158"/>
-    </row>
-    <row r="159" ht="15.75" customHeight="1">
-      <c r="A159"/>
-      <c r="B159"/>
-      <c r="C159"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1">
-      <c r="A160"/>
-      <c r="B160"/>
-      <c r="C160"/>
-    </row>
-    <row r="161" ht="15.75" customHeight="1">
-      <c r="A161"/>
-      <c r="B161"/>
-      <c r="C161"/>
-    </row>
-    <row r="162" ht="15.75" customHeight="1">
-      <c r="A162"/>
-      <c r="B162"/>
-      <c r="C162"/>
-    </row>
-    <row r="163" ht="15.75" customHeight="1">
-      <c r="A163"/>
-      <c r="B163"/>
-      <c r="C163"/>
-    </row>
-    <row r="164" ht="15.75" customHeight="1">
-      <c r="A164"/>
-      <c r="B164"/>
-      <c r="C164"/>
-    </row>
-    <row r="165" ht="15.75" customHeight="1">
-      <c r="A165"/>
-      <c r="B165"/>
-      <c r="C165"/>
-    </row>
-    <row r="166" ht="15.75" customHeight="1">
-      <c r="A166"/>
-      <c r="B166"/>
-      <c r="C166"/>
-    </row>
-    <row r="167" ht="15.75" customHeight="1">
-      <c r="A167"/>
-      <c r="B167"/>
-      <c r="C167"/>
-    </row>
-    <row r="168" ht="15.75" customHeight="1">
-      <c r="A168"/>
-      <c r="B168"/>
-      <c r="C168"/>
-    </row>
-    <row r="169" ht="15.75" customHeight="1">
-      <c r="A169"/>
-      <c r="B169"/>
-      <c r="C169"/>
-    </row>
-    <row r="170" ht="15.75" customHeight="1">
-      <c r="A170"/>
-      <c r="B170"/>
-      <c r="C170"/>
-    </row>
-    <row r="171" ht="15.75" customHeight="1">
-      <c r="A171"/>
-      <c r="B171"/>
-      <c r="C171"/>
-    </row>
-    <row r="172" ht="15.75" customHeight="1">
-      <c r="A172"/>
-      <c r="B172"/>
-      <c r="C172"/>
-    </row>
-    <row r="173" ht="15.75" customHeight="1">
-      <c r="A173"/>
-      <c r="B173"/>
-      <c r="C173"/>
-    </row>
-    <row r="174" ht="15.75" customHeight="1">
-      <c r="A174"/>
-      <c r="B174"/>
-      <c r="C174"/>
-    </row>
-    <row r="175" ht="15.75" customHeight="1">
-      <c r="A175"/>
-      <c r="B175"/>
-      <c r="C175"/>
-    </row>
-    <row r="176" ht="15.75" customHeight="1">
-      <c r="A176"/>
-      <c r="B176"/>
-      <c r="C176"/>
-    </row>
-    <row r="177" ht="15.75" customHeight="1">
-      <c r="A177"/>
-      <c r="B177"/>
-      <c r="C177"/>
-    </row>
-    <row r="178" ht="15.75" customHeight="1">
-      <c r="A178"/>
-      <c r="B178"/>
-      <c r="C178"/>
-    </row>
-    <row r="179" ht="15.75" customHeight="1">
-      <c r="A179"/>
-      <c r="B179"/>
-      <c r="C179"/>
-    </row>
-    <row r="180" ht="15.75" customHeight="1">
-      <c r="A180"/>
-      <c r="B180"/>
-      <c r="C180"/>
-    </row>
-    <row r="181" ht="15.75" customHeight="1">
-      <c r="A181"/>
-      <c r="B181"/>
-      <c r="C181"/>
-    </row>
-    <row r="182" ht="15.75" customHeight="1">
-      <c r="A182"/>
-      <c r="B182"/>
-      <c r="C182"/>
-    </row>
-    <row r="183" ht="15.75" customHeight="1">
-      <c r="A183"/>
-      <c r="B183"/>
-      <c r="C183"/>
-    </row>
-    <row r="184" ht="15.75" customHeight="1">
-      <c r="A184"/>
-      <c r="B184"/>
-      <c r="C184"/>
-    </row>
-    <row r="185" ht="15.75" customHeight="1">
-      <c r="A185"/>
-      <c r="B185"/>
-      <c r="C185"/>
-    </row>
-    <row r="186" ht="15.75" customHeight="1">
-      <c r="A186"/>
-      <c r="B186"/>
-      <c r="C186"/>
-    </row>
-    <row r="187" ht="15.75" customHeight="1">
-      <c r="A187"/>
-      <c r="B187"/>
-      <c r="C187"/>
-    </row>
-    <row r="188" ht="15.75" customHeight="1">
-      <c r="A188"/>
-      <c r="B188"/>
-      <c r="C188"/>
-    </row>
-    <row r="189" ht="15.75" customHeight="1">
-      <c r="A189"/>
-      <c r="B189"/>
-      <c r="C189"/>
-    </row>
-    <row r="190" ht="15.75" customHeight="1">
-      <c r="A190"/>
-      <c r="B190"/>
-      <c r="C190"/>
-    </row>
-    <row r="191" ht="15.75" customHeight="1">
-      <c r="A191"/>
-      <c r="B191"/>
-      <c r="C191"/>
-    </row>
-    <row r="192" ht="15.75" customHeight="1">
-      <c r="A192"/>
-      <c r="B192"/>
-      <c r="C192"/>
-    </row>
-    <row r="193" ht="15.75" customHeight="1">
-      <c r="A193"/>
-      <c r="B193"/>
-      <c r="C193"/>
-    </row>
-    <row r="194" ht="15.75" customHeight="1">
-      <c r="A194"/>
-      <c r="B194"/>
-      <c r="C194"/>
-    </row>
-    <row r="195" ht="15.75" customHeight="1">
-      <c r="A195"/>
-      <c r="B195"/>
-      <c r="C195"/>
-    </row>
-    <row r="196" ht="15.75" customHeight="1">
-      <c r="A196"/>
-      <c r="B196"/>
-      <c r="C196"/>
-    </row>
-    <row r="197" ht="15.75" customHeight="1">
-      <c r="A197"/>
-      <c r="B197"/>
-      <c r="C197"/>
-    </row>
-    <row r="198" ht="15.75" customHeight="1">
-      <c r="A198"/>
-      <c r="B198"/>
-      <c r="C198"/>
-    </row>
-    <row r="199" ht="15.75" customHeight="1">
-      <c r="A199"/>
-      <c r="B199"/>
-      <c r="C199"/>
-    </row>
-    <row r="200" ht="15.75" customHeight="1">
-      <c r="A200"/>
-      <c r="B200"/>
-      <c r="C200"/>
-    </row>
-    <row r="201" ht="15.75" customHeight="1">
-      <c r="A201"/>
-      <c r="B201"/>
-      <c r="C201"/>
-    </row>
-    <row r="202" ht="15.75" customHeight="1">
-      <c r="A202"/>
-      <c r="B202"/>
-      <c r="C202"/>
-    </row>
-    <row r="203" ht="15.75" customHeight="1">
-      <c r="A203"/>
-      <c r="B203"/>
-      <c r="C203"/>
-    </row>
-    <row r="204" ht="15.75" customHeight="1">
-      <c r="A204"/>
-      <c r="B204"/>
-      <c r="C204"/>
-    </row>
-    <row r="205" ht="15.75" customHeight="1">
-      <c r="A205"/>
-      <c r="B205"/>
-      <c r="C205"/>
-    </row>
-    <row r="206" ht="15.75" customHeight="1">
-      <c r="A206"/>
-      <c r="B206"/>
-      <c r="C206"/>
-    </row>
-    <row r="207" ht="15.75" customHeight="1">
-      <c r="A207"/>
-      <c r="B207"/>
-      <c r="C207"/>
-    </row>
-    <row r="208" ht="15.75" customHeight="1">
-      <c r="A208"/>
-      <c r="B208"/>
-      <c r="C208"/>
-    </row>
-    <row r="209" ht="15.75" customHeight="1">
-      <c r="A209"/>
-      <c r="B209"/>
-      <c r="C209"/>
-    </row>
-    <row r="210" ht="15.75" customHeight="1">
-      <c r="A210"/>
-      <c r="B210"/>
-      <c r="C210"/>
-    </row>
-    <row r="211" ht="15.75" customHeight="1">
-      <c r="A211"/>
-      <c r="B211"/>
-      <c r="C211"/>
-    </row>
-    <row r="212" ht="15.75" customHeight="1">
-      <c r="A212"/>
-      <c r="B212"/>
-      <c r="C212"/>
-    </row>
-    <row r="213" ht="15.75" customHeight="1">
-      <c r="A213"/>
-      <c r="B213"/>
-      <c r="C213"/>
-    </row>
-    <row r="214" ht="15.75" customHeight="1">
-      <c r="A214"/>
-      <c r="B214"/>
-      <c r="C214"/>
-    </row>
-    <row r="215" ht="15.75" customHeight="1">
-      <c r="A215"/>
-      <c r="B215"/>
-      <c r="C215"/>
-    </row>
-    <row r="216" ht="15.75" customHeight="1">
-      <c r="A216"/>
-      <c r="B216"/>
-      <c r="C216"/>
-    </row>
-    <row r="217" ht="15.75" customHeight="1">
-      <c r="A217"/>
-      <c r="B217"/>
-      <c r="C217"/>
-    </row>
-    <row r="218" ht="15.75" customHeight="1">
-      <c r="A218"/>
-      <c r="B218"/>
-      <c r="C218"/>
-    </row>
-    <row r="219" ht="15.75" customHeight="1">
-      <c r="A219"/>
-      <c r="B219"/>
-      <c r="C219"/>
-    </row>
-    <row r="220" ht="15.75" customHeight="1">
-      <c r="A220"/>
-      <c r="B220"/>
-      <c r="C220"/>
-    </row>
-    <row r="221" ht="15.75" customHeight="1">
-      <c r="A221"/>
-      <c r="B221"/>
-      <c r="C221"/>
-    </row>
-    <row r="222" ht="15.75" customHeight="1">
-      <c r="A222"/>
-      <c r="B222"/>
-      <c r="C222"/>
-    </row>
-    <row r="223" ht="15.75" customHeight="1">
-      <c r="A223"/>
-      <c r="B223"/>
-      <c r="C223"/>
-    </row>
-    <row r="224" ht="15.75" customHeight="1">
-      <c r="A224"/>
-      <c r="B224"/>
-      <c r="C224"/>
-    </row>
-    <row r="225" ht="15.75" customHeight="1">
-      <c r="A225"/>
-      <c r="B225"/>
-      <c r="C225"/>
-    </row>
-    <row r="226" ht="15.75" customHeight="1">
-      <c r="A226"/>
-      <c r="B226"/>
-      <c r="C226"/>
-    </row>
-    <row r="227" ht="15.75" customHeight="1">
-      <c r="A227"/>
-      <c r="B227"/>
-      <c r="C227"/>
-    </row>
-    <row r="228" ht="15.75" customHeight="1">
-      <c r="A228"/>
-      <c r="B228"/>
-      <c r="C228"/>
-    </row>
-    <row r="229" ht="15.75" customHeight="1">
-      <c r="A229"/>
-      <c r="B229"/>
-      <c r="C229"/>
-    </row>
-    <row r="230" ht="15.75" customHeight="1">
-      <c r="A230"/>
-      <c r="B230"/>
-      <c r="C230"/>
-    </row>
-    <row r="231" ht="15.75" customHeight="1">
-      <c r="A231"/>
-      <c r="B231"/>
-      <c r="C231"/>
-    </row>
-    <row r="232" ht="15.75" customHeight="1">
-      <c r="A232"/>
-      <c r="B232"/>
-      <c r="C232"/>
-    </row>
-    <row r="233" ht="15.75" customHeight="1">
-      <c r="A233"/>
-      <c r="B233"/>
-      <c r="C233"/>
-    </row>
-    <row r="234" ht="15.75" customHeight="1">
-      <c r="A234"/>
-      <c r="B234"/>
-      <c r="C234"/>
-    </row>
-    <row r="235" ht="15.75" customHeight="1">
-      <c r="A235"/>
-      <c r="B235"/>
-      <c r="C235"/>
-    </row>
-    <row r="236" ht="15.75" customHeight="1">
-      <c r="A236"/>
-      <c r="B236"/>
-      <c r="C236"/>
-    </row>
-    <row r="237" ht="15.75" customHeight="1">
-      <c r="A237"/>
-      <c r="B237"/>
-      <c r="C237"/>
-    </row>
-    <row r="238" ht="15.75" customHeight="1">
-      <c r="A238"/>
-      <c r="B238"/>
-      <c r="C238"/>
-    </row>
-    <row r="239" ht="15.75" customHeight="1">
-      <c r="A239"/>
-      <c r="B239"/>
-      <c r="C239"/>
-    </row>
-    <row r="240" ht="15.75" customHeight="1">
-      <c r="A240"/>
-      <c r="B240"/>
-      <c r="C240"/>
-    </row>
-    <row r="241" ht="15.75" customHeight="1">
-      <c r="A241"/>
-      <c r="B241"/>
-      <c r="C241"/>
-    </row>
-    <row r="242" ht="15.75" customHeight="1">
-      <c r="A242"/>
-      <c r="B242"/>
-      <c r="C242"/>
-    </row>
-    <row r="243" ht="15.75" customHeight="1">
-      <c r="A243"/>
-      <c r="B243"/>
-      <c r="C243"/>
-    </row>
-    <row r="244" ht="15.75" customHeight="1">
-      <c r="A244"/>
-      <c r="B244"/>
-      <c r="C244"/>
-    </row>
-    <row r="245" ht="15.75" customHeight="1">
-      <c r="A245"/>
-      <c r="B245"/>
-      <c r="C245"/>
-    </row>
-    <row r="246" ht="15.75" customHeight="1">
-      <c r="A246"/>
-      <c r="B246"/>
-      <c r="C246"/>
-    </row>
-    <row r="247" ht="15.75" customHeight="1">
-      <c r="A247"/>
-      <c r="B247"/>
-      <c r="C247"/>
-    </row>
-    <row r="248" ht="15.75" customHeight="1">
-      <c r="A248"/>
-      <c r="B248"/>
-      <c r="C248"/>
-    </row>
-    <row r="249" ht="15.75" customHeight="1">
-      <c r="A249"/>
-      <c r="B249"/>
-      <c r="C249"/>
-    </row>
-    <row r="250" ht="15.75" customHeight="1">
-      <c r="A250"/>
-      <c r="B250"/>
-      <c r="C250"/>
-    </row>
-    <row r="251" ht="15.75" customHeight="1">
-      <c r="A251"/>
-      <c r="B251"/>
-      <c r="C251"/>
-    </row>
-    <row r="252" ht="15.75" customHeight="1">
-      <c r="A252"/>
-      <c r="B252"/>
-      <c r="C252"/>
-    </row>
-    <row r="253" ht="15.75" customHeight="1">
-      <c r="A253"/>
-      <c r="B253"/>
-      <c r="C253"/>
-    </row>
-    <row r="254" ht="15.75" customHeight="1">
-      <c r="A254"/>
-      <c r="B254"/>
-      <c r="C254"/>
-    </row>
-    <row r="255" ht="15.75" customHeight="1">
-      <c r="A255"/>
-      <c r="B255"/>
-      <c r="C255"/>
-    </row>
-    <row r="256" ht="15.75" customHeight="1">
-      <c r="A256"/>
-      <c r="B256"/>
-      <c r="C256"/>
-    </row>
-    <row r="257" ht="15.75" customHeight="1">
-      <c r="A257"/>
-      <c r="B257"/>
-      <c r="C257"/>
-    </row>
-    <row r="258" ht="15.75" customHeight="1">
-      <c r="A258"/>
-      <c r="B258"/>
-      <c r="C258"/>
-    </row>
-    <row r="259" ht="15.75" customHeight="1">
-      <c r="A259"/>
-      <c r="B259"/>
-      <c r="C259"/>
-    </row>
-    <row r="260" ht="15.75" customHeight="1">
-      <c r="A260"/>
-      <c r="B260"/>
-      <c r="C260"/>
-    </row>
-    <row r="261" ht="15.75" customHeight="1">
-      <c r="A261"/>
-      <c r="B261"/>
-      <c r="C261"/>
-    </row>
-    <row r="262" ht="15.75" customHeight="1">
-      <c r="A262"/>
-      <c r="B262"/>
-      <c r="C262"/>
-    </row>
-    <row r="263" ht="15.75" customHeight="1">
-      <c r="A263"/>
-      <c r="B263"/>
-      <c r="C263"/>
-    </row>
-    <row r="264" ht="15.75" customHeight="1">
-      <c r="A264"/>
-      <c r="B264"/>
-      <c r="C264"/>
-    </row>
-    <row r="265" ht="15.75" customHeight="1">
-      <c r="A265"/>
-      <c r="B265"/>
-      <c r="C265"/>
-    </row>
-    <row r="266" ht="15.75" customHeight="1">
-      <c r="A266"/>
-      <c r="B266"/>
-      <c r="C266"/>
-    </row>
-    <row r="267" ht="15.75" customHeight="1">
-      <c r="A267"/>
-      <c r="B267"/>
-      <c r="C267"/>
-    </row>
-    <row r="268" ht="15.75" customHeight="1">
-      <c r="A268"/>
-      <c r="B268"/>
-      <c r="C268"/>
-    </row>
-    <row r="269" ht="15.75" customHeight="1">
-      <c r="A269"/>
-      <c r="B269"/>
-      <c r="C269"/>
-    </row>
-    <row r="270" ht="15.75" customHeight="1">
-      <c r="A270"/>
-      <c r="B270"/>
-      <c r="C270"/>
-    </row>
-    <row r="271" ht="15.75" customHeight="1">
-      <c r="A271"/>
-      <c r="B271"/>
-      <c r="C271"/>
-    </row>
-    <row r="272" ht="15.75" customHeight="1">
-      <c r="A272"/>
-      <c r="B272"/>
-      <c r="C272"/>
-    </row>
-    <row r="273" ht="15.75" customHeight="1">
-      <c r="A273"/>
-      <c r="B273"/>
-      <c r="C273"/>
-    </row>
-    <row r="274" ht="15.75" customHeight="1">
-      <c r="A274"/>
-      <c r="B274"/>
-      <c r="C274"/>
-    </row>
-    <row r="275" ht="15.75" customHeight="1">
-      <c r="A275"/>
-      <c r="B275"/>
-      <c r="C275"/>
-    </row>
-    <row r="276" ht="15.75" customHeight="1">
-      <c r="A276"/>
-      <c r="B276"/>
-      <c r="C276"/>
-    </row>
-    <row r="277" ht="15.75" customHeight="1">
-      <c r="A277"/>
-      <c r="B277"/>
-      <c r="C277"/>
-    </row>
-    <row r="278" ht="15.75" customHeight="1">
-      <c r="A278"/>
-      <c r="B278"/>
-      <c r="C278"/>
-    </row>
-    <row r="279" ht="15.75" customHeight="1">
-      <c r="A279"/>
-      <c r="B279"/>
-      <c r="C279"/>
-    </row>
-    <row r="280" ht="15.75" customHeight="1">
-      <c r="A280"/>
-      <c r="B280"/>
-      <c r="C280"/>
-    </row>
-    <row r="281" ht="15.75" customHeight="1">
-      <c r="A281"/>
-      <c r="B281"/>
-      <c r="C281"/>
-    </row>
-    <row r="282" ht="15.75" customHeight="1">
-      <c r="A282"/>
-      <c r="B282"/>
-      <c r="C282"/>
-    </row>
-    <row r="283" ht="15.75" customHeight="1">
-      <c r="A283"/>
-      <c r="B283"/>
-      <c r="C283"/>
-    </row>
-    <row r="284" ht="15.75" customHeight="1">
-      <c r="A284"/>
-      <c r="B284"/>
-      <c r="C284"/>
-    </row>
-    <row r="285" ht="15.75" customHeight="1">
-      <c r="A285"/>
-      <c r="B285"/>
-      <c r="C285"/>
-    </row>
-    <row r="286" ht="15.75" customHeight="1">
-      <c r="A286"/>
-      <c r="B286"/>
-      <c r="C286"/>
-    </row>
-    <row r="287" ht="15.75" customHeight="1">
-      <c r="A287"/>
-      <c r="B287"/>
-      <c r="C287"/>
-    </row>
-    <row r="288" ht="15.75" customHeight="1">
-      <c r="A288"/>
-      <c r="B288"/>
-      <c r="C288"/>
-    </row>
-    <row r="289" ht="15.75" customHeight="1">
-      <c r="A289"/>
-      <c r="B289"/>
-      <c r="C289"/>
-    </row>
-    <row r="290" ht="15.75" customHeight="1">
-      <c r="A290"/>
-      <c r="B290"/>
-      <c r="C290"/>
-    </row>
-    <row r="291" ht="15.75" customHeight="1">
-      <c r="A291"/>
-      <c r="B291"/>
-      <c r="C291"/>
-    </row>
-    <row r="292" ht="15.75" customHeight="1">
-      <c r="A292"/>
-      <c r="B292"/>
-      <c r="C292"/>
-    </row>
-    <row r="293" ht="15.75" customHeight="1">
-      <c r="A293"/>
-      <c r="B293"/>
-      <c r="C293"/>
-    </row>
-    <row r="294" ht="15.75" customHeight="1">
-      <c r="A294"/>
-      <c r="B294"/>
-      <c r="C294"/>
-    </row>
-    <row r="295" ht="15.75" customHeight="1">
-      <c r="A295"/>
-      <c r="B295"/>
-      <c r="C295"/>
-    </row>
-    <row r="296" ht="15.75" customHeight="1">
-      <c r="A296"/>
-      <c r="B296"/>
-      <c r="C296"/>
-    </row>
-    <row r="297" ht="15.75" customHeight="1">
-      <c r="A297"/>
-      <c r="B297"/>
-      <c r="C297"/>
-    </row>
-    <row r="298" ht="15.75" customHeight="1">
-      <c r="A298"/>
-      <c r="B298"/>
-      <c r="C298"/>
-    </row>
-    <row r="299" ht="15.75" customHeight="1">
-      <c r="A299"/>
-      <c r="B299"/>
-      <c r="C299"/>
-    </row>
-    <row r="300" ht="15.75" customHeight="1">
-      <c r="A300"/>
-      <c r="B300"/>
-      <c r="C300"/>
-    </row>
-    <row r="301" ht="15.75" customHeight="1">
-      <c r="A301"/>
-      <c r="B301"/>
-      <c r="C301"/>
-    </row>
-    <row r="302" ht="15.75" customHeight="1">
-      <c r="A302"/>
-      <c r="B302"/>
-      <c r="C302"/>
-    </row>
-    <row r="303" ht="15.75" customHeight="1">
-      <c r="A303"/>
-      <c r="B303"/>
-      <c r="C303"/>
-    </row>
-    <row r="304" ht="15.75" customHeight="1">
-      <c r="A304"/>
-      <c r="B304"/>
-      <c r="C304"/>
-    </row>
-    <row r="305" ht="15.75" customHeight="1">
-      <c r="A305"/>
-      <c r="B305"/>
-      <c r="C305"/>
-    </row>
-    <row r="306" ht="15.75" customHeight="1">
-      <c r="A306"/>
-      <c r="B306"/>
-      <c r="C306"/>
-    </row>
-    <row r="307" ht="15.75" customHeight="1">
-      <c r="A307"/>
-      <c r="B307"/>
-      <c r="C307"/>
-    </row>
-    <row r="308" ht="15.75" customHeight="1">
-      <c r="A308"/>
-      <c r="B308"/>
-      <c r="C308"/>
-    </row>
-    <row r="309" ht="15.75" customHeight="1">
-      <c r="A309"/>
-      <c r="B309"/>
-      <c r="C309"/>
-    </row>
-    <row r="310" ht="15.75" customHeight="1">
-      <c r="A310"/>
-      <c r="B310"/>
-      <c r="C310"/>
-    </row>
-    <row r="311" ht="15.75" customHeight="1">
-      <c r="A311"/>
-      <c r="B311"/>
-      <c r="C311"/>
-    </row>
-    <row r="312" ht="15.75" customHeight="1">
-      <c r="A312"/>
-      <c r="B312"/>
-      <c r="C312"/>
-    </row>
-    <row r="313" ht="15.75" customHeight="1">
-      <c r="A313"/>
-      <c r="B313"/>
-      <c r="C313"/>
-    </row>
-    <row r="314" ht="15.75" customHeight="1">
-      <c r="A314"/>
-      <c r="B314"/>
-      <c r="C314"/>
-    </row>
-    <row r="315" ht="15.75" customHeight="1">
-      <c r="A315"/>
-      <c r="B315"/>
-      <c r="C315"/>
-    </row>
-    <row r="316" ht="15.75" customHeight="1">
-      <c r="A316"/>
-      <c r="B316"/>
-      <c r="C316"/>
-    </row>
-    <row r="317" ht="15.75" customHeight="1">
-      <c r="A317"/>
-      <c r="B317"/>
-      <c r="C317"/>
-    </row>
-    <row r="318" ht="15.75" customHeight="1">
-      <c r="A318"/>
-      <c r="B318"/>
-      <c r="C318"/>
-    </row>
-    <row r="319" ht="15.75" customHeight="1">
-      <c r="A319"/>
-      <c r="B319"/>
-      <c r="C319"/>
-    </row>
-    <row r="320" ht="15.75" customHeight="1">
-      <c r="A320"/>
-      <c r="B320"/>
-      <c r="C320"/>
-    </row>
-    <row r="321" ht="15.75" customHeight="1">
-      <c r="A321"/>
-      <c r="B321"/>
-      <c r="C321"/>
-    </row>
-    <row r="322" ht="15.75" customHeight="1">
-      <c r="A322"/>
-      <c r="B322"/>
-      <c r="C322"/>
-    </row>
-    <row r="323" ht="15.75" customHeight="1">
-      <c r="A323"/>
-      <c r="B323"/>
-      <c r="C323"/>
-    </row>
-    <row r="324" ht="15.75" customHeight="1">
-      <c r="A324"/>
-      <c r="B324"/>
-      <c r="C324"/>
-    </row>
-    <row r="325" ht="15.75" customHeight="1">
-      <c r="A325"/>
-      <c r="B325"/>
-      <c r="C325"/>
-    </row>
-    <row r="326" ht="15.75" customHeight="1">
-      <c r="A326"/>
-      <c r="B326"/>
-      <c r="C326"/>
-    </row>
-    <row r="327" ht="15.75" customHeight="1">
-      <c r="A327"/>
-      <c r="B327"/>
-      <c r="C327"/>
-    </row>
-    <row r="328" ht="15.75" customHeight="1">
-      <c r="A328"/>
-      <c r="B328"/>
-      <c r="C328"/>
-    </row>
-    <row r="329" ht="15.75" customHeight="1">
-      <c r="A329"/>
-      <c r="B329"/>
-      <c r="C329"/>
-    </row>
-    <row r="330" ht="15.75" customHeight="1">
-      <c r="A330"/>
-      <c r="B330"/>
-      <c r="C330"/>
-    </row>
-    <row r="331" ht="15.75" customHeight="1">
-      <c r="A331"/>
-      <c r="B331"/>
-      <c r="C331"/>
-    </row>
-    <row r="332" ht="15.75" customHeight="1">
-      <c r="A332"/>
-      <c r="B332"/>
-      <c r="C332"/>
-    </row>
-    <row r="333" ht="15.75" customHeight="1">
-      <c r="A333"/>
-      <c r="B333"/>
-      <c r="C333"/>
-    </row>
-    <row r="334" ht="15.75" customHeight="1">
-      <c r="A334"/>
-      <c r="B334"/>
-      <c r="C334"/>
-    </row>
-    <row r="335" ht="15.75" customHeight="1">
-      <c r="A335"/>
-      <c r="B335"/>
-      <c r="C335"/>
-    </row>
-    <row r="336" ht="15.75" customHeight="1">
-      <c r="A336"/>
-      <c r="B336"/>
-      <c r="C336"/>
-    </row>
-    <row r="337" ht="15.75" customHeight="1">
-      <c r="A337"/>
-      <c r="B337"/>
-      <c r="C337"/>
-    </row>
-    <row r="338" ht="15.75" customHeight="1">
-      <c r="A338"/>
-      <c r="B338"/>
-      <c r="C338"/>
-    </row>
-    <row r="339" ht="15.75" customHeight="1">
-      <c r="A339"/>
-      <c r="B339"/>
-      <c r="C339"/>
-    </row>
-    <row r="340" ht="15.75" customHeight="1">
-      <c r="A340"/>
-      <c r="B340"/>
-      <c r="C340"/>
-    </row>
-    <row r="341" ht="15.75" customHeight="1">
-      <c r="A341"/>
-      <c r="B341"/>
-      <c r="C341"/>
-    </row>
-    <row r="342" ht="15.75" customHeight="1">
-      <c r="A342"/>
-      <c r="B342"/>
-      <c r="C342"/>
-    </row>
-    <row r="343" ht="15.75" customHeight="1">
-      <c r="A343"/>
-      <c r="B343"/>
-      <c r="C343"/>
-    </row>
-    <row r="344" ht="15.75" customHeight="1">
-      <c r="A344"/>
-      <c r="B344"/>
-      <c r="C344"/>
-    </row>
-    <row r="345" ht="15.75" customHeight="1">
-      <c r="A345"/>
-      <c r="B345"/>
-      <c r="C345"/>
-    </row>
-    <row r="346" ht="15.75" customHeight="1">
-      <c r="A346"/>
-      <c r="B346"/>
-      <c r="C346"/>
-    </row>
-    <row r="347" ht="15.75" customHeight="1">
-      <c r="A347"/>
-      <c r="B347"/>
-      <c r="C347"/>
-    </row>
-    <row r="348" ht="15.75" customHeight="1">
-      <c r="A348"/>
-      <c r="B348"/>
-      <c r="C348"/>
-    </row>
-    <row r="349" ht="15.75" customHeight="1">
-      <c r="A349"/>
-      <c r="B349"/>
-      <c r="C349"/>
-    </row>
-    <row r="350" ht="15.75" customHeight="1">
-      <c r="A350"/>
-      <c r="B350"/>
-      <c r="C350"/>
-    </row>
-    <row r="351" ht="15.75" customHeight="1">
-      <c r="A351"/>
-      <c r="B351"/>
-      <c r="C351"/>
-    </row>
-    <row r="352" ht="15.75" customHeight="1">
-      <c r="A352"/>
-      <c r="B352"/>
-      <c r="C352"/>
-    </row>
-    <row r="353" ht="15.75" customHeight="1">
-      <c r="A353"/>
-      <c r="B353"/>
-      <c r="C353"/>
-    </row>
-    <row r="354" ht="15.75" customHeight="1">
-      <c r="A354"/>
-      <c r="B354"/>
-      <c r="C354"/>
-    </row>
-    <row r="355" ht="15.75" customHeight="1">
-      <c r="A355"/>
-      <c r="B355"/>
-      <c r="C355"/>
-    </row>
-    <row r="356" ht="15.75" customHeight="1">
-      <c r="A356"/>
-      <c r="B356"/>
-      <c r="C356"/>
-    </row>
-    <row r="357" ht="15.75" customHeight="1">
-      <c r="A357"/>
-      <c r="B357"/>
-      <c r="C357"/>
-    </row>
-    <row r="358" ht="15.75" customHeight="1">
-      <c r="A358"/>
-      <c r="B358"/>
-      <c r="C358"/>
-    </row>
-    <row r="359" ht="15.75" customHeight="1">
-      <c r="A359"/>
-      <c r="B359"/>
-      <c r="C359"/>
-    </row>
-    <row r="360" ht="15.75" customHeight="1">
-      <c r="A360"/>
-      <c r="B360"/>
-      <c r="C360"/>
-    </row>
-    <row r="361" ht="15.75" customHeight="1">
-      <c r="A361"/>
-      <c r="B361"/>
-      <c r="C361"/>
-    </row>
-    <row r="362" ht="15.75" customHeight="1">
-      <c r="A362"/>
-      <c r="B362"/>
-      <c r="C362"/>
-    </row>
-    <row r="363" ht="15.75" customHeight="1">
-      <c r="A363"/>
-      <c r="B363"/>
-      <c r="C363"/>
-    </row>
-    <row r="364" ht="15.75" customHeight="1">
-      <c r="A364"/>
-      <c r="B364"/>
-      <c r="C364"/>
-    </row>
-    <row r="365" ht="15.75" customHeight="1">
-      <c r="A365"/>
-      <c r="B365"/>
-      <c r="C365"/>
-    </row>
-    <row r="366" ht="15.75" customHeight="1">
-      <c r="A366"/>
-      <c r="B366"/>
-      <c r="C366"/>
-    </row>
-    <row r="367" ht="15.75" customHeight="1">
-      <c r="A367"/>
-      <c r="B367"/>
-      <c r="C367"/>
-    </row>
-    <row r="368" ht="15.75" customHeight="1">
-      <c r="A368"/>
-      <c r="B368"/>
-      <c r="C368"/>
-    </row>
-    <row r="369" ht="15.75" customHeight="1">
-      <c r="A369"/>
-      <c r="B369"/>
-      <c r="C369"/>
-    </row>
-    <row r="370" ht="15.75" customHeight="1">
-      <c r="A370"/>
-      <c r="B370"/>
-      <c r="C370"/>
-    </row>
-    <row r="371" ht="15.75" customHeight="1">
-      <c r="A371"/>
-      <c r="B371"/>
-      <c r="C371"/>
-    </row>
-    <row r="372" ht="15.75" customHeight="1">
-      <c r="A372"/>
-      <c r="B372"/>
-      <c r="C372"/>
-    </row>
-    <row r="373" ht="15.75" customHeight="1">
-      <c r="A373"/>
-      <c r="B373"/>
-      <c r="C373"/>
-    </row>
-    <row r="374" ht="15.75" customHeight="1">
-      <c r="A374"/>
-      <c r="B374"/>
-      <c r="C374"/>
-    </row>
-    <row r="375" ht="15.75" customHeight="1">
-      <c r="A375"/>
-      <c r="B375"/>
-      <c r="C375"/>
-    </row>
-    <row r="376" ht="15.75" customHeight="1">
-      <c r="A376"/>
-      <c r="B376"/>
-      <c r="C376"/>
-    </row>
-    <row r="377" ht="15.75" customHeight="1">
-      <c r="A377"/>
-      <c r="B377"/>
-      <c r="C377"/>
-    </row>
-    <row r="378" ht="15.75" customHeight="1">
-      <c r="A378"/>
-      <c r="B378"/>
-      <c r="C378"/>
-    </row>
-    <row r="379" ht="15.75" customHeight="1">
-      <c r="A379"/>
-      <c r="B379"/>
-      <c r="C379"/>
-    </row>
-    <row r="380" ht="15.75" customHeight="1">
-      <c r="A380"/>
-      <c r="B380"/>
-      <c r="C380"/>
-    </row>
-    <row r="381" ht="15.75" customHeight="1">
-      <c r="A381"/>
-      <c r="B381"/>
-      <c r="C381"/>
-    </row>
-    <row r="382" ht="15.75" customHeight="1">
-      <c r="A382"/>
-      <c r="B382"/>
-      <c r="C382"/>
-    </row>
-    <row r="383" ht="15.75" customHeight="1">
-      <c r="A383"/>
-      <c r="B383"/>
-      <c r="C383"/>
-    </row>
-    <row r="384" ht="15.75" customHeight="1">
-      <c r="A384"/>
-      <c r="B384"/>
-      <c r="C384"/>
-    </row>
-    <row r="385" ht="15.75" customHeight="1">
-      <c r="A385"/>
-      <c r="B385"/>
-      <c r="C385"/>
-    </row>
-    <row r="386" ht="15.75" customHeight="1">
-      <c r="A386"/>
-      <c r="B386"/>
-      <c r="C386"/>
-    </row>
-    <row r="387" ht="15.75" customHeight="1">
-      <c r="A387"/>
-      <c r="B387"/>
-      <c r="C387"/>
-    </row>
-    <row r="388" ht="15.75" customHeight="1">
-      <c r="A388"/>
-      <c r="B388"/>
-      <c r="C388"/>
-    </row>
-    <row r="389" ht="15.75" customHeight="1">
-      <c r="A389"/>
-      <c r="B389"/>
-      <c r="C389"/>
-    </row>
-    <row r="390" ht="15.75" customHeight="1">
-      <c r="A390"/>
-      <c r="B390"/>
-      <c r="C390"/>
-    </row>
-    <row r="391" ht="15.75" customHeight="1">
-      <c r="A391"/>
-      <c r="B391"/>
-      <c r="C391"/>
-    </row>
-    <row r="392" ht="15.75" customHeight="1">
-      <c r="A392"/>
-      <c r="B392"/>
-      <c r="C392"/>
-    </row>
-    <row r="393" ht="15.75" customHeight="1">
-      <c r="A393"/>
-      <c r="B393"/>
-      <c r="C393"/>
-    </row>
-    <row r="394" ht="15.75" customHeight="1">
-      <c r="A394"/>
-      <c r="B394"/>
-      <c r="C394"/>
-    </row>
-    <row r="395" ht="15.75" customHeight="1">
-      <c r="A395"/>
-      <c r="B395"/>
-      <c r="C395"/>
-    </row>
-    <row r="396" ht="15.75" customHeight="1">
-      <c r="A396"/>
-      <c r="B396"/>
-      <c r="C396"/>
-    </row>
-    <row r="397" ht="15.75" customHeight="1">
-      <c r="A397"/>
-      <c r="B397"/>
-      <c r="C397"/>
-    </row>
-    <row r="398" ht="15.75" customHeight="1">
-      <c r="A398"/>
-      <c r="B398"/>
-      <c r="C398"/>
-    </row>
-    <row r="399" ht="15.75" customHeight="1">
-      <c r="A399"/>
-      <c r="B399"/>
-      <c r="C399"/>
-    </row>
-    <row r="400" ht="15.75" customHeight="1">
-      <c r="A400"/>
-      <c r="B400"/>
-      <c r="C400"/>
-    </row>
-    <row r="401" ht="15.75" customHeight="1">
-      <c r="A401"/>
-      <c r="B401"/>
-      <c r="C401"/>
-    </row>
-    <row r="402" ht="15.75" customHeight="1">
-      <c r="A402"/>
-      <c r="B402"/>
-      <c r="C402"/>
-    </row>
-    <row r="403" ht="15.75" customHeight="1">
-      <c r="A403"/>
-      <c r="B403"/>
-      <c r="C403"/>
-    </row>
-    <row r="404" ht="15.75" customHeight="1">
-      <c r="A404"/>
-      <c r="B404"/>
-      <c r="C404"/>
-    </row>
-    <row r="405" ht="15.75" customHeight="1">
-      <c r="A405"/>
-      <c r="B405"/>
-      <c r="C405"/>
-    </row>
-    <row r="406" ht="15.75" customHeight="1">
-      <c r="A406"/>
-      <c r="B406"/>
-      <c r="C406"/>
-    </row>
-    <row r="407" ht="15.75" customHeight="1">
-      <c r="A407"/>
-      <c r="B407"/>
-      <c r="C407"/>
-    </row>
-    <row r="408" ht="15.75" customHeight="1">
-      <c r="A408"/>
-      <c r="B408"/>
-      <c r="C408"/>
-    </row>
-    <row r="409" ht="15.75" customHeight="1">
-      <c r="A409"/>
-      <c r="B409"/>
-      <c r="C409"/>
-    </row>
-    <row r="410" ht="15.75" customHeight="1">
-      <c r="A410"/>
-      <c r="B410"/>
-      <c r="C410"/>
-    </row>
-    <row r="411" ht="15.75" customHeight="1">
-      <c r="A411"/>
-      <c r="B411"/>
-      <c r="C411"/>
-    </row>
-    <row r="412" ht="15.75" customHeight="1">
-      <c r="A412"/>
-      <c r="B412"/>
-      <c r="C412"/>
-    </row>
-    <row r="413" ht="15.75" customHeight="1">
-      <c r="A413"/>
-      <c r="B413"/>
-      <c r="C413"/>
-    </row>
-    <row r="414" ht="15.75" customHeight="1">
-      <c r="A414"/>
-      <c r="B414"/>
-      <c r="C414"/>
-    </row>
-    <row r="415" ht="15.75" customHeight="1">
-      <c r="A415"/>
-      <c r="B415"/>
-      <c r="C415"/>
-    </row>
-    <row r="416" ht="15.75" customHeight="1">
-      <c r="A416"/>
-      <c r="B416"/>
-      <c r="C416"/>
-    </row>
-    <row r="417" ht="15.75" customHeight="1">
-      <c r="A417"/>
-      <c r="B417"/>
-      <c r="C417"/>
-    </row>
-    <row r="418" ht="15.75" customHeight="1">
-      <c r="A418"/>
-      <c r="B418"/>
-      <c r="C418"/>
-    </row>
-    <row r="419" ht="15.75" customHeight="1">
-      <c r="A419"/>
-      <c r="B419"/>
-      <c r="C419"/>
-    </row>
-    <row r="420" ht="15.75" customHeight="1">
-      <c r="A420"/>
-      <c r="B420"/>
-      <c r="C420"/>
-    </row>
-    <row r="421" ht="15.75" customHeight="1">
-      <c r="A421"/>
-      <c r="B421"/>
-      <c r="C421"/>
-    </row>
-    <row r="422" ht="15.75" customHeight="1">
-      <c r="A422"/>
-      <c r="B422"/>
-      <c r="C422"/>
-    </row>
-    <row r="423" ht="15.75" customHeight="1">
-      <c r="A423"/>
-      <c r="B423"/>
-      <c r="C423"/>
-    </row>
-    <row r="424" ht="15.75" customHeight="1">
-      <c r="A424"/>
-      <c r="B424"/>
-      <c r="C424"/>
-    </row>
-    <row r="425" ht="15.75" customHeight="1">
-      <c r="A425"/>
-      <c r="B425"/>
-      <c r="C425"/>
-    </row>
-    <row r="426" ht="15.75" customHeight="1">
-      <c r="A426"/>
-      <c r="B426"/>
-      <c r="C426"/>
-    </row>
-    <row r="427" ht="15.75" customHeight="1">
-      <c r="A427"/>
-      <c r="B427"/>
-      <c r="C427"/>
-    </row>
-    <row r="428" ht="15.75" customHeight="1">
-      <c r="A428"/>
-      <c r="B428"/>
-      <c r="C428"/>
-    </row>
-    <row r="429" ht="15.75" customHeight="1">
-      <c r="A429"/>
-      <c r="B429"/>
-      <c r="C429"/>
-    </row>
-    <row r="430" ht="15.75" customHeight="1">
-      <c r="A430"/>
-      <c r="B430"/>
-      <c r="C430"/>
-    </row>
-    <row r="431" ht="15.75" customHeight="1">
-      <c r="A431"/>
-      <c r="B431"/>
-      <c r="C431"/>
-    </row>
-    <row r="432" ht="15.75" customHeight="1">
-      <c r="A432"/>
-      <c r="B432"/>
-      <c r="C432"/>
-    </row>
-    <row r="433" ht="15.75" customHeight="1">
-      <c r="A433"/>
-      <c r="B433"/>
-      <c r="C433"/>
-    </row>
-    <row r="434" ht="15.75" customHeight="1">
-      <c r="A434"/>
-      <c r="B434"/>
-      <c r="C434"/>
-    </row>
-    <row r="435" ht="15.75" customHeight="1">
-      <c r="A435"/>
-      <c r="B435"/>
-      <c r="C435"/>
-    </row>
-    <row r="436" ht="15.75" customHeight="1">
-      <c r="A436"/>
-      <c r="B436"/>
-      <c r="C436"/>
-    </row>
-    <row r="437" ht="15.75" customHeight="1">
-      <c r="A437"/>
-      <c r="B437"/>
-      <c r="C437"/>
-    </row>
-    <row r="438" ht="15.75" customHeight="1">
-      <c r="A438"/>
-      <c r="B438"/>
-      <c r="C438"/>
-    </row>
-    <row r="439" ht="15.75" customHeight="1">
-      <c r="A439"/>
-      <c r="B439"/>
-      <c r="C439"/>
-    </row>
-    <row r="440" ht="15.75" customHeight="1">
-      <c r="A440"/>
-      <c r="B440"/>
-      <c r="C440"/>
-    </row>
-    <row r="441" ht="15.75" customHeight="1">
-      <c r="A441"/>
-      <c r="B441"/>
-      <c r="C441"/>
-    </row>
-    <row r="442" ht="15.75" customHeight="1">
-      <c r="A442"/>
-      <c r="B442"/>
-      <c r="C442"/>
-    </row>
-    <row r="443" ht="15.75" customHeight="1">
-      <c r="A443"/>
-      <c r="B443"/>
-      <c r="C443"/>
-    </row>
-    <row r="444" ht="15.75" customHeight="1">
-      <c r="A444"/>
-      <c r="B444"/>
-      <c r="C444"/>
-    </row>
-    <row r="445" ht="15.75" customHeight="1">
-      <c r="A445"/>
-      <c r="B445"/>
-      <c r="C445"/>
-    </row>
-    <row r="446" ht="15.75" customHeight="1">
-      <c r="A446"/>
-      <c r="B446"/>
-      <c r="C446"/>
-    </row>
-    <row r="447" ht="15.75" customHeight="1">
-      <c r="A447"/>
-      <c r="B447"/>
-      <c r="C447"/>
-    </row>
-    <row r="448" ht="15.75" customHeight="1">
-      <c r="A448"/>
-      <c r="B448"/>
-      <c r="C448"/>
-    </row>
-    <row r="449" ht="15.75" customHeight="1">
-      <c r="A449"/>
-      <c r="B449"/>
-      <c r="C449"/>
-    </row>
-    <row r="450" ht="15.75" customHeight="1">
-      <c r="A450"/>
-      <c r="B450"/>
-      <c r="C450"/>
-    </row>
-    <row r="451" ht="15.75" customHeight="1">
-      <c r="A451"/>
-      <c r="B451"/>
-      <c r="C451"/>
-    </row>
-    <row r="452" ht="15.75" customHeight="1">
-      <c r="A452"/>
-      <c r="B452"/>
-      <c r="C452"/>
-    </row>
-    <row r="453" ht="15.75" customHeight="1">
-      <c r="A453"/>
-      <c r="B453"/>
-      <c r="C453"/>
-    </row>
-    <row r="454" ht="15.75" customHeight="1">
-      <c r="A454"/>
-      <c r="B454"/>
-      <c r="C454"/>
-    </row>
-    <row r="455" ht="15.75" customHeight="1">
-      <c r="A455"/>
-      <c r="B455"/>
-      <c r="C455"/>
-    </row>
-    <row r="456" ht="15.75" customHeight="1">
-      <c r="A456"/>
-      <c r="B456"/>
-      <c r="C456"/>
-    </row>
-    <row r="457" ht="15.75" customHeight="1">
-      <c r="A457"/>
-      <c r="B457"/>
-      <c r="C457"/>
-    </row>
-    <row r="458" ht="15.75" customHeight="1">
-      <c r="A458"/>
-      <c r="B458"/>
-      <c r="C458"/>
-    </row>
-    <row r="459" ht="15.75" customHeight="1">
-      <c r="A459"/>
-      <c r="B459"/>
-      <c r="C459"/>
-    </row>
-    <row r="460" ht="15.75" customHeight="1">
-      <c r="A460"/>
-      <c r="B460"/>
-      <c r="C460"/>
-    </row>
-    <row r="461" ht="15.75" customHeight="1">
-      <c r="A461"/>
-      <c r="B461"/>
-      <c r="C461"/>
-    </row>
-    <row r="462" ht="15.75" customHeight="1">
-      <c r="A462"/>
-      <c r="B462"/>
-      <c r="C462"/>
-    </row>
-    <row r="463" ht="15.75" customHeight="1">
-      <c r="A463"/>
-      <c r="B463"/>
-      <c r="C463"/>
-    </row>
-    <row r="464" ht="15.75" customHeight="1">
-      <c r="A464"/>
-      <c r="B464"/>
-      <c r="C464"/>
-    </row>
-    <row r="465" ht="15.75" customHeight="1">
-      <c r="A465"/>
-      <c r="B465"/>
-      <c r="C465"/>
-    </row>
-    <row r="466" ht="15.75" customHeight="1">
-      <c r="A466"/>
-      <c r="B466"/>
-      <c r="C466"/>
-    </row>
-    <row r="467" ht="15.75" customHeight="1">
-      <c r="A467"/>
-      <c r="B467"/>
-      <c r="C467"/>
-    </row>
-    <row r="468" ht="15.75" customHeight="1">
-      <c r="A468"/>
-      <c r="B468"/>
-      <c r="C468"/>
-    </row>
-    <row r="469" ht="15.75" customHeight="1">
-      <c r="A469"/>
-      <c r="B469"/>
-      <c r="C469"/>
-    </row>
-    <row r="470" ht="15.75" customHeight="1">
-      <c r="A470"/>
-      <c r="B470"/>
-      <c r="C470"/>
-    </row>
-    <row r="471" ht="15.75" customHeight="1">
-      <c r="A471"/>
-      <c r="B471"/>
-      <c r="C471"/>
-    </row>
-    <row r="472" ht="15.75" customHeight="1">
-      <c r="A472"/>
-      <c r="B472"/>
-      <c r="C472"/>
-    </row>
-    <row r="473" ht="15.75" customHeight="1">
-      <c r="A473"/>
-      <c r="B473"/>
-      <c r="C473"/>
-    </row>
-    <row r="474" ht="15.75" customHeight="1">
-      <c r="A474"/>
-      <c r="B474"/>
-      <c r="C474"/>
-    </row>
-    <row r="475" ht="15.75" customHeight="1">
-      <c r="A475"/>
-      <c r="B475"/>
-      <c r="C475"/>
-    </row>
-    <row r="476" ht="15.75" customHeight="1">
-      <c r="A476"/>
-      <c r="B476"/>
-      <c r="C476"/>
-    </row>
-    <row r="477" ht="15.75" customHeight="1">
-      <c r="A477"/>
-      <c r="B477"/>
-      <c r="C477"/>
-    </row>
-    <row r="478" ht="15.75" customHeight="1">
-      <c r="A478"/>
-      <c r="B478"/>
-      <c r="C478"/>
-    </row>
-    <row r="479" ht="15.75" customHeight="1">
-      <c r="A479"/>
-      <c r="B479"/>
-      <c r="C479"/>
-    </row>
-    <row r="480" ht="15.75" customHeight="1">
-      <c r="A480"/>
-      <c r="B480"/>
-      <c r="C480"/>
-    </row>
-    <row r="481" ht="15.75" customHeight="1">
-      <c r="A481"/>
-      <c r="B481"/>
-      <c r="C481"/>
-    </row>
-    <row r="482" ht="15.75" customHeight="1">
-      <c r="A482"/>
-      <c r="B482"/>
-      <c r="C482"/>
-    </row>
-    <row r="483" ht="15.75" customHeight="1">
-      <c r="A483"/>
-      <c r="B483"/>
-      <c r="C483"/>
-    </row>
-    <row r="484" ht="15.75" customHeight="1">
-      <c r="A484"/>
-      <c r="B484"/>
-      <c r="C484"/>
-    </row>
-    <row r="485" ht="15.75" customHeight="1">
-      <c r="A485"/>
-      <c r="B485"/>
-      <c r="C485"/>
-    </row>
-    <row r="486" ht="15.75" customHeight="1">
-      <c r="A486"/>
-      <c r="B486"/>
-      <c r="C486"/>
-    </row>
-    <row r="487" ht="15.75" customHeight="1">
-      <c r="A487"/>
-      <c r="B487"/>
-      <c r="C487"/>
-    </row>
-    <row r="488" ht="15.75" customHeight="1">
-      <c r="A488"/>
-      <c r="B488"/>
-      <c r="C488"/>
-    </row>
-    <row r="489" ht="15.75" customHeight="1">
-      <c r="A489"/>
-      <c r="B489"/>
-      <c r="C489"/>
-    </row>
-    <row r="490" ht="15.75" customHeight="1">
-      <c r="A490"/>
-      <c r="B490"/>
-      <c r="C490"/>
-    </row>
-    <row r="491" ht="15.75" customHeight="1">
-      <c r="A491"/>
-      <c r="B491"/>
-      <c r="C491"/>
-    </row>
-    <row r="492" ht="15.75" customHeight="1">
-      <c r="A492"/>
-      <c r="B492"/>
-      <c r="C492"/>
-    </row>
-    <row r="493" ht="15.75" customHeight="1">
-      <c r="A493"/>
-      <c r="B493"/>
-      <c r="C493"/>
-    </row>
-    <row r="494" ht="15.75" customHeight="1">
-      <c r="A494"/>
-      <c r="B494"/>
-      <c r="C494"/>
-    </row>
-    <row r="495" ht="15.75" customHeight="1">
-      <c r="A495"/>
-      <c r="B495"/>
-      <c r="C495"/>
-    </row>
-    <row r="496" ht="15.75" customHeight="1">
-      <c r="A496"/>
-      <c r="B496"/>
-      <c r="C496"/>
-    </row>
-    <row r="497" ht="15.75" customHeight="1">
-      <c r="A497"/>
-      <c r="B497"/>
-      <c r="C497"/>
-    </row>
-    <row r="498" ht="15.75" customHeight="1">
-      <c r="A498"/>
-      <c r="B498"/>
-      <c r="C498"/>
-    </row>
-    <row r="499" ht="15.75" customHeight="1">
-      <c r="A499"/>
-      <c r="B499"/>
-      <c r="C499"/>
-    </row>
-    <row r="500" ht="15.75" customHeight="1">
-      <c r="A500"/>
-      <c r="B500"/>
-      <c r="C500"/>
-    </row>
-    <row r="501" ht="15.75" customHeight="1">
-      <c r="A501"/>
-      <c r="B501"/>
-      <c r="C501"/>
-    </row>
-    <row r="502" ht="15.75" customHeight="1">
-      <c r="A502"/>
-      <c r="B502"/>
-      <c r="C502"/>
-    </row>
-    <row r="503" ht="15.75" customHeight="1">
-      <c r="A503"/>
-      <c r="B503"/>
-      <c r="C503"/>
-    </row>
-    <row r="504" ht="15.75" customHeight="1">
-      <c r="A504"/>
-      <c r="B504"/>
-      <c r="C504"/>
-    </row>
-    <row r="505" ht="15.75" customHeight="1">
-      <c r="A505"/>
-      <c r="B505"/>
-      <c r="C505"/>
-    </row>
-    <row r="506" ht="15.75" customHeight="1">
-      <c r="A506"/>
-      <c r="B506"/>
-      <c r="C506"/>
-    </row>
-    <row r="507" ht="15.75" customHeight="1">
-      <c r="A507"/>
-      <c r="B507"/>
-      <c r="C507"/>
-    </row>
-    <row r="508" ht="15.75" customHeight="1">
-      <c r="A508"/>
-      <c r="B508"/>
-      <c r="C508"/>
-    </row>
-    <row r="509" ht="15.75" customHeight="1">
-      <c r="A509"/>
-      <c r="B509"/>
-      <c r="C509"/>
-    </row>
-    <row r="510" ht="15.75" customHeight="1">
-      <c r="A510"/>
-      <c r="B510"/>
-      <c r="C510"/>
-    </row>
-    <row r="511" ht="15.75" customHeight="1">
-      <c r="A511"/>
-      <c r="B511"/>
-      <c r="C511"/>
-    </row>
-    <row r="512" ht="15.75" customHeight="1">
-      <c r="A512"/>
-      <c r="B512"/>
-      <c r="C512"/>
-    </row>
-    <row r="513" ht="15.75" customHeight="1">
-      <c r="A513"/>
-      <c r="B513"/>
-      <c r="C513"/>
-    </row>
-    <row r="514" ht="15.75" customHeight="1">
-      <c r="A514"/>
-      <c r="B514"/>
-      <c r="C514"/>
-    </row>
-    <row r="515" ht="15.75" customHeight="1">
-      <c r="A515"/>
-      <c r="B515"/>
-      <c r="C515"/>
-    </row>
-    <row r="516" ht="15.75" customHeight="1">
-      <c r="A516"/>
-      <c r="B516"/>
-      <c r="C516"/>
-    </row>
-    <row r="517" ht="15.75" customHeight="1">
-      <c r="A517"/>
-      <c r="B517"/>
-      <c r="C517"/>
-    </row>
-    <row r="518" ht="15.75" customHeight="1">
-      <c r="A518"/>
-      <c r="B518"/>
-      <c r="C518"/>
-    </row>
-    <row r="519" ht="15.75" customHeight="1">
-      <c r="A519"/>
-      <c r="B519"/>
-      <c r="C519"/>
-    </row>
-    <row r="520" ht="15.75" customHeight="1">
-      <c r="A520"/>
-      <c r="B520"/>
-      <c r="C520"/>
-    </row>
-    <row r="521" ht="15.75" customHeight="1">
-      <c r="A521"/>
-      <c r="B521"/>
-      <c r="C521"/>
-    </row>
-    <row r="522" ht="15.75" customHeight="1">
-      <c r="A522"/>
-      <c r="B522"/>
-      <c r="C522"/>
-    </row>
-    <row r="523" ht="15.75" customHeight="1">
-      <c r="A523"/>
-      <c r="B523"/>
-      <c r="C523"/>
-    </row>
-    <row r="524" ht="15.75" customHeight="1">
-      <c r="A524"/>
-      <c r="B524"/>
-      <c r="C524"/>
-    </row>
-    <row r="525" ht="15.75" customHeight="1">
-      <c r="A525"/>
-      <c r="B525"/>
-      <c r="C525"/>
-    </row>
-    <row r="526" ht="15.75" customHeight="1">
-      <c r="A526"/>
-      <c r="B526"/>
-      <c r="C526"/>
-    </row>
-    <row r="527" ht="15.75" customHeight="1">
-      <c r="A527"/>
-      <c r="B527"/>
-      <c r="C527"/>
-    </row>
-    <row r="528" ht="15.75" customHeight="1">
-      <c r="A528"/>
-      <c r="B528"/>
-      <c r="C528"/>
-    </row>
-    <row r="529" ht="15.75" customHeight="1">
-      <c r="A529"/>
-      <c r="B529"/>
-      <c r="C529"/>
-    </row>
-    <row r="530" ht="15.75" customHeight="1">
-      <c r="A530"/>
-      <c r="B530"/>
-      <c r="C530"/>
-    </row>
-    <row r="531" ht="15.75" customHeight="1">
-      <c r="A531"/>
-      <c r="B531"/>
-      <c r="C531"/>
-    </row>
-    <row r="532" ht="15.75" customHeight="1">
-      <c r="A532"/>
-      <c r="B532"/>
-      <c r="C532"/>
-    </row>
-    <row r="533" ht="15.75" customHeight="1">
-      <c r="A533"/>
-      <c r="B533"/>
-      <c r="C533"/>
-    </row>
-    <row r="534" ht="15.75" customHeight="1">
-      <c r="A534"/>
-      <c r="B534"/>
-      <c r="C534"/>
-    </row>
-    <row r="535" ht="15.75" customHeight="1">
-      <c r="A535"/>
-      <c r="B535"/>
-      <c r="C535"/>
-    </row>
-    <row r="536" ht="15.75" customHeight="1">
-      <c r="A536"/>
-      <c r="B536"/>
-      <c r="C536"/>
-    </row>
-    <row r="537" ht="15.75" customHeight="1">
-      <c r="A537"/>
-      <c r="B537"/>
-      <c r="C537"/>
-    </row>
-    <row r="538" ht="15.75" customHeight="1">
-      <c r="A538"/>
-      <c r="B538"/>
-      <c r="C538"/>
-    </row>
-    <row r="539" ht="15.75" customHeight="1">
-      <c r="A539"/>
-      <c r="B539"/>
-      <c r="C539"/>
-    </row>
-    <row r="540" ht="15.75" customHeight="1">
-      <c r="A540"/>
-      <c r="B540"/>
-      <c r="C540"/>
-    </row>
-    <row r="541" ht="15.75" customHeight="1">
-      <c r="A541"/>
-      <c r="B541"/>
-      <c r="C541"/>
-    </row>
-    <row r="542" ht="15.75" customHeight="1">
-      <c r="A542"/>
-      <c r="B542"/>
-      <c r="C542"/>
-    </row>
-    <row r="543" ht="15.75" customHeight="1">
-      <c r="A543"/>
-      <c r="B543"/>
-      <c r="C543"/>
-    </row>
-    <row r="544" ht="15.75" customHeight="1">
-      <c r="A544"/>
-      <c r="B544"/>
-      <c r="C544"/>
-    </row>
-    <row r="545" ht="15.75" customHeight="1">
-      <c r="A545"/>
-      <c r="B545"/>
-      <c r="C545"/>
-    </row>
-    <row r="546" ht="15.75" customHeight="1">
-      <c r="A546"/>
-      <c r="B546"/>
-      <c r="C546"/>
-    </row>
-    <row r="547" ht="15.75" customHeight="1">
-      <c r="A547"/>
-      <c r="B547"/>
-      <c r="C547"/>
-    </row>
-    <row r="548" ht="15.75" customHeight="1">
-      <c r="A548"/>
-      <c r="B548"/>
-      <c r="C548"/>
-    </row>
-    <row r="549" ht="15.75" customHeight="1">
-      <c r="A549"/>
-      <c r="B549"/>
-      <c r="C549"/>
-    </row>
-    <row r="550" ht="15.75" customHeight="1">
-      <c r="A550"/>
-      <c r="B550"/>
-      <c r="C550"/>
-    </row>
-    <row r="551" ht="15.75" customHeight="1">
-      <c r="A551"/>
-      <c r="B551"/>
-      <c r="C551"/>
-    </row>
-    <row r="552" ht="15.75" customHeight="1">
-      <c r="A552"/>
-      <c r="B552"/>
-      <c r="C552"/>
-    </row>
-    <row r="553" ht="15.75" customHeight="1">
-      <c r="A553"/>
-      <c r="B553"/>
-      <c r="C553"/>
-    </row>
-    <row r="554" ht="15.75" customHeight="1">
-      <c r="A554"/>
-      <c r="B554"/>
-      <c r="C554"/>
-    </row>
-    <row r="555" ht="15.75" customHeight="1">
-      <c r="A555"/>
-      <c r="B555"/>
-      <c r="C555"/>
-    </row>
-    <row r="556" ht="15.75" customHeight="1">
-      <c r="A556"/>
-      <c r="B556"/>
-      <c r="C556"/>
-    </row>
-    <row r="557" ht="15.75" customHeight="1">
-      <c r="A557"/>
-      <c r="B557"/>
-      <c r="C557"/>
-    </row>
-    <row r="558" ht="15.75" customHeight="1">
-      <c r="A558"/>
-      <c r="B558"/>
-      <c r="C558"/>
-    </row>
-    <row r="559" ht="15.75" customHeight="1">
-      <c r="A559"/>
-      <c r="B559"/>
-      <c r="C559"/>
-    </row>
-    <row r="560" ht="15.75" customHeight="1">
-      <c r="A560"/>
-      <c r="B560"/>
-      <c r="C560"/>
-    </row>
-    <row r="561" ht="15.75" customHeight="1">
-      <c r="A561"/>
-      <c r="B561"/>
-      <c r="C561"/>
-    </row>
-    <row r="562" ht="15.75" customHeight="1">
-      <c r="A562"/>
-      <c r="B562"/>
-      <c r="C562"/>
-    </row>
-    <row r="563" ht="15.75" customHeight="1">
-      <c r="A563"/>
-      <c r="B563"/>
-      <c r="C563"/>
-    </row>
-    <row r="564" ht="15.75" customHeight="1">
-      <c r="A564"/>
-      <c r="B564"/>
-      <c r="C564"/>
-    </row>
-    <row r="565" ht="15.75" customHeight="1">
-      <c r="A565"/>
-      <c r="B565"/>
-      <c r="C565"/>
-    </row>
-    <row r="566" ht="15.75" customHeight="1">
-      <c r="A566"/>
-      <c r="B566"/>
-      <c r="C566"/>
-    </row>
-    <row r="567" ht="15.75" customHeight="1">
-      <c r="A567"/>
-      <c r="B567"/>
-      <c r="C567"/>
-    </row>
-    <row r="568" ht="15.75" customHeight="1">
-      <c r="A568"/>
-      <c r="B568"/>
-      <c r="C568"/>
-    </row>
-    <row r="569" ht="15.75" customHeight="1">
-      <c r="A569"/>
-      <c r="B569"/>
-      <c r="C569"/>
-    </row>
-    <row r="570" ht="15.75" customHeight="1">
-      <c r="A570"/>
-      <c r="B570"/>
-      <c r="C570"/>
-    </row>
-    <row r="571" ht="15.75" customHeight="1">
-      <c r="A571"/>
-      <c r="B571"/>
-      <c r="C571"/>
-    </row>
-    <row r="572" ht="15.75" customHeight="1">
-      <c r="A572"/>
-      <c r="B572"/>
-      <c r="C572"/>
-    </row>
-    <row r="573" ht="15.75" customHeight="1">
-      <c r="A573"/>
-      <c r="B573"/>
-      <c r="C573"/>
-    </row>
-    <row r="574" ht="15.75" customHeight="1">
-      <c r="A574"/>
-      <c r="B574"/>
-      <c r="C574"/>
-    </row>
-    <row r="575" ht="15.75" customHeight="1">
-      <c r="A575"/>
-      <c r="B575"/>
-      <c r="C575"/>
-    </row>
-    <row r="576" ht="15.75" customHeight="1">
-      <c r="A576"/>
-      <c r="B576"/>
-      <c r="C576"/>
-    </row>
-    <row r="577" ht="15.75" customHeight="1">
-      <c r="A577"/>
-      <c r="B577"/>
-      <c r="C577"/>
-    </row>
-    <row r="578" ht="15.75" customHeight="1">
-      <c r="A578"/>
-      <c r="B578"/>
-      <c r="C578"/>
-    </row>
-    <row r="579" ht="15.75" customHeight="1">
-      <c r="A579"/>
-      <c r="B579"/>
-      <c r="C579"/>
-    </row>
-    <row r="580" ht="15.75" customHeight="1">
-      <c r="A580"/>
-      <c r="B580"/>
-      <c r="C580"/>
-    </row>
-    <row r="581" ht="15.75" customHeight="1">
-      <c r="A581"/>
-      <c r="B581"/>
-      <c r="C581"/>
-    </row>
-    <row r="582" ht="15.75" customHeight="1">
-      <c r="A582"/>
-      <c r="B582"/>
-      <c r="C582"/>
-    </row>
-    <row r="583" ht="15.75" customHeight="1">
-      <c r="A583"/>
-      <c r="B583"/>
-      <c r="C583"/>
-    </row>
-    <row r="584" ht="15.75" customHeight="1">
-      <c r="A584"/>
-      <c r="B584"/>
-      <c r="C584"/>
-    </row>
-    <row r="585" ht="15.75" customHeight="1">
-      <c r="A585"/>
-      <c r="B585"/>
-      <c r="C585"/>
-    </row>
-    <row r="586" ht="15.75" customHeight="1">
-      <c r="A586"/>
-      <c r="B586"/>
-      <c r="C586"/>
-    </row>
-    <row r="587" ht="15.75" customHeight="1">
-      <c r="A587"/>
-      <c r="B587"/>
-      <c r="C587"/>
-    </row>
-    <row r="588" ht="15.75" customHeight="1">
-      <c r="A588"/>
-      <c r="B588"/>
-      <c r="C588"/>
-    </row>
-    <row r="589" ht="15.75" customHeight="1">
-      <c r="A589"/>
-      <c r="B589"/>
-      <c r="C589"/>
-    </row>
-    <row r="590" ht="15.75" customHeight="1">
-      <c r="A590"/>
-      <c r="B590"/>
-      <c r="C590"/>
-    </row>
-    <row r="591" ht="15.75" customHeight="1">
-      <c r="A591"/>
-      <c r="B591"/>
-      <c r="C591"/>
-    </row>
-    <row r="592" ht="15.75" customHeight="1">
-      <c r="A592"/>
-      <c r="B592"/>
-      <c r="C592"/>
-    </row>
-    <row r="593" ht="15.75" customHeight="1">
-      <c r="A593"/>
-      <c r="B593"/>
-      <c r="C593"/>
-    </row>
-    <row r="594" ht="15.75" customHeight="1">
-      <c r="A594"/>
-      <c r="B594"/>
-      <c r="C594"/>
-    </row>
-    <row r="595" ht="15.75" customHeight="1">
-      <c r="A595"/>
-      <c r="B595"/>
-      <c r="C595"/>
-    </row>
-    <row r="596" ht="15.75" customHeight="1">
-      <c r="A596"/>
-      <c r="B596"/>
-      <c r="C596"/>
-    </row>
-    <row r="597" ht="15.75" customHeight="1">
-      <c r="A597"/>
-      <c r="B597"/>
-      <c r="C597"/>
-    </row>
-    <row r="598" ht="15.75" customHeight="1">
-      <c r="A598"/>
-      <c r="B598"/>
-      <c r="C598"/>
-    </row>
-    <row r="599" ht="15.75" customHeight="1">
-      <c r="A599"/>
-      <c r="B599"/>
-      <c r="C599"/>
-    </row>
-    <row r="600" ht="15.75" customHeight="1">
-      <c r="A600"/>
-      <c r="B600"/>
-      <c r="C600"/>
-    </row>
-    <row r="601" ht="15.75" customHeight="1">
-      <c r="A601"/>
-      <c r="B601"/>
-      <c r="C601"/>
-    </row>
-    <row r="602" ht="15.75" customHeight="1">
-      <c r="A602"/>
-      <c r="B602"/>
-      <c r="C602"/>
-    </row>
-    <row r="603" ht="15.75" customHeight="1">
-      <c r="A603"/>
-      <c r="B603"/>
-      <c r="C603"/>
-    </row>
-    <row r="604" ht="15.75" customHeight="1">
-      <c r="A604"/>
-      <c r="B604"/>
-      <c r="C604"/>
-    </row>
-    <row r="605" ht="15.75" customHeight="1">
-      <c r="A605"/>
-      <c r="B605"/>
-      <c r="C605"/>
-    </row>
-    <row r="606" ht="15.75" customHeight="1">
-      <c r="A606"/>
-      <c r="B606"/>
-      <c r="C606"/>
-    </row>
-    <row r="607" ht="15.75" customHeight="1">
-      <c r="A607"/>
-      <c r="B607"/>
-      <c r="C607"/>
-    </row>
-    <row r="608" ht="15.75" customHeight="1">
-      <c r="A608"/>
-      <c r="B608"/>
-      <c r="C608"/>
-    </row>
-    <row r="609" ht="15.75" customHeight="1">
-      <c r="A609"/>
-      <c r="B609"/>
-      <c r="C609"/>
-    </row>
-    <row r="610" ht="15.75" customHeight="1">
-      <c r="A610"/>
-      <c r="B610"/>
-      <c r="C610"/>
-    </row>
-    <row r="611" ht="15.75" customHeight="1">
-      <c r="A611"/>
-      <c r="B611"/>
-      <c r="C611"/>
-    </row>
-    <row r="612" ht="15.75" customHeight="1">
-      <c r="A612"/>
-      <c r="B612"/>
-      <c r="C612"/>
-    </row>
-    <row r="613" ht="15.75" customHeight="1">
-      <c r="A613"/>
-      <c r="B613"/>
-      <c r="C613"/>
-    </row>
-    <row r="614" ht="15.75" customHeight="1">
-      <c r="A614"/>
-      <c r="B614"/>
-      <c r="C614"/>
-    </row>
-    <row r="615" ht="15.75" customHeight="1">
-      <c r="A615"/>
-      <c r="B615"/>
-      <c r="C615"/>
-    </row>
-    <row r="616" ht="15.75" customHeight="1">
-      <c r="A616"/>
-      <c r="B616"/>
-      <c r="C616"/>
-    </row>
-    <row r="617" ht="15.75" customHeight="1">
-      <c r="A617"/>
-      <c r="B617"/>
-      <c r="C617"/>
-    </row>
-    <row r="618" ht="15.75" customHeight="1">
-      <c r="A618"/>
-      <c r="B618"/>
-      <c r="C618"/>
-    </row>
-    <row r="619" ht="15.75" customHeight="1">
-      <c r="A619"/>
-      <c r="B619"/>
-      <c r="C619"/>
-    </row>
-    <row r="620" ht="15.75" customHeight="1">
-      <c r="A620"/>
-      <c r="B620"/>
-      <c r="C620"/>
-    </row>
-    <row r="621" ht="15.75" customHeight="1">
-      <c r="A621"/>
-      <c r="B621"/>
-      <c r="C621"/>
-    </row>
-    <row r="622" ht="15.75" customHeight="1">
-      <c r="A622"/>
-      <c r="B622"/>
-      <c r="C622"/>
-    </row>
-    <row r="623" ht="15.75" customHeight="1">
-      <c r="A623"/>
-      <c r="B623"/>
-      <c r="C623"/>
-    </row>
-    <row r="624" ht="15.75" customHeight="1">
-      <c r="A624"/>
-      <c r="B624"/>
-      <c r="C624"/>
-    </row>
-    <row r="625" ht="15.75" customHeight="1">
-      <c r="A625"/>
-      <c r="B625"/>
-      <c r="C625"/>
-    </row>
-    <row r="626" ht="15.75" customHeight="1">
-      <c r="A626"/>
-      <c r="B626"/>
-      <c r="C626"/>
-    </row>
-    <row r="627" ht="15.75" customHeight="1">
-      <c r="A627"/>
-      <c r="B627"/>
-      <c r="C627"/>
-    </row>
-    <row r="628" ht="15.75" customHeight="1">
-      <c r="A628"/>
-      <c r="B628"/>
-      <c r="C628"/>
-    </row>
-    <row r="629" ht="15.75" customHeight="1">
-      <c r="A629"/>
-      <c r="B629"/>
-      <c r="C629"/>
-    </row>
-    <row r="630" ht="15.75" customHeight="1">
-      <c r="A630"/>
-      <c r="B630"/>
-      <c r="C630"/>
-    </row>
-    <row r="631" ht="15.75" customHeight="1">
-      <c r="A631"/>
-      <c r="B631"/>
-      <c r="C631"/>
-    </row>
-    <row r="632" ht="15.75" customHeight="1">
-      <c r="A632"/>
-      <c r="B632"/>
-      <c r="C632"/>
-    </row>
-    <row r="633" ht="15.75" customHeight="1">
-      <c r="A633"/>
-      <c r="B633"/>
-      <c r="C633"/>
-    </row>
-    <row r="634" ht="15.75" customHeight="1">
-      <c r="A634"/>
-      <c r="B634"/>
-      <c r="C634"/>
-    </row>
-    <row r="635" ht="15.75" customHeight="1">
-      <c r="A635"/>
-      <c r="B635"/>
-      <c r="C635"/>
-    </row>
-    <row r="636" ht="15.75" customHeight="1">
-      <c r="A636"/>
-      <c r="B636"/>
-      <c r="C636"/>
-    </row>
-    <row r="637" ht="15.75" customHeight="1">
-      <c r="A637"/>
-      <c r="B637"/>
-      <c r="C637"/>
-    </row>
-    <row r="638" ht="15.75" customHeight="1">
-      <c r="A638"/>
-      <c r="B638"/>
-      <c r="C638"/>
-    </row>
-    <row r="639" ht="15.75" customHeight="1">
-      <c r="A639"/>
-      <c r="B639"/>
-      <c r="C639"/>
-    </row>
-    <row r="640" ht="15.75" customHeight="1">
-      <c r="A640"/>
-      <c r="B640"/>
-      <c r="C640"/>
-    </row>
-    <row r="641" ht="15.75" customHeight="1">
-      <c r="A641"/>
-      <c r="B641"/>
-      <c r="C641"/>
-    </row>
-    <row r="642" ht="15.75" customHeight="1">
-      <c r="A642"/>
-      <c r="B642"/>
-      <c r="C642"/>
-    </row>
-    <row r="643" ht="15.75" customHeight="1">
-      <c r="A643"/>
-      <c r="B643"/>
-      <c r="C643"/>
-    </row>
-    <row r="644" ht="15.75" customHeight="1">
-      <c r="A644"/>
-      <c r="B644"/>
-      <c r="C644"/>
-    </row>
-    <row r="645" ht="15.75" customHeight="1">
-      <c r="A645"/>
-      <c r="B645"/>
-      <c r="C645"/>
-    </row>
-    <row r="646" ht="15.75" customHeight="1">
-      <c r="A646"/>
-      <c r="B646"/>
-      <c r="C646"/>
-    </row>
-    <row r="647" ht="15.75" customHeight="1">
-      <c r="A647"/>
-      <c r="B647"/>
-      <c r="C647"/>
-    </row>
-    <row r="648" ht="15.75" customHeight="1">
-      <c r="A648"/>
-      <c r="B648"/>
-      <c r="C648"/>
-    </row>
-    <row r="649" ht="15.75" customHeight="1">
-      <c r="A649"/>
-      <c r="B649"/>
-      <c r="C649"/>
-    </row>
-    <row r="650" ht="15.75" customHeight="1">
-      <c r="A650"/>
-      <c r="B650"/>
-      <c r="C650"/>
-    </row>
-    <row r="651" ht="15.75" customHeight="1">
-      <c r="A651"/>
-      <c r="B651"/>
-      <c r="C651"/>
-    </row>
-    <row r="652" ht="15.75" customHeight="1">
-      <c r="A652"/>
-      <c r="B652"/>
-      <c r="C652"/>
-    </row>
-    <row r="653" ht="15.75" customHeight="1">
-      <c r="A653"/>
-      <c r="B653"/>
-      <c r="C653"/>
-    </row>
-    <row r="654" ht="15.75" customHeight="1">
-      <c r="A654"/>
-      <c r="B654"/>
-      <c r="C654"/>
-    </row>
-    <row r="655" ht="15.75" customHeight="1">
-      <c r="A655"/>
-      <c r="B655"/>
-      <c r="C655"/>
-    </row>
-    <row r="656" ht="15.75" customHeight="1">
-      <c r="A656"/>
-      <c r="B656"/>
-      <c r="C656"/>
-    </row>
-    <row r="657" ht="15.75" customHeight="1">
-      <c r="A657"/>
-      <c r="B657"/>
-      <c r="C657"/>
-    </row>
-    <row r="658" ht="15.75" customHeight="1">
-      <c r="A658"/>
-      <c r="B658"/>
-      <c r="C658"/>
-    </row>
-    <row r="659" ht="15.75" customHeight="1">
-      <c r="A659"/>
-      <c r="B659"/>
-      <c r="C659"/>
-    </row>
-    <row r="660" ht="15.75" customHeight="1">
-      <c r="A660"/>
-      <c r="B660"/>
-      <c r="C660"/>
-    </row>
-    <row r="661" ht="15.75" customHeight="1">
-      <c r="A661"/>
-      <c r="B661"/>
-      <c r="C661"/>
-    </row>
-    <row r="662" ht="15.75" customHeight="1">
-      <c r="A662"/>
-      <c r="B662"/>
-      <c r="C662"/>
-    </row>
-    <row r="663" ht="15.75" customHeight="1">
-      <c r="A663"/>
-      <c r="B663"/>
-      <c r="C663"/>
-    </row>
-    <row r="664" ht="15.75" customHeight="1">
-      <c r="A664"/>
-      <c r="B664"/>
-      <c r="C664"/>
-    </row>
-    <row r="665" ht="15.75" customHeight="1">
-      <c r="A665"/>
-      <c r="B665"/>
-      <c r="C665"/>
-    </row>
-    <row r="666" ht="15.75" customHeight="1">
-      <c r="A666"/>
-      <c r="B666"/>
-      <c r="C666"/>
-    </row>
-    <row r="667" ht="15.75" customHeight="1">
-      <c r="A667"/>
-      <c r="B667"/>
-      <c r="C667"/>
-    </row>
-    <row r="668" ht="15.75" customHeight="1">
-      <c r="A668"/>
-      <c r="B668"/>
-      <c r="C668"/>
-    </row>
-    <row r="669" ht="15.75" customHeight="1">
-      <c r="A669"/>
-      <c r="B669"/>
-      <c r="C669"/>
-    </row>
-    <row r="670" ht="15.75" customHeight="1">
-      <c r="A670"/>
-      <c r="B670"/>
-      <c r="C670"/>
-    </row>
-    <row r="671" ht="15.75" customHeight="1">
-      <c r="A671"/>
-      <c r="B671"/>
-      <c r="C671"/>
-    </row>
-    <row r="672" ht="15.75" customHeight="1">
-      <c r="A672"/>
-      <c r="B672"/>
-      <c r="C672"/>
-    </row>
-    <row r="673" ht="15.75" customHeight="1">
-      <c r="A673"/>
-      <c r="B673"/>
-      <c r="C673"/>
-    </row>
-    <row r="674" ht="15.75" customHeight="1">
-      <c r="A674"/>
-      <c r="B674"/>
-      <c r="C674"/>
-    </row>
-    <row r="675" ht="15.75" customHeight="1">
-      <c r="A675"/>
-      <c r="B675"/>
-      <c r="C675"/>
-    </row>
-    <row r="676" ht="15.75" customHeight="1">
-      <c r="A676"/>
-      <c r="B676"/>
-      <c r="C676"/>
-    </row>
-    <row r="677" ht="15.75" customHeight="1">
-      <c r="A677"/>
-      <c r="B677"/>
-      <c r="C677"/>
-    </row>
-    <row r="678" ht="15.75" customHeight="1">
-      <c r="A678"/>
-      <c r="B678"/>
-      <c r="C678"/>
-    </row>
-    <row r="679" ht="15.75" customHeight="1">
-      <c r="A679"/>
-      <c r="B679"/>
-      <c r="C679"/>
-    </row>
-    <row r="680" ht="15.75" customHeight="1">
-      <c r="A680"/>
-      <c r="B680"/>
-      <c r="C680"/>
-    </row>
-    <row r="681" ht="15.75" customHeight="1">
-      <c r="A681"/>
-      <c r="B681"/>
-      <c r="C681"/>
-    </row>
-    <row r="682" ht="15.75" customHeight="1">
-      <c r="A682"/>
-      <c r="B682"/>
-      <c r="C682"/>
-    </row>
-    <row r="683" ht="15.75" customHeight="1">
-      <c r="A683"/>
-      <c r="B683"/>
-      <c r="C683"/>
-    </row>
-    <row r="684" ht="15.75" customHeight="1">
-      <c r="A684"/>
-      <c r="B684"/>
-      <c r="C684"/>
-    </row>
-    <row r="685" ht="15.75" customHeight="1">
-      <c r="A685"/>
-      <c r="B685"/>
-      <c r="C685"/>
-    </row>
-    <row r="686" ht="15.75" customHeight="1">
-      <c r="A686"/>
-      <c r="B686"/>
-      <c r="C686"/>
-    </row>
-    <row r="687" ht="15.75" customHeight="1">
-      <c r="A687"/>
-      <c r="B687"/>
-      <c r="C687"/>
-    </row>
-    <row r="688" ht="15.75" customHeight="1">
-      <c r="A688"/>
-      <c r="B688"/>
-      <c r="C688"/>
-    </row>
-    <row r="689" ht="15.75" customHeight="1">
-      <c r="A689"/>
-      <c r="B689"/>
-      <c r="C689"/>
-    </row>
-    <row r="690" ht="15.75" customHeight="1">
-      <c r="A690"/>
-      <c r="B690"/>
-      <c r="C690"/>
-    </row>
-    <row r="691" ht="15.75" customHeight="1">
-      <c r="A691"/>
-      <c r="B691"/>
-      <c r="C691"/>
-    </row>
-    <row r="692" ht="15.75" customHeight="1">
-      <c r="A692"/>
-      <c r="B692"/>
-      <c r="C692"/>
-    </row>
-    <row r="693" ht="15.75" customHeight="1">
-      <c r="A693"/>
-      <c r="B693"/>
-      <c r="C693"/>
-    </row>
-    <row r="694" ht="15.75" customHeight="1">
-      <c r="A694"/>
-      <c r="B694"/>
-      <c r="C694"/>
-    </row>
-    <row r="695" ht="15.75" customHeight="1">
-      <c r="A695"/>
-      <c r="B695"/>
-      <c r="C695"/>
-    </row>
-    <row r="696" ht="15.75" customHeight="1">
-      <c r="A696"/>
-      <c r="B696"/>
-      <c r="C696"/>
-    </row>
-    <row r="697" ht="15.75" customHeight="1">
-      <c r="A697"/>
-      <c r="B697"/>
-      <c r="C697"/>
-    </row>
-    <row r="698" ht="15.75" customHeight="1">
-      <c r="A698"/>
-      <c r="B698"/>
-      <c r="C698"/>
-    </row>
-    <row r="699" ht="15.75" customHeight="1">
-      <c r="A699"/>
-      <c r="B699"/>
-      <c r="C699"/>
-    </row>
-    <row r="700" ht="15.75" customHeight="1">
-      <c r="A700"/>
-      <c r="B700"/>
-      <c r="C700"/>
-    </row>
-    <row r="701" ht="15.75" customHeight="1">
-      <c r="A701"/>
-      <c r="B701"/>
-      <c r="C701"/>
-    </row>
-    <row r="702" ht="15.75" customHeight="1">
-      <c r="A702"/>
-      <c r="B702"/>
-      <c r="C702"/>
-    </row>
-    <row r="703" ht="15.75" customHeight="1">
-      <c r="A703"/>
-      <c r="B703"/>
-      <c r="C703"/>
-    </row>
-    <row r="704" ht="15.75" customHeight="1">
-      <c r="A704"/>
-      <c r="B704"/>
-      <c r="C704"/>
-    </row>
-    <row r="705" ht="15.75" customHeight="1">
-      <c r="A705"/>
-      <c r="B705"/>
-      <c r="C705"/>
-    </row>
-    <row r="706" ht="15.75" customHeight="1">
-      <c r="A706"/>
-      <c r="B706"/>
-      <c r="C706"/>
-    </row>
-    <row r="707" ht="15.75" customHeight="1">
-      <c r="A707"/>
-      <c r="B707"/>
-      <c r="C707"/>
-    </row>
-    <row r="708" ht="15.75" customHeight="1">
-      <c r="A708"/>
-      <c r="B708"/>
-      <c r="C708"/>
-    </row>
-    <row r="709" ht="15.75" customHeight="1">
-      <c r="A709"/>
-      <c r="B709"/>
-      <c r="C709"/>
-    </row>
-    <row r="710" ht="15.75" customHeight="1">
-      <c r="A710"/>
-      <c r="B710"/>
-      <c r="C710"/>
-    </row>
-    <row r="711" ht="15.75" customHeight="1">
-      <c r="A711"/>
-      <c r="B711"/>
-      <c r="C711"/>
-    </row>
-    <row r="712" ht="15.75" customHeight="1">
-      <c r="A712"/>
-      <c r="B712"/>
-      <c r="C712"/>
-    </row>
-    <row r="713" ht="15.75" customHeight="1">
-      <c r="A713"/>
-      <c r="B713"/>
-      <c r="C713"/>
-    </row>
-    <row r="714" ht="15.75" customHeight="1">
-      <c r="A714"/>
-      <c r="B714"/>
-      <c r="C714"/>
-    </row>
-    <row r="715" ht="15.75" customHeight="1">
-      <c r="A715"/>
-      <c r="B715"/>
-      <c r="C715"/>
-    </row>
-    <row r="716" ht="15.75" customHeight="1">
-      <c r="A716"/>
-      <c r="B716"/>
-      <c r="C716"/>
-    </row>
-    <row r="717" ht="15.75" customHeight="1">
-      <c r="A717"/>
-      <c r="B717"/>
-      <c r="C717"/>
-    </row>
-    <row r="718" ht="15.75" customHeight="1">
-      <c r="A718"/>
-      <c r="B718"/>
-      <c r="C718"/>
-    </row>
-    <row r="719" ht="15.75" customHeight="1">
-      <c r="A719"/>
-      <c r="B719"/>
-      <c r="C719"/>
-    </row>
-    <row r="720" ht="15.75" customHeight="1">
-      <c r="A720"/>
-      <c r="B720"/>
-      <c r="C720"/>
-    </row>
-    <row r="721" ht="15.75" customHeight="1">
-      <c r="A721"/>
-      <c r="B721"/>
-      <c r="C721"/>
-    </row>
-    <row r="722" ht="15.75" customHeight="1">
-      <c r="A722"/>
-      <c r="B722"/>
-      <c r="C722"/>
-    </row>
-    <row r="723" ht="15.75" customHeight="1">
-      <c r="A723"/>
-      <c r="B723"/>
-      <c r="C723"/>
-    </row>
-    <row r="724" ht="15.75" customHeight="1">
-      <c r="A724"/>
-      <c r="B724"/>
-      <c r="C724"/>
-    </row>
-    <row r="725" ht="15.75" customHeight="1">
-      <c r="A725"/>
-      <c r="B725"/>
-      <c r="C725"/>
-    </row>
-    <row r="726" ht="15.75" customHeight="1">
-      <c r="A726"/>
-      <c r="B726"/>
-      <c r="C726"/>
-    </row>
-    <row r="727" ht="15.75" customHeight="1">
-      <c r="A727"/>
-      <c r="B727"/>
-      <c r="C727"/>
-    </row>
-    <row r="728" ht="15.75" customHeight="1">
-      <c r="A728"/>
-      <c r="B728"/>
-      <c r="C728"/>
-    </row>
-    <row r="729" ht="15.75" customHeight="1">
-      <c r="A729"/>
-      <c r="B729"/>
-      <c r="C729"/>
-    </row>
-    <row r="730" ht="15.75" customHeight="1">
-      <c r="A730"/>
-      <c r="B730"/>
-      <c r="C730"/>
-    </row>
-    <row r="731" ht="15.75" customHeight="1">
-      <c r="A731"/>
-      <c r="B731"/>
-      <c r="C731"/>
-    </row>
-    <row r="732" ht="15.75" customHeight="1">
-      <c r="A732"/>
-      <c r="B732"/>
-      <c r="C732"/>
-    </row>
-    <row r="733" ht="15.75" customHeight="1">
-      <c r="A733"/>
-      <c r="B733"/>
-      <c r="C733"/>
-    </row>
-    <row r="734" ht="15.75" customHeight="1">
-      <c r="A734"/>
-      <c r="B734"/>
-      <c r="C734"/>
-    </row>
-    <row r="735" ht="15.75" customHeight="1">
-      <c r="A735"/>
-      <c r="B735"/>
-      <c r="C735"/>
-    </row>
-    <row r="736" ht="15.75" customHeight="1">
-      <c r="A736"/>
-      <c r="B736"/>
-      <c r="C736"/>
-    </row>
-    <row r="737" ht="15.75" customHeight="1">
-      <c r="A737"/>
-      <c r="B737"/>
-      <c r="C737"/>
-    </row>
-    <row r="738" ht="15.75" customHeight="1">
-      <c r="A738"/>
-      <c r="B738"/>
-      <c r="C738"/>
-    </row>
-    <row r="739" ht="15.75" customHeight="1">
-      <c r="A739"/>
-      <c r="B739"/>
-      <c r="C739"/>
-    </row>
-    <row r="740" ht="15.75" customHeight="1">
-      <c r="A740"/>
-      <c r="B740"/>
-      <c r="C740"/>
-    </row>
-    <row r="741" ht="15.75" customHeight="1">
-      <c r="A741"/>
-      <c r="B741"/>
-      <c r="C741"/>
-    </row>
-    <row r="742" ht="15.75" customHeight="1">
-      <c r="A742"/>
-      <c r="B742"/>
-      <c r="C742"/>
-    </row>
-    <row r="743" ht="15.75" customHeight="1">
-      <c r="A743"/>
-      <c r="B743"/>
-      <c r="C743"/>
-    </row>
-    <row r="744" ht="15.75" customHeight="1">
-      <c r="A744"/>
-      <c r="B744"/>
-      <c r="C744"/>
-    </row>
-    <row r="745" ht="15.75" customHeight="1">
-      <c r="A745"/>
-      <c r="B745"/>
-      <c r="C745"/>
-    </row>
-    <row r="746" ht="15.75" customHeight="1">
-      <c r="A746"/>
-      <c r="B746"/>
-      <c r="C746"/>
-    </row>
-    <row r="747" ht="15.75" customHeight="1">
-      <c r="A747"/>
-      <c r="B747"/>
-      <c r="C747"/>
-    </row>
-    <row r="748" ht="15.75" customHeight="1">
-      <c r="A748"/>
-      <c r="B748"/>
-      <c r="C748"/>
-    </row>
-    <row r="749" ht="15.75" customHeight="1">
-      <c r="A749"/>
-      <c r="B749"/>
-      <c r="C749"/>
-    </row>
-    <row r="750" ht="15.75" customHeight="1">
-      <c r="A750"/>
-      <c r="B750"/>
-      <c r="C750"/>
-    </row>
-    <row r="751" ht="15.75" customHeight="1">
-      <c r="A751"/>
-      <c r="B751"/>
-      <c r="C751"/>
-    </row>
-    <row r="752" ht="15.75" customHeight="1">
-      <c r="A752"/>
-      <c r="B752"/>
-      <c r="C752"/>
-    </row>
-    <row r="753" ht="15.75" customHeight="1">
-      <c r="A753"/>
-      <c r="B753"/>
-      <c r="C753"/>
-    </row>
-    <row r="754" ht="15.75" customHeight="1">
-      <c r="A754"/>
-      <c r="B754"/>
-      <c r="C754"/>
-    </row>
-    <row r="755" ht="15.75" customHeight="1">
-      <c r="A755"/>
-      <c r="B755"/>
-      <c r="C755"/>
-    </row>
-    <row r="756" ht="15.75" customHeight="1">
-      <c r="A756"/>
-      <c r="B756"/>
-      <c r="C756"/>
-    </row>
-    <row r="757" ht="15.75" customHeight="1">
-      <c r="A757"/>
-      <c r="B757"/>
-      <c r="C757"/>
-    </row>
-    <row r="758" ht="15.75" customHeight="1">
-      <c r="A758"/>
-      <c r="B758"/>
-      <c r="C758"/>
-    </row>
-    <row r="759" ht="15.75" customHeight="1">
-      <c r="A759"/>
-      <c r="B759"/>
-      <c r="C759"/>
-    </row>
-    <row r="760" ht="15.75" customHeight="1">
-      <c r="A760"/>
-      <c r="B760"/>
-      <c r="C760"/>
-    </row>
-    <row r="761" ht="15.75" customHeight="1">
-      <c r="A761"/>
-      <c r="B761"/>
-      <c r="C761"/>
-    </row>
-    <row r="762" ht="15.75" customHeight="1">
-      <c r="A762"/>
-      <c r="B762"/>
-      <c r="C762"/>
-    </row>
-    <row r="763" ht="15.75" customHeight="1">
-      <c r="A763"/>
-      <c r="B763"/>
-      <c r="C763"/>
-    </row>
-    <row r="764" ht="15.75" customHeight="1">
-      <c r="A764"/>
-      <c r="B764"/>
-      <c r="C764"/>
-    </row>
-    <row r="765" ht="15.75" customHeight="1">
-      <c r="A765"/>
-      <c r="B765"/>
-      <c r="C765"/>
-    </row>
-    <row r="766" ht="15.75" customHeight="1">
-      <c r="A766"/>
-      <c r="B766"/>
-      <c r="C766"/>
-    </row>
-    <row r="767" ht="15.75" customHeight="1">
-      <c r="A767"/>
-      <c r="B767"/>
-      <c r="C767"/>
-    </row>
-    <row r="768" ht="15.75" customHeight="1">
-      <c r="A768"/>
-      <c r="B768"/>
-      <c r="C768"/>
-    </row>
-    <row r="769" ht="15.75" customHeight="1">
-      <c r="A769"/>
-      <c r="B769"/>
-      <c r="C769"/>
-    </row>
-    <row r="770" ht="15.75" customHeight="1">
-      <c r="A770"/>
-      <c r="B770"/>
-      <c r="C770"/>
-    </row>
-    <row r="771" ht="15.75" customHeight="1">
-      <c r="A771"/>
-      <c r="B771"/>
-      <c r="C771"/>
-    </row>
-    <row r="772" ht="15.75" customHeight="1">
-      <c r="A772"/>
-      <c r="B772"/>
-      <c r="C772"/>
-    </row>
-    <row r="773" ht="15.75" customHeight="1">
-      <c r="A773"/>
-      <c r="B773"/>
-      <c r="C773"/>
-    </row>
-    <row r="774" ht="15.75" customHeight="1">
-      <c r="A774"/>
-      <c r="B774"/>
-      <c r="C774"/>
-    </row>
-    <row r="775" ht="15.75" customHeight="1">
-      <c r="A775"/>
-      <c r="B775"/>
-      <c r="C775"/>
-    </row>
-    <row r="776" ht="15.75" customHeight="1">
-      <c r="A776"/>
-      <c r="B776"/>
-      <c r="C776"/>
-    </row>
-    <row r="777" ht="15.75" customHeight="1">
-      <c r="A777"/>
-      <c r="B777"/>
-      <c r="C777"/>
-    </row>
-    <row r="778" ht="15.75" customHeight="1">
-      <c r="A778"/>
-      <c r="B778"/>
-      <c r="C778"/>
-    </row>
-    <row r="779" ht="15.75" customHeight="1">
-      <c r="A779"/>
-      <c r="B779"/>
-      <c r="C779"/>
-    </row>
-    <row r="780" ht="15.75" customHeight="1">
-      <c r="A780"/>
-      <c r="B780"/>
-      <c r="C780"/>
-    </row>
-    <row r="781" ht="15.75" customHeight="1">
-      <c r="A781"/>
-      <c r="B781"/>
-      <c r="C781"/>
-    </row>
-    <row r="782" ht="15.75" customHeight="1">
-      <c r="A782"/>
-      <c r="B782"/>
-      <c r="C782"/>
-    </row>
-    <row r="783" ht="15.75" customHeight="1">
-      <c r="A783"/>
-      <c r="B783"/>
-      <c r="C783"/>
-    </row>
-    <row r="784" ht="15.75" customHeight="1">
-      <c r="A784"/>
-      <c r="B784"/>
-      <c r="C784"/>
-    </row>
-    <row r="785" ht="15.75" customHeight="1">
-      <c r="A785"/>
-      <c r="B785"/>
-      <c r="C785"/>
-    </row>
-    <row r="786" ht="15.75" customHeight="1">
-      <c r="A786"/>
-      <c r="B786"/>
-      <c r="C786"/>
-    </row>
-    <row r="787" ht="15.75" customHeight="1">
-      <c r="A787"/>
-      <c r="B787"/>
-      <c r="C787"/>
-    </row>
-    <row r="788" ht="15.75" customHeight="1">
-      <c r="A788"/>
-      <c r="B788"/>
-      <c r="C788"/>
-    </row>
-    <row r="789" ht="15.75" customHeight="1">
-      <c r="A789"/>
-      <c r="B789"/>
-      <c r="C789"/>
-    </row>
-    <row r="790" ht="15.75" customHeight="1">
-      <c r="A790"/>
-      <c r="B790"/>
-      <c r="C790"/>
-    </row>
-    <row r="791" ht="15.75" customHeight="1">
-      <c r="A791"/>
-      <c r="B791"/>
-      <c r="C791"/>
-    </row>
-    <row r="792" ht="15.75" customHeight="1">
-      <c r="A792"/>
-      <c r="B792"/>
-      <c r="C792"/>
-    </row>
-    <row r="793" ht="15.75" customHeight="1">
-      <c r="A793"/>
-      <c r="B793"/>
-      <c r="C793"/>
-    </row>
-    <row r="794" ht="15.75" customHeight="1">
-      <c r="A794"/>
-      <c r="B794"/>
-      <c r="C794"/>
-    </row>
-    <row r="795" ht="15.75" customHeight="1">
-      <c r="A795"/>
-      <c r="B795"/>
-      <c r="C795"/>
-    </row>
-    <row r="796" ht="15.75" customHeight="1">
-      <c r="A796"/>
-      <c r="B796"/>
-      <c r="C796"/>
-    </row>
-    <row r="797" ht="15.75" customHeight="1">
-      <c r="A797"/>
-      <c r="B797"/>
-      <c r="C797"/>
-    </row>
-    <row r="798" ht="15.75" customHeight="1">
-      <c r="A798"/>
-      <c r="B798"/>
-      <c r="C798"/>
-    </row>
-    <row r="799" ht="15.75" customHeight="1">
-      <c r="A799"/>
-      <c r="B799"/>
-      <c r="C799"/>
-    </row>
-    <row r="800" ht="15.75" customHeight="1">
-      <c r="A800"/>
-      <c r="B800"/>
-      <c r="C800"/>
-    </row>
-    <row r="801" ht="15.75" customHeight="1">
-      <c r="A801"/>
-      <c r="B801"/>
-      <c r="C801"/>
-    </row>
-    <row r="802" ht="15.75" customHeight="1">
-      <c r="A802"/>
-      <c r="B802"/>
-      <c r="C802"/>
-    </row>
-    <row r="803" ht="15.75" customHeight="1">
-      <c r="A803"/>
-      <c r="B803"/>
-      <c r="C803"/>
-    </row>
-    <row r="804" ht="15.75" customHeight="1">
-      <c r="A804"/>
-      <c r="B804"/>
-      <c r="C804"/>
-    </row>
-    <row r="805" ht="15.75" customHeight="1">
-      <c r="A805"/>
-      <c r="B805"/>
-      <c r="C805"/>
-    </row>
-    <row r="806" ht="15.75" customHeight="1">
-      <c r="A806"/>
-      <c r="B806"/>
-      <c r="C806"/>
-    </row>
-    <row r="807" ht="15.75" customHeight="1">
-      <c r="A807"/>
-      <c r="B807"/>
-      <c r="C807"/>
-    </row>
-    <row r="808" ht="15.75" customHeight="1">
-      <c r="A808"/>
-      <c r="B808"/>
-      <c r="C808"/>
-    </row>
-    <row r="809" ht="15.75" customHeight="1">
-      <c r="A809"/>
-      <c r="B809"/>
-      <c r="C809"/>
-    </row>
-    <row r="810" ht="15.75" customHeight="1">
-      <c r="A810"/>
-      <c r="B810"/>
-      <c r="C810"/>
-    </row>
-    <row r="811" ht="15.75" customHeight="1">
-      <c r="A811"/>
-      <c r="B811"/>
-      <c r="C811"/>
-    </row>
-    <row r="812" ht="15.75" customHeight="1">
-      <c r="A812"/>
-      <c r="B812"/>
-      <c r="C812"/>
-    </row>
-    <row r="813" ht="15.75" customHeight="1">
-      <c r="A813"/>
-      <c r="B813"/>
-      <c r="C813"/>
-    </row>
-    <row r="814" ht="15.75" customHeight="1">
-      <c r="A814"/>
-      <c r="B814"/>
-      <c r="C814"/>
-    </row>
-    <row r="815" ht="15.75" customHeight="1">
-      <c r="A815"/>
-      <c r="B815"/>
-      <c r="C815"/>
-    </row>
-    <row r="816" ht="15.75" customHeight="1">
-      <c r="A816"/>
-      <c r="B816"/>
-      <c r="C816"/>
-    </row>
-    <row r="817" ht="15.75" customHeight="1">
-      <c r="A817"/>
-      <c r="B817"/>
-      <c r="C817"/>
-    </row>
-    <row r="818" ht="15.75" customHeight="1">
-      <c r="A818"/>
-      <c r="B818"/>
-      <c r="C818"/>
-    </row>
-    <row r="819" ht="15.75" customHeight="1">
-      <c r="A819"/>
-      <c r="B819"/>
-      <c r="C819"/>
-    </row>
-    <row r="820" ht="15.75" customHeight="1">
-      <c r="A820"/>
-      <c r="B820"/>
-      <c r="C820"/>
-    </row>
-    <row r="821" ht="15.75" customHeight="1">
-      <c r="A821"/>
-      <c r="B821"/>
-      <c r="C821"/>
-    </row>
-    <row r="822" ht="15.75" customHeight="1">
-      <c r="A822"/>
-      <c r="B822"/>
-      <c r="C822"/>
-    </row>
-    <row r="823" ht="15.75" customHeight="1">
-      <c r="A823"/>
-      <c r="B823"/>
-      <c r="C823"/>
-    </row>
-    <row r="824" ht="15.75" customHeight="1">
-      <c r="A824"/>
-      <c r="B824"/>
-      <c r="C824"/>
-    </row>
-    <row r="825" ht="15.75" customHeight="1">
-      <c r="A825"/>
-      <c r="B825"/>
-      <c r="C825"/>
-    </row>
-    <row r="826" ht="15.75" customHeight="1">
-      <c r="A826"/>
-      <c r="B826"/>
-      <c r="C826"/>
-    </row>
-    <row r="827" ht="15.75" customHeight="1">
-      <c r="A827"/>
-      <c r="B827"/>
-      <c r="C827"/>
-    </row>
-    <row r="828" ht="15.75" customHeight="1">
-      <c r="A828"/>
-      <c r="B828"/>
-      <c r="C828"/>
-    </row>
-    <row r="829" ht="15.75" customHeight="1">
-      <c r="A829"/>
-      <c r="B829"/>
-      <c r="C829"/>
-    </row>
-    <row r="830" ht="15.75" customHeight="1">
-      <c r="A830"/>
-      <c r="B830"/>
-      <c r="C830"/>
-    </row>
-    <row r="831" ht="15.75" customHeight="1">
-      <c r="A831"/>
-      <c r="B831"/>
-      <c r="C831"/>
-    </row>
-    <row r="832" ht="15.75" customHeight="1">
-      <c r="A832"/>
-      <c r="B832"/>
-      <c r="C832"/>
-    </row>
-    <row r="833" ht="15.75" customHeight="1">
-      <c r="A833"/>
-      <c r="B833"/>
-      <c r="C833"/>
-    </row>
-    <row r="834" ht="15.75" customHeight="1">
-      <c r="A834"/>
-      <c r="B834"/>
-      <c r="C834"/>
-    </row>
-    <row r="835" ht="15.75" customHeight="1">
-      <c r="A835"/>
-      <c r="B835"/>
-      <c r="C835"/>
-    </row>
-    <row r="836" ht="15.75" customHeight="1">
-      <c r="A836"/>
-      <c r="B836"/>
-      <c r="C836"/>
-    </row>
-    <row r="837" ht="15.75" customHeight="1">
-      <c r="A837"/>
-      <c r="B837"/>
-      <c r="C837"/>
-    </row>
-    <row r="838" ht="15.75" customHeight="1">
-      <c r="A838"/>
-      <c r="B838"/>
-      <c r="C838"/>
-    </row>
-    <row r="839" ht="15.75" customHeight="1">
-      <c r="A839"/>
-      <c r="B839"/>
-      <c r="C839"/>
-    </row>
-    <row r="840" ht="15.75" customHeight="1">
-      <c r="A840"/>
-      <c r="B840"/>
-      <c r="C840"/>
-    </row>
-    <row r="841" ht="15.75" customHeight="1">
-      <c r="A841"/>
-      <c r="B841"/>
-      <c r="C841"/>
-    </row>
-    <row r="842" ht="15.75" customHeight="1">
-      <c r="A842"/>
-      <c r="B842"/>
-      <c r="C842"/>
-    </row>
-    <row r="843" ht="15.75" customHeight="1">
-      <c r="A843"/>
-      <c r="B843"/>
-      <c r="C843"/>
-    </row>
-    <row r="844" ht="15.75" customHeight="1">
-      <c r="A844"/>
-      <c r="B844"/>
-      <c r="C844"/>
-    </row>
-    <row r="845" ht="15.75" customHeight="1">
-      <c r="A845"/>
-      <c r="B845"/>
-      <c r="C845"/>
-    </row>
-    <row r="846" ht="15.75" customHeight="1">
-      <c r="A846"/>
-      <c r="B846"/>
-      <c r="C846"/>
-    </row>
-    <row r="847" ht="15.75" customHeight="1">
-      <c r="A847"/>
-      <c r="B847"/>
-      <c r="C847"/>
-    </row>
-    <row r="848" ht="15.75" customHeight="1">
-      <c r="A848"/>
-      <c r="B848"/>
-      <c r="C848"/>
-    </row>
-    <row r="849" ht="15.75" customHeight="1">
-      <c r="A849"/>
-      <c r="B849"/>
-      <c r="C849"/>
-    </row>
-    <row r="850" ht="15.75" customHeight="1">
-      <c r="A850"/>
-      <c r="B850"/>
-      <c r="C850"/>
-    </row>
-    <row r="851" ht="15.75" customHeight="1">
-      <c r="A851"/>
-      <c r="B851"/>
-      <c r="C851"/>
-    </row>
-    <row r="852" ht="15.75" customHeight="1">
-      <c r="A852"/>
-      <c r="B852"/>
-      <c r="C852"/>
-    </row>
-    <row r="853" ht="15.75" customHeight="1">
-      <c r="A853"/>
-      <c r="B853"/>
-      <c r="C853"/>
-    </row>
-    <row r="854" ht="15.75" customHeight="1">
-      <c r="A854"/>
-      <c r="B854"/>
-      <c r="C854"/>
-    </row>
-    <row r="855" ht="15.75" customHeight="1">
-      <c r="A855"/>
-      <c r="B855"/>
-      <c r="C855"/>
-    </row>
-    <row r="856" ht="15.75" customHeight="1">
-      <c r="A856"/>
-      <c r="B856"/>
-      <c r="C856"/>
-    </row>
-    <row r="857" ht="15.75" customHeight="1">
-      <c r="A857"/>
-      <c r="B857"/>
-      <c r="C857"/>
-    </row>
-    <row r="858" ht="15.75" customHeight="1">
-      <c r="A858"/>
-      <c r="B858"/>
-      <c r="C858"/>
-    </row>
-    <row r="859" ht="15.75" customHeight="1">
-      <c r="A859"/>
-      <c r="B859"/>
-      <c r="C859"/>
-    </row>
-    <row r="860" ht="15.75" customHeight="1">
-      <c r="A860"/>
-      <c r="B860"/>
-      <c r="C860"/>
-    </row>
-    <row r="861" ht="15.75" customHeight="1">
-      <c r="A861"/>
-      <c r="B861"/>
-      <c r="C861"/>
-    </row>
-    <row r="862" ht="15.75" customHeight="1">
-      <c r="A862"/>
-      <c r="B862"/>
-      <c r="C862"/>
-    </row>
-    <row r="863" ht="15.75" customHeight="1">
-      <c r="A863"/>
-      <c r="B863"/>
-      <c r="C863"/>
-    </row>
-    <row r="864" ht="15.75" customHeight="1">
-      <c r="A864"/>
-      <c r="B864"/>
-      <c r="C864"/>
-    </row>
-    <row r="865" ht="15.75" customHeight="1">
-      <c r="A865"/>
-      <c r="B865"/>
-      <c r="C865"/>
-    </row>
-    <row r="866" ht="15.75" customHeight="1">
-      <c r="A866"/>
-      <c r="B866"/>
-      <c r="C866"/>
-    </row>
-    <row r="867" ht="15.75" customHeight="1">
-      <c r="A867"/>
-      <c r="B867"/>
-      <c r="C867"/>
-    </row>
-    <row r="868" ht="15.75" customHeight="1">
-      <c r="A868"/>
-      <c r="B868"/>
-      <c r="C868"/>
-    </row>
-    <row r="869" ht="15.75" customHeight="1">
-      <c r="A869"/>
-      <c r="B869"/>
-      <c r="C869"/>
-    </row>
-    <row r="870" ht="15.75" customHeight="1">
-      <c r="A870"/>
-      <c r="B870"/>
-      <c r="C870"/>
-    </row>
-    <row r="871" ht="15.75" customHeight="1">
-      <c r="A871"/>
-      <c r="B871"/>
-      <c r="C871"/>
-    </row>
-    <row r="872" ht="15.75" customHeight="1">
-      <c r="A872"/>
-      <c r="B872"/>
-      <c r="C872"/>
-    </row>
-    <row r="873" ht="15.75" customHeight="1">
-      <c r="A873"/>
-      <c r="B873"/>
-      <c r="C873"/>
-    </row>
-    <row r="874" ht="15.75" customHeight="1">
-      <c r="A874"/>
-      <c r="B874"/>
-      <c r="C874"/>
-    </row>
-    <row r="875" ht="15.75" customHeight="1">
-      <c r="A875"/>
-      <c r="B875"/>
-      <c r="C875"/>
-    </row>
-    <row r="876" ht="15.75" customHeight="1">
-      <c r="A876"/>
-      <c r="B876"/>
-      <c r="C876"/>
-    </row>
-    <row r="877" ht="15.75" customHeight="1">
-      <c r="A877"/>
-      <c r="B877"/>
-      <c r="C877"/>
-    </row>
-    <row r="878" ht="15.75" customHeight="1">
-      <c r="A878"/>
-      <c r="B878"/>
-      <c r="C878"/>
-    </row>
-    <row r="879" ht="15.75" customHeight="1">
-      <c r="A879"/>
-      <c r="B879"/>
-      <c r="C879"/>
-    </row>
-    <row r="880" ht="15.75" customHeight="1">
-      <c r="A880"/>
-      <c r="B880"/>
-      <c r="C880"/>
-    </row>
-    <row r="881" ht="15.75" customHeight="1">
-      <c r="A881"/>
-      <c r="B881"/>
-      <c r="C881"/>
-    </row>
-    <row r="882" ht="15.75" customHeight="1">
-      <c r="A882"/>
-      <c r="B882"/>
-      <c r="C882"/>
-    </row>
-    <row r="883" ht="15.75" customHeight="1">
-      <c r="A883"/>
-      <c r="B883"/>
-      <c r="C883"/>
-    </row>
-    <row r="884" ht="15.75" customHeight="1">
-      <c r="A884"/>
-      <c r="B884"/>
-      <c r="C884"/>
-    </row>
-    <row r="885" ht="15.75" customHeight="1">
-      <c r="A885"/>
-      <c r="B885"/>
-      <c r="C885"/>
-    </row>
-    <row r="886" ht="15.75" customHeight="1">
-      <c r="A886"/>
-      <c r="B886"/>
-      <c r="C886"/>
-    </row>
-    <row r="887" ht="15.75" customHeight="1">
-      <c r="A887"/>
-      <c r="B887"/>
-      <c r="C887"/>
-    </row>
-    <row r="888" ht="15.75" customHeight="1">
-      <c r="A888"/>
-      <c r="B888"/>
-      <c r="C888"/>
-    </row>
-    <row r="889" ht="15.75" customHeight="1">
-      <c r="A889"/>
-      <c r="B889"/>
-      <c r="C889"/>
-    </row>
-    <row r="890" ht="15.75" customHeight="1">
-      <c r="A890"/>
-      <c r="B890"/>
-      <c r="C890"/>
-    </row>
-    <row r="891" ht="15.75" customHeight="1">
-      <c r="A891"/>
-      <c r="B891"/>
-      <c r="C891"/>
-    </row>
-    <row r="892" ht="15.75" customHeight="1">
-      <c r="A892"/>
-      <c r="B892"/>
-      <c r="C892"/>
-    </row>
-    <row r="893" ht="15.75" customHeight="1">
-      <c r="A893"/>
-      <c r="B893"/>
-      <c r="C893"/>
-    </row>
-    <row r="894" ht="15.75" customHeight="1">
-      <c r="A894"/>
-      <c r="B894"/>
-      <c r="C894"/>
-    </row>
-    <row r="895" ht="15.75" customHeight="1">
-      <c r="A895"/>
-      <c r="B895"/>
-      <c r="C895"/>
-    </row>
-    <row r="896" ht="15.75" customHeight="1">
-      <c r="A896"/>
-      <c r="B896"/>
-      <c r="C896"/>
-    </row>
-    <row r="897" ht="15.75" customHeight="1">
-      <c r="A897"/>
-      <c r="B897"/>
-      <c r="C897"/>
-    </row>
-    <row r="898" ht="15.75" customHeight="1">
-      <c r="A898"/>
-      <c r="B898"/>
-      <c r="C898"/>
-    </row>
-    <row r="899" ht="15.75" customHeight="1">
-      <c r="A899"/>
-      <c r="B899"/>
-      <c r="C899"/>
-    </row>
-    <row r="900" ht="15.75" customHeight="1">
-      <c r="A900"/>
-      <c r="B900"/>
-      <c r="C900"/>
-    </row>
-    <row r="901" ht="15.75" customHeight="1">
-      <c r="A901"/>
-      <c r="B901"/>
-      <c r="C901"/>
-    </row>
-    <row r="902" ht="15.75" customHeight="1">
-      <c r="A902"/>
-      <c r="B902"/>
-      <c r="C902"/>
-    </row>
-    <row r="903" ht="15.75" customHeight="1">
-      <c r="A903"/>
-      <c r="B903"/>
-      <c r="C903"/>
-    </row>
-    <row r="904" ht="15.75" customHeight="1">
-      <c r="A904"/>
-      <c r="B904"/>
-      <c r="C904"/>
-    </row>
-    <row r="905" ht="15.75" customHeight="1">
-      <c r="A905"/>
-      <c r="B905"/>
-      <c r="C905"/>
-    </row>
-    <row r="906" ht="15.75" customHeight="1">
-      <c r="A906"/>
-      <c r="B906"/>
-      <c r="C906"/>
-    </row>
-    <row r="907" ht="15.75" customHeight="1">
-      <c r="A907"/>
-      <c r="B907"/>
-      <c r="C907"/>
-    </row>
-    <row r="908" ht="15.75" customHeight="1">
-      <c r="A908"/>
-      <c r="B908"/>
-      <c r="C908"/>
-    </row>
-    <row r="909" ht="15.75" customHeight="1">
-      <c r="A909"/>
-      <c r="B909"/>
-      <c r="C909"/>
-    </row>
-    <row r="910" ht="15.75" customHeight="1">
-      <c r="A910"/>
-      <c r="B910"/>
-      <c r="C910"/>
-    </row>
-    <row r="911" ht="15.75" customHeight="1">
-      <c r="A911"/>
-      <c r="B911"/>
-      <c r="C911"/>
-    </row>
-    <row r="912" ht="15.75" customHeight="1">
-      <c r="A912"/>
-      <c r="B912"/>
-      <c r="C912"/>
-    </row>
-    <row r="913" ht="15.75" customHeight="1">
-      <c r="A913"/>
-      <c r="B913"/>
-      <c r="C913"/>
-    </row>
-    <row r="914" ht="15.75" customHeight="1">
-      <c r="A914"/>
-      <c r="B914"/>
-      <c r="C914"/>
-    </row>
-    <row r="915" ht="15.75" customHeight="1">
-      <c r="A915"/>
-      <c r="B915"/>
-      <c r="C915"/>
-    </row>
-    <row r="916" ht="15.75" customHeight="1">
-      <c r="A916"/>
-      <c r="B916"/>
-      <c r="C916"/>
-    </row>
-    <row r="917" ht="15.75" customHeight="1">
-      <c r="A917"/>
-      <c r="B917"/>
-      <c r="C917"/>
-    </row>
-    <row r="918" ht="15.75" customHeight="1">
-      <c r="A918"/>
-      <c r="B918"/>
-      <c r="C918"/>
-    </row>
-    <row r="919" ht="15.75" customHeight="1">
-      <c r="A919"/>
-      <c r="B919"/>
-      <c r="C919"/>
-    </row>
-    <row r="920" ht="15.75" customHeight="1">
-      <c r="A920"/>
-      <c r="B920"/>
-      <c r="C920"/>
-    </row>
-    <row r="921" ht="15.75" customHeight="1">
-      <c r="A921"/>
-      <c r="B921"/>
-      <c r="C921"/>
-    </row>
-    <row r="922" ht="15.75" customHeight="1">
-      <c r="A922"/>
-      <c r="B922"/>
-      <c r="C922"/>
-    </row>
-    <row r="923" ht="15.75" customHeight="1">
-      <c r="A923"/>
-      <c r="B923"/>
-      <c r="C923"/>
-    </row>
-    <row r="924" ht="15.75" customHeight="1">
-      <c r="A924"/>
-      <c r="B924"/>
-      <c r="C924"/>
-    </row>
-    <row r="925" ht="15.75" customHeight="1">
-      <c r="A925"/>
-      <c r="B925"/>
-      <c r="C925"/>
-    </row>
-    <row r="926" ht="15.75" customHeight="1">
-      <c r="A926"/>
-      <c r="B926"/>
-      <c r="C926"/>
-    </row>
-    <row r="927" ht="15.75" customHeight="1">
-      <c r="A927"/>
-      <c r="B927"/>
-      <c r="C927"/>
-    </row>
-    <row r="928" ht="15.75" customHeight="1">
-      <c r="A928"/>
-      <c r="B928"/>
-      <c r="C928"/>
-    </row>
-    <row r="929" ht="15.75" customHeight="1">
-      <c r="A929"/>
-      <c r="B929"/>
-      <c r="C929"/>
-    </row>
-    <row r="930" ht="15.75" customHeight="1">
-      <c r="A930"/>
-      <c r="B930"/>
-      <c r="C930"/>
-    </row>
-    <row r="931" ht="15.75" customHeight="1">
-      <c r="A931"/>
-      <c r="B931"/>
-      <c r="C931"/>
-    </row>
-    <row r="932" ht="15.75" customHeight="1">
-      <c r="A932"/>
-      <c r="B932"/>
-      <c r="C932"/>
-    </row>
-    <row r="933" ht="15.75" customHeight="1">
-      <c r="A933"/>
-      <c r="B933"/>
-      <c r="C933"/>
-    </row>
-    <row r="934" ht="15.75" customHeight="1">
-      <c r="A934"/>
-      <c r="B934"/>
-      <c r="C934"/>
-    </row>
-    <row r="935" ht="15.75" customHeight="1">
-      <c r="A935"/>
-      <c r="B935"/>
-      <c r="C935"/>
-    </row>
-    <row r="936" ht="15.75" customHeight="1">
-      <c r="A936"/>
-      <c r="B936"/>
-      <c r="C936"/>
-    </row>
-    <row r="937" ht="15.75" customHeight="1">
-      <c r="A937"/>
-      <c r="B937"/>
-      <c r="C937"/>
-    </row>
-    <row r="938" ht="15.75" customHeight="1">
-      <c r="A938"/>
-      <c r="B938"/>
-      <c r="C938"/>
-    </row>
-    <row r="939" ht="15.75" customHeight="1">
-      <c r="A939"/>
-      <c r="B939"/>
-      <c r="C939"/>
-    </row>
-    <row r="940" ht="15.75" customHeight="1">
-      <c r="A940"/>
-      <c r="B940"/>
-      <c r="C940"/>
-    </row>
-    <row r="941" ht="15.75" customHeight="1">
-      <c r="A941"/>
-      <c r="B941"/>
-      <c r="C941"/>
-    </row>
-    <row r="942" ht="15.75" customHeight="1">
-      <c r="A942"/>
-      <c r="B942"/>
-      <c r="C942"/>
-    </row>
-    <row r="943" ht="15.75" customHeight="1">
-      <c r="A943"/>
-      <c r="B943"/>
-      <c r="C943"/>
-    </row>
-    <row r="944" ht="15.75" customHeight="1">
-      <c r="A944"/>
-      <c r="B944"/>
-      <c r="C944"/>
-    </row>
-    <row r="945" ht="15.75" customHeight="1">
-      <c r="A945"/>
-      <c r="B945"/>
-      <c r="C945"/>
-    </row>
-    <row r="946" ht="15.75" customHeight="1">
-      <c r="A946"/>
-      <c r="B946"/>
-      <c r="C946"/>
-    </row>
-    <row r="947" ht="15.75" customHeight="1">
-      <c r="A947"/>
-      <c r="B947"/>
-      <c r="C947"/>
-    </row>
-    <row r="948" ht="15.75" customHeight="1">
-      <c r="A948"/>
-      <c r="B948"/>
-      <c r="C948"/>
-    </row>
-    <row r="949" ht="15.75" customHeight="1">
-      <c r="A949"/>
-      <c r="B949"/>
-      <c r="C949"/>
-    </row>
-    <row r="950" ht="15.75" customHeight="1">
-      <c r="A950"/>
-      <c r="B950"/>
-      <c r="C950"/>
-    </row>
-    <row r="951" ht="15.75" customHeight="1">
-      <c r="A951"/>
-      <c r="B951"/>
-      <c r="C951"/>
-    </row>
-    <row r="952" ht="15.75" customHeight="1">
-      <c r="A952"/>
-      <c r="B952"/>
-      <c r="C952"/>
-    </row>
-    <row r="953" ht="15.75" customHeight="1">
-      <c r="A953"/>
-      <c r="B953"/>
-      <c r="C953"/>
-    </row>
-    <row r="954" ht="15.75" customHeight="1">
-      <c r="A954"/>
-      <c r="B954"/>
-      <c r="C954"/>
-    </row>
-    <row r="955" ht="15.75" customHeight="1">
-      <c r="A955"/>
-      <c r="B955"/>
-      <c r="C955"/>
-    </row>
-    <row r="956" ht="15.75" customHeight="1">
-      <c r="A956"/>
-      <c r="B956"/>
-      <c r="C956"/>
-    </row>
-    <row r="957" ht="15.75" customHeight="1">
-      <c r="A957"/>
-      <c r="B957"/>
-      <c r="C957"/>
-    </row>
-    <row r="958" ht="15.75" customHeight="1">
-      <c r="A958"/>
-      <c r="B958"/>
-      <c r="C958"/>
-    </row>
-    <row r="959" ht="15.75" customHeight="1">
-      <c r="A959"/>
-      <c r="B959"/>
-      <c r="C959"/>
-    </row>
-    <row r="960" ht="15.75" customHeight="1">
-      <c r="A960"/>
-      <c r="B960"/>
-      <c r="C960"/>
-    </row>
-    <row r="961" ht="15.75" customHeight="1">
-      <c r="A961"/>
-      <c r="B961"/>
-      <c r="C961"/>
-    </row>
-    <row r="962" ht="15.75" customHeight="1">
-      <c r="A962"/>
-      <c r="B962"/>
-      <c r="C962"/>
-    </row>
-    <row r="963" ht="15.75" customHeight="1">
-      <c r="A963"/>
-      <c r="B963"/>
-      <c r="C963"/>
-    </row>
-    <row r="964" ht="15.75" customHeight="1">
-      <c r="A964"/>
-      <c r="B964"/>
-      <c r="C964"/>
-    </row>
-    <row r="965" ht="15.75" customHeight="1">
-      <c r="A965"/>
-      <c r="B965"/>
-      <c r="C965"/>
-    </row>
-    <row r="966" ht="15.75" customHeight="1">
-      <c r="A966"/>
-      <c r="B966"/>
-      <c r="C966"/>
-    </row>
-    <row r="967" ht="15.75" customHeight="1">
-      <c r="A967"/>
-      <c r="B967"/>
-      <c r="C967"/>
-    </row>
-    <row r="968" ht="15.75" customHeight="1">
-      <c r="A968"/>
-      <c r="B968"/>
-      <c r="C968"/>
-    </row>
-    <row r="969" ht="15.75" customHeight="1">
-      <c r="A969"/>
-      <c r="B969"/>
-      <c r="C969"/>
-    </row>
-    <row r="970" ht="15.75" customHeight="1">
-      <c r="A970"/>
-      <c r="B970"/>
-      <c r="C970"/>
-    </row>
-    <row r="971" ht="15.75" customHeight="1">
-      <c r="A971"/>
-      <c r="B971"/>
-      <c r="C971"/>
-    </row>
-    <row r="972" ht="15.75" customHeight="1">
-      <c r="A972"/>
-      <c r="B972"/>
-      <c r="C972"/>
-    </row>
-    <row r="973" ht="15.75" customHeight="1">
-      <c r="A973"/>
-      <c r="B973"/>
-      <c r="C973"/>
-    </row>
-    <row r="974" ht="15.75" customHeight="1">
-      <c r="A974"/>
-      <c r="B974"/>
-      <c r="C974"/>
-    </row>
-    <row r="975" ht="15.75" customHeight="1">
-      <c r="A975"/>
-      <c r="B975"/>
-      <c r="C975"/>
-    </row>
-    <row r="976" ht="15.75" customHeight="1">
-      <c r="A976"/>
-      <c r="B976"/>
-      <c r="C976"/>
-    </row>
-    <row r="977" ht="15.75" customHeight="1">
-      <c r="A977"/>
-      <c r="B977"/>
-      <c r="C977"/>
-    </row>
-    <row r="978" ht="15.75" customHeight="1">
-      <c r="A978"/>
-      <c r="B978"/>
-      <c r="C978"/>
-    </row>
-    <row r="979" ht="15.75" customHeight="1">
-      <c r="A979"/>
-      <c r="B979"/>
-      <c r="C979"/>
-    </row>
-    <row r="980" ht="15.75" customHeight="1">
-      <c r="A980"/>
-      <c r="B980"/>
-      <c r="C980"/>
-    </row>
-    <row r="981" ht="15.75" customHeight="1">
-      <c r="A981"/>
-      <c r="B981"/>
-      <c r="C981"/>
-    </row>
-    <row r="982" ht="15.75" customHeight="1">
-      <c r="A982"/>
-      <c r="B982"/>
-      <c r="C982"/>
-    </row>
-    <row r="983" ht="15.75" customHeight="1">
-      <c r="A983"/>
-      <c r="B983"/>
-      <c r="C983"/>
-    </row>
-    <row r="984" ht="15.75" customHeight="1">
-      <c r="A984"/>
-      <c r="B984"/>
-      <c r="C984"/>
-    </row>
-    <row r="985" ht="15.75" customHeight="1">
-      <c r="A985"/>
-      <c r="B985"/>
-      <c r="C985"/>
-    </row>
-    <row r="986" ht="15.75" customHeight="1">
-      <c r="A986"/>
-      <c r="B986"/>
-      <c r="C986"/>
-    </row>
-    <row r="987" ht="15.75" customHeight="1">
-      <c r="A987"/>
-      <c r="B987"/>
-      <c r="C987"/>
-    </row>
-    <row r="988" ht="15.75" customHeight="1">
-      <c r="A988"/>
-      <c r="B988"/>
-      <c r="C988"/>
-    </row>
-    <row r="989" ht="15.75" customHeight="1">
-      <c r="A989"/>
-      <c r="B989"/>
-      <c r="C989"/>
-    </row>
-    <row r="990" ht="15.75" customHeight="1">
-      <c r="A990"/>
-      <c r="B990"/>
-      <c r="C990"/>
-    </row>
-    <row r="991" ht="15.75" customHeight="1">
-      <c r="A991"/>
-      <c r="B991"/>
-      <c r="C991"/>
-    </row>
-    <row r="992" ht="15.75" customHeight="1">
-      <c r="A992"/>
-      <c r="B992"/>
-      <c r="C992"/>
-    </row>
-    <row r="993" ht="15.75" customHeight="1">
-      <c r="A993"/>
-      <c r="B993"/>
-      <c r="C993"/>
-    </row>
-    <row r="994" ht="15.75" customHeight="1">
-      <c r="A994"/>
-      <c r="B994"/>
-      <c r="C994"/>
-    </row>
-    <row r="995" ht="15.75" customHeight="1">
-      <c r="A995"/>
-      <c r="B995"/>
-      <c r="C995"/>
-    </row>
-    <row r="996" ht="15.75" customHeight="1">
-      <c r="A996"/>
-      <c r="B996"/>
-      <c r="C996"/>
-    </row>
-    <row r="997" ht="15.75" customHeight="1">
-      <c r="A997"/>
-      <c r="B997"/>
-      <c r="C997"/>
-    </row>
-    <row r="998" ht="15.75" customHeight="1">
-      <c r="A998"/>
-      <c r="B998"/>
-      <c r="C998"/>
-    </row>
-    <row r="999" ht="15.75" customHeight="1">
-      <c r="A999"/>
-      <c r="B999"/>
-      <c r="C999"/>
-    </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000"/>
-      <c r="B1000"/>
-      <c r="C1000"/>
-    </row>
+      <c r="A115" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B115" s="70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="117" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="118" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="119" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="120" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="121" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="122" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="123" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="124" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="125" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="126" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
@@ -30209,9 +26557,10 @@
     <hyperlink ref="B108" r:id="rId25" xr:uid="{6F667C07-E809-4FC2-A38E-07D0078533A2}"/>
     <hyperlink ref="C108" r:id="rId26" xr:uid="{4954E5AB-145F-42F2-9F39-50A066F877AB}"/>
     <hyperlink ref="B112" r:id="rId27" location="inbox;commoninbox@mmh-demo.com;Mmh@2017" xr:uid="{890D1DE2-9D14-49FF-A9FE-F78E18DF3369}"/>
+    <hyperlink ref="B115" r:id="rId28" xr:uid="{8D8D6357-CC5A-4EA6-B1A0-6A61B4057C17}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId28"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId29"/>
 </worksheet>
 </file>
 
@@ -30220,13 +26569,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C1000"/>
+  <dimension ref="A1:F1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="48.7109375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="141.42578125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="116.42578125" collapsed="true"/>
-    <col min="4" max="6" customWidth="true" width="14.42578125" collapsed="true"/>
+    <col min="1" max="1" width="48.7109375" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="141.42578125" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="116.42578125" customWidth="1" collapsed="1"/>
+    <col min="4" max="6" width="14.42578125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30644,7 +26993,7 @@
         <v>103</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>544</v>
+        <v>1231</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>545</v>
@@ -30962,7 +27311,7 @@
       <c r="A82" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="35" t="s">
         <v>450</v>
       </c>
       <c r="C82" s="14" t="s">
@@ -33378,10 +29727,10 @@
   <dimension ref="A1:W1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="62.28515625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="97.7109375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="132.85546875" collapsed="true"/>
-    <col min="4" max="6" customWidth="true" width="14.42578125" collapsed="true"/>
+    <col min="1" max="1" width="62.28515625" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="97.7109375" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="132.85546875" customWidth="1" collapsed="1"/>
+    <col min="4" max="6" width="14.42578125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">

--- a/config/testdata/testdata.xlsx
+++ b/config/testdata/testdata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WEB_AND_MR_AUTOMATION_SCRIPT\config\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mobile_Apps\config\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4811ADD5-FE42-43BE-AC25-D0C0840286A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E483A6-2BCF-44E2-AACE-0FD72A4B8A47}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Happy_Path_Patient_Web_and_MR" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="1234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="1236">
   <si>
     <t>KEY</t>
   </si>
@@ -1910,9 +1910,6 @@
   </si>
   <si>
     <t>FRIENDS_AND_FAMILY_BOOK_VISIT_APPOINTMENT</t>
-  </si>
-  <si>
-    <t>Automation1_Loc1;Automation1_Loc1;Myself (AUTO AUTOCHRISC1);A new issue;Phone;9:00 AM;GP2;022;533420;AFTER_THREE_DAYS;Automation_Practice1_Loc1;Automation1_Loc2</t>
   </si>
   <si>
     <t>VM03Location;VM03Location;Family Member;MMHtest;Child;Visit;9:00 AM;Dr Sam Eaves;AFTER_FIVE_DAYS</t>
@@ -3717,9 +3714,6 @@
     <t>VM03Location;vm03practicepat1</t>
   </si>
   <si>
-    <t>Beating the Blues Program;Chrisc;AutoPat1;Male;Chriscautopat_RANDOM;Chriscautopat_RANDOM;</t>
-  </si>
-  <si>
     <t>NEW_PROVIDER_REGISTER_NEW_CLIENT</t>
   </si>
   <si>
@@ -3754,6 +3748,18 @@
   </si>
   <si>
     <t>Automation1_Loc1;Automation1_Loc1;Internal Communication;Patient;Auto;Received Msg Testing_RANDOM;Body : Received Message Testing_RANDOM;MMHtest.jpg;Compose Message_RANDOM;Body : Reply Message Testing_RANDOM;Compose Message Testing_RANDOM;TestAutomation</t>
+  </si>
+  <si>
+    <t>HOTFIX</t>
+  </si>
+  <si>
+    <t>https://v2webhotfix.mmh-demo.com/home</t>
+  </si>
+  <si>
+    <t>Automation1_Loc1;Automation1_Loc1;Myself (AUTO AUTOCHRISC1);Ravi;Child;A new issue;Phone;9:00 AM;GP2;022;533420;AFTER_THREE_DAYS;Automation_Practice1_Loc1;Automation1_Loc2</t>
+  </si>
+  <si>
+    <t>Beating the Blues Program;Chrisc;AutoPat1;Male;Chriscautopat@mmh-demo.com;Chriscautopat@mmh-demo.com;</t>
   </si>
 </sst>
 </file>
@@ -3955,7 +3961,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -4150,12 +4156,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4339,6 +4356,9 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4578,7 +4598,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -4605,13 +4625,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C2" s="70" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="69" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -4641,7 +4661,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="70" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>7</v>
@@ -4701,14 +4721,14 @@
     </row>
     <row r="5" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A5" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>1148</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>1149</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="7" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -4792,7 +4812,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>12</v>
@@ -4855,13 +4875,13 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -4946,13 +4966,13 @@
         <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>1152</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>1153</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -5095,13 +5115,13 @@
         <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>1154</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>1155</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -5161,13 +5181,13 @@
         <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -5244,13 +5264,13 @@
         <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>1157</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>1158</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -5310,13 +5330,13 @@
         <v>41</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -5396,7 +5416,7 @@
         <v>12</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>12</v>
@@ -5854,7 +5874,7 @@
         <v>66</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>66</v>
@@ -6066,13 +6086,13 @@
         <v>79</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>81</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -6193,7 +6213,7 @@
         <v>89</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>89</v>
@@ -6317,7 +6337,7 @@
         <v>89</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>89</v>
@@ -6408,7 +6428,7 @@
         <v>89</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>89</v>
@@ -6833,7 +6853,7 @@
         <v>119</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>119</v>
@@ -6866,7 +6886,7 @@
         <v>121</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>121</v>
@@ -6899,7 +6919,7 @@
         <v>123</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>123</v>
@@ -6998,7 +7018,7 @@
         <v>129</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>129</v>
@@ -7261,7 +7281,7 @@
         <v>146</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>146</v>
@@ -7291,7 +7311,7 @@
         <v>148</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>148</v>
@@ -7318,7 +7338,7 @@
         <v>150</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>150</v>
@@ -7598,7 +7618,7 @@
         <v>166</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>166</v>
@@ -7628,7 +7648,7 @@
         <v>168</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>168</v>
@@ -7658,7 +7678,7 @@
         <v>170</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>170</v>
@@ -7926,7 +7946,7 @@
         <v>183</v>
       </c>
       <c r="C111" s="33" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="D111" s="33" t="s">
         <v>183</v>
@@ -8055,7 +8075,7 @@
         <v>191</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>191</v>
@@ -8088,7 +8108,7 @@
         <v>183</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>183</v>
@@ -8121,7 +8141,7 @@
         <v>194</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="D117" s="19" t="s">
         <v>194</v>
@@ -8179,7 +8199,7 @@
         <v>196</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>196</v>
@@ -8212,7 +8232,7 @@
         <v>198</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>198</v>
@@ -8245,7 +8265,7 @@
         <v>200</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>200</v>
@@ -8501,7 +8521,7 @@
         <v>212</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>212</v>
@@ -8534,7 +8554,7 @@
         <v>214</v>
       </c>
       <c r="C130" s="20" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D130" s="15" t="s">
         <v>214</v>
@@ -8625,7 +8645,7 @@
         <v>219</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>219</v>
@@ -8658,7 +8678,7 @@
         <v>221</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>221</v>
@@ -8779,10 +8799,10 @@
         <v>228</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>229</v>
@@ -8815,7 +8835,7 @@
         <v>231</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>231</v>
@@ -8848,7 +8868,7 @@
         <v>233</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>233</v>
@@ -9355,7 +9375,7 @@
         <v>260</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>260</v>
@@ -9388,7 +9408,7 @@
         <v>262</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>262</v>
@@ -9421,7 +9441,7 @@
         <v>264</v>
       </c>
       <c r="C158" s="24" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D158" s="23" t="s">
         <v>264</v>
@@ -9454,7 +9474,7 @@
         <v>266</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>266</v>
@@ -9553,7 +9573,7 @@
         <v>273</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>273</v>
@@ -9696,14 +9716,14 @@
     </row>
     <row r="167" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A167" s="12" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B167" s="12" t="s">
         <v>1188</v>
-      </c>
-      <c r="B167" s="12" t="s">
-        <v>1189</v>
       </c>
       <c r="C167" s="12"/>
       <c r="D167" s="33" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
@@ -9727,14 +9747,14 @@
     </row>
     <row r="168" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A168" s="12" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C168" s="12"/>
       <c r="D168" s="33" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
@@ -9758,14 +9778,14 @@
     </row>
     <row r="169" spans="1:23" ht="13.5" customHeight="1">
       <c r="A169" s="25" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B169" s="25" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C169" s="25"/>
       <c r="D169" s="25" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
@@ -17087,7 +17107,7 @@
         <v>347</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C69" s="27"/>
       <c r="D69" s="27"/>
@@ -17195,7 +17215,7 @@
         <v>351</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C73" s="27"/>
       <c r="D73" s="27"/>
@@ -17223,7 +17243,7 @@
         <v>352</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C74" s="27"/>
       <c r="D74" s="27"/>
@@ -24944,7 +24964,7 @@
     <row r="30" spans="1:2" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="31" spans="1:2" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="55" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15.75" customHeight="1" thickBot="1"/>
@@ -24953,16 +24973,16 @@
         <v>528</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A35" s="33" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>9</v>
@@ -24973,127 +24993,127 @@
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A36" s="33" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C36" s="57" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A37" s="33" t="s">
+        <v>687</v>
+      </c>
+      <c r="B37" s="33" t="s">
         <v>688</v>
       </c>
-      <c r="B37" s="33" t="s">
-        <v>689</v>
-      </c>
       <c r="C37" s="33" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A38" s="33" t="s">
+        <v>689</v>
+      </c>
+      <c r="B38" s="33" t="s">
         <v>690</v>
       </c>
-      <c r="B38" s="33" t="s">
+      <c r="C38" s="33" t="s">
         <v>691</v>
-      </c>
-      <c r="C38" s="33" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A40" s="33" t="s">
+        <v>692</v>
+      </c>
+      <c r="B40" s="33" t="s">
         <v>693</v>
       </c>
-      <c r="B40" s="33" t="s">
+      <c r="C40" s="33" t="s">
         <v>694</v>
-      </c>
-      <c r="C40" s="33" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A41" s="33" t="s">
+        <v>695</v>
+      </c>
+      <c r="B41" s="33" t="s">
         <v>696</v>
       </c>
-      <c r="B41" s="33" t="s">
-        <v>697</v>
-      </c>
       <c r="C41" s="33" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A42" s="33" t="s">
+        <v>697</v>
+      </c>
+      <c r="B42" s="33" t="s">
         <v>698</v>
       </c>
-      <c r="B42" s="33" t="s">
+      <c r="C42" s="33" t="s">
         <v>699</v>
-      </c>
-      <c r="C42" s="33" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="44" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A44" s="33" t="s">
+        <v>700</v>
+      </c>
+      <c r="B44" s="33" t="s">
         <v>701</v>
       </c>
-      <c r="B44" s="33" t="s">
-        <v>702</v>
-      </c>
       <c r="C44" s="33" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A45" s="33" t="s">
+        <v>702</v>
+      </c>
+      <c r="B45" s="33" t="s">
         <v>703</v>
       </c>
-      <c r="B45" s="33" t="s">
-        <v>704</v>
-      </c>
       <c r="C45" s="33" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="47" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A47" s="33" t="s">
+        <v>704</v>
+      </c>
+      <c r="B47" s="33" t="s">
         <v>705</v>
       </c>
-      <c r="B47" s="33" t="s">
+      <c r="C47" s="33" t="s">
         <v>706</v>
-      </c>
-      <c r="C47" s="33" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="49" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A49" s="21" t="s">
+        <v>707</v>
+      </c>
+      <c r="B49" s="33" t="s">
         <v>708</v>
       </c>
-      <c r="B49" s="33" t="s">
+      <c r="C49" s="33" t="s">
         <v>709</v>
-      </c>
-      <c r="C49" s="33" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A50" s="21" t="s">
+        <v>710</v>
+      </c>
+      <c r="B50" s="33" t="s">
         <v>711</v>
       </c>
-      <c r="B50" s="33" t="s">
-        <v>712</v>
-      </c>
       <c r="C50" s="33" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15.75" customHeight="1" thickBot="1"/>
@@ -25435,12 +25455,12 @@
     <row r="89" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="90" spans="1:3" ht="15.75" customHeight="1">
       <c r="B90" s="66" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15.75" customHeight="1">
       <c r="A91" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B91" t="s">
         <v>4</v>
@@ -25452,180 +25472,180 @@
     <row r="92" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="93" spans="1:3" ht="15.75" customHeight="1">
       <c r="A93" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B93" s="68" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C93" s="68" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15.75" customHeight="1">
       <c r="A94" s="67" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B94" s="68" t="s">
         <v>1195</v>
       </c>
-      <c r="B94" s="68" t="s">
-        <v>1196</v>
-      </c>
       <c r="C94" s="68" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="96" spans="1:3" ht="15.75" customHeight="1">
       <c r="A96" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B96" s="68" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C96" s="68" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.75" customHeight="1">
       <c r="A97" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B97" s="68" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C97" s="68" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="99" spans="1:3" ht="15.75" customHeight="1">
       <c r="A99" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B99" s="68" t="s">
         <v>1203</v>
       </c>
-      <c r="B99" s="68" t="s">
-        <v>1204</v>
-      </c>
       <c r="C99" s="68" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.75" customHeight="1">
       <c r="A100" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B100" s="68" t="s">
         <v>1205</v>
       </c>
-      <c r="B100" s="68" t="s">
-        <v>1206</v>
-      </c>
       <c r="C100" s="68" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.75" customHeight="1">
       <c r="A101" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B101" s="68" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C101" s="68" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="103" spans="1:3" ht="15.75" customHeight="1">
       <c r="A103" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B103" s="68" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="C103" s="68" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="105" spans="1:3" ht="15.75" customHeight="1">
       <c r="A105" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B105" t="s">
         <v>1212</v>
       </c>
-      <c r="B105" t="s">
-        <v>1213</v>
-      </c>
       <c r="C105" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="15.75" customHeight="1">
       <c r="A106" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C106" t="s">
         <v>1214</v>
-      </c>
-      <c r="B106" t="s">
-        <v>1226</v>
-      </c>
-      <c r="C106" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15.75" customHeight="1">
       <c r="A107" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B107" s="68" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="C107" s="68" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="15.75" customHeight="1">
       <c r="A108" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B108" s="68" t="s">
         <v>1217</v>
       </c>
-      <c r="B108" s="68" t="s">
-        <v>1218</v>
-      </c>
       <c r="C108" s="68" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="110" spans="1:3" ht="15.75" customHeight="1">
       <c r="A110" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B110" t="s">
         <v>1219</v>
-      </c>
-      <c r="B110" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15.75" customHeight="1">
       <c r="A111" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B111" t="s">
-        <v>1221</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15.75" customHeight="1">
       <c r="A112" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B112" s="68" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="114" spans="1:3" ht="15.75" customHeight="1">
       <c r="A114" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B114" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C114" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75" customHeight="1">
       <c r="A115" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B115" s="68" t="s">
         <v>9</v>
@@ -26563,10 +26583,11 @@
     <col min="1" max="1" width="48.7109375" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="141.42578125" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="116.42578125" customWidth="1" collapsed="1"/>
-    <col min="4" max="6" width="14.42578125" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="114.42578125" customWidth="1" collapsed="1"/>
+    <col min="5" max="6" width="14.42578125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
@@ -26576,19 +26597,25 @@
       <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="71" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" thickBot="1">
       <c r="A2" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="C2" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" thickBot="1">
       <c r="A3" s="12" t="s">
         <v>6</v>
       </c>
@@ -26598,8 +26625,11 @@
       <c r="C3" s="12" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" thickBot="1">
       <c r="A4" s="12" t="s">
         <v>8</v>
       </c>
@@ -26609,8 +26639,11 @@
       <c r="C4" s="12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1">
+      <c r="D4" s="33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" thickBot="1">
       <c r="A5" s="12" t="s">
         <v>454</v>
       </c>
@@ -26620,20 +26653,27 @@
       <c r="C5" s="12" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" thickBot="1">
       <c r="A6" s="41"/>
       <c r="B6" s="41" t="s">
         <v>481</v>
       </c>
       <c r="C6" s="41"/>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" s="41" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" thickBot="1">
       <c r="A7" s="7"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="33"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" thickBot="1">
       <c r="A8" s="42" t="s">
         <v>482</v>
       </c>
@@ -26643,8 +26683,11 @@
       <c r="C8" s="12" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="33" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" thickBot="1">
       <c r="A9" s="42" t="s">
         <v>485</v>
       </c>
@@ -26654,8 +26697,11 @@
       <c r="C9" s="12" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="45">
+      <c r="D9" s="33" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="45.75" thickBot="1">
       <c r="A10" s="12" t="s">
         <v>488</v>
       </c>
@@ -26665,8 +26711,11 @@
       <c r="C10" s="12" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="30">
+      <c r="D10" s="33" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="45.75" thickBot="1">
       <c r="A11" s="12" t="s">
         <v>491</v>
       </c>
@@ -26676,8 +26725,11 @@
       <c r="C11" s="12" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="45">
+      <c r="D11" s="33" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="45.75" thickBot="1">
       <c r="A12" s="12" t="s">
         <v>494</v>
       </c>
@@ -26687,8 +26739,11 @@
       <c r="C12" s="12" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="45">
+      <c r="D12" s="33" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="45.75" thickBot="1">
       <c r="A13" s="12" t="s">
         <v>497</v>
       </c>
@@ -26698,8 +26753,11 @@
       <c r="C13" s="12" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="45">
+      <c r="D13" s="33" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="45.75" thickBot="1">
       <c r="A14" s="12" t="s">
         <v>500</v>
       </c>
@@ -26709,8 +26767,11 @@
       <c r="C14" s="12" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" s="33" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" thickBot="1">
       <c r="A15" s="12" t="s">
         <v>503</v>
       </c>
@@ -26720,8 +26781,11 @@
       <c r="C15" s="12" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="30">
+      <c r="D15" s="33" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="30.75" thickBot="1">
       <c r="A16" s="12" t="s">
         <v>505</v>
       </c>
@@ -26731,8 +26795,11 @@
       <c r="C16" s="12" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" s="33" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" thickBot="1">
       <c r="A17" s="12" t="s">
         <v>507</v>
       </c>
@@ -26742,8 +26809,11 @@
       <c r="C17" s="12" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" s="33" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" thickBot="1">
       <c r="A18" s="12" t="s">
         <v>510</v>
       </c>
@@ -26753,8 +26823,11 @@
       <c r="C18" s="12" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" s="33" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" thickBot="1">
       <c r="A19" s="12" t="s">
         <v>512</v>
       </c>
@@ -26764,8 +26837,11 @@
       <c r="C19" s="12" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="30">
+      <c r="D19" s="43" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="30.75" thickBot="1">
       <c r="A20" s="12" t="s">
         <v>515</v>
       </c>
@@ -26775,8 +26851,11 @@
       <c r="C20" s="12" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D20" s="33" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="12" t="s">
         <v>518</v>
       </c>
@@ -26786,8 +26865,11 @@
       <c r="C21" s="12" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D21" s="33" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="12" t="s">
         <v>521</v>
       </c>
@@ -26797,50 +26879,63 @@
       <c r="C22" s="12" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D22" s="33" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D23" s="33"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D24" s="33"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D25" s="33"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D26" s="33"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D27" s="33"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D28" s="33"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D29" s="33"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A30" s="41"/>
       <c r="B30" s="41" t="s">
         <v>524</v>
       </c>
       <c r="C30" s="41"/>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D30" s="41" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A31" s="12" t="s">
         <v>525</v>
       </c>
@@ -26850,8 +26945,11 @@
       <c r="C31" s="7" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D31" s="33" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A32" s="12" t="s">
         <v>528</v>
       </c>
@@ -26861,8 +26959,11 @@
       <c r="C32" s="44" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D32" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A33" s="12" t="s">
         <v>62</v>
       </c>
@@ -26872,8 +26973,11 @@
       <c r="C33" s="1" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D33" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A34" s="12" t="s">
         <v>65</v>
       </c>
@@ -26883,8 +26987,11 @@
       <c r="C34" s="1" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D34" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A35" s="12" t="s">
         <v>534</v>
       </c>
@@ -26894,8 +27001,11 @@
       <c r="C35" s="12" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D35" s="33" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A36" s="12" t="s">
         <v>106</v>
       </c>
@@ -26905,13 +27015,17 @@
       <c r="C36" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D36" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
-    </row>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D37" s="33"/>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A38" s="1" t="s">
         <v>88</v>
       </c>
@@ -26921,8 +27035,11 @@
       <c r="C38" s="1" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D38" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A39" s="45" t="s">
         <v>90</v>
       </c>
@@ -26932,13 +27049,17 @@
       <c r="C39" s="1" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D39" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
-    </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D40" s="33"/>
+    </row>
+    <row r="41" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A41" s="21" t="s">
         <v>70</v>
       </c>
@@ -26948,8 +27069,11 @@
       <c r="C41" s="1" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D41" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A42" s="1" t="s">
         <v>73</v>
       </c>
@@ -26959,13 +27083,17 @@
       <c r="C42" s="1" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D42" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A43" s="12"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
-    </row>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D43" s="33"/>
+    </row>
+    <row r="44" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A44" s="12" t="s">
         <v>100</v>
       </c>
@@ -26975,24 +27103,31 @@
       <c r="C44" s="1" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D44" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A45" s="12" t="s">
         <v>103</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D45" s="33" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A46" s="12"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
-    </row>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D46" s="1"/>
+    </row>
+    <row r="47" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A47" s="12" t="s">
         <v>79</v>
       </c>
@@ -27002,8 +27137,11 @@
       <c r="C47" s="1" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D47" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A48" s="1" t="s">
         <v>82</v>
       </c>
@@ -27013,20 +27151,27 @@
       <c r="C48" s="1" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D48" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A49" s="46"/>
       <c r="B49" s="46" t="s">
         <v>550</v>
       </c>
       <c r="C49" s="46"/>
-    </row>
-    <row r="50" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D49" s="46" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A50" s="12"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
-    </row>
-    <row r="51" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D50" s="33"/>
+    </row>
+    <row r="51" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A51" s="1" t="s">
         <v>551</v>
       </c>
@@ -27036,24 +27181,31 @@
       <c r="C51" s="1" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D51" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A52" s="1" t="s">
         <v>263</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="C52" s="47" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D52" s="23" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
-    </row>
-    <row r="54" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D53" s="1"/>
+    </row>
+    <row r="54" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A54" s="1" t="s">
         <v>267</v>
       </c>
@@ -27061,10 +27213,13 @@
         <v>268</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="15.75" customHeight="1">
+        <v>1230</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A55" s="1" t="s">
         <v>554</v>
       </c>
@@ -27074,8 +27229,11 @@
       <c r="C55" s="1" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D55" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A56" s="1" t="s">
         <v>555</v>
       </c>
@@ -27085,8 +27243,11 @@
       <c r="C56" s="1" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D56" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A57" s="1" t="s">
         <v>556</v>
       </c>
@@ -27096,8 +27257,11 @@
       <c r="C57" s="1" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D57" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A58" s="40" t="s">
         <v>261</v>
       </c>
@@ -27107,8 +27271,11 @@
       <c r="C58" s="1" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D58" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A59" s="1" t="s">
         <v>248</v>
       </c>
@@ -27116,8 +27283,11 @@
         <v>249</v>
       </c>
       <c r="C59" s="1"/>
-    </row>
-    <row r="60" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D59" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A60" s="1" t="s">
         <v>67</v>
       </c>
@@ -27125,15 +27295,21 @@
         <v>558</v>
       </c>
       <c r="C60" s="12"/>
-    </row>
-    <row r="61" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D60" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A61" s="46"/>
       <c r="B61" s="46" t="s">
         <v>559</v>
       </c>
       <c r="C61" s="46"/>
-    </row>
-    <row r="62" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D61" s="46" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A62" s="1" t="s">
         <v>62</v>
       </c>
@@ -27141,8 +27317,11 @@
         <v>560</v>
       </c>
       <c r="C62" s="12"/>
-    </row>
-    <row r="63" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D62" s="1" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A63" s="1" t="s">
         <v>65</v>
       </c>
@@ -27150,8 +27329,11 @@
         <v>561</v>
       </c>
       <c r="C63" s="12"/>
-    </row>
-    <row r="64" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D63" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A64" s="12" t="s">
         <v>19</v>
       </c>
@@ -27161,8 +27343,11 @@
       <c r="C64" s="12" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D64" s="33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A65" s="12" t="s">
         <v>108</v>
       </c>
@@ -27172,8 +27357,11 @@
       <c r="C65" s="1" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D65" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A66" s="12" t="s">
         <v>110</v>
       </c>
@@ -27183,40 +27371,51 @@
       <c r="C66" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D66" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A67" s="12"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
-    </row>
-    <row r="68" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D67" s="33"/>
+    </row>
+    <row r="68" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A68" s="12"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
-    </row>
-    <row r="69" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D68" s="33"/>
+    </row>
+    <row r="69" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
-    </row>
-    <row r="70" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D69" s="33"/>
+    </row>
+    <row r="70" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A70" s="12"/>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
-    </row>
-    <row r="71" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D70" s="33"/>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
-    </row>
-    <row r="72" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D71" s="33"/>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A72" s="46"/>
       <c r="B72" s="46" t="s">
         <v>562</v>
       </c>
       <c r="C72" s="46"/>
-    </row>
-    <row r="73" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D72" s="46" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A73" s="12" t="s">
         <v>563</v>
       </c>
@@ -27226,8 +27425,11 @@
       <c r="C73" s="12" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D73" s="33" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A74" s="12" t="s">
         <v>565</v>
       </c>
@@ -27237,8 +27439,11 @@
       <c r="C74" s="12" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D74" s="33" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A75" s="12"/>
       <c r="B75" s="12" t="s">
         <v>567</v>
@@ -27246,8 +27451,11 @@
       <c r="C75" s="12" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D75" s="33" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A76" s="12" t="s">
         <v>568</v>
       </c>
@@ -27257,13 +27465,17 @@
       <c r="C76" s="1" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D76" s="1" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="12"/>
-    </row>
-    <row r="78" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D77" s="1"/>
+    </row>
+    <row r="78" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A78" s="12" t="s">
         <v>571</v>
       </c>
@@ -27271,20 +27483,27 @@
         <v>567</v>
       </c>
       <c r="C78" s="12"/>
-    </row>
-    <row r="79" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D78" s="33" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A79" s="46"/>
       <c r="B79" s="46" t="s">
         <v>572</v>
       </c>
       <c r="C79" s="46"/>
-    </row>
-    <row r="80" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D79" s="46" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A80" s="12"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
-    </row>
-    <row r="81" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D80" s="33"/>
+    </row>
+    <row r="81" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A81" s="12" t="s">
         <v>447</v>
       </c>
@@ -27294,8 +27513,11 @@
       <c r="C81" s="12" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D81" s="33" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A82" s="12" t="s">
         <v>449</v>
       </c>
@@ -27305,8 +27527,11 @@
       <c r="C82" s="12" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D82" s="33" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A83" s="12" t="s">
         <v>451</v>
       </c>
@@ -27316,8 +27541,11 @@
       <c r="C83" s="12" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D83" s="33" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A84" s="12" t="s">
         <v>477</v>
       </c>
@@ -27327,8 +27555,11 @@
       <c r="C84" s="12" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D84" s="33" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A85" s="12" t="s">
         <v>576</v>
       </c>
@@ -27336,30 +27567,39 @@
         <v>577</v>
       </c>
       <c r="C85" s="12"/>
-    </row>
-    <row r="86" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D85" s="33" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A86" s="46"/>
       <c r="B86" s="46" t="s">
         <v>578</v>
       </c>
       <c r="C86" s="46"/>
-    </row>
-    <row r="87" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D86" s="46" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A87" s="12"/>
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
-    </row>
-    <row r="88" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D87" s="33"/>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A88" s="12"/>
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
-    </row>
-    <row r="89" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D88" s="33"/>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A89" s="12"/>
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
-    </row>
-    <row r="90" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D89" s="33"/>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A90" s="12" t="s">
         <v>11</v>
       </c>
@@ -27369,8 +27609,11 @@
       <c r="C90" s="12" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D90" s="33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A91" s="12" t="s">
         <v>13</v>
       </c>
@@ -27380,8 +27623,11 @@
       <c r="C91" s="12" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D91" s="33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A92" s="12" t="s">
         <v>19</v>
       </c>
@@ -27391,8 +27637,11 @@
       <c r="C92" s="12" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D92" s="33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A93" s="12" t="s">
         <v>16</v>
       </c>
@@ -27402,8 +27651,11 @@
       <c r="C93" s="12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D93" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A94" s="12" t="s">
         <v>51</v>
       </c>
@@ -27413,8 +27665,11 @@
       <c r="C94" s="12" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D94" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A95" s="12" t="s">
         <v>582</v>
       </c>
@@ -27424,13 +27679,17 @@
       <c r="C95" s="12" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D95" s="33" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
-    </row>
-    <row r="97" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D96" s="33"/>
+    </row>
+    <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A97" s="1" t="s">
         <v>21</v>
       </c>
@@ -27440,8 +27699,11 @@
       <c r="C97" s="1" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D97" s="33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A98" s="1" t="s">
         <v>23</v>
       </c>
@@ -27451,8 +27713,11 @@
       <c r="C98" s="1" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D98" s="33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A99" s="1" t="s">
         <v>26</v>
       </c>
@@ -27462,20 +27727,27 @@
       <c r="C99" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D99" s="33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A100" s="12"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
-    </row>
-    <row r="101" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D100" s="33"/>
+    </row>
+    <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A101" s="41"/>
       <c r="B101" s="48" t="s">
         <v>587</v>
       </c>
       <c r="C101" s="41"/>
-    </row>
-    <row r="102" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D101" s="48" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A102" s="40" t="s">
         <v>457</v>
       </c>
@@ -27485,8 +27757,11 @@
       <c r="C102" s="19" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D102" s="33" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A103" s="12" t="s">
         <v>459</v>
       </c>
@@ -27496,8 +27771,11 @@
       <c r="C103" s="12" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D103" s="33" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A104" s="12" t="s">
         <v>461</v>
       </c>
@@ -27507,8 +27785,11 @@
       <c r="C104" s="12" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D104" s="33" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A105" s="12" t="s">
         <v>54</v>
       </c>
@@ -27518,13 +27799,17 @@
       <c r="C105" s="12" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D105" s="33" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A106" s="12"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
-    </row>
-    <row r="107" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D106" s="33"/>
+    </row>
+    <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A107" s="12" t="s">
         <v>468</v>
       </c>
@@ -27534,8 +27819,11 @@
       <c r="C107" s="12" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D107" s="33" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A108" s="12" t="s">
         <v>469</v>
       </c>
@@ -27545,8 +27833,11 @@
       <c r="C108" s="12" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D108" s="33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A109" s="12" t="s">
         <v>596</v>
       </c>
@@ -27556,13 +27847,17 @@
       <c r="C109" s="12" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D109" s="33" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A110" s="12"/>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
-    </row>
-    <row r="111" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D110" s="33"/>
+    </row>
+    <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A111" s="12" t="s">
         <v>598</v>
       </c>
@@ -27572,8 +27867,11 @@
       <c r="C111" s="19" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D111" s="33" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A112" s="12" t="s">
         <v>600</v>
       </c>
@@ -27583,13 +27881,17 @@
       <c r="C112" s="19" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D112" s="33" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A113" s="12"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
-    </row>
-    <row r="114" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D113" s="33"/>
+    </row>
+    <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A114" s="12" t="s">
         <v>602</v>
       </c>
@@ -27599,8 +27901,11 @@
       <c r="C114" s="19" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D114" s="33" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A115" s="12" t="s">
         <v>463</v>
       </c>
@@ -27610,8 +27915,11 @@
       <c r="C115" s="19" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D115" s="33" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A116" s="12" t="s">
         <v>606</v>
       </c>
@@ -27621,13 +27929,17 @@
       <c r="C116" s="19" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D116" s="33" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A117" s="12"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
-    </row>
-    <row r="118" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D117" s="33"/>
+    </row>
+    <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A118" s="12" t="s">
         <v>608</v>
       </c>
@@ -27637,8 +27949,11 @@
       <c r="C118" s="1" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D118" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A119" s="12" t="s">
         <v>611</v>
       </c>
@@ -27648,8 +27963,11 @@
       <c r="C119" s="1" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D119" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A120" s="12" t="s">
         <v>614</v>
       </c>
@@ -27659,13 +27977,17 @@
       <c r="C120" s="19" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D120" s="33" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A121" s="12"/>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
-    </row>
-    <row r="122" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D121" s="33"/>
+    </row>
+    <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A122" s="12" t="s">
         <v>465</v>
       </c>
@@ -27675,8 +27997,11 @@
       <c r="C122" s="19" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D122" s="33" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A123" s="12" t="s">
         <v>616</v>
       </c>
@@ -27686,8 +28011,11 @@
       <c r="C123" s="19" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D123" s="33" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A124" s="12" t="s">
         <v>617</v>
       </c>
@@ -27697,13 +28025,17 @@
       <c r="C124" s="1" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D124" s="1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A125" s="12"/>
       <c r="B125" s="12"/>
       <c r="C125" s="12"/>
-    </row>
-    <row r="126" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D125" s="33"/>
+    </row>
+    <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A126" s="12" t="s">
         <v>619</v>
       </c>
@@ -27713,8 +28045,11 @@
       <c r="C126" s="12" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D126" s="33" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A127" s="12" t="s">
         <v>622</v>
       </c>
@@ -27724,8 +28059,11 @@
       <c r="C127" s="12" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D127" s="33" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A128" s="12" t="s">
         <v>467</v>
       </c>
@@ -27735,13 +28073,17 @@
       <c r="C128" s="12" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D128" s="33" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
-    </row>
-    <row r="130" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D129" s="33"/>
+    </row>
+    <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A130" s="12" t="s">
         <v>472</v>
       </c>
@@ -27751,26 +28093,33 @@
       <c r="C130" s="12" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D130" s="33" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
-    </row>
-    <row r="132" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D131" s="33"/>
+    </row>
+    <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A132" s="12" t="s">
         <v>626</v>
       </c>
       <c r="B132" s="12" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C132" s="12" t="s">
         <v>627</v>
       </c>
-      <c r="C132" s="12" t="s">
+      <c r="D132" s="33" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A133" s="12" t="s">
         <v>628</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A133" s="12" t="s">
-        <v>629</v>
       </c>
       <c r="B133" s="12" t="s">
         <v>14</v>
@@ -27778,10 +28127,13 @@
       <c r="C133" s="12" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D133" s="33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A134" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B134" s="12" t="s">
         <v>446</v>
@@ -27789,86 +28141,109 @@
       <c r="C134" s="12" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D134" s="33" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A135" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="B135" s="12" t="s">
         <v>631</v>
       </c>
-      <c r="B135" s="12" t="s">
+      <c r="C135" s="12" t="s">
         <v>632</v>
       </c>
-      <c r="C135" s="12" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D135" s="33" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A136" s="12"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
-    </row>
-    <row r="137" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D136" s="33"/>
+    </row>
+    <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A137" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="B137" s="12" t="s">
         <v>634</v>
       </c>
-      <c r="B137" s="12" t="s">
+      <c r="C137" s="12" t="s">
         <v>635</v>
       </c>
-      <c r="C137" s="12" t="s">
+      <c r="D137" s="33" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A138" s="49" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A138" s="49" t="s">
+      <c r="B138" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="B138" s="12" t="s">
+      <c r="C138" s="12" t="s">
         <v>638</v>
       </c>
-      <c r="C138" s="12" t="s">
+      <c r="D138" s="33" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A139" s="12" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A139" s="12" t="s">
+      <c r="B139" s="12" t="s">
         <v>640</v>
       </c>
-      <c r="B139" s="12" t="s">
+      <c r="C139" s="12" t="s">
         <v>641</v>
       </c>
-      <c r="C139" s="12" t="s">
+      <c r="D139" s="33" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A140" s="12" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A140" s="12" t="s">
+      <c r="B140" s="12" t="s">
         <v>643</v>
       </c>
-      <c r="B140" s="12" t="s">
+      <c r="C140" s="12" t="s">
         <v>644</v>
       </c>
-      <c r="C140" s="12" t="s">
+      <c r="D140" s="33" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A141" s="12" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A141" s="12" t="s">
+      <c r="B141" s="12" t="s">
         <v>646</v>
       </c>
-      <c r="B141" s="12" t="s">
+      <c r="C141" s="12" t="s">
         <v>647</v>
       </c>
-      <c r="C141" s="12" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D141" s="33" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A142" s="12"/>
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
-    </row>
-    <row r="143" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D142" s="33"/>
+    </row>
+    <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A143" s="12" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B143" s="12" t="s">
         <v>448</v>
@@ -27876,8 +28251,11 @@
       <c r="C143" s="12" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D143" s="33" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A144" s="12" t="s">
         <v>470</v>
       </c>
@@ -27885,15 +28263,21 @@
         <v>471</v>
       </c>
       <c r="C144" s="12"/>
-    </row>
-    <row r="145" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D144" s="33" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A145" s="46"/>
       <c r="B145" s="46" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C145" s="46"/>
-    </row>
-    <row r="146" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D145" s="46" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A146" s="12" t="s">
         <v>474</v>
       </c>
@@ -27901,10 +28285,13 @@
         <v>475</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="15.75" customHeight="1">
+        <v>650</v>
+      </c>
+      <c r="D146" s="33" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A147" s="12" t="s">
         <v>36</v>
       </c>
@@ -27912,10 +28299,13 @@
         <v>476</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="15.75" customHeight="1">
+        <v>651</v>
+      </c>
+      <c r="D147" s="33" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A148" s="12" t="s">
         <v>38</v>
       </c>
@@ -27925,13 +28315,17 @@
       <c r="C148" s="12" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D148" s="33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="12"/>
-    </row>
-    <row r="150" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D149" s="33"/>
+    </row>
+    <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A150" s="12" t="s">
         <v>41</v>
       </c>
@@ -27941,25 +28335,33 @@
       <c r="C150" s="12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D150" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A151" s="50"/>
       <c r="B151" s="50"/>
       <c r="C151" s="50"/>
-    </row>
-    <row r="152" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D151" s="50"/>
+    </row>
+    <row r="152" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A152" s="8"/>
       <c r="B152" s="51"/>
       <c r="C152" s="51"/>
-    </row>
-    <row r="153" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D152" s="51"/>
+    </row>
+    <row r="153" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A153" s="52"/>
       <c r="B153" s="53" t="s">
         <v>562</v>
       </c>
       <c r="C153" s="53"/>
-    </row>
-    <row r="154" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D153" s="53" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A154" s="8" t="s">
         <v>563</v>
       </c>
@@ -27969,8 +28371,11 @@
       <c r="C154" s="51" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D154" s="51" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A155" s="8" t="s">
         <v>565</v>
       </c>
@@ -27980,8 +28385,11 @@
       <c r="C155" s="51" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D155" s="51" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A156" s="8"/>
       <c r="B156" s="51" t="s">
         <v>567</v>
@@ -27989,38 +28397,51 @@
       <c r="C156" s="51" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D156" s="51" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A157" s="12"/>
       <c r="B157" s="12"/>
       <c r="C157" s="12"/>
-    </row>
-    <row r="158" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D157" s="33"/>
+    </row>
+    <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A158" s="41"/>
       <c r="B158" s="48" t="s">
+        <v>652</v>
+      </c>
+      <c r="C158" s="41"/>
+      <c r="D158" s="48" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A159" s="12" t="s">
         <v>653</v>
       </c>
-      <c r="C158" s="41"/>
-    </row>
-    <row r="159" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A159" s="12" t="s">
+      <c r="B159" s="12" t="s">
         <v>654</v>
       </c>
-      <c r="B159" s="12" t="s">
+      <c r="C159" s="12"/>
+      <c r="D159" s="33" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A160" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="C159" s="12"/>
-    </row>
-    <row r="160" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A160" s="12" t="s">
+      <c r="B160" s="12" t="s">
         <v>656</v>
       </c>
-      <c r="B160" s="12" t="s">
-        <v>657</v>
-      </c>
       <c r="C160" s="12"/>
-    </row>
-    <row r="161" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D160" s="33" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A161" s="12" t="s">
         <v>479</v>
       </c>
@@ -28028,90 +28449,103 @@
         <v>480</v>
       </c>
       <c r="C161" s="12"/>
-    </row>
-    <row r="162" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D161" s="33" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A162" s="12"/>
       <c r="B162" s="12"/>
       <c r="C162" s="12"/>
-    </row>
-    <row r="163" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D162" s="33"/>
+    </row>
+    <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A163" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B163" s="19" t="s">
         <v>658</v>
       </c>
-      <c r="B163" s="19" t="s">
+      <c r="C163" s="12"/>
+      <c r="D163" s="19" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A164" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="C163" s="12"/>
-    </row>
-    <row r="164" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A164" s="1" t="s">
+      <c r="B164" s="12" t="s">
         <v>660</v>
       </c>
-      <c r="B164" s="12" t="s">
+      <c r="C164" s="12"/>
+      <c r="D164" s="33" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A165" s="1" t="s">
         <v>661</v>
-      </c>
-      <c r="C164" s="12"/>
-    </row>
-    <row r="165" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A165" s="1" t="s">
-        <v>662</v>
       </c>
       <c r="B165" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C165" s="12"/>
-    </row>
-    <row r="166" spans="1:3" ht="15.75" customHeight="1">
+      <c r="D165" s="33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A166" s="12"/>
       <c r="B166" s="12"/>
       <c r="C166" s="12"/>
     </row>
-    <row r="167" spans="1:3" ht="15.75" customHeight="1">
+    <row r="167" spans="1:4" ht="15.75" customHeight="1">
       <c r="A167" s="12"/>
       <c r="B167" s="12"/>
       <c r="C167" s="12"/>
     </row>
-    <row r="168" spans="1:3" ht="15.75" customHeight="1">
+    <row r="168" spans="1:4" ht="15.75" customHeight="1">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="12"/>
     </row>
-    <row r="169" spans="1:3" ht="15.75" customHeight="1">
+    <row r="169" spans="1:4" ht="15.75" customHeight="1">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="12"/>
     </row>
-    <row r="170" spans="1:3" ht="15.75" customHeight="1">
+    <row r="170" spans="1:4" ht="15.75" customHeight="1">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="12"/>
     </row>
-    <row r="171" spans="1:3" ht="15.75" customHeight="1">
+    <row r="171" spans="1:4" ht="15.75" customHeight="1">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="12"/>
     </row>
-    <row r="172" spans="1:3" ht="15.75" customHeight="1">
+    <row r="172" spans="1:4" ht="15.75" customHeight="1">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
     </row>
-    <row r="173" spans="1:3" ht="15.75" customHeight="1">
+    <row r="173" spans="1:4" ht="15.75" customHeight="1">
       <c r="A173" s="12"/>
       <c r="B173" s="12"/>
       <c r="C173" s="12"/>
     </row>
-    <row r="174" spans="1:3" ht="15.75" customHeight="1">
+    <row r="174" spans="1:4" ht="15.75" customHeight="1">
       <c r="A174" s="12"/>
       <c r="B174" s="12"/>
       <c r="C174" s="12"/>
     </row>
-    <row r="175" spans="1:3" ht="15.75" customHeight="1">
+    <row r="175" spans="1:4" ht="15.75" customHeight="1">
       <c r="A175" s="12"/>
       <c r="B175" s="12"/>
       <c r="C175" s="12"/>
     </row>
-    <row r="176" spans="1:3" ht="15.75" customHeight="1">
+    <row r="176" spans="1:4" ht="15.75" customHeight="1">
       <c r="A176" s="12"/>
       <c r="B176" s="12"/>
       <c r="C176" s="12"/>
@@ -29699,8 +30133,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{546507F0-DD95-4DDD-B6A1-8A333C91220E}"/>
+    <hyperlink ref="D3" r:id="rId4" xr:uid="{3EFD36B0-2228-45CC-AC19-2290C035AA1A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -29798,7 +30233,7 @@
         <v>249</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="43.5">
@@ -29806,32 +30241,32 @@
         <v>251</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>664</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="30">
       <c r="A13" s="12" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B13" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>664</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="A14" s="12" t="s">
+        <v>666</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="12" t="s">
         <v>668</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="30">
@@ -29839,10 +30274,10 @@
         <v>441</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>670</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -29875,7 +30310,7 @@
         <v>268</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -29908,12 +30343,12 @@
         <v>273</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>557</v>
@@ -29928,10 +30363,10 @@
         <v>259</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1"/>
@@ -29949,7 +30384,7 @@
         <v>12</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
@@ -29994,7 +30429,7 @@
         <v>22</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="13.5" customHeight="1">
@@ -30029,7 +30464,7 @@
         <v>29</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="13.5" customHeight="1">
@@ -30064,7 +30499,7 @@
         <v>37</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.5" customHeight="1">
@@ -30099,7 +30534,7 @@
         <v>12</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1">
@@ -30144,7 +30579,7 @@
         <v>49</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1"/>
@@ -30168,211 +30603,211 @@
         <v>55</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1"/>
     <row r="59" spans="1:3" ht="13.5" customHeight="1"/>
     <row r="60" spans="1:3" ht="13.5" customHeight="1">
       <c r="B60" s="55" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1"/>
     <row r="62" spans="1:3" ht="13.5" customHeight="1">
       <c r="A62" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="B62" s="64" t="s">
         <v>683</v>
       </c>
-      <c r="B62" s="64" t="s">
-        <v>684</v>
-      </c>
       <c r="C62" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.5" customHeight="1"/>
     <row r="64" spans="1:3" ht="13.5" customHeight="1">
       <c r="A64" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="B64" s="64" t="s">
         <v>685</v>
       </c>
-      <c r="B64" s="64" t="s">
-        <v>686</v>
-      </c>
       <c r="C64" s="5" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="13.5" customHeight="1">
       <c r="A65" s="12" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C65" s="57" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="13.5" customHeight="1">
       <c r="A66" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="B66" s="12" t="s">
         <v>688</v>
       </c>
-      <c r="B66" s="12" t="s">
-        <v>689</v>
-      </c>
       <c r="C66" s="12" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15.75" customHeight="1">
       <c r="A67" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="B67" s="12" t="s">
         <v>690</v>
       </c>
-      <c r="B67" s="12" t="s">
+      <c r="C67" s="12" t="s">
         <v>691</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="69" spans="1:3" ht="15.75" customHeight="1">
       <c r="A69" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B69" s="12" t="s">
         <v>693</v>
       </c>
-      <c r="B69" s="12" t="s">
+      <c r="C69" s="12" t="s">
         <v>694</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15.75" customHeight="1">
       <c r="A70" s="12" t="s">
+        <v>695</v>
+      </c>
+      <c r="B70" s="12" t="s">
         <v>696</v>
       </c>
-      <c r="B70" s="12" t="s">
-        <v>697</v>
-      </c>
       <c r="C70" s="12" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="15.75" customHeight="1">
       <c r="A71" s="12" t="s">
+        <v>697</v>
+      </c>
+      <c r="B71" s="12" t="s">
         <v>698</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="C71" s="12" t="s">
         <v>699</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="73" spans="1:3" ht="15.75" customHeight="1">
       <c r="A73" s="12" t="s">
+        <v>700</v>
+      </c>
+      <c r="B73" s="12" t="s">
         <v>701</v>
       </c>
-      <c r="B73" s="12" t="s">
-        <v>702</v>
-      </c>
       <c r="C73" s="12" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15.75" customHeight="1">
       <c r="A74" s="12" t="s">
+        <v>702</v>
+      </c>
+      <c r="B74" s="12" t="s">
         <v>703</v>
       </c>
-      <c r="B74" s="12" t="s">
-        <v>704</v>
-      </c>
       <c r="C74" s="12" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="76" spans="1:3" ht="15.75" customHeight="1">
       <c r="A76" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="B76" s="12" t="s">
         <v>705</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="C76" s="12" t="s">
         <v>706</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="78" spans="1:3" ht="15.75" customHeight="1">
       <c r="A78" s="21" t="s">
+        <v>707</v>
+      </c>
+      <c r="B78" s="12" t="s">
         <v>708</v>
       </c>
-      <c r="B78" s="12" t="s">
+      <c r="C78" s="12" t="s">
         <v>709</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15.75" customHeight="1">
       <c r="A79" s="21" t="s">
+        <v>710</v>
+      </c>
+      <c r="B79" s="12" t="s">
         <v>711</v>
       </c>
-      <c r="B79" s="12" t="s">
-        <v>712</v>
-      </c>
       <c r="C79" s="12" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="81" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="82" spans="1:3" ht="15.75" customHeight="1">
       <c r="B82" s="55" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="84" spans="1:3" ht="15" customHeight="1">
       <c r="A84" s="21" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>448</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="86" spans="1:3" ht="15" customHeight="1">
       <c r="A86" s="21" t="s">
+        <v>715</v>
+      </c>
+      <c r="B86" s="12" t="s">
         <v>716</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="C86" s="12" t="s">
         <v>717</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15.75" customHeight="1">
       <c r="A87" s="21" t="s">
+        <v>718</v>
+      </c>
+      <c r="B87" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="B87" s="12" t="s">
-        <v>720</v>
-      </c>
       <c r="C87" s="12" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="89" spans="1:3" ht="15" customHeight="1">
       <c r="B89" s="55" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15.75" customHeight="1"/>
@@ -30380,75 +30815,75 @@
     <row r="92" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="93" spans="1:3" ht="15.75" customHeight="1">
       <c r="A93" s="21" t="s">
+        <v>721</v>
+      </c>
+      <c r="B93" s="12" t="s">
         <v>722</v>
       </c>
-      <c r="B93" s="12" t="s">
-        <v>723</v>
-      </c>
       <c r="C93" s="12" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15.75" customHeight="1">
       <c r="A94" s="21" t="s">
+        <v>723</v>
+      </c>
+      <c r="B94" s="12" t="s">
         <v>724</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="C94" s="12" t="s">
         <v>725</v>
-      </c>
-      <c r="C94" s="12" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15.75" customHeight="1">
       <c r="A95" s="21" t="s">
+        <v>726</v>
+      </c>
+      <c r="B95" s="12" t="s">
         <v>727</v>
       </c>
-      <c r="B95" s="12" t="s">
+      <c r="C95" s="12" t="s">
         <v>728</v>
-      </c>
-      <c r="C95" s="12" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="97" spans="1:3" ht="15.75" customHeight="1">
       <c r="A97" s="21" t="s">
+        <v>729</v>
+      </c>
+      <c r="B97" s="12" t="s">
         <v>730</v>
       </c>
-      <c r="B97" s="12" t="s">
-        <v>731</v>
-      </c>
       <c r="C97" s="12" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15" customHeight="1">
       <c r="A98" s="21" t="s">
+        <v>731</v>
+      </c>
+      <c r="B98" s="12" t="s">
         <v>732</v>
       </c>
-      <c r="B98" s="12" t="s">
+      <c r="C98" s="12" t="s">
         <v>733</v>
-      </c>
-      <c r="C98" s="12" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.75" customHeight="1">
       <c r="A99" s="21" t="s">
+        <v>734</v>
+      </c>
+      <c r="B99" s="12" t="s">
         <v>735</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="C99" s="12" t="s">
         <v>736</v>
-      </c>
-      <c r="C99" s="12" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="101" spans="1:3" ht="15" customHeight="1">
       <c r="B101" s="55" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.75" customHeight="1"/>
@@ -30457,193 +30892,193 @@
     <row r="105" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="106" spans="1:3" ht="15.75" customHeight="1">
       <c r="A106" s="21" t="s">
+        <v>738</v>
+      </c>
+      <c r="B106" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="B106" s="12" t="s">
-        <v>740</v>
-      </c>
       <c r="C106" s="12" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15.75" customHeight="1">
       <c r="A107" s="21" t="s">
+        <v>740</v>
+      </c>
+      <c r="B107" s="12" t="s">
         <v>741</v>
       </c>
-      <c r="B107" s="12" t="s">
-        <v>742</v>
-      </c>
       <c r="C107" s="12" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="15.75" customHeight="1">
       <c r="A108" s="21" t="s">
+        <v>742</v>
+      </c>
+      <c r="B108" s="12" t="s">
         <v>743</v>
       </c>
-      <c r="B108" s="12" t="s">
-        <v>744</v>
-      </c>
       <c r="C108" s="12" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="15.75" customHeight="1">
       <c r="A109" s="21" t="s">
+        <v>744</v>
+      </c>
+      <c r="B109" s="12" t="s">
         <v>745</v>
       </c>
-      <c r="B109" s="12" t="s">
+      <c r="C109" s="12" t="s">
         <v>746</v>
-      </c>
-      <c r="C109" s="12" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="15.75" customHeight="1">
       <c r="A110" s="12" t="s">
+        <v>747</v>
+      </c>
+      <c r="B110" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="B110" s="12" t="s">
+      <c r="C110" s="12" t="s">
         <v>749</v>
-      </c>
-      <c r="C110" s="12" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15.75" customHeight="1">
       <c r="A111" s="12" t="s">
+        <v>750</v>
+      </c>
+      <c r="B111" s="12" t="s">
         <v>751</v>
       </c>
-      <c r="B111" s="12" t="s">
+      <c r="C111" s="12" t="s">
         <v>752</v>
-      </c>
-      <c r="C111" s="12" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15.75" customHeight="1">
       <c r="A112" s="12" t="s">
+        <v>753</v>
+      </c>
+      <c r="B112" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="B112" s="12" t="s">
+      <c r="C112" s="12" t="s">
         <v>755</v>
-      </c>
-      <c r="C112" s="12" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="114" spans="1:3" ht="15.75" customHeight="1">
       <c r="A114" s="12" t="s">
+        <v>756</v>
+      </c>
+      <c r="B114" s="12" t="s">
         <v>757</v>
       </c>
-      <c r="B114" s="12" t="s">
+      <c r="C114" s="12" t="s">
         <v>758</v>
-      </c>
-      <c r="C114" s="12" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75" customHeight="1">
       <c r="A115" s="12" t="s">
+        <v>759</v>
+      </c>
+      <c r="B115" s="12" t="s">
         <v>760</v>
       </c>
-      <c r="B115" s="12" t="s">
+      <c r="C115" s="12" t="s">
         <v>761</v>
-      </c>
-      <c r="C115" s="12" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15.75" customHeight="1">
       <c r="A116" s="12" t="s">
+        <v>762</v>
+      </c>
+      <c r="B116" s="12" t="s">
         <v>763</v>
       </c>
-      <c r="B116" s="12" t="s">
+      <c r="C116" s="12" t="s">
         <v>764</v>
-      </c>
-      <c r="C116" s="12" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="118" spans="1:3" ht="15.75" customHeight="1">
       <c r="A118" s="12" t="s">
+        <v>765</v>
+      </c>
+      <c r="B118" s="12" t="s">
         <v>766</v>
       </c>
-      <c r="B118" s="12" t="s">
+      <c r="C118" s="12" t="s">
         <v>767</v>
-      </c>
-      <c r="C118" s="12" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="15.75" customHeight="1">
       <c r="A119" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="B119" s="12" t="s">
         <v>769</v>
       </c>
-      <c r="B119" s="12" t="s">
-        <v>770</v>
-      </c>
       <c r="C119" s="12" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="15.75" customHeight="1">
       <c r="A120" s="12" t="s">
+        <v>770</v>
+      </c>
+      <c r="B120" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="B120" s="12" t="s">
+      <c r="C120" s="12" t="s">
         <v>772</v>
-      </c>
-      <c r="C120" s="12" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="122" spans="1:3" ht="15" customHeight="1">
       <c r="A122" s="12" t="s">
+        <v>773</v>
+      </c>
+      <c r="B122" s="12" t="s">
         <v>774</v>
       </c>
-      <c r="B122" s="12" t="s">
+      <c r="C122" s="12" t="s">
         <v>775</v>
-      </c>
-      <c r="C122" s="12" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="124" spans="1:3" ht="15.75" customHeight="1">
       <c r="A124" s="21" t="s">
+        <v>776</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="C124" s="1" t="s">
         <v>778</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15.75" customHeight="1">
       <c r="A125" s="21" t="s">
+        <v>779</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>781</v>
-      </c>
       <c r="C125" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15.75" customHeight="1">
       <c r="A126" s="21" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15.75" customHeight="1"/>
@@ -30654,24 +31089,24 @@
     </row>
     <row r="129" spans="1:3" ht="15.75" customHeight="1">
       <c r="A129" s="12" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="15" customHeight="1">
       <c r="A130" s="21" t="s">
+        <v>784</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
         <v>786</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="15.75" customHeight="1"/>
@@ -30683,7 +31118,7 @@
         <v>63</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="15.75" customHeight="1">
@@ -30694,7 +31129,7 @@
         <v>66</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="15.75" customHeight="1">
@@ -30705,7 +31140,7 @@
         <v>68</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="15.75" customHeight="1"/>
@@ -30761,7 +31196,7 @@
         <v>83</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="15.75" customHeight="1">
@@ -30793,7 +31228,7 @@
         <v>91</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="15.75" customHeight="1">
@@ -30825,7 +31260,7 @@
         <v>91</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="15.75" customHeight="1"/>
@@ -30849,7 +31284,7 @@
         <v>91</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="15.75" customHeight="1"/>
@@ -30884,7 +31319,7 @@
         <v>113</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="15.75" customHeight="1">
@@ -30895,7 +31330,7 @@
         <v>116</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="15.75" customHeight="1"/>
@@ -30913,7 +31348,7 @@
         <v>119</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="15.75" customHeight="1">
@@ -30924,7 +31359,7 @@
         <v>121</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="15.75" customHeight="1">
@@ -30935,7 +31370,7 @@
         <v>123</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="15" customHeight="1">
@@ -31023,7 +31458,7 @@
         <v>140</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="15.75" customHeight="1">
@@ -31031,7 +31466,7 @@
         <v>141</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>143</v>
@@ -31039,24 +31474,24 @@
     </row>
     <row r="179" spans="1:3" ht="15.75" customHeight="1">
       <c r="A179" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>799</v>
-      </c>
       <c r="C179" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="15.75" customHeight="1">
       <c r="A180" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C180" s="1" t="s">
         <v>801</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15.75" customHeight="1"/>
@@ -31065,10 +31500,10 @@
         <v>145</v>
       </c>
       <c r="B182" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="C182" s="1" t="s">
         <v>803</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15.75" customHeight="1">
@@ -31076,10 +31511,10 @@
         <v>147</v>
       </c>
       <c r="B183" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="C183" s="1" t="s">
         <v>805</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="15.75" customHeight="1">
@@ -31087,10 +31522,10 @@
         <v>149</v>
       </c>
       <c r="B184" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="C184" s="1" t="s">
         <v>807</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15.75" customHeight="1">
@@ -31142,7 +31577,7 @@
         <v>159</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>160</v>
@@ -31172,7 +31607,7 @@
     </row>
     <row r="192" spans="1:3" ht="15.75" customHeight="1">
       <c r="A192" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>162</v>
@@ -31183,10 +31618,10 @@
     </row>
     <row r="193" spans="1:3" ht="15.75" customHeight="1">
       <c r="A193" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>811</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>812</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>162</v>
@@ -31198,10 +31633,10 @@
         <v>165</v>
       </c>
       <c r="B195" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C195" s="1" t="s">
         <v>813</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15.75" customHeight="1">
@@ -31209,10 +31644,10 @@
         <v>167</v>
       </c>
       <c r="B196" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="C196" s="1" t="s">
         <v>815</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="15.75" customHeight="1">
@@ -31220,10 +31655,10 @@
         <v>169</v>
       </c>
       <c r="B197" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="C197" s="1" t="s">
         <v>817</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="15.75" customHeight="1">
@@ -31245,7 +31680,7 @@
         <v>174</v>
       </c>
       <c r="C199" s="58" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="15.75" customHeight="1">
@@ -31283,10 +31718,10 @@
     </row>
     <row r="203" spans="1:3" ht="15.75" customHeight="1">
       <c r="A203" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>820</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>821</v>
       </c>
       <c r="C203" s="59" t="s">
         <v>177</v>
@@ -31294,13 +31729,13 @@
     </row>
     <row r="204" spans="1:3" ht="15.75" customHeight="1">
       <c r="A204" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="C204" s="59" t="s">
         <v>823</v>
-      </c>
-      <c r="C204" s="59" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="15.75" customHeight="1">
@@ -31308,7 +31743,7 @@
         <v>192</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>183</v>
@@ -31342,10 +31777,10 @@
         <v>182</v>
       </c>
       <c r="B209" s="12" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C209" s="12" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="15.75" customHeight="1">
@@ -31386,7 +31821,7 @@
         <v>190</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>191</v>
@@ -31394,10 +31829,10 @@
     </row>
     <row r="214" spans="1:3" ht="15.75" customHeight="1">
       <c r="A214" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>191</v>
@@ -31405,13 +31840,13 @@
     </row>
     <row r="215" spans="1:3" ht="15.75" customHeight="1">
       <c r="A215" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
         <v>829</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="15.75" customHeight="1"/>
@@ -31420,10 +31855,10 @@
         <v>195</v>
       </c>
       <c r="B217" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="C217" s="1" t="s">
         <v>831</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="15.75" customHeight="1">
@@ -31431,10 +31866,10 @@
         <v>197</v>
       </c>
       <c r="B218" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="C218" s="1" t="s">
         <v>833</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="15.75" customHeight="1">
@@ -31442,10 +31877,10 @@
         <v>199</v>
       </c>
       <c r="B219" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="C219" s="1" t="s">
         <v>835</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="15.75" customHeight="1">
@@ -31497,7 +31932,7 @@
         <v>208</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>209</v>
@@ -31508,7 +31943,7 @@
         <v>210</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>209</v>
@@ -31516,10 +31951,10 @@
     </row>
     <row r="226" spans="1:3" ht="15.75" customHeight="1">
       <c r="A226" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>209</v>
@@ -31527,10 +31962,10 @@
     </row>
     <row r="227" spans="1:3" ht="15.75" customHeight="1">
       <c r="A227" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>839</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>840</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>209</v>
@@ -31545,7 +31980,7 @@
         <v>212</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="15.75" customHeight="1">
@@ -31556,7 +31991,7 @@
         <v>214</v>
       </c>
       <c r="C230" s="15" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="15.75" customHeight="1">
@@ -31567,7 +32002,7 @@
         <v>216</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="15.75" customHeight="1"/>
@@ -31576,10 +32011,10 @@
         <v>218</v>
       </c>
       <c r="B233" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="C233" s="1" t="s">
         <v>844</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="15.75" customHeight="1">
@@ -31587,10 +32022,10 @@
         <v>220</v>
       </c>
       <c r="B234" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="C234" s="1" t="s">
         <v>846</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="15.75" customHeight="1">
@@ -31621,10 +32056,10 @@
         <v>228</v>
       </c>
       <c r="B238" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="C238" s="1" t="s">
         <v>848</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="15.75" customHeight="1">
@@ -31632,10 +32067,10 @@
         <v>230</v>
       </c>
       <c r="B239" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="C239" s="1" t="s">
         <v>850</v>
-      </c>
-      <c r="C239" s="1" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="15.75" customHeight="1">
@@ -31646,7 +32081,7 @@
         <v>233</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="15.75" customHeight="1">
@@ -31695,18 +32130,18 @@
     </row>
     <row r="245" spans="1:3" ht="15.75" customHeight="1">
       <c r="A245" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>854</v>
-      </c>
       <c r="C245" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15.75" customHeight="1">
       <c r="A246" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>237</v>
@@ -31717,7 +32152,7 @@
     </row>
     <row r="247" spans="1:3" ht="15.75" customHeight="1">
       <c r="A247" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>242</v>
@@ -31730,24 +32165,24 @@
     <row r="249" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="250" spans="1:3" ht="15.75" customHeight="1">
       <c r="B250" s="55" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="252" spans="1:3" ht="15.75" customHeight="1">
       <c r="A252" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B252" s="4" t="s">
         <v>529</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="15.75" customHeight="1">
       <c r="A253" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>9</v>
@@ -31762,60 +32197,60 @@
         <v>46</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="257" spans="1:3" ht="15.75" customHeight="1">
       <c r="A257" s="12" t="s">
+        <v>860</v>
+      </c>
+      <c r="B257" s="12" t="s">
         <v>861</v>
       </c>
-      <c r="B257" s="12" t="s">
-        <v>862</v>
-      </c>
       <c r="C257" s="12" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="15.75" customHeight="1">
       <c r="A258" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="B258" s="12" t="s">
         <v>863</v>
       </c>
-      <c r="B258" s="12" t="s">
-        <v>864</v>
-      </c>
       <c r="C258" s="12" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="15.75" customHeight="1">
       <c r="A259" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="B259" s="12" t="s">
         <v>865</v>
       </c>
-      <c r="B259" s="12" t="s">
-        <v>866</v>
-      </c>
       <c r="C259" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="15.75" customHeight="1">
       <c r="A260" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="B260" s="12" t="s">
         <v>867</v>
       </c>
-      <c r="B260" s="12" t="s">
-        <v>868</v>
-      </c>
       <c r="C260" s="12" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="15.75" customHeight="1">
       <c r="A261" s="12" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B261" s="32">
         <v>2</v>
@@ -31826,52 +32261,52 @@
     </row>
     <row r="262" spans="1:3" ht="15.75" customHeight="1">
       <c r="A262" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="B262" s="12" t="s">
         <v>870</v>
       </c>
-      <c r="B262" s="12" t="s">
-        <v>871</v>
-      </c>
       <c r="C262" s="12" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="264" spans="1:3" ht="15.75" customHeight="1">
       <c r="A264" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="B264" s="12" t="s">
         <v>872</v>
       </c>
-      <c r="B264" s="12" t="s">
-        <v>873</v>
-      </c>
       <c r="C264" s="12" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="15.75" customHeight="1">
       <c r="A265" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="B265" s="12" t="s">
         <v>874</v>
       </c>
-      <c r="B265" s="12" t="s">
-        <v>875</v>
-      </c>
       <c r="C265" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="15.75" customHeight="1">
       <c r="A266" s="12" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B266" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C266" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="15.75" customHeight="1">
       <c r="A267" s="12" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B267" s="32">
         <v>7</v>
@@ -31882,7 +32317,7 @@
     </row>
     <row r="268" spans="1:3" ht="15.75" customHeight="1">
       <c r="A268" s="12" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B268" s="32">
         <v>8</v>
@@ -31893,74 +32328,74 @@
     </row>
     <row r="269" spans="1:3" ht="15.75" customHeight="1">
       <c r="A269" s="12" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B269" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C269" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="271" spans="1:3" ht="15.75" customHeight="1">
       <c r="A271" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>881</v>
-      </c>
       <c r="C271" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="15.75" customHeight="1">
       <c r="A272" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="B272" s="12" t="s">
         <v>882</v>
       </c>
-      <c r="B272" s="12" t="s">
-        <v>883</v>
-      </c>
       <c r="C272" s="12" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="15.75" customHeight="1">
       <c r="A273" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="B273" s="60" t="s">
         <v>884</v>
       </c>
-      <c r="B273" s="60" t="s">
-        <v>885</v>
-      </c>
       <c r="C273" s="60" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="15.75" customHeight="1">
       <c r="A274" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="B274" s="1" t="s">
-        <v>887</v>
-      </c>
       <c r="C274" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="15.75" customHeight="1">
       <c r="A275" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B275" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C275" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="15.75" customHeight="1">
       <c r="A276" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B276" s="32">
         <v>120</v>
@@ -31971,74 +32406,74 @@
     </row>
     <row r="277" spans="1:3" ht="15.75" customHeight="1">
       <c r="A277" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="B277" s="12" t="s">
         <v>890</v>
       </c>
-      <c r="B277" s="12" t="s">
-        <v>891</v>
-      </c>
       <c r="C277" s="12" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="15.75" customHeight="1">
       <c r="A278" s="12" t="s">
+        <v>891</v>
+      </c>
+      <c r="B278" s="12" t="s">
         <v>892</v>
       </c>
-      <c r="B278" s="12" t="s">
-        <v>893</v>
-      </c>
       <c r="C278" s="12" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="280" spans="1:3" ht="15.75" customHeight="1">
       <c r="A280" s="12" t="s">
+        <v>893</v>
+      </c>
+      <c r="B280" s="12" t="s">
         <v>894</v>
       </c>
-      <c r="B280" s="12" t="s">
-        <v>895</v>
-      </c>
       <c r="C280" s="12" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="15.75" customHeight="1">
       <c r="A281" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="B281" s="12" t="s">
         <v>896</v>
       </c>
-      <c r="B281" s="12" t="s">
-        <v>897</v>
-      </c>
       <c r="C281" s="12" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="15.75" customHeight="1">
       <c r="A282" s="12" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B282" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C282" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="15.75" customHeight="1">
       <c r="A283" s="12" t="s">
+        <v>898</v>
+      </c>
+      <c r="B283" s="12" t="s">
         <v>899</v>
       </c>
-      <c r="B283" s="12" t="s">
-        <v>900</v>
-      </c>
       <c r="C283" s="60" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="15.75" customHeight="1">
       <c r="A284" s="12" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B284" s="32">
         <v>6</v>
@@ -32049,52 +32484,52 @@
     </row>
     <row r="285" spans="1:3" ht="15.75" customHeight="1">
       <c r="A285" s="12" t="s">
+        <v>901</v>
+      </c>
+      <c r="B285" s="12" t="s">
         <v>902</v>
       </c>
-      <c r="B285" s="12" t="s">
-        <v>903</v>
-      </c>
       <c r="C285" s="12" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="287" spans="1:3" ht="15.75" customHeight="1">
       <c r="A287" s="12" t="s">
+        <v>903</v>
+      </c>
+      <c r="B287" s="12" t="s">
         <v>904</v>
       </c>
-      <c r="B287" s="12" t="s">
-        <v>905</v>
-      </c>
       <c r="C287" s="12" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="15.75" customHeight="1">
       <c r="A288" s="12" t="s">
+        <v>905</v>
+      </c>
+      <c r="B288" s="12" t="s">
         <v>906</v>
       </c>
-      <c r="B288" s="12" t="s">
-        <v>907</v>
-      </c>
       <c r="C288" s="12" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="15.75" customHeight="1">
       <c r="A289" s="12" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B289" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C289" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="15.75" customHeight="1">
       <c r="A290" s="12" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B290" s="32">
         <v>9</v>
@@ -32105,7 +32540,7 @@
     </row>
     <row r="291" spans="1:3" ht="15.75" customHeight="1">
       <c r="A291" s="12" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B291" s="32">
         <v>10</v>
@@ -32116,52 +32551,52 @@
     </row>
     <row r="292" spans="1:3" ht="15.75" customHeight="1">
       <c r="A292" s="12" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B292" s="12" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="294" spans="1:3" ht="15.75" customHeight="1">
       <c r="A294" s="12" t="s">
+        <v>911</v>
+      </c>
+      <c r="B294" s="12" t="s">
         <v>912</v>
       </c>
-      <c r="B294" s="12" t="s">
-        <v>913</v>
-      </c>
       <c r="C294" s="12" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="15.75" customHeight="1">
       <c r="A295" s="12" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B295" s="12" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C295" s="12" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="15.75" customHeight="1">
       <c r="A296" s="12" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B296" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="15.75" customHeight="1">
       <c r="A297" s="12" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B297" s="32">
         <v>12</v>
@@ -32172,7 +32607,7 @@
     </row>
     <row r="298" spans="1:3" ht="15.75" customHeight="1">
       <c r="A298" s="12" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B298" s="32">
         <v>13</v>
@@ -32183,74 +32618,74 @@
     </row>
     <row r="299" spans="1:3" ht="15.75" customHeight="1">
       <c r="A299" s="12" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B299" s="12" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C299" s="12" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="301" spans="1:3" ht="15.75" customHeight="1">
       <c r="A301" s="12" t="s">
+        <v>918</v>
+      </c>
+      <c r="B301" s="12" t="s">
         <v>919</v>
       </c>
-      <c r="B301" s="12" t="s">
-        <v>920</v>
-      </c>
       <c r="C301" s="12" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="15.75" customHeight="1">
       <c r="A302" s="12" t="s">
+        <v>920</v>
+      </c>
+      <c r="B302" s="12" t="s">
         <v>921</v>
       </c>
-      <c r="B302" s="12" t="s">
-        <v>922</v>
-      </c>
       <c r="C302" s="12" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="15.75" customHeight="1">
       <c r="A303" s="12" t="s">
+        <v>922</v>
+      </c>
+      <c r="B303" s="12" t="s">
         <v>923</v>
       </c>
-      <c r="B303" s="12" t="s">
-        <v>924</v>
-      </c>
       <c r="C303" s="12" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="15.75" customHeight="1">
       <c r="A304" s="12" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B304" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C304" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="15.75" customHeight="1">
       <c r="A305" s="12" t="s">
+        <v>925</v>
+      </c>
+      <c r="B305" s="12" t="s">
         <v>926</v>
       </c>
-      <c r="B305" s="12" t="s">
-        <v>927</v>
-      </c>
       <c r="C305" s="12" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="15.75" customHeight="1">
       <c r="A306" s="12" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B306" s="61">
         <v>13</v>
@@ -32261,63 +32696,63 @@
     </row>
     <row r="307" spans="1:3" ht="15.75" customHeight="1">
       <c r="A307" s="12" t="s">
+        <v>928</v>
+      </c>
+      <c r="B307" s="12" t="s">
         <v>929</v>
       </c>
-      <c r="B307" s="12" t="s">
-        <v>930</v>
-      </c>
       <c r="C307" s="12" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="309" spans="1:3" ht="15.75" customHeight="1">
       <c r="A309" s="12" t="s">
+        <v>930</v>
+      </c>
+      <c r="B309" s="12" t="s">
         <v>931</v>
       </c>
-      <c r="B309" s="12" t="s">
-        <v>932</v>
-      </c>
       <c r="C309" s="12" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="15.75" customHeight="1">
       <c r="A310" s="12" t="s">
+        <v>932</v>
+      </c>
+      <c r="B310" s="12" t="s">
         <v>933</v>
       </c>
-      <c r="B310" s="12" t="s">
-        <v>934</v>
-      </c>
       <c r="C310" s="12" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="15.75" customHeight="1">
       <c r="A311" s="12" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B311" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C311" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="15.75" customHeight="1">
       <c r="A312" s="12" t="s">
+        <v>935</v>
+      </c>
+      <c r="B312" s="12" t="s">
         <v>936</v>
       </c>
-      <c r="B312" s="12" t="s">
-        <v>937</v>
-      </c>
       <c r="C312" s="12" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="15.75" customHeight="1">
       <c r="A313" s="12" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B313" s="32">
         <v>6</v>
@@ -32328,74 +32763,74 @@
     </row>
     <row r="314" spans="1:3" ht="15.75" customHeight="1">
       <c r="A314" s="12" t="s">
+        <v>938</v>
+      </c>
+      <c r="B314" s="12" t="s">
         <v>939</v>
       </c>
-      <c r="B314" s="12" t="s">
-        <v>940</v>
-      </c>
       <c r="C314" s="12" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="316" spans="1:3" ht="15.75" customHeight="1">
       <c r="A316" s="12" t="s">
+        <v>940</v>
+      </c>
+      <c r="B316" s="12" t="s">
         <v>941</v>
       </c>
-      <c r="B316" s="12" t="s">
-        <v>942</v>
-      </c>
       <c r="C316" s="12" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="15.75" customHeight="1">
       <c r="A317" s="12" t="s">
+        <v>942</v>
+      </c>
+      <c r="B317" s="12" t="s">
         <v>943</v>
       </c>
-      <c r="B317" s="12" t="s">
-        <v>944</v>
-      </c>
       <c r="C317" s="12" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="15.75" customHeight="1">
       <c r="A318" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="B318" s="12" t="s">
         <v>945</v>
       </c>
-      <c r="B318" s="12" t="s">
-        <v>946</v>
-      </c>
       <c r="C318" s="12" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="15.75" customHeight="1">
       <c r="A319" s="12" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B319" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C319" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="15.75" customHeight="1">
       <c r="A320" s="12" t="s">
+        <v>947</v>
+      </c>
+      <c r="B320" s="12" t="s">
         <v>948</v>
       </c>
-      <c r="B320" s="12" t="s">
-        <v>949</v>
-      </c>
       <c r="C320" s="12" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="15.75" customHeight="1">
       <c r="A321" s="12" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B321" s="32">
         <v>12</v>
@@ -32406,63 +32841,63 @@
     </row>
     <row r="322" spans="1:3" ht="15.75" customHeight="1">
       <c r="A322" s="12" t="s">
+        <v>950</v>
+      </c>
+      <c r="B322" s="12" t="s">
         <v>951</v>
       </c>
-      <c r="B322" s="12" t="s">
-        <v>952</v>
-      </c>
       <c r="C322" s="12" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="324" spans="1:3" ht="15.75" customHeight="1">
       <c r="A324" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="B324" s="12" t="s">
         <v>953</v>
       </c>
-      <c r="B324" s="12" t="s">
-        <v>954</v>
-      </c>
       <c r="C324" s="12" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="15.75" customHeight="1">
       <c r="A325" s="12" t="s">
+        <v>954</v>
+      </c>
+      <c r="B325" s="12" t="s">
         <v>955</v>
       </c>
-      <c r="B325" s="12" t="s">
-        <v>956</v>
-      </c>
       <c r="C325" s="12" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="15.75" customHeight="1">
       <c r="A326" s="12" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B326" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C326" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="15.75" customHeight="1">
       <c r="A327" s="12" t="s">
+        <v>957</v>
+      </c>
+      <c r="B327" s="12" t="s">
         <v>958</v>
       </c>
-      <c r="B327" s="12" t="s">
-        <v>959</v>
-      </c>
       <c r="C327" s="12" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="15.75" customHeight="1">
       <c r="A328" s="12" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B328" s="32">
         <v>7</v>
@@ -32473,63 +32908,63 @@
     </row>
     <row r="329" spans="1:3" ht="15.75" customHeight="1">
       <c r="A329" s="12" t="s">
+        <v>960</v>
+      </c>
+      <c r="B329" s="12" t="s">
         <v>961</v>
       </c>
-      <c r="B329" s="12" t="s">
-        <v>962</v>
-      </c>
       <c r="C329" s="12" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="331" spans="1:3" ht="15.75" customHeight="1">
       <c r="A331" s="12" t="s">
+        <v>962</v>
+      </c>
+      <c r="B331" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="B331" s="12" t="s">
-        <v>964</v>
-      </c>
       <c r="C331" s="12" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="15.75" customHeight="1">
       <c r="A332" s="12" t="s">
+        <v>964</v>
+      </c>
+      <c r="B332" s="12" t="s">
         <v>965</v>
       </c>
-      <c r="B332" s="12" t="s">
-        <v>966</v>
-      </c>
       <c r="C332" s="12" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="15.75" customHeight="1">
       <c r="A333" s="12" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B333" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C333" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="15.75" customHeight="1">
       <c r="A334" s="12" t="s">
+        <v>967</v>
+      </c>
+      <c r="B334" s="12" t="s">
         <v>968</v>
       </c>
-      <c r="B334" s="12" t="s">
-        <v>969</v>
-      </c>
       <c r="C334" s="12" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="15.75" customHeight="1">
       <c r="A335" s="12" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B335" s="32">
         <v>3</v>
@@ -32540,63 +32975,63 @@
     </row>
     <row r="336" spans="1:3" ht="15.75" customHeight="1">
       <c r="A336" s="12" t="s">
+        <v>970</v>
+      </c>
+      <c r="B336" s="12" t="s">
         <v>971</v>
       </c>
-      <c r="B336" s="12" t="s">
-        <v>972</v>
-      </c>
       <c r="C336" s="12" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="338" spans="1:3" ht="15.75" customHeight="1">
       <c r="A338" s="12" t="s">
+        <v>972</v>
+      </c>
+      <c r="B338" s="12" t="s">
         <v>973</v>
       </c>
-      <c r="B338" s="12" t="s">
-        <v>974</v>
-      </c>
       <c r="C338" s="12" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="15.75" customHeight="1">
       <c r="A339" s="12" t="s">
+        <v>974</v>
+      </c>
+      <c r="B339" s="12" t="s">
         <v>975</v>
       </c>
-      <c r="B339" s="12" t="s">
-        <v>976</v>
-      </c>
       <c r="C339" s="12" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="15.75" customHeight="1">
       <c r="A340" s="12" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B340" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C340" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="15.75" customHeight="1">
       <c r="A341" s="12" t="s">
+        <v>977</v>
+      </c>
+      <c r="B341" s="12" t="s">
         <v>978</v>
       </c>
-      <c r="B341" s="12" t="s">
-        <v>979</v>
-      </c>
       <c r="C341" s="12" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="15.75" customHeight="1">
       <c r="A342" s="12" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B342" s="32">
         <v>3</v>
@@ -32607,63 +33042,63 @@
     </row>
     <row r="343" spans="1:3" ht="15.75" customHeight="1">
       <c r="A343" s="12" t="s">
+        <v>980</v>
+      </c>
+      <c r="B343" s="12" t="s">
         <v>981</v>
       </c>
-      <c r="B343" s="12" t="s">
-        <v>982</v>
-      </c>
       <c r="C343" s="12" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="345" spans="1:3" ht="15.75" customHeight="1">
       <c r="A345" s="12" t="s">
+        <v>982</v>
+      </c>
+      <c r="B345" s="12" t="s">
         <v>983</v>
       </c>
-      <c r="B345" s="12" t="s">
-        <v>984</v>
-      </c>
       <c r="C345" s="12" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="15.75" customHeight="1">
       <c r="A346" s="12" t="s">
+        <v>984</v>
+      </c>
+      <c r="B346" s="12" t="s">
         <v>985</v>
       </c>
-      <c r="B346" s="12" t="s">
-        <v>986</v>
-      </c>
       <c r="C346" s="12" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="15.75" customHeight="1">
       <c r="A347" s="12" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B347" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C347" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="15.75" customHeight="1">
       <c r="A348" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="B348" s="12" t="s">
         <v>988</v>
       </c>
-      <c r="B348" s="12" t="s">
-        <v>989</v>
-      </c>
       <c r="C348" s="12" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="15.75" customHeight="1">
       <c r="A349" s="12" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B349" s="32">
         <v>3</v>
@@ -32674,63 +33109,63 @@
     </row>
     <row r="350" spans="1:3" ht="15.75" customHeight="1">
       <c r="A350" s="12" t="s">
+        <v>990</v>
+      </c>
+      <c r="B350" s="12" t="s">
         <v>991</v>
       </c>
-      <c r="B350" s="12" t="s">
-        <v>992</v>
-      </c>
       <c r="C350" s="12" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="352" spans="1:3" ht="15.75" customHeight="1">
       <c r="A352" s="12" t="s">
+        <v>992</v>
+      </c>
+      <c r="B352" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="B352" s="12" t="s">
-        <v>994</v>
-      </c>
       <c r="C352" s="12" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="15.75" customHeight="1">
       <c r="A353" s="12" t="s">
+        <v>994</v>
+      </c>
+      <c r="B353" s="12" t="s">
         <v>995</v>
       </c>
-      <c r="B353" s="12" t="s">
-        <v>996</v>
-      </c>
       <c r="C353" s="12" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="15.75" customHeight="1">
       <c r="A354" s="12" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B354" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C354" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="15.75" customHeight="1">
       <c r="A355" s="12" t="s">
+        <v>997</v>
+      </c>
+      <c r="B355" s="60" t="s">
         <v>998</v>
       </c>
-      <c r="B355" s="60" t="s">
-        <v>999</v>
-      </c>
       <c r="C355" s="60" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="15.75" customHeight="1">
       <c r="A356" s="12" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B356" s="32">
         <v>3</v>
@@ -32741,74 +33176,74 @@
     </row>
     <row r="357" spans="1:3" ht="15.75" customHeight="1">
       <c r="A357" s="12" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B357" s="12" t="s">
         <v>1001</v>
       </c>
-      <c r="B357" s="12" t="s">
-        <v>1002</v>
-      </c>
       <c r="C357" s="12" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="359" spans="1:3" ht="15.75" customHeight="1">
       <c r="A359" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B359" s="12" t="s">
         <v>1003</v>
       </c>
-      <c r="B359" s="12" t="s">
-        <v>1004</v>
-      </c>
       <c r="C359" s="12" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="15.75" customHeight="1">
       <c r="A360" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B360" s="12" t="s">
         <v>1005</v>
       </c>
-      <c r="B360" s="12" t="s">
-        <v>1006</v>
-      </c>
       <c r="C360" s="12" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="15.75" customHeight="1">
       <c r="A361" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B361" s="12" t="s">
         <v>1007</v>
       </c>
-      <c r="B361" s="12" t="s">
-        <v>1008</v>
-      </c>
       <c r="C361" s="12" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="15.75" customHeight="1">
       <c r="A362" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B362" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C362" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="15.75" customHeight="1">
       <c r="A363" s="12" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B363" s="12" t="s">
         <v>1010</v>
       </c>
-      <c r="B363" s="12" t="s">
-        <v>1011</v>
-      </c>
       <c r="C363" s="12" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15.75" customHeight="1">
       <c r="A364" s="12" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B364" s="32">
         <v>6</v>
@@ -32819,63 +33254,63 @@
     </row>
     <row r="365" spans="1:3" ht="15.75" customHeight="1">
       <c r="A365" s="12" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B365" s="12" t="s">
         <v>1013</v>
       </c>
-      <c r="B365" s="12" t="s">
-        <v>1014</v>
-      </c>
       <c r="C365" s="12" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="367" spans="1:3" ht="15.75" customHeight="1">
       <c r="A367" s="12" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B367" s="12" t="s">
         <v>1015</v>
       </c>
-      <c r="B367" s="12" t="s">
-        <v>1016</v>
-      </c>
       <c r="C367" s="12" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15.75" customHeight="1">
       <c r="A368" s="12" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B368" s="12" t="s">
         <v>1017</v>
       </c>
-      <c r="B368" s="12" t="s">
-        <v>1018</v>
-      </c>
       <c r="C368" s="12" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="15.75" customHeight="1">
       <c r="A369" s="12" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B369" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C369" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="15.75" customHeight="1">
       <c r="A370" s="12" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B370" s="12" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C370" s="12" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="15.75" customHeight="1">
       <c r="A371" s="12" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B371" s="32">
         <v>6</v>
@@ -32886,64 +33321,64 @@
     </row>
     <row r="372" spans="1:3" ht="15.75" customHeight="1">
       <c r="A372" s="12" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B372" s="12" t="s">
         <v>1022</v>
       </c>
-      <c r="B372" s="12" t="s">
-        <v>1023</v>
-      </c>
       <c r="C372" s="12" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="15.75" customHeight="1">
       <c r="A373" s="12" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B373" s="12" t="s">
         <v>1024</v>
       </c>
-      <c r="B373" s="12" t="s">
-        <v>1025</v>
-      </c>
       <c r="C373" s="12" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="375" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="376" spans="1:3" ht="15.75" customHeight="1">
       <c r="A376" s="12" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B376" s="12" t="s">
         <v>1026</v>
       </c>
-      <c r="B376" s="12" t="s">
-        <v>1027</v>
-      </c>
       <c r="C376" s="12" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="15.75" customHeight="1">
       <c r="A377" s="12" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B377" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C377" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="15.75" customHeight="1">
       <c r="A378" s="12" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B378" s="12" t="s">
         <v>1029</v>
       </c>
-      <c r="B378" s="12" t="s">
-        <v>1030</v>
-      </c>
       <c r="C378" s="12" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="15.75" customHeight="1">
       <c r="A379" s="12" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B379" s="32">
         <v>50</v>
@@ -32954,7 +33389,7 @@
     </row>
     <row r="380" spans="1:3" ht="15.75" customHeight="1">
       <c r="A380" s="12" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B380" s="32">
         <v>55</v>
@@ -32965,13 +33400,13 @@
     </row>
     <row r="381" spans="1:3" ht="15.75" customHeight="1">
       <c r="A381" s="12" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B381" s="12" t="s">
         <v>1033</v>
       </c>
-      <c r="B381" s="12" t="s">
-        <v>1034</v>
-      </c>
       <c r="C381" s="12" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="15.75" customHeight="1"/>
@@ -32979,602 +33414,602 @@
     <row r="384" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="385" spans="1:3" ht="15.75" customHeight="1">
       <c r="B385" s="55" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="387" spans="1:3" ht="15.75" customHeight="1">
       <c r="A387" s="12" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B387" s="12" t="s">
         <v>1036</v>
       </c>
-      <c r="B387" s="12" t="s">
-        <v>1037</v>
-      </c>
       <c r="C387" s="12" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="15.75" customHeight="1">
       <c r="A388" s="12" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B388" s="12" t="s">
         <v>1038</v>
       </c>
-      <c r="B388" s="12" t="s">
-        <v>1039</v>
-      </c>
       <c r="C388" s="12" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="15.75" customHeight="1">
       <c r="A389" s="12" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B389" s="12" t="s">
         <v>1040</v>
       </c>
-      <c r="B389" s="12" t="s">
-        <v>1041</v>
-      </c>
       <c r="C389" s="12" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="15.75" customHeight="1">
       <c r="A390" s="12" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B390" s="12" t="s">
         <v>1042</v>
       </c>
-      <c r="B390" s="12" t="s">
-        <v>1043</v>
-      </c>
       <c r="C390" s="12" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="15.75" customHeight="1">
       <c r="A391" s="12" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B391" s="12" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C391" s="12" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="15.75" customHeight="1">
       <c r="A392" s="12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B392" s="12" t="s">
         <v>1045</v>
       </c>
-      <c r="B392" s="12" t="s">
-        <v>1046</v>
-      </c>
       <c r="C392" s="12" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="394" spans="1:3" ht="15.75" customHeight="1">
       <c r="B394" s="55" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="396" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="397" spans="1:3" ht="15.75" customHeight="1">
       <c r="A397" s="12" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B397" s="12" t="s">
         <v>1048</v>
       </c>
-      <c r="B397" s="12" t="s">
-        <v>1049</v>
-      </c>
       <c r="C397" s="12" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="15.75" customHeight="1">
       <c r="A398" s="12" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B398" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="B398" s="12" t="s">
-        <v>1051</v>
-      </c>
       <c r="C398" s="12" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="15.75" customHeight="1">
       <c r="A399" s="12" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B399" s="12" t="s">
         <v>1052</v>
       </c>
-      <c r="B399" s="12" t="s">
-        <v>1053</v>
-      </c>
       <c r="C399" s="12" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="15.75" customHeight="1">
       <c r="A400" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B400" s="12" t="s">
         <v>1054</v>
       </c>
-      <c r="B400" s="12" t="s">
-        <v>1055</v>
-      </c>
       <c r="C400" s="12" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="15.75" customHeight="1">
       <c r="A401" s="12" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B401" s="12" t="s">
         <v>1056</v>
       </c>
-      <c r="B401" s="12" t="s">
-        <v>1057</v>
-      </c>
       <c r="C401" s="12" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="15.75" customHeight="1">
       <c r="A402" s="12" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B402" s="12" t="s">
         <v>1058</v>
       </c>
-      <c r="B402" s="12" t="s">
-        <v>1059</v>
-      </c>
       <c r="C402" s="12" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="15.75" customHeight="1">
       <c r="A403" s="12" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B403" s="12" t="s">
         <v>1060</v>
       </c>
-      <c r="B403" s="12" t="s">
-        <v>1061</v>
-      </c>
       <c r="C403" s="12" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="15.75" customHeight="1">
       <c r="A404" s="12" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B404" s="12" t="s">
         <v>1062</v>
       </c>
-      <c r="B404" s="12" t="s">
-        <v>1063</v>
-      </c>
       <c r="C404" s="12" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="15.75" customHeight="1">
       <c r="A405" s="12" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B405" s="12" t="s">
         <v>1064</v>
       </c>
-      <c r="B405" s="12" t="s">
-        <v>1065</v>
-      </c>
       <c r="C405" s="12" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="15.75" customHeight="1">
       <c r="A406" s="12" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B406" s="12" t="s">
         <v>1066</v>
       </c>
-      <c r="B406" s="12" t="s">
-        <v>1067</v>
-      </c>
       <c r="C406" s="12" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="15.75" customHeight="1">
       <c r="A407" s="12" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B407" s="12" t="s">
         <v>1068</v>
       </c>
-      <c r="B407" s="12" t="s">
-        <v>1069</v>
-      </c>
       <c r="C407" s="12" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="15.75" customHeight="1">
       <c r="A408" s="12" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B408" s="12" t="s">
         <v>1070</v>
       </c>
-      <c r="B408" s="12" t="s">
-        <v>1071</v>
-      </c>
       <c r="C408" s="12" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="15.75" customHeight="1">
       <c r="A409" s="12" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B409" s="12" t="s">
         <v>1072</v>
       </c>
-      <c r="B409" s="12" t="s">
-        <v>1073</v>
-      </c>
       <c r="C409" s="12" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="15.75" customHeight="1">
       <c r="A410" s="12" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B410" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C410" s="12" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="15.75" customHeight="1">
       <c r="A411" s="12" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B411" s="12" t="s">
         <v>1075</v>
       </c>
-      <c r="B411" s="12" t="s">
-        <v>1076</v>
-      </c>
       <c r="C411" s="12" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="15.75" customHeight="1">
       <c r="A412" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B412" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B412" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C412" s="12" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="15.75" customHeight="1">
       <c r="A413" s="12" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B413" s="12" t="s">
         <v>1079</v>
       </c>
-      <c r="B413" s="12" t="s">
-        <v>1080</v>
-      </c>
       <c r="C413" s="12" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="15.75" customHeight="1">
       <c r="A414" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B414" s="12" t="s">
         <v>1081</v>
       </c>
-      <c r="B414" s="12" t="s">
-        <v>1082</v>
-      </c>
       <c r="C414" s="12" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="15.75" customHeight="1">
       <c r="A415" s="12" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B415" s="12" t="s">
         <v>1083</v>
       </c>
-      <c r="B415" s="12" t="s">
-        <v>1084</v>
-      </c>
       <c r="C415" s="12" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="15.75" customHeight="1">
       <c r="A416" s="12" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B416" s="12" t="s">
         <v>1085</v>
       </c>
-      <c r="B416" s="12" t="s">
-        <v>1086</v>
-      </c>
       <c r="C416" s="12" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="15.75" customHeight="1">
       <c r="A417" s="12" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B417" s="12" t="s">
         <v>1087</v>
       </c>
-      <c r="B417" s="12" t="s">
-        <v>1088</v>
-      </c>
       <c r="C417" s="12" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="15.75" customHeight="1">
       <c r="A418" s="12" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B418" s="12" t="s">
         <v>1089</v>
       </c>
-      <c r="B418" s="12" t="s">
-        <v>1090</v>
-      </c>
       <c r="C418" s="12" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15.75" customHeight="1">
       <c r="A419" s="12" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B419" s="12" t="s">
         <v>1091</v>
       </c>
-      <c r="B419" s="12" t="s">
-        <v>1092</v>
-      </c>
       <c r="C419" s="12" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="15.75" customHeight="1">
       <c r="A420" s="12" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B420" s="12" t="s">
         <v>1093</v>
       </c>
-      <c r="B420" s="12" t="s">
-        <v>1094</v>
-      </c>
       <c r="C420" s="12" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15.75" customHeight="1">
       <c r="A421" s="12" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B421" s="12" t="s">
         <v>1095</v>
       </c>
-      <c r="B421" s="12" t="s">
-        <v>1096</v>
-      </c>
       <c r="C421" s="12" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="15.75" customHeight="1">
       <c r="A422" s="12" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B422" s="12" t="s">
         <v>1097</v>
       </c>
-      <c r="B422" s="12" t="s">
-        <v>1098</v>
-      </c>
       <c r="C422" s="12" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15.75" customHeight="1">
       <c r="A423" s="12" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B423" s="12" t="s">
         <v>1099</v>
       </c>
-      <c r="B423" s="12" t="s">
-        <v>1100</v>
-      </c>
       <c r="C423" s="12" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15.75" customHeight="1">
       <c r="A424" s="12" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B424" s="12" t="s">
         <v>1101</v>
       </c>
-      <c r="B424" s="12" t="s">
-        <v>1102</v>
-      </c>
       <c r="C424" s="12" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="15.75" customHeight="1">
       <c r="A425" s="12" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B425" s="12" t="s">
         <v>1103</v>
       </c>
-      <c r="B425" s="12" t="s">
-        <v>1104</v>
-      </c>
       <c r="C425" s="12" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15.75" customHeight="1">
       <c r="A426" s="12" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B426" s="12" t="s">
         <v>1105</v>
       </c>
-      <c r="B426" s="12" t="s">
-        <v>1106</v>
-      </c>
       <c r="C426" s="12" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="15.75" customHeight="1">
       <c r="A427" s="12" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B427" s="12" t="s">
         <v>1107</v>
       </c>
-      <c r="B427" s="12" t="s">
-        <v>1108</v>
-      </c>
       <c r="C427" s="12" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="15.75" customHeight="1">
       <c r="A428" s="12" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B428" s="12" t="s">
         <v>1109</v>
       </c>
-      <c r="B428" s="12" t="s">
-        <v>1110</v>
-      </c>
       <c r="C428" s="12" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="15.75" customHeight="1">
       <c r="A429" s="12" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B429" s="12" t="s">
         <v>1111</v>
       </c>
-      <c r="B429" s="12" t="s">
-        <v>1112</v>
-      </c>
       <c r="C429" s="12" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15.75" customHeight="1">
       <c r="A430" s="12" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B430" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="B430" s="12" t="s">
-        <v>1114</v>
-      </c>
       <c r="C430" s="12" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="432" spans="1:3" ht="15.75" customHeight="1">
       <c r="A432" s="12" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B432" s="12" t="s">
         <v>1115</v>
       </c>
-      <c r="B432" s="12" t="s">
-        <v>1116</v>
-      </c>
       <c r="C432" s="12" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="15.75" customHeight="1">
       <c r="A433" s="12" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B433" s="12" t="s">
         <v>1117</v>
       </c>
-      <c r="B433" s="12" t="s">
-        <v>1118</v>
-      </c>
       <c r="C433" s="12" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="15.75" customHeight="1">
       <c r="A434" s="12" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B434" s="12" t="s">
         <v>1119</v>
       </c>
-      <c r="B434" s="12" t="s">
-        <v>1120</v>
-      </c>
       <c r="C434" s="12" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="15.75" customHeight="1">
       <c r="A435" s="12" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B435" s="12" t="s">
         <v>1121</v>
       </c>
-      <c r="B435" s="12" t="s">
-        <v>1122</v>
-      </c>
       <c r="C435" s="12" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="15.75" customHeight="1">
       <c r="A436" s="12" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B436" s="12" t="s">
         <v>1123</v>
       </c>
-      <c r="B436" s="12" t="s">
-        <v>1124</v>
-      </c>
       <c r="C436" s="12" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="438" spans="1:3" ht="15.75" customHeight="1">
       <c r="A438" s="12" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B438" s="12" t="s">
         <v>1125</v>
       </c>
-      <c r="B438" s="12" t="s">
-        <v>1126</v>
-      </c>
       <c r="C438" s="12" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="15.75" customHeight="1">
       <c r="A439" s="12" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B439" s="12" t="s">
         <v>1127</v>
       </c>
-      <c r="B439" s="12" t="s">
-        <v>1128</v>
-      </c>
       <c r="C439" s="12" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="15.75" customHeight="1">
       <c r="A440" s="12" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B440" s="12" t="s">
         <v>1129</v>
       </c>
-      <c r="B440" s="12" t="s">
-        <v>1130</v>
-      </c>
       <c r="C440" s="12" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="15.75" customHeight="1">
       <c r="A441" s="12" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B441" s="12" t="s">
         <v>1131</v>
       </c>
-      <c r="B441" s="12" t="s">
-        <v>1132</v>
-      </c>
       <c r="C441" s="12" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="15.75" customHeight="1">
       <c r="A442" s="12" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B442" s="12" t="s">
         <v>1133</v>
       </c>
-      <c r="B442" s="12" t="s">
-        <v>1134</v>
-      </c>
       <c r="C442" s="12" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="15.75" customHeight="1">
       <c r="A443" s="12" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B443" s="12" t="s">
         <v>1135</v>
       </c>
-      <c r="B443" s="12" t="s">
-        <v>1136</v>
-      </c>
       <c r="C443" s="12" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="15.75" customHeight="1">
       <c r="B444" s="55" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="446" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="447" spans="1:3" ht="15.75" customHeight="1">
       <c r="A447" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B447" s="64" t="s">
         <v>1138</v>
       </c>
-      <c r="B447" s="64" t="s">
-        <v>1139</v>
-      </c>
       <c r="C447" s="12" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="15.75" customHeight="1">
       <c r="A448" s="12" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B448" s="12" t="s">
         <v>9</v>
@@ -33586,7 +34021,7 @@
     <row r="449" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="450" spans="1:3" ht="15.75" customHeight="1">
       <c r="A450" s="62" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B450" s="63" t="s">
         <v>7</v>
@@ -33596,12 +34031,12 @@
     <row r="452" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="453" spans="1:3" ht="15.75" customHeight="1">
       <c r="B453" s="66" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="15.75" customHeight="1">
       <c r="A454" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B454" t="s">
         <v>4</v>
@@ -33613,108 +34048,108 @@
     <row r="455" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="456" spans="1:3" ht="15.75" customHeight="1">
       <c r="A456" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B456" s="68" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="15.75" customHeight="1">
       <c r="A457" s="67" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B457" s="68" t="s">
         <v>1195</v>
       </c>
-      <c r="B457" s="68" t="s">
-        <v>1196</v>
-      </c>
       <c r="C457" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="459" spans="1:3" ht="15.75" customHeight="1">
       <c r="A459" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B459" s="68" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C459" s="68" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="15.75" customHeight="1">
       <c r="A460" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B460" s="68" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C460" s="68" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="462" spans="1:3" ht="15.75" customHeight="1">
       <c r="A462" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B462" s="68" t="s">
         <v>1203</v>
       </c>
-      <c r="B462" s="68" t="s">
-        <v>1204</v>
-      </c>
       <c r="C462" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="15.75" customHeight="1">
       <c r="A463" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B463" s="68" t="s">
         <v>1205</v>
-      </c>
-      <c r="B463" s="68" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="15.75" customHeight="1">
       <c r="A464" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B464" s="68" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="465" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="466" spans="1:2" ht="15.75" customHeight="1">
       <c r="A466" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B466" s="68" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="467" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="468" spans="1:2" ht="15.75" customHeight="1">
       <c r="A468" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B468" t="s">
         <v>1212</v>
-      </c>
-      <c r="B468" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="469" spans="1:2" ht="15.75" customHeight="1">
       <c r="A469" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B469" t="s">
         <v>1214</v>
-      </c>
-      <c r="B469" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="470" spans="1:2" ht="15.75" customHeight="1">
       <c r="A470" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="471" spans="1:2" ht="15.75" customHeight="1">
       <c r="A471" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="472" spans="1:2" ht="15.75" customHeight="1"/>

--- a/config/testdata/testdata.xlsx
+++ b/config/testdata/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MMHNZ_V2_AUTOMATION\config\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267F8896-1D29-455D-AD65-2DDA36EB07BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84742FD-445A-4D32-AE6D-F8063DF0CC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Happy_Path_Patient_Web_and_MR" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="1286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="1299">
   <si>
     <t>KEY</t>
   </si>
@@ -3914,12 +3914,51 @@
   <si>
     <t>Automation1_HC1;Invite for Video Consultation;Video Consultations Msg Testing_RANDOM</t>
   </si>
+  <si>
+    <t>13 Feb 2025;13 Feb 2025;Lab Test;;Automation1_Loc1</t>
+  </si>
+  <si>
+    <t>Automation1_Loc1;GP1 A1 L1</t>
+  </si>
+  <si>
+    <t>Lab Results Test</t>
+  </si>
+  <si>
+    <t>SMS_LOCATION</t>
+  </si>
+  <si>
+    <t>Automation1_HC1;Secure Message - SMS</t>
+  </si>
+  <si>
+    <t>VM07 HC Evo Prod;Secure Message - SMS</t>
+  </si>
+  <si>
+    <t>REASON_DATA</t>
+  </si>
+  <si>
+    <t>Automation</t>
+  </si>
+  <si>
+    <t>UPADTE_REASON_DATA</t>
+  </si>
+  <si>
+    <t>AutomationUpdate</t>
+  </si>
+  <si>
+    <t>Automation1_Loc1;Automation Pre Screening Questionnaire</t>
+  </si>
+  <si>
+    <t>VM07 Loc1 Evo Prod;Automation Pre Screening Questionnaire</t>
+  </si>
+  <si>
+    <t>PRE_SCREENING_QUESTIONNAIRE_DATA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4073,6 +4112,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF5C92FF"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="13">
@@ -4362,7 +4407,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4603,6 +4648,9 @@
     <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -8764,7 +8812,7 @@
         <v>201</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>1251</v>
+        <v>1286</v>
       </c>
       <c r="C129" s="78" t="s">
         <v>1190</v>
@@ -8797,7 +8845,7 @@
         <v>203</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>1151</v>
+        <v>1287</v>
       </c>
       <c r="C130" s="87" t="s">
         <v>1100</v>
@@ -8830,7 +8878,7 @@
         <v>205</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>206</v>
+        <v>1288</v>
       </c>
       <c r="C131" s="78" t="s">
         <v>207</v>
@@ -29403,33 +29451,71 @@
       <c r="C166" s="64" t="s">
         <v>1272</v>
       </c>
+      <c r="D166" s="9" t="s">
+        <v>1212</v>
+      </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A167" s="9"/>
-      <c r="B167" s="9"/>
-      <c r="C167" s="9"/>
+      <c r="A167" s="9" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B167" s="9" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C167" s="64" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D167" s="9" t="s">
+        <v>1290</v>
+      </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A168" s="9"/>
-      <c r="B168" s="9"/>
-      <c r="C168" s="9"/>
-    </row>
-    <row r="169" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A169" s="9"/>
-      <c r="B169" s="9"/>
-      <c r="C169" s="9"/>
-    </row>
-    <row r="170" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A170" s="9"/>
-      <c r="B170" s="9"/>
-      <c r="C170" s="9"/>
-    </row>
-    <row r="171" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A171" s="9"/>
+      <c r="A168" s="9" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B168" s="9" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C168" s="9" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A169" s="94" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C169" s="9" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D169" s="9" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A170" s="9" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B170" s="9" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C170" s="9" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D170" s="9" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
     </row>
-    <row r="172" spans="1:4" ht="15.75" customHeight="1">
+    <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A172" s="9"/>
       <c r="B172" s="9"/>
       <c r="C172" s="9"/>

--- a/config/testdata/testdata.xlsx
+++ b/config/testdata/testdata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MMHNZ_V2_AUTOMATION\config\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation_Framework\MMHNZ_V2_AUTOMATION\config\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{562B582F-ECF7-4B17-A2A1-02158F8B54AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95304062-A25B-449B-A016-C57D1FAD0ABF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="1266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="1265">
   <si>
     <t>KEY</t>
   </si>
@@ -3532,9 +3532,6 @@
   </si>
   <si>
     <t>Automation1_HC1;Invite for Video Consultation;Video Consultations Msg Testing_RANDOM</t>
-  </si>
-  <si>
-    <t>13 Feb 2025;13 Feb 2025;Lab Test;;Automation1_Loc1</t>
   </si>
   <si>
     <t>Automation1_Loc1;GP1 A1 L1</t>
@@ -4824,7 +4821,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C2" s="74" t="s">
         <v>1048</v>
@@ -8719,7 +8716,7 @@
         <v>188</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>1159</v>
+        <v>1261</v>
       </c>
       <c r="C129" s="76" t="s">
         <v>1065</v>
@@ -8752,7 +8749,7 @@
         <v>189</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C130" s="85" t="s">
         <v>976</v>
@@ -8785,7 +8782,7 @@
         <v>190</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C131" s="76" t="s">
         <v>192</v>
@@ -8843,7 +8840,7 @@
         <v>193</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C133" s="76" t="s">
         <v>1066</v>
@@ -16164,7 +16161,7 @@
         <v>218</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C12" s="76" t="s">
         <v>1132</v>
@@ -16175,10 +16172,10 @@
         <v>557</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -16189,7 +16186,7 @@
         <v>559</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="30">
@@ -16197,10 +16194,10 @@
         <v>375</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -16233,7 +16230,7 @@
         <v>1079</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -16587,7 +16584,7 @@
         <v>571</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>573</v>
@@ -16599,7 +16596,7 @@
         <v>574</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>576</v>
@@ -16610,7 +16607,7 @@
         <v>577</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C70" s="9" t="s">
         <v>578</v>
@@ -16621,7 +16618,7 @@
         <v>579</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C71" s="9" t="s">
         <v>581</v>
@@ -16668,7 +16665,7 @@
         <v>589</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>591</v>
@@ -16701,7 +16698,7 @@
         <v>382</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" customHeight="1"/>
@@ -16710,10 +16707,10 @@
         <v>596</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15.75" customHeight="1">
@@ -16862,10 +16859,10 @@
         <v>626</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15.75" customHeight="1">
@@ -16873,10 +16870,10 @@
         <v>627</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15.75" customHeight="1">
@@ -16884,10 +16881,10 @@
         <v>628</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75" customHeight="1"/>
@@ -16896,10 +16893,10 @@
         <v>629</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75" customHeight="1">
@@ -16907,10 +16904,10 @@
         <v>630</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15.75" customHeight="1">
@@ -16918,10 +16915,10 @@
         <v>631</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15.75" customHeight="1"/>
@@ -16967,7 +16964,7 @@
         <v>641</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75" customHeight="1"/>
@@ -16979,7 +16976,7 @@
         <v>643</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15.75" customHeight="1">
@@ -16990,7 +16987,7 @@
         <v>645</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15.75" customHeight="1">
@@ -17001,7 +16998,7 @@
         <v>645</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15.75" customHeight="1"/>
@@ -17909,7 +17906,7 @@
         <v>188</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C229" s="76" t="s">
         <v>1065</v>
@@ -17920,7 +17917,7 @@
         <v>189</v>
       </c>
       <c r="B230" s="10" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C230" s="85" t="s">
         <v>976</v>
@@ -17931,7 +17928,7 @@
         <v>190</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C231" s="76" t="s">
         <v>192</v>
@@ -17943,7 +17940,7 @@
         <v>193</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C233" s="76" t="s">
         <v>1066</v>
@@ -21290,7 +21287,7 @@
         <v>39</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
@@ -22106,7 +22103,7 @@
         <v>281</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C54" s="18"/>
       <c r="D54" s="18"/>
@@ -22134,7 +22131,7 @@
         <v>282</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C55" s="18"/>
       <c r="D55" s="18"/>
@@ -22162,7 +22159,7 @@
         <v>283</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C56" s="18"/>
       <c r="D56" s="18"/>
@@ -22190,7 +22187,7 @@
         <v>284</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C57" s="18"/>
       <c r="D57" s="18"/>
@@ -22218,7 +22215,7 @@
         <v>285</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C58" s="18"/>
       <c r="D58" s="18"/>
@@ -22246,7 +22243,7 @@
         <v>286</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C59" s="18"/>
       <c r="D59" s="18"/>
@@ -22274,7 +22271,7 @@
         <v>287</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C60" s="18"/>
       <c r="D60" s="18"/>
@@ -22302,7 +22299,7 @@
         <v>288</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C61" s="18"/>
       <c r="D61" s="18"/>
@@ -22330,7 +22327,7 @@
         <v>289</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C62" s="18"/>
       <c r="D62" s="18"/>
@@ -22358,7 +22355,7 @@
         <v>290</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C63" s="18"/>
       <c r="D63" s="18"/>
@@ -22386,7 +22383,7 @@
         <v>291</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C64" s="18"/>
       <c r="D64" s="18"/>
@@ -22414,7 +22411,7 @@
         <v>292</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C65" s="18"/>
       <c r="D65" s="18"/>
@@ -22442,7 +22439,7 @@
         <v>293</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C66" s="18"/>
       <c r="D66" s="18"/>
@@ -22470,7 +22467,7 @@
         <v>294</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C67" s="18"/>
       <c r="D67" s="18"/>
@@ -22522,7 +22519,7 @@
         <v>295</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="C69" s="18"/>
       <c r="D69" s="18"/>
@@ -22578,7 +22575,7 @@
         <v>298</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C71" s="18"/>
       <c r="D71" s="18"/>
@@ -22630,7 +22627,7 @@
         <v>299</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C73" s="18"/>
       <c r="D73" s="18"/>
@@ -22658,7 +22655,7 @@
         <v>300</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C74" s="18"/>
       <c r="D74" s="18"/>
@@ -23142,7 +23139,7 @@
         <v>319</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C92" s="18"/>
       <c r="D92" s="18"/>
@@ -23170,7 +23167,7 @@
         <v>320</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C93" s="18"/>
       <c r="D93" s="18"/>
@@ -23278,7 +23275,7 @@
         <v>323</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C97" s="18"/>
       <c r="D97" s="18"/>
@@ -23306,7 +23303,7 @@
         <v>324</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C98" s="18"/>
       <c r="D98" s="18"/>
@@ -23334,7 +23331,7 @@
         <v>325</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C99" s="18"/>
       <c r="D99" s="18"/>
@@ -23386,7 +23383,7 @@
         <v>326</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C101" s="18"/>
       <c r="D101" s="18"/>
@@ -23442,7 +23439,7 @@
         <v>327</v>
       </c>
       <c r="B103" s="22" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C103" s="18"/>
       <c r="D103" s="18"/>
@@ -23522,7 +23519,7 @@
         <v>330</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C106" s="18"/>
       <c r="D106" s="18"/>
@@ -23550,7 +23547,7 @@
         <v>331</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C107" s="18"/>
       <c r="D107" s="18"/>
@@ -23702,7 +23699,7 @@
         <v>333</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C113" s="18"/>
       <c r="D113" s="18"/>
@@ -23754,7 +23751,7 @@
         <v>334</v>
       </c>
       <c r="B115" s="24" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C115" s="18"/>
       <c r="D115" s="18"/>
@@ -23806,7 +23803,7 @@
         <v>335</v>
       </c>
       <c r="B117" s="93" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C117" s="18"/>
       <c r="D117" s="18"/>
@@ -24114,7 +24111,7 @@
         <v>340</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C129" s="18"/>
       <c r="D129" s="18"/>
@@ -24170,7 +24167,7 @@
         <v>341</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C131" s="18"/>
       <c r="D131" s="18"/>
@@ -24922,7 +24919,7 @@
         <v>370</v>
       </c>
       <c r="B159" s="95" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C159" s="18"/>
       <c r="D159" s="18"/>
@@ -25298,7 +25295,7 @@
         <v>441</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C173" s="18"/>
       <c r="D173" s="18"/>
@@ -25347,10 +25344,10 @@
     </row>
     <row r="175" spans="1:22" ht="15.75" customHeight="1">
       <c r="A175" s="92" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B175" s="95" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C175" s="18"/>
       <c r="D175" s="18"/>
@@ -25375,10 +25372,10 @@
     </row>
     <row r="176" spans="1:22" ht="15.75" customHeight="1">
       <c r="A176" s="92" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B176" s="95" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C176" s="18"/>
       <c r="D176" s="18"/>
@@ -25403,10 +25400,10 @@
     </row>
     <row r="177" spans="1:22" ht="15.75" customHeight="1">
       <c r="A177" s="92" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B177" s="95" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C177" s="18"/>
       <c r="D177" s="18"/>
@@ -25431,10 +25428,10 @@
     </row>
     <row r="178" spans="1:22" ht="15.75" customHeight="1">
       <c r="A178" s="92" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B178" s="95" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="C178" s="18"/>
       <c r="D178" s="18"/>
@@ -25459,10 +25456,10 @@
     </row>
     <row r="179" spans="1:22" ht="15.75" customHeight="1">
       <c r="A179" s="92" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B179" s="95" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C179" s="18"/>
       <c r="D179" s="18"/>
@@ -25571,10 +25568,10 @@
     </row>
     <row r="183" spans="1:22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A183" s="92" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B183" s="95" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C183" s="18"/>
       <c r="D183" s="18"/>
@@ -25629,10 +25626,10 @@
     </row>
     <row r="185" spans="1:22" ht="15.75" customHeight="1">
       <c r="A185" s="92" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B185" s="95" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="C185" s="18"/>
       <c r="D185" s="18"/>
@@ -25681,10 +25678,10 @@
     </row>
     <row r="187" spans="1:22" ht="15.75" customHeight="1">
       <c r="A187" s="92" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B187" s="95" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C187" s="18"/>
       <c r="D187" s="18"/>
@@ -32075,7 +32072,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C2" s="51" t="s">
         <v>1048</v>
@@ -32273,10 +32270,10 @@
         <v>441</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C17" s="62" t="s">
         <v>1219</v>
-      </c>
-      <c r="C17" s="62" t="s">
-        <v>1220</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>442</v>
@@ -32550,7 +32547,7 @@
         <v>67</v>
       </c>
       <c r="C42" s="60" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>67</v>
@@ -32584,7 +32581,7 @@
         <v>1070</v>
       </c>
       <c r="C45" s="60" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>1070</v>
@@ -32595,13 +32592,13 @@
         <v>89</v>
       </c>
       <c r="B46" s="9" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C46" s="60" t="s">
         <v>1224</v>
       </c>
-      <c r="C46" s="60" t="s">
-        <v>1225</v>
-      </c>
       <c r="D46" s="9" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
@@ -32632,7 +32629,7 @@
         <v>482</v>
       </c>
       <c r="C49" s="60" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>482</v>
@@ -34044,58 +34041,58 @@
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A169" s="9" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B169" s="9" t="s">
         <v>1162</v>
       </c>
-      <c r="B169" s="9" t="s">
+      <c r="C169" s="62" t="s">
         <v>1163</v>
       </c>
-      <c r="C169" s="62" t="s">
-        <v>1164</v>
-      </c>
       <c r="D169" s="9" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A170" s="9" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B170" s="9" t="s">
         <v>1165</v>
       </c>
-      <c r="B170" s="9" t="s">
-        <v>1166</v>
-      </c>
       <c r="C170" s="9" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D170" s="9" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A171" s="92" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B171" s="9" t="s">
         <v>1167</v>
       </c>
-      <c r="B171" s="9" t="s">
-        <v>1168</v>
-      </c>
       <c r="C171" s="9" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D171" s="9" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A172" s="9" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B172" s="9" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C172" s="9" t="s">
         <v>1169</v>
       </c>
-      <c r="C172" s="9" t="s">
-        <v>1170</v>
-      </c>
       <c r="D172" s="9" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
@@ -34105,39 +34102,39 @@
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A174" s="29"/>
       <c r="B174" s="35" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C174" s="66"/>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A175" s="9" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="C175" s="62" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="D175" s="9" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A176" s="9" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B176" s="9" t="s">
         <v>1231</v>
-      </c>
-      <c r="B176" s="9" t="s">
-        <v>1232</v>
       </c>
       <c r="C176" s="9"/>
     </row>
     <row r="177" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A177" s="92" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B177" s="9" t="s">
         <v>1233</v>
-      </c>
-      <c r="B177" s="9" t="s">
-        <v>1234</v>
       </c>
       <c r="C177" s="9"/>
     </row>

--- a/config/testdata/testdata.xlsx
+++ b/config/testdata/testdata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation_Framework\MMHNZ_V2_AUTOMATION\config\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MMHNZ_V2_AUTOMATION\config\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95304062-A25B-449B-A016-C57D1FAD0ABF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0C8326-C362-4610-AC69-4FCF85F670DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Happy_Path_Patient_Web_and_MR" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="1265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2632" uniqueCount="1299">
   <si>
     <t>KEY</t>
   </si>
@@ -3744,21 +3744,12 @@
     <t>VM07 HC Evo Prod;VM07 Loc1 Evo Prod;Dr B Beta</t>
   </si>
   <si>
-    <t>Automation1_HC1;Automation1_Loc1;Gp2white4;456;Doctor</t>
-  </si>
-  <si>
     <t>EDIT_MANAGE_PROVIDERS_DETAILS</t>
   </si>
   <si>
-    <t>Automation1_HC1;Automation1_Loc1;Gp2white4;456;Nurse</t>
-  </si>
-  <si>
     <t>ENABLED_PROVIDER_DATA</t>
   </si>
   <si>
-    <t>Gp2white4</t>
-  </si>
-  <si>
     <t>Automation1_HC1;Automation1_Loc1;Lab Result enquiry;Clinical Staff;Gp2White;Draft Message_RANDOM;Draft Message Testing_RANDOM;MMHtest.jpg</t>
   </si>
   <si>
@@ -3850,6 +3841,117 @@
   </si>
   <si>
     <t>https://v2portalbau.mmh-demo.com/home</t>
+  </si>
+  <si>
+    <t>EMAIL_CSC_CARD</t>
+  </si>
+  <si>
+    <t>Autochrisc4@mmh-demo.com</t>
+  </si>
+  <si>
+    <t>Autochrisc5@mmh-demo.com</t>
+  </si>
+  <si>
+    <t>EMAIL_HUHC_CARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appointments CSC &amp; HUSC Card </t>
+  </si>
+  <si>
+    <t>Automation1_HC1;Automation1_Loc3;Myself (AUTO AUTOCHRISC1);A new issue;Visit;9:00 AM;Gp4 White;AFTER_THREE_DAYS</t>
+  </si>
+  <si>
+    <t>Visit;Automation1_Loc3;Gp4 White</t>
+  </si>
+  <si>
+    <t>Pending;Gp4 White;AFTER_THREE_DAYS;A new issue|Wheel Chair</t>
+  </si>
+  <si>
+    <t>BOOK_VISIT_APPOINTMENT_NURSE_ACC_NO</t>
+  </si>
+  <si>
+    <t>VISIT_APPOINTMENT_DETAILS_NURSE_ACC_NO</t>
+  </si>
+  <si>
+    <t>VISIT_APPOINTMENT_SUMMARY_NURSE_ACC_NO</t>
+  </si>
+  <si>
+    <t>CARD_APPOINTMENT_DETAILS_NURSE_ACC_NO</t>
+  </si>
+  <si>
+    <t>Automation1_Loc3;Gp4 White;APPROVED</t>
+  </si>
+  <si>
+    <t>BOOK_VISIT_APPOINTMENT_NURSE_ACC_YES</t>
+  </si>
+  <si>
+    <t>VISIT_APPOINTMENT_DETAILS_NURSE_ACC_YES</t>
+  </si>
+  <si>
+    <t>VISIT_APPOINTMENT_SUMMARY_NURSE_ACC_YES</t>
+  </si>
+  <si>
+    <t>CARD_APPOINTMENT_DETAILS_NURSE_ACC_YES</t>
+  </si>
+  <si>
+    <t>Automation1_HC1;Automation1_Loc3;Myself (AUTO AUTOCHRISC1);A new issue;Visit;9:00 AM;Gp6 White;AFTER_THREE_DAYS</t>
+  </si>
+  <si>
+    <t>Visit;Automation1_Loc3;Gp6 White</t>
+  </si>
+  <si>
+    <t>Pending;Gp6 White;AFTER_THREE_DAYS;A new issue|Wheel Chair</t>
+  </si>
+  <si>
+    <t>Automation1_Loc3;Gp6 White;APPROVED</t>
+  </si>
+  <si>
+    <t>Gp4 White</t>
+  </si>
+  <si>
+    <t>Automation1_HC1;Automation1_Loc3;Gp4 White;GP4;Nurse</t>
+  </si>
+  <si>
+    <t>DATA FOR PATIENT TO COLLECT TO PRESCRIPTION NURSE</t>
+  </si>
+  <si>
+    <t>Automation1_Loc3;Gp2White;Patient to Collect Script;Next Day;Trasylol 500,000KIU/50ml Inj;Repeat Medication Testing for PATIENT TO COLLECT</t>
+  </si>
+  <si>
+    <t>DATA MEDS PAY BY USING ONLINE A2A CSC CARD</t>
+  </si>
+  <si>
+    <t>VERIFICATION DATA FOR MEDS PAY BY USING A2A CSC CARD</t>
+  </si>
+  <si>
+    <t>Automation1_Loc1;Gp2White;Deliver Meds by Pharmacy;Select from my saved list;ZOOM Pharmacy home delivery; 1: 123, Auckland Central;48 Hours;Prostin Vr 500mcg/1ml Inj;Repeat Medication Testing for Delivery Meds by Pharmacy;ZOOM Pharmacy home delivery</t>
+  </si>
+  <si>
+    <t>Automation1_Loc1;Prostin Vr 500mcg/1ml Inj;pending;ZOOM Pharmacy home delivery;48 Hours;GP2WHITE</t>
+  </si>
+  <si>
+    <t>DATA MEDS PAY BY USING ONLINE A2A HUHC CARD</t>
+  </si>
+  <si>
+    <t>VERIFICATION DATA FOR MEDS PAY BY USING A2A HUHC CARD</t>
+  </si>
+  <si>
+    <t>Automation1_HC1;Automation1_Loc1;Myself (AUTO AUTOCHRISC5);A new issue;Visit;9:00 AM;GP2WHITE;AFTER_THREE_DAYS</t>
+  </si>
+  <si>
+    <t>BOOK_VISIT_APPOINTMENT_USING_CSC_CARD_PAYMENT</t>
+  </si>
+  <si>
+    <t>VISIT_APPOINTMENT_DETAILS_CSC_USING_CARD_PAYMENT</t>
+  </si>
+  <si>
+    <t>BOOK_VISIT_APPOINTMENT_USING_HUHC_CARD_PAYMENT</t>
+  </si>
+  <si>
+    <t>VISIT_APPOINTMENT_DETAILS_UHC_USING_CARD_PAYMENT</t>
+  </si>
+  <si>
+    <t>Automation1_HC1;Automation1_Loc1;Myself (AUTO AUTOCHRISC4);A new issue;Visit;9:00 AM;GP2WHITE;AFTER_THREE_DAYS</t>
   </si>
 </sst>
 </file>
@@ -4305,7 +4407,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4537,7 +4639,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4773,11 +4874,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W1000"/>
+  <dimension ref="A1:W1017"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="69.5703125" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="102.85546875" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="121.140625" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="161.140625" style="58" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="102.28515625" customWidth="1" collapsed="1"/>
     <col min="5" max="23" width="8.85546875" customWidth="1" collapsed="1"/>
@@ -4821,7 +4922,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="C2" s="74" t="s">
         <v>1048</v>
@@ -4884,17 +4985,13 @@
     </row>
     <row r="4" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="76" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>1262</v>
+      </c>
+      <c r="B4" s="57" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C4" s="75"/>
+      <c r="D4" s="4"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -4917,15 +5014,13 @@
     </row>
     <row r="5" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A5" s="1" t="s">
-        <v>969</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>970</v>
-      </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="5" t="s">
-        <v>970</v>
-      </c>
+        <v>1265</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C5" s="75"/>
+      <c r="D5" s="4"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -4947,13 +5042,17 @@
       <c r="W5" s="2"/>
     </row>
     <row r="6" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="8" t="s">
-        <v>8</v>
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -4976,10 +5075,16 @@
       <c r="W6" s="2"/>
     </row>
     <row r="7" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>970</v>
+      </c>
       <c r="C7" s="77"/>
-      <c r="D7" s="1"/>
+      <c r="D7" s="5" t="s">
+        <v>970</v>
+      </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -5001,17 +5106,13 @@
       <c r="W7" s="2"/>
     </row>
     <row r="8" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C8" s="76" t="s">
-        <v>1127</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>1072</v>
+      <c r="A8" s="7"/>
+      <c r="B8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="78"/>
+      <c r="D8" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -5034,18 +5135,10 @@
       <c r="W8" s="2"/>
     </row>
     <row r="9" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="76" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="1"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -5068,16 +5161,16 @@
     </row>
     <row r="10" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>971</v>
+        <v>1072</v>
       </c>
       <c r="C10" s="76" t="s">
-        <v>16</v>
+        <v>1127</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>971</v>
+        <v>1072</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -5101,16 +5194,16 @@
     </row>
     <row r="11" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C11" s="76" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -5133,10 +5226,18 @@
       <c r="W11" s="2"/>
     </row>
     <row r="12" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="C12" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>971</v>
+      </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -5159,16 +5260,16 @@
     </row>
     <row r="13" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1073</v>
+        <v>18</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>1128</v>
+        <v>18</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1073</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -5191,18 +5292,10 @@
       <c r="W13" s="2"/>
     </row>
     <row r="14" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="76" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="1"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -5225,16 +5318,16 @@
     </row>
     <row r="15" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>1073</v>
       </c>
       <c r="C15" s="76" t="s">
-        <v>16</v>
+        <v>1128</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>25</v>
+        <v>1073</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -5257,10 +5350,18 @@
       <c r="W15" s="2"/>
     </row>
     <row r="16" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="1"/>
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="76" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -5282,10 +5383,18 @@
       <c r="W16" s="2"/>
     </row>
     <row r="17" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -5307,18 +5416,10 @@
       <c r="W17" s="2"/>
     </row>
     <row r="18" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C18" s="76" t="s">
-        <v>1129</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>1074</v>
-      </c>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="1"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -5340,18 +5441,10 @@
       <c r="W18" s="2"/>
     </row>
     <row r="19" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="76" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="1"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -5374,16 +5467,16 @@
     </row>
     <row r="20" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>972</v>
+        <v>1074</v>
       </c>
       <c r="C20" s="76" t="s">
-        <v>16</v>
+        <v>1129</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>972</v>
+        <v>1074</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -5406,10 +5499,18 @@
       <c r="W20" s="2"/>
     </row>
     <row r="21" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="77"/>
-      <c r="D21" s="1"/>
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -5431,10 +5532,18 @@
       <c r="W21" s="2"/>
     </row>
     <row r="22" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="C22" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>972</v>
+      </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -5456,18 +5565,10 @@
       <c r="W22" s="2"/>
     </row>
     <row r="23" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C23" s="76" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>1075</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="1"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -5489,18 +5590,10 @@
       <c r="W23" s="2"/>
     </row>
     <row r="24" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="76" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="1"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -5523,16 +5616,16 @@
     </row>
     <row r="25" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>973</v>
+        <v>1075</v>
       </c>
       <c r="C25" s="76" t="s">
-        <v>16</v>
+        <v>1130</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>973</v>
+        <v>1075</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -5555,10 +5648,18 @@
       <c r="W25" s="2"/>
     </row>
     <row r="26" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="77"/>
-      <c r="D26" s="1"/>
+      <c r="A26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -5580,10 +5681,18 @@
       <c r="W26" s="2"/>
     </row>
     <row r="27" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="77"/>
-      <c r="D27" s="1"/>
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="C27" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>973</v>
+      </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -5605,18 +5714,10 @@
       <c r="W27" s="2"/>
     </row>
     <row r="28" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C28" s="76" t="s">
-        <v>1127</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>1072</v>
-      </c>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="1"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -5638,18 +5739,10 @@
       <c r="W28" s="2"/>
     </row>
     <row r="29" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="76" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="1"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -5672,16 +5765,16 @@
     </row>
     <row r="30" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>38</v>
+        <v>1072</v>
       </c>
       <c r="C30" s="76" t="s">
-        <v>38</v>
+        <v>1127</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>38</v>
+        <v>1072</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -5705,16 +5798,16 @@
     </row>
     <row r="31" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C31" s="76" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -5737,10 +5830,18 @@
       <c r="W31" s="2"/>
     </row>
     <row r="32" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="77"/>
-      <c r="D32" s="1"/>
+      <c r="A32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -5763,16 +5864,16 @@
     </row>
     <row r="33" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C33" s="76" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -5820,10 +5921,18 @@
       <c r="W34" s="2"/>
     </row>
     <row r="35" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="1"/>
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -5845,18 +5954,10 @@
       <c r="W35" s="2"/>
     </row>
     <row r="36" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="1"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -5878,18 +5979,10 @@
       <c r="W36" s="2"/>
     </row>
     <row r="37" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A37" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="76" t="s">
-        <v>49</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="1"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -5912,16 +6005,16 @@
     </row>
     <row r="38" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A38" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C38" s="77" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="C38" s="76" t="s">
+        <v>46</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -5945,16 +6038,16 @@
     </row>
     <row r="39" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="78" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="C39" s="76" t="s">
+        <v>49</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -5977,13 +6070,17 @@
       <c r="W39" s="2"/>
     </row>
     <row r="40" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A40" s="7"/>
-      <c r="B40" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="77"/>
-      <c r="D40" s="8" t="s">
-        <v>54</v>
+      <c r="A40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="77" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -6006,10 +6103,18 @@
       <c r="W40" s="2"/>
     </row>
     <row r="41" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="79"/>
-      <c r="D41" s="1"/>
+      <c r="A41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="78" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -6031,18 +6136,7 @@
       <c r="W41" s="2"/>
     </row>
     <row r="42" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A42" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C42" s="76" t="s">
-        <v>57</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="C42"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -6064,18 +6158,10 @@
       <c r="W42" s="2"/>
     </row>
     <row r="43" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A43" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C43" s="76" t="s">
-        <v>966</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="B43" s="8" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C43"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -6098,16 +6184,16 @@
     </row>
     <row r="44" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A44" s="1" t="s">
-        <v>60</v>
+        <v>1270</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>61</v>
+        <v>1267</v>
       </c>
       <c r="C44" s="76" t="s">
-        <v>62</v>
+        <v>1127</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>61</v>
+        <v>1072</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -6130,10 +6216,18 @@
       <c r="W44" s="2"/>
     </row>
     <row r="45" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="77"/>
-      <c r="D45" s="9"/>
+      <c r="A45" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C45" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -6154,18 +6248,18 @@
       <c r="V45" s="2"/>
       <c r="W45" s="2"/>
     </row>
-    <row r="46" spans="1:23" ht="18.75" customHeight="1" thickBot="1">
+    <row r="46" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A46" s="1" t="s">
-        <v>63</v>
+        <v>1272</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>64</v>
+        <v>1269</v>
       </c>
       <c r="C46" s="76" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>64</v>
+        <v>971</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -6189,16 +6283,16 @@
     </row>
     <row r="47" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A47" s="1" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C47" s="76" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -6220,19 +6314,14 @@
       <c r="V47" s="2"/>
       <c r="W47" s="2"/>
     </row>
-    <row r="48" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A48" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C48" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>70</v>
-      </c>
+    <row r="48" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A48" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C48"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -6253,11 +6342,8 @@
       <c r="V48" s="2"/>
       <c r="W48" s="2"/>
     </row>
-    <row r="49" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="77"/>
-      <c r="D49" s="1"/>
+    <row r="49" spans="1:23" ht="13.5" customHeight="1">
+      <c r="C49"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -6279,18 +6365,7 @@
       <c r="W49" s="2"/>
     </row>
     <row r="50" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A50" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C50" s="76" t="s">
-        <v>73</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>1045</v>
-      </c>
+      <c r="C50"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -6313,16 +6388,13 @@
     </row>
     <row r="51" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A51" s="1" t="s">
-        <v>74</v>
+        <v>1275</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1046</v>
+        <v>1279</v>
       </c>
       <c r="C51" s="76" t="s">
-        <v>75</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>1046</v>
+        <v>1127</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -6346,16 +6418,13 @@
     </row>
     <row r="52" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A52" s="1" t="s">
-        <v>76</v>
+        <v>1276</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1047</v>
+        <v>1280</v>
       </c>
       <c r="C52" s="76" t="s">
-        <v>77</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>1047</v>
+        <v>13</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -6378,10 +6447,15 @@
       <c r="W52" s="2"/>
     </row>
     <row r="53" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A53" s="9"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="77"/>
-      <c r="D53" s="1"/>
+      <c r="A53" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C53" s="76" t="s">
+        <v>16</v>
+      </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -6404,16 +6478,13 @@
     </row>
     <row r="54" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A54" s="1" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1039</v>
+        <v>18</v>
       </c>
       <c r="C54" s="76" t="s">
-        <v>989</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>1039</v>
+        <v>18</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -6435,19 +6506,14 @@
       <c r="V54" s="2"/>
       <c r="W54" s="2"/>
     </row>
-    <row r="55" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A55" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C55" s="76" t="s">
-        <v>80</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>1041</v>
-      </c>
+    <row r="55" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A55" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C55"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -6469,18 +6535,7 @@
       <c r="W55" s="2"/>
     </row>
     <row r="56" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A56" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C56" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>1043</v>
-      </c>
+      <c r="C56"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -6502,10 +6557,14 @@
       <c r="W56" s="2"/>
     </row>
     <row r="57" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
+      <c r="A57" s="7"/>
+      <c r="B57" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="C57" s="77"/>
-      <c r="D57" s="9"/>
+      <c r="D57" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -6527,18 +6586,10 @@
       <c r="W57" s="2"/>
     </row>
     <row r="58" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A58" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C58" s="76" t="s">
-        <v>989</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>1039</v>
-      </c>
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="79"/>
+      <c r="D58" s="1"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -6561,16 +6612,16 @@
     </row>
     <row r="59" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A59" s="1" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>1041</v>
+        <v>56</v>
       </c>
       <c r="C59" s="76" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1041</v>
+        <v>56</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
@@ -6593,10 +6644,18 @@
       <c r="W59" s="2"/>
     </row>
     <row r="60" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A60" s="9"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="77"/>
-      <c r="D60" s="9"/>
+      <c r="A60" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C60" s="76" t="s">
+        <v>966</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -6619,16 +6678,16 @@
     </row>
     <row r="61" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A61" s="1" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1039</v>
+        <v>61</v>
       </c>
       <c r="C61" s="76" t="s">
-        <v>989</v>
+        <v>62</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1039</v>
+        <v>61</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
@@ -6651,18 +6710,10 @@
       <c r="W61" s="2"/>
     </row>
     <row r="62" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A62" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C62" s="76" t="s">
-        <v>80</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>1041</v>
-      </c>
+      <c r="A62" s="9"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="9"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -6683,11 +6734,19 @@
       <c r="V62" s="2"/>
       <c r="W62" s="2"/>
     </row>
-    <row r="63" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="77"/>
-      <c r="D63" s="1"/>
+    <row r="63" spans="1:23" ht="18.75" customHeight="1" thickBot="1">
+      <c r="A63" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -6709,17 +6768,17 @@
       <c r="W63" s="2"/>
     </row>
     <row r="64" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A64" s="9" t="s">
-        <v>87</v>
+      <c r="A64" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1040</v>
+        <v>67</v>
       </c>
       <c r="C64" s="76" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1040</v>
+        <v>67</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
@@ -6742,17 +6801,17 @@
       <c r="W64" s="2"/>
     </row>
     <row r="65" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A65" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C65" s="77" t="s">
-        <v>90</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>1042</v>
+      <c r="A65" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C65" s="76" t="s">
+        <v>71</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
@@ -6775,18 +6834,10 @@
       <c r="W65" s="2"/>
     </row>
     <row r="66" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A66" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C66" s="76" t="s">
-        <v>92</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="77"/>
+      <c r="D66" s="1"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -6808,10 +6859,18 @@
       <c r="W66" s="2"/>
     </row>
     <row r="67" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="77"/>
-      <c r="D67" s="1"/>
+      <c r="A67" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C67" s="76" t="s">
+        <v>73</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -6834,16 +6893,16 @@
     </row>
     <row r="68" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A68" s="1" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C68" s="76" t="s">
-        <v>1044</v>
+        <v>75</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
@@ -6867,16 +6926,16 @@
     </row>
     <row r="69" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A69" s="1" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>96</v>
+        <v>1047</v>
       </c>
       <c r="C69" s="76" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>96</v>
+        <v>1047</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
@@ -6899,18 +6958,10 @@
       <c r="W69" s="2"/>
     </row>
     <row r="70" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A70" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C70" s="76" t="s">
-        <v>99</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="A70" s="9"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="77"/>
+      <c r="D70" s="1"/>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -6933,16 +6984,16 @@
     </row>
     <row r="71" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A71" s="1" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>101</v>
+        <v>1039</v>
       </c>
       <c r="C71" s="76" t="s">
-        <v>101</v>
+        <v>989</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>101</v>
+        <v>1039</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
@@ -6965,10 +7016,18 @@
       <c r="W71" s="2"/>
     </row>
     <row r="72" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A72" s="1"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="78"/>
-      <c r="D72" s="5"/>
+      <c r="A72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C72" s="76" t="s">
+        <v>80</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>1041</v>
+      </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -6990,13 +7049,17 @@
       <c r="W72" s="2"/>
     </row>
     <row r="73" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A73" s="7"/>
-      <c r="B73" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C73" s="77"/>
-      <c r="D73" s="8" t="s">
-        <v>102</v>
+      <c r="A73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C73" s="76" t="s">
+        <v>82</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>1043</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
@@ -7021,7 +7084,7 @@
     <row r="74" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
-      <c r="C74" s="79"/>
+      <c r="C74" s="77"/>
       <c r="D74" s="9"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
@@ -7045,16 +7108,16 @@
     </row>
     <row r="75" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A75" s="1" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>1027</v>
+        <v>1039</v>
       </c>
       <c r="C75" s="76" t="s">
-        <v>1061</v>
+        <v>989</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>1027</v>
+        <v>1039</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
@@ -7078,16 +7141,16 @@
     </row>
     <row r="76" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A76" s="1" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="C76" s="76" t="s">
-        <v>1049</v>
+        <v>80</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
@@ -7110,18 +7173,10 @@
       <c r="W76" s="2"/>
     </row>
     <row r="77" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A77" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C77" s="76" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>106</v>
-      </c>
+      <c r="A77" s="9"/>
+      <c r="B77" s="9"/>
+      <c r="C77" s="77"/>
+      <c r="D77" s="9"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -7144,16 +7199,16 @@
     </row>
     <row r="78" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A78" s="1" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>108</v>
+        <v>1039</v>
       </c>
       <c r="C78" s="76" t="s">
-        <v>108</v>
+        <v>989</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>108</v>
+        <v>1039</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
@@ -7177,16 +7232,16 @@
     </row>
     <row r="79" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A79" s="1" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>110</v>
+        <v>1041</v>
       </c>
       <c r="C79" s="76" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>110</v>
+        <v>1041</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
@@ -7209,18 +7264,10 @@
       <c r="W79" s="2"/>
     </row>
     <row r="80" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A80" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C80" s="76" t="s">
-        <v>113</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>112</v>
-      </c>
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="77"/>
+      <c r="D80" s="1"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -7242,17 +7289,17 @@
       <c r="W80" s="2"/>
     </row>
     <row r="81" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A81" s="1" t="s">
-        <v>114</v>
+      <c r="A81" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>115</v>
+        <v>1040</v>
       </c>
       <c r="C81" s="76" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>115</v>
+        <v>1040</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
@@ -7275,17 +7322,17 @@
       <c r="W81" s="2"/>
     </row>
     <row r="82" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A82" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C82" s="76" t="s">
-        <v>117</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>117</v>
+      <c r="A82" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C82" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>1042</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
@@ -7303,19 +7350,22 @@
       <c r="R82" s="2"/>
       <c r="S82" s="2"/>
       <c r="T82" s="2"/>
+      <c r="U82" s="2"/>
+      <c r="V82" s="2"/>
+      <c r="W82" s="2"/>
     </row>
     <row r="83" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A83" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B83" s="1">
-        <v>1</v>
-      </c>
-      <c r="C83" s="80">
-        <v>1</v>
-      </c>
-      <c r="D83" s="1">
-        <v>1</v>
+      <c r="A83" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C83" s="76" t="s">
+        <v>92</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
@@ -7330,20 +7380,18 @@
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
       <c r="Q83" s="2"/>
+      <c r="R83" s="2"/>
+      <c r="S83" s="2"/>
+      <c r="T83" s="2"/>
+      <c r="U83" s="2"/>
+      <c r="V83" s="2"/>
+      <c r="W83" s="2"/>
     </row>
     <row r="84" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A84" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="C84" s="77" t="s">
-        <v>120</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>120</v>
-      </c>
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="77"/>
+      <c r="D84" s="1"/>
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -7360,19 +7408,22 @@
       <c r="R84" s="2"/>
       <c r="S84" s="2"/>
       <c r="T84" s="2"/>
+      <c r="U84" s="2"/>
+      <c r="V84" s="2"/>
+      <c r="W84" s="2"/>
     </row>
     <row r="85" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A85" s="1" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C85" s="81" t="s">
-        <v>123</v>
+        <v>1044</v>
+      </c>
+      <c r="C85" s="76" t="s">
+        <v>1044</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>122</v>
+        <v>1044</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
@@ -7387,19 +7438,25 @@
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
       <c r="Q85" s="2"/>
+      <c r="R85" s="2"/>
+      <c r="S85" s="2"/>
+      <c r="T85" s="2"/>
+      <c r="U85" s="2"/>
+      <c r="V85" s="2"/>
+      <c r="W85" s="2"/>
     </row>
     <row r="86" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A86" s="1" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="C86" s="76" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
@@ -7417,17 +7474,22 @@
       <c r="R86" s="2"/>
       <c r="S86" s="2"/>
       <c r="T86" s="2"/>
+      <c r="U86" s="2"/>
+      <c r="V86" s="2"/>
+      <c r="W86" s="2"/>
     </row>
     <row r="87" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A87" s="9" t="s">
-        <v>127</v>
+      <c r="A87" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C87" s="77"/>
+        <v>98</v>
+      </c>
+      <c r="C87" s="76" t="s">
+        <v>99</v>
+      </c>
       <c r="D87" s="1" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
@@ -7450,10 +7512,18 @@
       <c r="W87" s="2"/>
     </row>
     <row r="88" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A88" s="9"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="77"/>
-      <c r="D88" s="9"/>
+      <c r="A88" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C88" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -7470,20 +7540,15 @@
       <c r="R88" s="2"/>
       <c r="S88" s="2"/>
       <c r="T88" s="2"/>
+      <c r="U88" s="2"/>
+      <c r="V88" s="2"/>
+      <c r="W88" s="2"/>
     </row>
     <row r="89" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A89" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C89" s="76" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>1029</v>
-      </c>
+      <c r="A89" s="1"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="78"/>
+      <c r="D89" s="5"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -7500,19 +7565,18 @@
       <c r="R89" s="2"/>
       <c r="S89" s="2"/>
       <c r="T89" s="2"/>
+      <c r="U89" s="2"/>
+      <c r="V89" s="2"/>
+      <c r="W89" s="2"/>
     </row>
     <row r="90" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A90" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C90" s="76" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>1030</v>
+      <c r="A90" s="7"/>
+      <c r="B90" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C90" s="77"/>
+      <c r="D90" s="8" t="s">
+        <v>102</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
@@ -7527,20 +7591,18 @@
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
       <c r="Q90" s="2"/>
+      <c r="R90" s="2"/>
+      <c r="S90" s="2"/>
+      <c r="T90" s="2"/>
+      <c r="U90" s="2"/>
+      <c r="V90" s="2"/>
+      <c r="W90" s="2"/>
     </row>
     <row r="91" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A91" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C91" s="76" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>131</v>
-      </c>
+      <c r="A91" s="9"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="79"/>
+      <c r="D91" s="9"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -7562,17 +7624,17 @@
       <c r="W91" s="2"/>
     </row>
     <row r="92" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A92" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C92" s="77" t="s">
-        <v>133</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>133</v>
+      <c r="A92" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C92" s="76" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>1027</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
@@ -7590,19 +7652,22 @@
       <c r="R92" s="2"/>
       <c r="S92" s="2"/>
       <c r="T92" s="2"/>
+      <c r="U92" s="2"/>
+      <c r="V92" s="2"/>
+      <c r="W92" s="2"/>
     </row>
     <row r="93" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A93" s="1" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>135</v>
+        <v>1028</v>
       </c>
       <c r="C93" s="76" t="s">
-        <v>135</v>
+        <v>1049</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>135</v>
+        <v>1028</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
@@ -7626,16 +7691,16 @@
     </row>
     <row r="94" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A94" s="1" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="C94" s="76" t="s">
-        <v>137</v>
+        <v>1050</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
@@ -7658,17 +7723,17 @@
       <c r="W94" s="2"/>
     </row>
     <row r="95" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A95" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="C95" s="82" t="s">
-        <v>139</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>139</v>
+      <c r="A95" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C95" s="76" t="s">
+        <v>108</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
@@ -7692,16 +7757,16 @@
     </row>
     <row r="96" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A96" s="1" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="C96" s="76" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
@@ -7725,16 +7790,16 @@
     </row>
     <row r="97" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A97" s="1" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="C97" s="76" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
@@ -7752,19 +7817,22 @@
       <c r="R97" s="2"/>
       <c r="S97" s="2"/>
       <c r="T97" s="2"/>
+      <c r="U97" s="2"/>
+      <c r="V97" s="2"/>
+      <c r="W97" s="2"/>
     </row>
     <row r="98" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A98" s="1" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="C98" s="76" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
@@ -7782,12 +7850,23 @@
       <c r="R98" s="2"/>
       <c r="S98" s="2"/>
       <c r="T98" s="2"/>
+      <c r="U98" s="2"/>
+      <c r="V98" s="2"/>
+      <c r="W98" s="2"/>
     </row>
     <row r="99" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A99" s="9"/>
-      <c r="B99" s="9"/>
-      <c r="C99" s="77"/>
-      <c r="D99" s="9"/>
+      <c r="A99" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C99" s="76" t="s">
+        <v>117</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
@@ -7804,22 +7883,19 @@
       <c r="R99" s="2"/>
       <c r="S99" s="2"/>
       <c r="T99" s="2"/>
-      <c r="U99" s="2"/>
-      <c r="V99" s="2"/>
-      <c r="W99" s="2"/>
     </row>
     <row r="100" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A100" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C100" s="76" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>1031</v>
+        <v>118</v>
+      </c>
+      <c r="B100" s="1">
+        <v>1</v>
+      </c>
+      <c r="C100" s="80">
+        <v>1</v>
+      </c>
+      <c r="D100" s="1">
+        <v>1</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
@@ -7834,22 +7910,19 @@
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
       <c r="Q100" s="2"/>
-      <c r="R100" s="2"/>
-      <c r="S100" s="2"/>
-      <c r="T100" s="2"/>
     </row>
     <row r="101" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A101" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C101" s="76" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>1032</v>
+        <v>119</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C101" s="77" t="s">
+        <v>120</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>120</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
@@ -7870,16 +7943,16 @@
     </row>
     <row r="102" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A102" s="1" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C102" s="76" t="s">
-        <v>1054</v>
+        <v>122</v>
+      </c>
+      <c r="C102" s="81" t="s">
+        <v>123</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
@@ -7894,22 +7967,19 @@
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
       <c r="Q102" s="2"/>
-      <c r="R102" s="2"/>
-      <c r="S102" s="2"/>
-      <c r="T102" s="2"/>
     </row>
     <row r="103" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A103" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C103" s="77" t="s">
-        <v>151</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>151</v>
+      <c r="A103" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C103" s="76" t="s">
+        <v>126</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
@@ -7930,16 +8000,14 @@
     </row>
     <row r="104" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A104" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C104" s="83" t="s">
-        <v>153</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>153</v>
+        <v>127</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C104" s="77"/>
+      <c r="D104" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
@@ -7957,20 +8025,15 @@
       <c r="R104" s="2"/>
       <c r="S104" s="2"/>
       <c r="T104" s="2"/>
+      <c r="U104" s="2"/>
+      <c r="V104" s="2"/>
+      <c r="W104" s="2"/>
     </row>
     <row r="105" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A105" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B105" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C105" s="82" t="s">
-        <v>151</v>
-      </c>
-      <c r="D105" s="11" t="s">
-        <v>151</v>
-      </c>
+      <c r="A105" s="9"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="77"/>
+      <c r="D105" s="9"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
@@ -7987,22 +8050,19 @@
       <c r="R105" s="2"/>
       <c r="S105" s="2"/>
       <c r="T105" s="2"/>
-      <c r="U105" s="2"/>
-      <c r="V105" s="2"/>
-      <c r="W105" s="2"/>
     </row>
     <row r="106" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A106" s="1" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>156</v>
+        <v>1029</v>
       </c>
       <c r="C106" s="76" t="s">
-        <v>156</v>
+        <v>1062</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>156</v>
+        <v>1029</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
@@ -8022,17 +8082,17 @@
       <c r="T106" s="2"/>
     </row>
     <row r="107" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A107" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C107" s="77" t="s">
-        <v>156</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>156</v>
+      <c r="A107" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C107" s="76" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>1030</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
@@ -8047,15 +8107,20 @@
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
       <c r="Q107" s="2"/>
-      <c r="R107" s="2"/>
-      <c r="S107" s="2"/>
-      <c r="T107" s="2"/>
     </row>
     <row r="108" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A108" s="9"/>
-      <c r="B108" s="9"/>
-      <c r="C108" s="77"/>
-      <c r="D108" s="9"/>
+      <c r="A108" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C108" s="76" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -8077,17 +8142,17 @@
       <c r="W108" s="2"/>
     </row>
     <row r="109" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A109" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C109" s="76" t="s">
-        <v>159</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>159</v>
+      <c r="A109" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C109" s="77" t="s">
+        <v>133</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
@@ -8108,16 +8173,16 @@
     </row>
     <row r="110" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A110" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B110" s="1">
-        <v>123</v>
-      </c>
-      <c r="C110" s="80">
-        <v>123</v>
-      </c>
-      <c r="D110" s="1">
-        <v>123</v>
+        <v>134</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C110" s="76" t="s">
+        <v>135</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
@@ -8135,19 +8200,22 @@
       <c r="R110" s="2"/>
       <c r="S110" s="2"/>
       <c r="T110" s="2"/>
+      <c r="U110" s="2"/>
+      <c r="V110" s="2"/>
+      <c r="W110" s="2"/>
     </row>
     <row r="111" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A111" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B111" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C111" s="84" t="s">
-        <v>974</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>162</v>
+      <c r="A111" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C111" s="76" t="s">
+        <v>137</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
@@ -8165,19 +8233,22 @@
       <c r="R111" s="2"/>
       <c r="S111" s="2"/>
       <c r="T111" s="2"/>
+      <c r="U111" s="2"/>
+      <c r="V111" s="2"/>
+      <c r="W111" s="2"/>
     </row>
     <row r="112" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A112" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C112" s="76" t="s">
-        <v>164</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>164</v>
+      <c r="A112" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C112" s="82" t="s">
+        <v>139</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>139</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
@@ -8201,16 +8272,16 @@
     </row>
     <row r="113" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A113" s="1" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="C113" s="76" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
@@ -8234,16 +8305,16 @@
     </row>
     <row r="114" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A114" s="1" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="C114" s="76" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
@@ -8261,22 +8332,19 @@
       <c r="R114" s="2"/>
       <c r="S114" s="2"/>
       <c r="T114" s="2"/>
-      <c r="U114" s="2"/>
-      <c r="V114" s="2"/>
-      <c r="W114" s="2"/>
     </row>
     <row r="115" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A115" s="1" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="C115" s="76" t="s">
-        <v>967</v>
+        <v>145</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
@@ -8294,23 +8362,12 @@
       <c r="R115" s="2"/>
       <c r="S115" s="2"/>
       <c r="T115" s="2"/>
-      <c r="U115" s="2"/>
-      <c r="V115" s="2"/>
-      <c r="W115" s="2"/>
     </row>
     <row r="116" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A116" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C116" s="76" t="s">
-        <v>974</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>162</v>
-      </c>
+      <c r="A116" s="9"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="77"/>
+      <c r="D116" s="9"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -8332,17 +8389,17 @@
       <c r="W116" s="2"/>
     </row>
     <row r="117" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A117" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="B117" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="C117" s="77" t="s">
-        <v>975</v>
-      </c>
-      <c r="D117" s="12" t="s">
-        <v>173</v>
+      <c r="A117" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C117" s="76" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>1031</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
@@ -8360,15 +8417,20 @@
       <c r="R117" s="2"/>
       <c r="S117" s="2"/>
       <c r="T117" s="2"/>
-      <c r="U117" s="2"/>
-      <c r="V117" s="2"/>
-      <c r="W117" s="2"/>
     </row>
     <row r="118" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A118" s="9"/>
-      <c r="B118" s="9"/>
-      <c r="C118" s="77"/>
-      <c r="D118" s="9"/>
+      <c r="A118" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C118" s="76" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>1032</v>
+      </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -8385,22 +8447,19 @@
       <c r="R118" s="2"/>
       <c r="S118" s="2"/>
       <c r="T118" s="2"/>
-      <c r="U118" s="2"/>
-      <c r="V118" s="2"/>
-      <c r="W118" s="2"/>
     </row>
     <row r="119" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A119" s="1" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>1035</v>
+        <v>149</v>
       </c>
       <c r="C119" s="76" t="s">
-        <v>1064</v>
+        <v>1054</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>1035</v>
+        <v>149</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
@@ -8418,22 +8477,19 @@
       <c r="R119" s="2"/>
       <c r="S119" s="2"/>
       <c r="T119" s="2"/>
-      <c r="U119" s="2"/>
-      <c r="V119" s="2"/>
-      <c r="W119" s="2"/>
     </row>
     <row r="120" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A120" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C120" s="76" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>1036</v>
+      <c r="A120" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C120" s="77" t="s">
+        <v>151</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>151</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
@@ -8451,22 +8507,19 @@
       <c r="R120" s="2"/>
       <c r="S120" s="2"/>
       <c r="T120" s="2"/>
-      <c r="U120" s="2"/>
-      <c r="V120" s="2"/>
-      <c r="W120" s="2"/>
     </row>
     <row r="121" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A121" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C121" s="76" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>177</v>
+      <c r="A121" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C121" s="83" t="s">
+        <v>153</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
@@ -8484,22 +8537,19 @@
       <c r="R121" s="2"/>
       <c r="S121" s="2"/>
       <c r="T121" s="2"/>
-      <c r="U121" s="2"/>
-      <c r="V121" s="2"/>
-      <c r="W121" s="2"/>
     </row>
     <row r="122" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A122" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="B122" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C122" s="77" t="s">
-        <v>179</v>
-      </c>
-      <c r="D122" s="9" t="s">
-        <v>179</v>
+      <c r="A122" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B122" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C122" s="82" t="s">
+        <v>151</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>151</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
@@ -8522,17 +8572,17 @@
       <c r="W122" s="2"/>
     </row>
     <row r="123" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A123" s="9" t="s">
-        <v>180</v>
+      <c r="A123" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="C123" s="76" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
@@ -8550,22 +8600,19 @@
       <c r="R123" s="2"/>
       <c r="S123" s="2"/>
       <c r="T123" s="2"/>
-      <c r="U123" s="2"/>
-      <c r="V123" s="2"/>
-      <c r="W123" s="2"/>
     </row>
     <row r="124" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A124" s="9" t="s">
-        <v>182</v>
+      <c r="A124" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="C124" s="77" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
@@ -8583,23 +8630,12 @@
       <c r="R124" s="2"/>
       <c r="S124" s="2"/>
       <c r="T124" s="2"/>
-      <c r="U124" s="2"/>
-      <c r="V124" s="2"/>
-      <c r="W124" s="2"/>
     </row>
     <row r="125" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A125" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C125" s="76" t="s">
-        <v>179</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>179</v>
-      </c>
+      <c r="A125" s="9"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="77"/>
+      <c r="D125" s="9"/>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
@@ -8622,16 +8658,16 @@
     </row>
     <row r="126" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A126" s="1" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="C126" s="76" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
@@ -8649,22 +8685,19 @@
       <c r="R126" s="2"/>
       <c r="S126" s="2"/>
       <c r="T126" s="2"/>
-      <c r="U126" s="2"/>
-      <c r="V126" s="2"/>
-      <c r="W126" s="2"/>
     </row>
     <row r="127" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A127" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C127" s="76" t="s">
-        <v>186</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>186</v>
+        <v>160</v>
+      </c>
+      <c r="B127" s="1">
+        <v>123</v>
+      </c>
+      <c r="C127" s="80">
+        <v>123</v>
+      </c>
+      <c r="D127" s="1">
+        <v>123</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
@@ -8682,15 +8715,20 @@
       <c r="R127" s="2"/>
       <c r="S127" s="2"/>
       <c r="T127" s="2"/>
-      <c r="U127" s="2"/>
-      <c r="V127" s="2"/>
-      <c r="W127" s="2"/>
     </row>
     <row r="128" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A128" s="9"/>
-      <c r="B128" s="9"/>
-      <c r="C128" s="77"/>
-      <c r="D128" s="9"/>
+      <c r="A128" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B128" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C128" s="84" t="s">
+        <v>974</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>162</v>
+      </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
@@ -8707,22 +8745,19 @@
       <c r="R128" s="2"/>
       <c r="S128" s="2"/>
       <c r="T128" s="2"/>
-      <c r="U128" s="2"/>
-      <c r="V128" s="2"/>
-      <c r="W128" s="2"/>
     </row>
     <row r="129" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A129" s="1" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>1261</v>
+        <v>164</v>
       </c>
       <c r="C129" s="76" t="s">
-        <v>1065</v>
+        <v>164</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>1125</v>
+        <v>164</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
@@ -8746,16 +8781,16 @@
     </row>
     <row r="130" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A130" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B130" s="10" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C130" s="85" t="s">
-        <v>976</v>
-      </c>
-      <c r="D130" s="10" t="s">
-        <v>1026</v>
+        <v>165</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C130" s="76" t="s">
+        <v>159</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
@@ -8779,16 +8814,16 @@
     </row>
     <row r="131" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A131" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>1160</v>
+        <v>167</v>
       </c>
       <c r="C131" s="76" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
@@ -8811,10 +8846,18 @@
       <c r="W131" s="2"/>
     </row>
     <row r="132" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A132" s="9"/>
-      <c r="B132" s="9"/>
-      <c r="C132" s="77"/>
-      <c r="D132" s="9"/>
+      <c r="A132" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C132" s="76" t="s">
+        <v>967</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
@@ -8837,16 +8880,16 @@
     </row>
     <row r="133" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A133" s="1" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>1262</v>
+        <v>162</v>
       </c>
       <c r="C133" s="76" t="s">
-        <v>1066</v>
+        <v>974</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>1037</v>
+        <v>162</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
@@ -8869,17 +8912,17 @@
       <c r="W133" s="2"/>
     </row>
     <row r="134" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A134" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C134" s="76" t="s">
-        <v>1058</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>1038</v>
+      <c r="A134" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C134" s="77" t="s">
+        <v>975</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>173</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
@@ -8902,18 +8945,10 @@
       <c r="W134" s="2"/>
     </row>
     <row r="135" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A135" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C135" s="76" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>1033</v>
-      </c>
+      <c r="A135" s="9"/>
+      <c r="B135" s="9"/>
+      <c r="C135" s="77"/>
+      <c r="D135" s="9"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
@@ -8936,16 +8971,16 @@
     </row>
     <row r="136" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A136" s="1" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C136" s="76" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
@@ -8968,10 +9003,18 @@
       <c r="W136" s="2"/>
     </row>
     <row r="137" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A137" s="9"/>
-      <c r="B137" s="9"/>
-      <c r="C137" s="77"/>
-      <c r="D137" s="9"/>
+      <c r="A137" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C137" s="76" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>1036</v>
+      </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
@@ -8994,16 +9037,16 @@
     </row>
     <row r="138" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A138" s="1" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>1019</v>
+        <v>177</v>
       </c>
       <c r="C138" s="76" t="s">
-        <v>1067</v>
+        <v>1056</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>1019</v>
+        <v>177</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
@@ -9026,17 +9069,17 @@
       <c r="W138" s="2"/>
     </row>
     <row r="139" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A139" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C139" s="76" t="s">
-        <v>977</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>199</v>
+      <c r="A139" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C139" s="77" t="s">
+        <v>179</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>179</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
@@ -9059,17 +9102,17 @@
       <c r="W139" s="2"/>
     </row>
     <row r="140" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A140" s="1" t="s">
-        <v>200</v>
+      <c r="A140" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="C140" s="76" t="s">
-        <v>978</v>
+        <v>181</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
@@ -9093,16 +9136,16 @@
     </row>
     <row r="141" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A141" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="B141" s="11" t="s">
-        <v>203</v>
+        <v>182</v>
+      </c>
+      <c r="B141" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="C141" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="D141" s="11" t="s">
-        <v>203</v>
+        <v>183</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
@@ -9125,17 +9168,17 @@
       <c r="W141" s="2"/>
     </row>
     <row r="142" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A142" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B142" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="C142" s="77" t="s">
-        <v>205</v>
-      </c>
-      <c r="D142" s="9" t="s">
-        <v>205</v>
+      <c r="A142" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C142" s="76" t="s">
+        <v>179</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
@@ -9158,17 +9201,17 @@
       <c r="W142" s="2"/>
     </row>
     <row r="143" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A143" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B143" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="C143" s="77" t="s">
-        <v>207</v>
-      </c>
-      <c r="D143" s="9" t="s">
-        <v>207</v>
+      <c r="A143" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C143" s="76" t="s">
+        <v>186</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
@@ -9192,16 +9235,16 @@
     </row>
     <row r="144" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A144" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="C144" s="76" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
@@ -9224,18 +9267,10 @@
       <c r="W144" s="2"/>
     </row>
     <row r="145" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A145" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C145" s="76" t="s">
-        <v>210</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>210</v>
-      </c>
+      <c r="A145" s="9"/>
+      <c r="B145" s="9"/>
+      <c r="C145" s="77"/>
+      <c r="D145" s="9"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
@@ -9257,10 +9292,18 @@
       <c r="W145" s="2"/>
     </row>
     <row r="146" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A146" s="9"/>
-      <c r="B146" s="5"/>
-      <c r="C146" s="78"/>
-      <c r="D146" s="5"/>
+      <c r="A146" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C146" s="76" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>1125</v>
+      </c>
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
@@ -9282,13 +9325,17 @@
       <c r="W146" s="2"/>
     </row>
     <row r="147" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A147" s="7"/>
-      <c r="B147" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="C147" s="77"/>
-      <c r="D147" s="8" t="s">
-        <v>211</v>
+      <c r="A147" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C147" s="85" t="s">
+        <v>976</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>1026</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
@@ -9311,10 +9358,18 @@
       <c r="W147" s="2"/>
     </row>
     <row r="148" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A148" s="9"/>
-      <c r="B148" s="9"/>
-      <c r="C148" s="79"/>
-      <c r="D148" s="9"/>
+      <c r="A148" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C148" s="76" t="s">
+        <v>192</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
@@ -9336,18 +9391,10 @@
       <c r="W148" s="2"/>
     </row>
     <row r="149" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A149" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C149" s="75" t="s">
-        <v>214</v>
-      </c>
-      <c r="D149" s="4" t="s">
-        <v>213</v>
-      </c>
+      <c r="A149" s="9"/>
+      <c r="B149" s="9"/>
+      <c r="C149" s="77"/>
+      <c r="D149" s="9"/>
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
@@ -9370,16 +9417,16 @@
     </row>
     <row r="150" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A150" s="1" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>7</v>
+        <v>1259</v>
       </c>
       <c r="C150" s="76" t="s">
-        <v>7</v>
+        <v>1066</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>7</v>
+        <v>1037</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
@@ -9403,16 +9450,16 @@
     </row>
     <row r="151" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A151" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>1076</v>
+        <v>1038</v>
       </c>
       <c r="C151" s="76" t="s">
-        <v>1131</v>
+        <v>1058</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>1076</v>
+        <v>1038</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
@@ -9435,17 +9482,17 @@
       <c r="W151" s="2"/>
     </row>
     <row r="152" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A152" s="13" t="s">
-        <v>218</v>
+      <c r="A152" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>1076</v>
+        <v>1033</v>
       </c>
       <c r="C152" s="76" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>1076</v>
+        <v>1033</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
@@ -9469,16 +9516,16 @@
     </row>
     <row r="153" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A153" s="1" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>220</v>
+        <v>1034</v>
       </c>
       <c r="C153" s="76" t="s">
-        <v>220</v>
+        <v>1057</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>220</v>
+        <v>1034</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
@@ -9501,18 +9548,10 @@
       <c r="W153" s="2"/>
     </row>
     <row r="154" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A154" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C154" s="76" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>1025</v>
-      </c>
+      <c r="A154" s="9"/>
+      <c r="B154" s="9"/>
+      <c r="C154" s="77"/>
+      <c r="D154" s="9"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
@@ -9535,16 +9574,16 @@
     </row>
     <row r="155" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A155" s="1" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>224</v>
+        <v>1019</v>
       </c>
       <c r="C155" s="76" t="s">
-        <v>224</v>
+        <v>1067</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>224</v>
+        <v>1019</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
@@ -9568,82 +9607,82 @@
     </row>
     <row r="156" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A156" s="1" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="C156" s="76" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E156" s="14"/>
-      <c r="F156" s="14"/>
-      <c r="G156" s="14"/>
-      <c r="H156" s="14"/>
-      <c r="I156" s="14"/>
-      <c r="J156" s="14"/>
-      <c r="K156" s="14"/>
-      <c r="L156" s="14"/>
-      <c r="M156" s="14"/>
-      <c r="N156" s="14"/>
-      <c r="O156" s="14"/>
-      <c r="P156" s="14"/>
-      <c r="Q156" s="14"/>
-      <c r="R156" s="14"/>
-      <c r="S156" s="14"/>
-      <c r="T156" s="14"/>
-      <c r="U156" s="14"/>
-      <c r="V156" s="14"/>
-      <c r="W156" s="14"/>
+        <v>199</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
+      <c r="G156" s="2"/>
+      <c r="H156" s="2"/>
+      <c r="I156" s="2"/>
+      <c r="J156" s="2"/>
+      <c r="K156" s="2"/>
+      <c r="L156" s="2"/>
+      <c r="M156" s="2"/>
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
+      <c r="P156" s="2"/>
+      <c r="Q156" s="2"/>
+      <c r="R156" s="2"/>
+      <c r="S156" s="2"/>
+      <c r="T156" s="2"/>
+      <c r="U156" s="2"/>
+      <c r="V156" s="2"/>
+      <c r="W156" s="2"/>
     </row>
     <row r="157" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A157" s="1" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C157" s="86" t="s">
-        <v>980</v>
+        <v>201</v>
+      </c>
+      <c r="C157" s="76" t="s">
+        <v>978</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E157" s="14"/>
-      <c r="F157" s="14"/>
-      <c r="G157" s="14"/>
-      <c r="H157" s="14"/>
-      <c r="I157" s="14"/>
-      <c r="J157" s="14"/>
-      <c r="K157" s="14"/>
-      <c r="L157" s="14"/>
-      <c r="M157" s="14"/>
-      <c r="N157" s="14"/>
-      <c r="O157" s="14"/>
-      <c r="P157" s="14"/>
-      <c r="Q157" s="14"/>
-      <c r="R157" s="14"/>
-      <c r="S157" s="14"/>
-      <c r="T157" s="14"/>
-      <c r="U157" s="14"/>
-      <c r="V157" s="14"/>
-      <c r="W157" s="14"/>
+        <v>201</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" s="2"/>
+      <c r="G157" s="2"/>
+      <c r="H157" s="2"/>
+      <c r="I157" s="2"/>
+      <c r="J157" s="2"/>
+      <c r="K157" s="2"/>
+      <c r="L157" s="2"/>
+      <c r="M157" s="2"/>
+      <c r="N157" s="2"/>
+      <c r="O157" s="2"/>
+      <c r="P157" s="2"/>
+      <c r="Q157" s="2"/>
+      <c r="R157" s="2"/>
+      <c r="S157" s="2"/>
+      <c r="T157" s="2"/>
+      <c r="U157" s="2"/>
+      <c r="V157" s="2"/>
+      <c r="W157" s="2"/>
     </row>
     <row r="158" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A158" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B158" s="15" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C158" s="87" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D158" s="15" t="s">
-        <v>1077</v>
+      <c r="A158" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C158" s="77" t="s">
+        <v>203</v>
+      </c>
+      <c r="D158" s="11" t="s">
+        <v>203</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
@@ -9666,17 +9705,17 @@
       <c r="W158" s="2"/>
     </row>
     <row r="159" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A159" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C159" s="76" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>1078</v>
+      <c r="A159" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C159" s="77" t="s">
+        <v>205</v>
+      </c>
+      <c r="D159" s="9" t="s">
+        <v>205</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
@@ -9699,17 +9738,17 @@
       <c r="W159" s="2"/>
     </row>
     <row r="160" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A160" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C160" s="76" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>1079</v>
+      <c r="A160" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B160" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C160" s="77" t="s">
+        <v>207</v>
+      </c>
+      <c r="D160" s="9" t="s">
+        <v>207</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
@@ -9733,16 +9772,16 @@
     </row>
     <row r="161" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A161" s="1" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="C161" s="76" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
@@ -9766,16 +9805,16 @@
     </row>
     <row r="162" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A162" s="1" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>1080</v>
+        <v>210</v>
       </c>
       <c r="C162" s="76" t="s">
-        <v>1136</v>
+        <v>210</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>1080</v>
+        <v>210</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
@@ -9798,18 +9837,10 @@
       <c r="W162" s="2"/>
     </row>
     <row r="163" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A163" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C163" s="76" t="s">
-        <v>237</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>237</v>
-      </c>
+      <c r="A163" s="9"/>
+      <c r="B163" s="5"/>
+      <c r="C163" s="78"/>
+      <c r="D163" s="5"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
@@ -9831,17 +9862,13 @@
       <c r="W163" s="2"/>
     </row>
     <row r="164" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A164" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C164" s="76" t="s">
-        <v>240</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>239</v>
+      <c r="A164" s="7"/>
+      <c r="B164" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C164" s="77"/>
+      <c r="D164" s="8" t="s">
+        <v>211</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
@@ -9866,7 +9893,7 @@
     <row r="165" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A165" s="9"/>
       <c r="B165" s="9"/>
-      <c r="C165" s="84"/>
+      <c r="C165" s="79"/>
       <c r="D165" s="9"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
@@ -9889,10 +9916,18 @@
       <c r="W165" s="2"/>
     </row>
     <row r="166" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A166" s="9"/>
-      <c r="B166" s="9"/>
-      <c r="C166" s="84"/>
-      <c r="D166" s="9"/>
+      <c r="A166" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C166" s="75" t="s">
+        <v>214</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>213</v>
+      </c>
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
@@ -9914,15 +9949,17 @@
       <c r="W166" s="2"/>
     </row>
     <row r="167" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A167" s="9" t="s">
-        <v>981</v>
-      </c>
-      <c r="B167" s="9" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C167" s="84"/>
-      <c r="D167" s="9" t="s">
-        <v>1081</v>
+      <c r="A167" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" s="76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
@@ -9945,15 +9982,17 @@
       <c r="W167" s="2"/>
     </row>
     <row r="168" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A168" s="9" t="s">
-        <v>982</v>
-      </c>
-      <c r="B168" s="9" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C168" s="84"/>
-      <c r="D168" s="9" t="s">
-        <v>1073</v>
+      <c r="A168" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C168" s="76" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>1076</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
@@ -9975,16 +10014,18 @@
       <c r="V168" s="2"/>
       <c r="W168" s="2"/>
     </row>
-    <row r="169" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A169" s="16" t="s">
-        <v>983</v>
-      </c>
-      <c r="B169" s="16" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C169" s="88"/>
-      <c r="D169" s="16" t="s">
-        <v>1074</v>
+    <row r="169" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A169" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C169" s="76" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>1076</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
@@ -10006,11 +10047,19 @@
       <c r="V169" s="2"/>
       <c r="W169" s="2"/>
     </row>
-    <row r="170" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A170" s="16"/>
-      <c r="B170" s="2"/>
-      <c r="C170" s="88"/>
-      <c r="D170" s="2"/>
+    <row r="170" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A170" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C170" s="76" t="s">
+        <v>220</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
@@ -10031,11 +10080,19 @@
       <c r="V170" s="2"/>
       <c r="W170" s="2"/>
     </row>
-    <row r="171" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A171" s="52"/>
-      <c r="B171" s="2"/>
-      <c r="C171" s="79"/>
-      <c r="D171" s="2"/>
+    <row r="171" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A171" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C171" s="76" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>1025</v>
+      </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
@@ -10056,9 +10113,19 @@
       <c r="V171" s="2"/>
       <c r="W171" s="2"/>
     </row>
-    <row r="172" spans="1:23" ht="13.5" customHeight="1">
-      <c r="C172" s="79"/>
-      <c r="D172" s="2"/>
+    <row r="172" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A172" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C172" s="76" t="s">
+        <v>224</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
@@ -10079,58 +10146,85 @@
       <c r="V172" s="2"/>
       <c r="W172" s="2"/>
     </row>
-    <row r="173" spans="1:23" ht="13.5" customHeight="1">
-      <c r="C173" s="79"/>
-      <c r="D173" s="2"/>
-      <c r="E173" s="2"/>
-      <c r="F173" s="2"/>
-      <c r="G173" s="2"/>
-      <c r="H173" s="2"/>
-      <c r="I173" s="2"/>
-      <c r="J173" s="2"/>
-      <c r="K173" s="2"/>
-      <c r="L173" s="2"/>
-      <c r="M173" s="2"/>
-      <c r="N173" s="2"/>
-      <c r="O173" s="2"/>
-      <c r="P173" s="2"/>
-      <c r="Q173" s="2"/>
-      <c r="R173" s="2"/>
-      <c r="S173" s="2"/>
-      <c r="T173" s="2"/>
-      <c r="U173" s="2"/>
-      <c r="V173" s="2"/>
-      <c r="W173" s="2"/>
-    </row>
-    <row r="174" spans="1:23" ht="13.5" customHeight="1">
-      <c r="B174" s="55"/>
-      <c r="C174" s="79"/>
-      <c r="D174" s="2"/>
-      <c r="E174" s="2"/>
-      <c r="F174" s="2"/>
-      <c r="G174" s="2"/>
-      <c r="H174" s="2"/>
-      <c r="I174" s="2"/>
-      <c r="J174" s="2"/>
-      <c r="K174" s="2"/>
-      <c r="L174" s="2"/>
-      <c r="M174" s="2"/>
-      <c r="N174" s="2"/>
-      <c r="O174" s="2"/>
-      <c r="P174" s="2"/>
-      <c r="Q174" s="2"/>
-      <c r="R174" s="2"/>
-      <c r="S174" s="2"/>
-      <c r="T174" s="2"/>
-      <c r="U174" s="2"/>
-      <c r="V174" s="2"/>
-      <c r="W174" s="2"/>
-    </row>
-    <row r="175" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A175" s="54"/>
-      <c r="B175" s="55"/>
-      <c r="C175" s="79"/>
-      <c r="D175" s="2"/>
+    <row r="173" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A173" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C173" s="76" t="s">
+        <v>979</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E173" s="14"/>
+      <c r="F173" s="14"/>
+      <c r="G173" s="14"/>
+      <c r="H173" s="14"/>
+      <c r="I173" s="14"/>
+      <c r="J173" s="14"/>
+      <c r="K173" s="14"/>
+      <c r="L173" s="14"/>
+      <c r="M173" s="14"/>
+      <c r="N173" s="14"/>
+      <c r="O173" s="14"/>
+      <c r="P173" s="14"/>
+      <c r="Q173" s="14"/>
+      <c r="R173" s="14"/>
+      <c r="S173" s="14"/>
+      <c r="T173" s="14"/>
+      <c r="U173" s="14"/>
+      <c r="V173" s="14"/>
+      <c r="W173" s="14"/>
+    </row>
+    <row r="174" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A174" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C174" s="86" t="s">
+        <v>980</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E174" s="14"/>
+      <c r="F174" s="14"/>
+      <c r="G174" s="14"/>
+      <c r="H174" s="14"/>
+      <c r="I174" s="14"/>
+      <c r="J174" s="14"/>
+      <c r="K174" s="14"/>
+      <c r="L174" s="14"/>
+      <c r="M174" s="14"/>
+      <c r="N174" s="14"/>
+      <c r="O174" s="14"/>
+      <c r="P174" s="14"/>
+      <c r="Q174" s="14"/>
+      <c r="R174" s="14"/>
+      <c r="S174" s="14"/>
+      <c r="T174" s="14"/>
+      <c r="U174" s="14"/>
+      <c r="V174" s="14"/>
+      <c r="W174" s="14"/>
+    </row>
+    <row r="175" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A175" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B175" s="15" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C175" s="87" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D175" s="15" t="s">
+        <v>1077</v>
+      </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
@@ -10151,9 +10245,19 @@
       <c r="V175" s="2"/>
       <c r="W175" s="2"/>
     </row>
-    <row r="176" spans="1:23" ht="13.5" customHeight="1">
-      <c r="C176" s="79"/>
-      <c r="D176" s="2"/>
+    <row r="176" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A176" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C176" s="76" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>1078</v>
+      </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
@@ -10174,10 +10278,19 @@
       <c r="V176" s="2"/>
       <c r="W176" s="2"/>
     </row>
-    <row r="177" spans="2:23" ht="13.5" customHeight="1">
-      <c r="B177" s="55"/>
-      <c r="C177" s="89"/>
-      <c r="D177" s="2"/>
+    <row r="177" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A177" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C177" s="76" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>1079</v>
+      </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
@@ -10198,10 +10311,19 @@
       <c r="V177" s="2"/>
       <c r="W177" s="2"/>
     </row>
-    <row r="178" spans="2:23" ht="13.5" customHeight="1">
-      <c r="B178" s="55"/>
-      <c r="C178" s="89"/>
-      <c r="D178" s="2"/>
+    <row r="178" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A178" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C178" s="76" t="s">
+        <v>234</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>234</v>
+      </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
@@ -10222,9 +10344,19 @@
       <c r="V178" s="2"/>
       <c r="W178" s="2"/>
     </row>
-    <row r="179" spans="2:23" ht="13.5" customHeight="1">
-      <c r="C179" s="79"/>
-      <c r="D179" s="2"/>
+    <row r="179" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A179" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C179" s="76" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>1080</v>
+      </c>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
@@ -10245,10 +10377,19 @@
       <c r="V179" s="2"/>
       <c r="W179" s="2"/>
     </row>
-    <row r="180" spans="2:23" ht="13.5" customHeight="1">
-      <c r="B180" s="55"/>
-      <c r="C180" s="79"/>
-      <c r="D180" s="2"/>
+    <row r="180" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A180" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C180" s="76" t="s">
+        <v>237</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>237</v>
+      </c>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
@@ -10269,10 +10410,19 @@
       <c r="V180" s="2"/>
       <c r="W180" s="2"/>
     </row>
-    <row r="181" spans="2:23" ht="13.5" customHeight="1">
-      <c r="B181" s="55"/>
-      <c r="C181" s="79"/>
-      <c r="D181" s="2"/>
+    <row r="181" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A181" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C181" s="76" t="s">
+        <v>240</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
@@ -10293,10 +10443,11 @@
       <c r="V181" s="2"/>
       <c r="W181" s="2"/>
     </row>
-    <row r="182" spans="2:23" ht="13.5" customHeight="1">
-      <c r="B182" s="55"/>
-      <c r="C182" s="79"/>
-      <c r="D182" s="2"/>
+    <row r="182" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A182" s="9"/>
+      <c r="B182" s="9"/>
+      <c r="C182" s="84"/>
+      <c r="D182" s="9"/>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
@@ -10317,9 +10468,11 @@
       <c r="V182" s="2"/>
       <c r="W182" s="2"/>
     </row>
-    <row r="183" spans="2:23" ht="13.5" customHeight="1">
-      <c r="C183" s="79"/>
-      <c r="D183" s="2"/>
+    <row r="183" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A183" s="9"/>
+      <c r="B183" s="9"/>
+      <c r="C183" s="84"/>
+      <c r="D183" s="9"/>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
@@ -10340,10 +10493,17 @@
       <c r="V183" s="2"/>
       <c r="W183" s="2"/>
     </row>
-    <row r="184" spans="2:23" ht="13.5" customHeight="1">
-      <c r="B184" s="55"/>
-      <c r="C184" s="79"/>
-      <c r="D184" s="2"/>
+    <row r="184" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A184" s="9" t="s">
+        <v>981</v>
+      </c>
+      <c r="B184" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C184" s="55"/>
+      <c r="D184" s="9" t="s">
+        <v>1081</v>
+      </c>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
@@ -10364,9 +10524,17 @@
       <c r="V184" s="2"/>
       <c r="W184" s="2"/>
     </row>
-    <row r="185" spans="2:23" ht="13.5" customHeight="1">
-      <c r="C185" s="79"/>
-      <c r="D185" s="2"/>
+    <row r="185" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A185" s="9" t="s">
+        <v>982</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C185"/>
+      <c r="D185" s="9" t="s">
+        <v>1073</v>
+      </c>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
@@ -10387,9 +10555,17 @@
       <c r="V185" s="2"/>
       <c r="W185" s="2"/>
     </row>
-    <row r="186" spans="2:23" ht="13.5" customHeight="1">
-      <c r="C186" s="79"/>
-      <c r="D186" s="2"/>
+    <row r="186" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A186" s="16" t="s">
+        <v>983</v>
+      </c>
+      <c r="B186" s="16" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C186" s="55"/>
+      <c r="D186" s="16" t="s">
+        <v>1074</v>
+      </c>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
@@ -10410,8 +10586,10 @@
       <c r="V186" s="2"/>
       <c r="W186" s="2"/>
     </row>
-    <row r="187" spans="2:23" ht="13.5" customHeight="1">
-      <c r="C187" s="79"/>
+    <row r="187" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A187" s="16"/>
+      <c r="B187" s="2"/>
+      <c r="C187" s="55"/>
       <c r="D187" s="2"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
@@ -10433,8 +10611,10 @@
       <c r="V187" s="2"/>
       <c r="W187" s="2"/>
     </row>
-    <row r="188" spans="2:23" ht="13.5" customHeight="1">
-      <c r="C188" s="79"/>
+    <row r="188" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A188" s="52"/>
+      <c r="B188" s="2"/>
+      <c r="C188"/>
       <c r="D188" s="2"/>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
@@ -10456,8 +10636,14 @@
       <c r="V188" s="2"/>
       <c r="W188" s="2"/>
     </row>
-    <row r="189" spans="2:23" ht="13.5" customHeight="1">
-      <c r="C189" s="79"/>
+    <row r="189" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A189" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C189" s="55"/>
       <c r="D189" s="2"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
@@ -10479,8 +10665,14 @@
       <c r="V189" s="2"/>
       <c r="W189" s="2"/>
     </row>
-    <row r="190" spans="2:23" ht="13.5" customHeight="1">
-      <c r="C190" s="79"/>
+    <row r="190" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A190" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C190" s="55"/>
       <c r="D190" s="2"/>
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
@@ -10502,8 +10694,9 @@
       <c r="V190" s="2"/>
       <c r="W190" s="2"/>
     </row>
-    <row r="191" spans="2:23" ht="13.5" customHeight="1">
-      <c r="C191" s="79"/>
+    <row r="191" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B191" s="55"/>
+      <c r="C191" s="55"/>
       <c r="D191" s="2"/>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
@@ -10525,8 +10718,14 @@
       <c r="V191" s="2"/>
       <c r="W191" s="2"/>
     </row>
-    <row r="192" spans="2:23" ht="13.5" customHeight="1">
-      <c r="C192" s="79"/>
+    <row r="192" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A192" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C192"/>
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
@@ -10548,8 +10747,14 @@
       <c r="V192" s="2"/>
       <c r="W192" s="2"/>
     </row>
-    <row r="193" spans="1:23" ht="13.5" customHeight="1">
-      <c r="C193" s="79"/>
+    <row r="193" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A193" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C193" s="55"/>
       <c r="D193" s="2"/>
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
@@ -10571,10 +10776,9 @@
       <c r="V193" s="2"/>
       <c r="W193" s="2"/>
     </row>
-    <row r="194" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A194" s="16"/>
-      <c r="B194" s="16"/>
-      <c r="C194" s="88"/>
+    <row r="194" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B194" s="55"/>
+      <c r="C194"/>
       <c r="D194" s="2"/>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
@@ -10596,10 +10800,16 @@
       <c r="V194" s="2"/>
       <c r="W194" s="2"/>
     </row>
-    <row r="195" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A195" s="16"/>
-      <c r="B195" s="16"/>
-      <c r="C195" s="88"/>
+    <row r="195" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A195" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C195" s="76" t="s">
+        <v>1127</v>
+      </c>
       <c r="D195" s="2"/>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
@@ -10621,10 +10831,16 @@
       <c r="V195" s="2"/>
       <c r="W195" s="2"/>
     </row>
-    <row r="196" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A196" s="16"/>
-      <c r="B196" s="16"/>
-      <c r="C196" s="88"/>
+    <row r="196" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A196" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C196" s="76" t="s">
+        <v>13</v>
+      </c>
       <c r="D196" s="2"/>
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
@@ -10646,10 +10862,16 @@
       <c r="V196" s="2"/>
       <c r="W196" s="2"/>
     </row>
-    <row r="197" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A197" s="17"/>
-      <c r="B197" s="17"/>
-      <c r="C197" s="90"/>
+    <row r="197" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A197" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C197" s="76" t="s">
+        <v>38</v>
+      </c>
       <c r="D197" s="2"/>
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
@@ -10671,10 +10893,16 @@
       <c r="V197" s="2"/>
       <c r="W197" s="2"/>
     </row>
-    <row r="198" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A198" s="17"/>
-      <c r="B198" s="17"/>
-      <c r="C198" s="90"/>
+    <row r="198" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A198" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C198" s="76" t="s">
+        <v>40</v>
+      </c>
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
@@ -10696,10 +10924,9 @@
       <c r="V198" s="2"/>
       <c r="W198" s="2"/>
     </row>
-    <row r="199" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A199" s="16"/>
-      <c r="B199" s="16"/>
-      <c r="C199" s="88"/>
+    <row r="199" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B199" s="55"/>
+      <c r="C199" s="55"/>
       <c r="D199" s="2"/>
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
@@ -10721,10 +10948,16 @@
       <c r="V199" s="2"/>
       <c r="W199" s="2"/>
     </row>
-    <row r="200" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A200" s="16"/>
-      <c r="B200" s="16"/>
-      <c r="C200" s="88"/>
+    <row r="200" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A200" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C200" s="76" t="s">
+        <v>1127</v>
+      </c>
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
@@ -10746,10 +10979,16 @@
       <c r="V200" s="2"/>
       <c r="W200" s="2"/>
     </row>
-    <row r="201" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A201" s="16"/>
-      <c r="B201" s="16"/>
-      <c r="C201" s="88"/>
+    <row r="201" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A201" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C201" s="76" t="s">
+        <v>13</v>
+      </c>
       <c r="D201" s="2"/>
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
@@ -10771,10 +11010,16 @@
       <c r="V201" s="2"/>
       <c r="W201" s="2"/>
     </row>
-    <row r="202" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A202" s="16"/>
-      <c r="B202" s="16"/>
-      <c r="C202" s="88"/>
+    <row r="202" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A202" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C202" s="76" t="s">
+        <v>38</v>
+      </c>
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
@@ -10796,10 +11041,16 @@
       <c r="V202" s="2"/>
       <c r="W202" s="2"/>
     </row>
-    <row r="203" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A203" s="16"/>
-      <c r="B203" s="16"/>
-      <c r="C203" s="88"/>
+    <row r="203" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A203" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C203" s="76" t="s">
+        <v>40</v>
+      </c>
       <c r="D203" s="2"/>
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
@@ -10822,9 +11073,7 @@
       <c r="W203" s="2"/>
     </row>
     <row r="204" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A204" s="16"/>
-      <c r="B204" s="16"/>
-      <c r="C204" s="88"/>
+      <c r="C204" s="79"/>
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
@@ -10847,9 +11096,7 @@
       <c r="W204" s="2"/>
     </row>
     <row r="205" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A205" s="16"/>
-      <c r="B205" s="16"/>
-      <c r="C205" s="88"/>
+      <c r="C205" s="79"/>
       <c r="D205" s="2"/>
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
@@ -10872,9 +11119,7 @@
       <c r="W205" s="2"/>
     </row>
     <row r="206" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A206" s="16"/>
-      <c r="B206" s="16"/>
-      <c r="C206" s="88"/>
+      <c r="C206" s="79"/>
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
@@ -10897,9 +11142,7 @@
       <c r="W206" s="2"/>
     </row>
     <row r="207" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A207" s="18"/>
-      <c r="B207" s="18"/>
-      <c r="C207" s="91"/>
+      <c r="C207" s="79"/>
       <c r="D207" s="2"/>
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
@@ -10922,9 +11165,7 @@
       <c r="W207" s="2"/>
     </row>
     <row r="208" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A208" s="18"/>
-      <c r="B208" s="18"/>
-      <c r="C208" s="91"/>
+      <c r="C208" s="79"/>
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
@@ -10947,9 +11188,7 @@
       <c r="W208" s="2"/>
     </row>
     <row r="209" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A209" s="18"/>
-      <c r="B209" s="18"/>
-      <c r="C209" s="91"/>
+      <c r="C209" s="79"/>
       <c r="D209" s="2"/>
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
@@ -10972,9 +11211,7 @@
       <c r="W209" s="2"/>
     </row>
     <row r="210" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A210" s="16"/>
-      <c r="B210" s="16"/>
-      <c r="C210" s="88"/>
+      <c r="C210" s="79"/>
       <c r="D210" s="2"/>
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
@@ -10997,9 +11234,9 @@
       <c r="W210" s="2"/>
     </row>
     <row r="211" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A211" s="18"/>
-      <c r="B211" s="18"/>
-      <c r="C211" s="91"/>
+      <c r="A211" s="16"/>
+      <c r="B211" s="16"/>
+      <c r="C211" s="88"/>
       <c r="D211" s="2"/>
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
@@ -11022,9 +11259,9 @@
       <c r="W211" s="2"/>
     </row>
     <row r="212" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A212" s="18"/>
-      <c r="B212" s="18"/>
-      <c r="C212" s="91"/>
+      <c r="A212" s="16"/>
+      <c r="B212" s="16"/>
+      <c r="C212" s="88"/>
       <c r="D212" s="2"/>
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
@@ -11047,9 +11284,9 @@
       <c r="W212" s="2"/>
     </row>
     <row r="213" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A213" s="18"/>
-      <c r="B213" s="18"/>
-      <c r="C213" s="91"/>
+      <c r="A213" s="16"/>
+      <c r="B213" s="16"/>
+      <c r="C213" s="88"/>
       <c r="D213" s="2"/>
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
@@ -11072,9 +11309,9 @@
       <c r="W213" s="2"/>
     </row>
     <row r="214" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A214" s="18"/>
-      <c r="B214" s="18"/>
-      <c r="C214" s="91"/>
+      <c r="A214" s="17"/>
+      <c r="B214" s="17"/>
+      <c r="C214" s="89"/>
       <c r="D214" s="2"/>
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
@@ -11097,9 +11334,9 @@
       <c r="W214" s="2"/>
     </row>
     <row r="215" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A215" s="18"/>
-      <c r="B215" s="18"/>
-      <c r="C215" s="91"/>
+      <c r="A215" s="17"/>
+      <c r="B215" s="17"/>
+      <c r="C215" s="89"/>
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
@@ -11122,9 +11359,9 @@
       <c r="W215" s="2"/>
     </row>
     <row r="216" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A216" s="18"/>
-      <c r="B216" s="18"/>
-      <c r="C216" s="91"/>
+      <c r="A216" s="16"/>
+      <c r="B216" s="16"/>
+      <c r="C216" s="88"/>
       <c r="D216" s="2"/>
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
@@ -11147,9 +11384,9 @@
       <c r="W216" s="2"/>
     </row>
     <row r="217" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A217" s="18"/>
-      <c r="B217" s="18"/>
-      <c r="C217" s="91"/>
+      <c r="A217" s="16"/>
+      <c r="B217" s="16"/>
+      <c r="C217" s="88"/>
       <c r="D217" s="2"/>
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
@@ -11172,9 +11409,9 @@
       <c r="W217" s="2"/>
     </row>
     <row r="218" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A218" s="18"/>
-      <c r="B218" s="18"/>
-      <c r="C218" s="91"/>
+      <c r="A218" s="16"/>
+      <c r="B218" s="16"/>
+      <c r="C218" s="88"/>
       <c r="D218" s="2"/>
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
@@ -11197,9 +11434,9 @@
       <c r="W218" s="2"/>
     </row>
     <row r="219" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A219" s="18"/>
-      <c r="B219" s="18"/>
-      <c r="C219" s="91"/>
+      <c r="A219" s="16"/>
+      <c r="B219" s="16"/>
+      <c r="C219" s="88"/>
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
@@ -11222,9 +11459,9 @@
       <c r="W219" s="2"/>
     </row>
     <row r="220" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A220" s="18"/>
-      <c r="B220" s="18"/>
-      <c r="C220" s="91"/>
+      <c r="A220" s="16"/>
+      <c r="B220" s="16"/>
+      <c r="C220" s="88"/>
       <c r="D220" s="2"/>
       <c r="E220" s="2"/>
       <c r="F220" s="2"/>
@@ -11247,9 +11484,9 @@
       <c r="W220" s="2"/>
     </row>
     <row r="221" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A221" s="18"/>
-      <c r="B221" s="18"/>
-      <c r="C221" s="91"/>
+      <c r="A221" s="16"/>
+      <c r="B221" s="16"/>
+      <c r="C221" s="88"/>
       <c r="D221" s="2"/>
       <c r="E221" s="2"/>
       <c r="F221" s="2"/>
@@ -11272,9 +11509,9 @@
       <c r="W221" s="2"/>
     </row>
     <row r="222" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A222" s="18"/>
-      <c r="B222" s="18"/>
-      <c r="C222" s="91"/>
+      <c r="A222" s="16"/>
+      <c r="B222" s="16"/>
+      <c r="C222" s="88"/>
       <c r="D222" s="2"/>
       <c r="E222" s="2"/>
       <c r="F222" s="2"/>
@@ -11297,9 +11534,9 @@
       <c r="W222" s="2"/>
     </row>
     <row r="223" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A223" s="18"/>
-      <c r="B223" s="18"/>
-      <c r="C223" s="91"/>
+      <c r="A223" s="16"/>
+      <c r="B223" s="16"/>
+      <c r="C223" s="88"/>
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
       <c r="F223" s="2"/>
@@ -11324,7 +11561,7 @@
     <row r="224" spans="1:23" ht="13.5" customHeight="1">
       <c r="A224" s="18"/>
       <c r="B224" s="18"/>
-      <c r="C224" s="91"/>
+      <c r="C224" s="90"/>
       <c r="D224" s="2"/>
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
@@ -11349,7 +11586,7 @@
     <row r="225" spans="1:23" ht="13.5" customHeight="1">
       <c r="A225" s="18"/>
       <c r="B225" s="18"/>
-      <c r="C225" s="91"/>
+      <c r="C225" s="90"/>
       <c r="D225" s="2"/>
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
@@ -11374,7 +11611,7 @@
     <row r="226" spans="1:23" ht="13.5" customHeight="1">
       <c r="A226" s="18"/>
       <c r="B226" s="18"/>
-      <c r="C226" s="91"/>
+      <c r="C226" s="90"/>
       <c r="D226" s="2"/>
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
@@ -11397,9 +11634,9 @@
       <c r="W226" s="2"/>
     </row>
     <row r="227" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A227" s="18"/>
-      <c r="B227" s="18"/>
-      <c r="C227" s="91"/>
+      <c r="A227" s="16"/>
+      <c r="B227" s="16"/>
+      <c r="C227" s="88"/>
       <c r="D227" s="2"/>
       <c r="E227" s="2"/>
       <c r="F227" s="2"/>
@@ -11424,7 +11661,7 @@
     <row r="228" spans="1:23" ht="13.5" customHeight="1">
       <c r="A228" s="18"/>
       <c r="B228" s="18"/>
-      <c r="C228" s="91"/>
+      <c r="C228" s="90"/>
       <c r="D228" s="2"/>
       <c r="E228" s="2"/>
       <c r="F228" s="2"/>
@@ -11449,7 +11686,7 @@
     <row r="229" spans="1:23" ht="13.5" customHeight="1">
       <c r="A229" s="18"/>
       <c r="B229" s="18"/>
-      <c r="C229" s="91"/>
+      <c r="C229" s="90"/>
       <c r="D229" s="2"/>
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
@@ -11472,8 +11709,8 @@
       <c r="W229" s="2"/>
     </row>
     <row r="230" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A230" s="17"/>
-      <c r="B230" s="17"/>
+      <c r="A230" s="18"/>
+      <c r="B230" s="18"/>
       <c r="C230" s="90"/>
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
@@ -11497,8 +11734,8 @@
       <c r="W230" s="2"/>
     </row>
     <row r="231" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A231" s="17"/>
-      <c r="B231" s="17"/>
+      <c r="A231" s="18"/>
+      <c r="B231" s="18"/>
       <c r="C231" s="90"/>
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
@@ -11522,8 +11759,8 @@
       <c r="W231" s="2"/>
     </row>
     <row r="232" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A232" s="17"/>
-      <c r="B232" s="17"/>
+      <c r="A232" s="18"/>
+      <c r="B232" s="18"/>
       <c r="C232" s="90"/>
       <c r="D232" s="2"/>
       <c r="E232" s="2"/>
@@ -11547,8 +11784,8 @@
       <c r="W232" s="2"/>
     </row>
     <row r="233" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A233" s="17"/>
-      <c r="B233" s="17"/>
+      <c r="A233" s="18"/>
+      <c r="B233" s="18"/>
       <c r="C233" s="90"/>
       <c r="D233" s="2"/>
       <c r="E233" s="2"/>
@@ -11572,8 +11809,8 @@
       <c r="W233" s="2"/>
     </row>
     <row r="234" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A234" s="17"/>
-      <c r="B234" s="17"/>
+      <c r="A234" s="18"/>
+      <c r="B234" s="18"/>
       <c r="C234" s="90"/>
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
@@ -11597,8 +11834,8 @@
       <c r="W234" s="2"/>
     </row>
     <row r="235" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A235" s="17"/>
-      <c r="B235" s="17"/>
+      <c r="A235" s="18"/>
+      <c r="B235" s="18"/>
       <c r="C235" s="90"/>
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
@@ -11622,8 +11859,8 @@
       <c r="W235" s="2"/>
     </row>
     <row r="236" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A236" s="17"/>
-      <c r="B236" s="17"/>
+      <c r="A236" s="18"/>
+      <c r="B236" s="18"/>
       <c r="C236" s="90"/>
       <c r="D236" s="2"/>
       <c r="E236" s="2"/>
@@ -11647,8 +11884,8 @@
       <c r="W236" s="2"/>
     </row>
     <row r="237" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A237" s="17"/>
-      <c r="B237" s="17"/>
+      <c r="A237" s="18"/>
+      <c r="B237" s="18"/>
       <c r="C237" s="90"/>
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
@@ -11672,8 +11909,8 @@
       <c r="W237" s="2"/>
     </row>
     <row r="238" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A238" s="17"/>
-      <c r="B238" s="17"/>
+      <c r="A238" s="18"/>
+      <c r="B238" s="18"/>
       <c r="C238" s="90"/>
       <c r="D238" s="2"/>
       <c r="E238" s="2"/>
@@ -11697,8 +11934,8 @@
       <c r="W238" s="2"/>
     </row>
     <row r="239" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A239" s="17"/>
-      <c r="B239" s="17"/>
+      <c r="A239" s="18"/>
+      <c r="B239" s="18"/>
       <c r="C239" s="90"/>
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
@@ -11722,8 +11959,8 @@
       <c r="W239" s="2"/>
     </row>
     <row r="240" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A240" s="17"/>
-      <c r="B240" s="17"/>
+      <c r="A240" s="18"/>
+      <c r="B240" s="18"/>
       <c r="C240" s="90"/>
       <c r="D240" s="2"/>
       <c r="E240" s="2"/>
@@ -11747,8 +11984,8 @@
       <c r="W240" s="2"/>
     </row>
     <row r="241" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A241" s="17"/>
-      <c r="B241" s="17"/>
+      <c r="A241" s="18"/>
+      <c r="B241" s="18"/>
       <c r="C241" s="90"/>
       <c r="D241" s="2"/>
       <c r="E241" s="2"/>
@@ -11772,8 +12009,8 @@
       <c r="W241" s="2"/>
     </row>
     <row r="242" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A242" s="17"/>
-      <c r="B242" s="17"/>
+      <c r="A242" s="18"/>
+      <c r="B242" s="18"/>
       <c r="C242" s="90"/>
       <c r="D242" s="2"/>
       <c r="E242" s="2"/>
@@ -11797,8 +12034,8 @@
       <c r="W242" s="2"/>
     </row>
     <row r="243" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A243" s="17"/>
-      <c r="B243" s="17"/>
+      <c r="A243" s="18"/>
+      <c r="B243" s="18"/>
       <c r="C243" s="90"/>
       <c r="D243" s="2"/>
       <c r="E243" s="2"/>
@@ -11822,8 +12059,8 @@
       <c r="W243" s="2"/>
     </row>
     <row r="244" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A244" s="17"/>
-      <c r="B244" s="17"/>
+      <c r="A244" s="18"/>
+      <c r="B244" s="18"/>
       <c r="C244" s="90"/>
       <c r="D244" s="2"/>
       <c r="E244" s="2"/>
@@ -11847,8 +12084,8 @@
       <c r="W244" s="2"/>
     </row>
     <row r="245" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A245" s="17"/>
-      <c r="B245" s="17"/>
+      <c r="A245" s="18"/>
+      <c r="B245" s="18"/>
       <c r="C245" s="90"/>
       <c r="D245" s="2"/>
       <c r="E245" s="2"/>
@@ -11872,8 +12109,8 @@
       <c r="W245" s="2"/>
     </row>
     <row r="246" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A246" s="17"/>
-      <c r="B246" s="17"/>
+      <c r="A246" s="18"/>
+      <c r="B246" s="18"/>
       <c r="C246" s="90"/>
       <c r="D246" s="2"/>
       <c r="E246" s="2"/>
@@ -11899,7 +12136,7 @@
     <row r="247" spans="1:23" ht="13.5" customHeight="1">
       <c r="A247" s="17"/>
       <c r="B247" s="17"/>
-      <c r="C247" s="90"/>
+      <c r="C247" s="89"/>
       <c r="D247" s="2"/>
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
@@ -11924,7 +12161,7 @@
     <row r="248" spans="1:23" ht="13.5" customHeight="1">
       <c r="A248" s="17"/>
       <c r="B248" s="17"/>
-      <c r="C248" s="90"/>
+      <c r="C248" s="89"/>
       <c r="D248" s="2"/>
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
@@ -11949,7 +12186,7 @@
     <row r="249" spans="1:23" ht="13.5" customHeight="1">
       <c r="A249" s="17"/>
       <c r="B249" s="17"/>
-      <c r="C249" s="90"/>
+      <c r="C249" s="89"/>
       <c r="D249" s="2"/>
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
@@ -11974,7 +12211,7 @@
     <row r="250" spans="1:23" ht="13.5" customHeight="1">
       <c r="A250" s="17"/>
       <c r="B250" s="17"/>
-      <c r="C250" s="90"/>
+      <c r="C250" s="89"/>
       <c r="D250" s="2"/>
       <c r="E250" s="2"/>
       <c r="F250" s="2"/>
@@ -11999,7 +12236,7 @@
     <row r="251" spans="1:23" ht="13.5" customHeight="1">
       <c r="A251" s="17"/>
       <c r="B251" s="17"/>
-      <c r="C251" s="90"/>
+      <c r="C251" s="89"/>
       <c r="D251" s="2"/>
       <c r="E251" s="2"/>
       <c r="F251" s="2"/>
@@ -12024,7 +12261,7 @@
     <row r="252" spans="1:23" ht="13.5" customHeight="1">
       <c r="A252" s="17"/>
       <c r="B252" s="17"/>
-      <c r="C252" s="90"/>
+      <c r="C252" s="89"/>
       <c r="D252" s="2"/>
       <c r="E252" s="2"/>
       <c r="F252" s="2"/>
@@ -12049,7 +12286,7 @@
     <row r="253" spans="1:23" ht="13.5" customHeight="1">
       <c r="A253" s="17"/>
       <c r="B253" s="17"/>
-      <c r="C253" s="90"/>
+      <c r="C253" s="89"/>
       <c r="D253" s="2"/>
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
@@ -12074,7 +12311,7 @@
     <row r="254" spans="1:23" ht="13.5" customHeight="1">
       <c r="A254" s="17"/>
       <c r="B254" s="17"/>
-      <c r="C254" s="90"/>
+      <c r="C254" s="89"/>
       <c r="D254" s="2"/>
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
@@ -12099,7 +12336,7 @@
     <row r="255" spans="1:23" ht="13.5" customHeight="1">
       <c r="A255" s="17"/>
       <c r="B255" s="17"/>
-      <c r="C255" s="90"/>
+      <c r="C255" s="89"/>
       <c r="D255" s="2"/>
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
@@ -12124,7 +12361,7 @@
     <row r="256" spans="1:23" ht="13.5" customHeight="1">
       <c r="A256" s="17"/>
       <c r="B256" s="17"/>
-      <c r="C256" s="90"/>
+      <c r="C256" s="89"/>
       <c r="D256" s="2"/>
       <c r="E256" s="2"/>
       <c r="F256" s="2"/>
@@ -12149,7 +12386,7 @@
     <row r="257" spans="1:23" ht="13.5" customHeight="1">
       <c r="A257" s="17"/>
       <c r="B257" s="17"/>
-      <c r="C257" s="90"/>
+      <c r="C257" s="89"/>
       <c r="D257" s="2"/>
       <c r="E257" s="2"/>
       <c r="F257" s="2"/>
@@ -12174,7 +12411,7 @@
     <row r="258" spans="1:23" ht="13.5" customHeight="1">
       <c r="A258" s="17"/>
       <c r="B258" s="17"/>
-      <c r="C258" s="90"/>
+      <c r="C258" s="89"/>
       <c r="D258" s="2"/>
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
@@ -12199,7 +12436,7 @@
     <row r="259" spans="1:23" ht="13.5" customHeight="1">
       <c r="A259" s="17"/>
       <c r="B259" s="17"/>
-      <c r="C259" s="90"/>
+      <c r="C259" s="89"/>
       <c r="D259" s="2"/>
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
@@ -12224,7 +12461,7 @@
     <row r="260" spans="1:23" ht="13.5" customHeight="1">
       <c r="A260" s="17"/>
       <c r="B260" s="17"/>
-      <c r="C260" s="90"/>
+      <c r="C260" s="89"/>
       <c r="D260" s="2"/>
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
@@ -12249,7 +12486,7 @@
     <row r="261" spans="1:23" ht="13.5" customHeight="1">
       <c r="A261" s="17"/>
       <c r="B261" s="17"/>
-      <c r="C261" s="90"/>
+      <c r="C261" s="89"/>
       <c r="D261" s="2"/>
       <c r="E261" s="2"/>
       <c r="F261" s="2"/>
@@ -12274,7 +12511,7 @@
     <row r="262" spans="1:23" ht="13.5" customHeight="1">
       <c r="A262" s="17"/>
       <c r="B262" s="17"/>
-      <c r="C262" s="90"/>
+      <c r="C262" s="89"/>
       <c r="D262" s="2"/>
       <c r="E262" s="2"/>
       <c r="F262" s="2"/>
@@ -12299,7 +12536,7 @@
     <row r="263" spans="1:23" ht="13.5" customHeight="1">
       <c r="A263" s="17"/>
       <c r="B263" s="17"/>
-      <c r="C263" s="90"/>
+      <c r="C263" s="89"/>
       <c r="D263" s="2"/>
       <c r="E263" s="2"/>
       <c r="F263" s="2"/>
@@ -12324,7 +12561,7 @@
     <row r="264" spans="1:23" ht="13.5" customHeight="1">
       <c r="A264" s="17"/>
       <c r="B264" s="17"/>
-      <c r="C264" s="90"/>
+      <c r="C264" s="89"/>
       <c r="D264" s="2"/>
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
@@ -12349,7 +12586,7 @@
     <row r="265" spans="1:23" ht="13.5" customHeight="1">
       <c r="A265" s="17"/>
       <c r="B265" s="17"/>
-      <c r="C265" s="90"/>
+      <c r="C265" s="89"/>
       <c r="D265" s="2"/>
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
@@ -12374,7 +12611,7 @@
     <row r="266" spans="1:23" ht="13.5" customHeight="1">
       <c r="A266" s="17"/>
       <c r="B266" s="17"/>
-      <c r="C266" s="90"/>
+      <c r="C266" s="89"/>
       <c r="D266" s="2"/>
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
@@ -12399,7 +12636,7 @@
     <row r="267" spans="1:23" ht="13.5" customHeight="1">
       <c r="A267" s="17"/>
       <c r="B267" s="17"/>
-      <c r="C267" s="90"/>
+      <c r="C267" s="89"/>
       <c r="D267" s="2"/>
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
@@ -12424,7 +12661,7 @@
     <row r="268" spans="1:23" ht="13.5" customHeight="1">
       <c r="A268" s="17"/>
       <c r="B268" s="17"/>
-      <c r="C268" s="90"/>
+      <c r="C268" s="89"/>
       <c r="D268" s="2"/>
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
@@ -12449,7 +12686,7 @@
     <row r="269" spans="1:23" ht="13.5" customHeight="1">
       <c r="A269" s="17"/>
       <c r="B269" s="17"/>
-      <c r="C269" s="90"/>
+      <c r="C269" s="89"/>
       <c r="D269" s="2"/>
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
@@ -12474,7 +12711,7 @@
     <row r="270" spans="1:23" ht="13.5" customHeight="1">
       <c r="A270" s="17"/>
       <c r="B270" s="17"/>
-      <c r="C270" s="90"/>
+      <c r="C270" s="89"/>
       <c r="D270" s="2"/>
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
@@ -12499,7 +12736,7 @@
     <row r="271" spans="1:23" ht="13.5" customHeight="1">
       <c r="A271" s="17"/>
       <c r="B271" s="17"/>
-      <c r="C271" s="90"/>
+      <c r="C271" s="89"/>
       <c r="D271" s="2"/>
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
@@ -12524,7 +12761,7 @@
     <row r="272" spans="1:23" ht="13.5" customHeight="1">
       <c r="A272" s="17"/>
       <c r="B272" s="17"/>
-      <c r="C272" s="90"/>
+      <c r="C272" s="89"/>
       <c r="D272" s="2"/>
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
@@ -12549,7 +12786,7 @@
     <row r="273" spans="1:23" ht="13.5" customHeight="1">
       <c r="A273" s="17"/>
       <c r="B273" s="17"/>
-      <c r="C273" s="90"/>
+      <c r="C273" s="89"/>
       <c r="D273" s="2"/>
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
@@ -12574,7 +12811,7 @@
     <row r="274" spans="1:23" ht="13.5" customHeight="1">
       <c r="A274" s="17"/>
       <c r="B274" s="17"/>
-      <c r="C274" s="90"/>
+      <c r="C274" s="89"/>
       <c r="D274" s="2"/>
       <c r="E274" s="2"/>
       <c r="F274" s="2"/>
@@ -12599,7 +12836,7 @@
     <row r="275" spans="1:23" ht="13.5" customHeight="1">
       <c r="A275" s="17"/>
       <c r="B275" s="17"/>
-      <c r="C275" s="90"/>
+      <c r="C275" s="89"/>
       <c r="D275" s="2"/>
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
@@ -12624,7 +12861,7 @@
     <row r="276" spans="1:23" ht="13.5" customHeight="1">
       <c r="A276" s="17"/>
       <c r="B276" s="17"/>
-      <c r="C276" s="90"/>
+      <c r="C276" s="89"/>
       <c r="D276" s="2"/>
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
@@ -12649,7 +12886,7 @@
     <row r="277" spans="1:23" ht="13.5" customHeight="1">
       <c r="A277" s="17"/>
       <c r="B277" s="17"/>
-      <c r="C277" s="90"/>
+      <c r="C277" s="89"/>
       <c r="D277" s="2"/>
       <c r="E277" s="2"/>
       <c r="F277" s="2"/>
@@ -12674,7 +12911,7 @@
     <row r="278" spans="1:23" ht="13.5" customHeight="1">
       <c r="A278" s="17"/>
       <c r="B278" s="17"/>
-      <c r="C278" s="90"/>
+      <c r="C278" s="89"/>
       <c r="D278" s="2"/>
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
@@ -12699,7 +12936,7 @@
     <row r="279" spans="1:23" ht="13.5" customHeight="1">
       <c r="A279" s="17"/>
       <c r="B279" s="17"/>
-      <c r="C279" s="90"/>
+      <c r="C279" s="89"/>
       <c r="D279" s="2"/>
       <c r="E279" s="2"/>
       <c r="F279" s="2"/>
@@ -12724,7 +12961,7 @@
     <row r="280" spans="1:23" ht="13.5" customHeight="1">
       <c r="A280" s="17"/>
       <c r="B280" s="17"/>
-      <c r="C280" s="90"/>
+      <c r="C280" s="89"/>
       <c r="D280" s="2"/>
       <c r="E280" s="2"/>
       <c r="F280" s="2"/>
@@ -12749,7 +12986,7 @@
     <row r="281" spans="1:23" ht="13.5" customHeight="1">
       <c r="A281" s="17"/>
       <c r="B281" s="17"/>
-      <c r="C281" s="90"/>
+      <c r="C281" s="89"/>
       <c r="D281" s="2"/>
       <c r="E281" s="2"/>
       <c r="F281" s="2"/>
@@ -12774,7 +13011,7 @@
     <row r="282" spans="1:23" ht="13.5" customHeight="1">
       <c r="A282" s="17"/>
       <c r="B282" s="17"/>
-      <c r="C282" s="90"/>
+      <c r="C282" s="89"/>
       <c r="D282" s="2"/>
       <c r="E282" s="2"/>
       <c r="F282" s="2"/>
@@ -12799,7 +13036,7 @@
     <row r="283" spans="1:23" ht="13.5" customHeight="1">
       <c r="A283" s="17"/>
       <c r="B283" s="17"/>
-      <c r="C283" s="90"/>
+      <c r="C283" s="89"/>
       <c r="D283" s="2"/>
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
@@ -12824,7 +13061,7 @@
     <row r="284" spans="1:23" ht="13.5" customHeight="1">
       <c r="A284" s="17"/>
       <c r="B284" s="17"/>
-      <c r="C284" s="90"/>
+      <c r="C284" s="89"/>
       <c r="D284" s="2"/>
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
@@ -12849,7 +13086,7 @@
     <row r="285" spans="1:23" ht="13.5" customHeight="1">
       <c r="A285" s="17"/>
       <c r="B285" s="17"/>
-      <c r="C285" s="90"/>
+      <c r="C285" s="89"/>
       <c r="D285" s="2"/>
       <c r="E285" s="2"/>
       <c r="F285" s="2"/>
@@ -12874,7 +13111,7 @@
     <row r="286" spans="1:23" ht="13.5" customHeight="1">
       <c r="A286" s="17"/>
       <c r="B286" s="17"/>
-      <c r="C286" s="90"/>
+      <c r="C286" s="89"/>
       <c r="D286" s="2"/>
       <c r="E286" s="2"/>
       <c r="F286" s="2"/>
@@ -12899,7 +13136,7 @@
     <row r="287" spans="1:23" ht="13.5" customHeight="1">
       <c r="A287" s="17"/>
       <c r="B287" s="17"/>
-      <c r="C287" s="90"/>
+      <c r="C287" s="89"/>
       <c r="D287" s="2"/>
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
@@ -12924,7 +13161,7 @@
     <row r="288" spans="1:23" ht="13.5" customHeight="1">
       <c r="A288" s="17"/>
       <c r="B288" s="17"/>
-      <c r="C288" s="90"/>
+      <c r="C288" s="89"/>
       <c r="D288" s="2"/>
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
@@ -12949,7 +13186,7 @@
     <row r="289" spans="1:23" ht="13.5" customHeight="1">
       <c r="A289" s="17"/>
       <c r="B289" s="17"/>
-      <c r="C289" s="90"/>
+      <c r="C289" s="89"/>
       <c r="D289" s="2"/>
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
@@ -12974,7 +13211,7 @@
     <row r="290" spans="1:23" ht="13.5" customHeight="1">
       <c r="A290" s="17"/>
       <c r="B290" s="17"/>
-      <c r="C290" s="90"/>
+      <c r="C290" s="89"/>
       <c r="D290" s="2"/>
       <c r="E290" s="2"/>
       <c r="F290" s="2"/>
@@ -12999,7 +13236,7 @@
     <row r="291" spans="1:23" ht="13.5" customHeight="1">
       <c r="A291" s="17"/>
       <c r="B291" s="17"/>
-      <c r="C291" s="90"/>
+      <c r="C291" s="89"/>
       <c r="D291" s="2"/>
       <c r="E291" s="2"/>
       <c r="F291" s="2"/>
@@ -13024,7 +13261,7 @@
     <row r="292" spans="1:23" ht="13.5" customHeight="1">
       <c r="A292" s="17"/>
       <c r="B292" s="17"/>
-      <c r="C292" s="90"/>
+      <c r="C292" s="89"/>
       <c r="D292" s="2"/>
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
@@ -13049,7 +13286,7 @@
     <row r="293" spans="1:23" ht="13.5" customHeight="1">
       <c r="A293" s="17"/>
       <c r="B293" s="17"/>
-      <c r="C293" s="90"/>
+      <c r="C293" s="89"/>
       <c r="D293" s="2"/>
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
@@ -13074,7 +13311,7 @@
     <row r="294" spans="1:23" ht="13.5" customHeight="1">
       <c r="A294" s="17"/>
       <c r="B294" s="17"/>
-      <c r="C294" s="90"/>
+      <c r="C294" s="89"/>
       <c r="D294" s="2"/>
       <c r="E294" s="2"/>
       <c r="F294" s="2"/>
@@ -13099,7 +13336,7 @@
     <row r="295" spans="1:23" ht="13.5" customHeight="1">
       <c r="A295" s="17"/>
       <c r="B295" s="17"/>
-      <c r="C295" s="90"/>
+      <c r="C295" s="89"/>
       <c r="D295" s="2"/>
       <c r="E295" s="2"/>
       <c r="F295" s="2"/>
@@ -13124,7 +13361,7 @@
     <row r="296" spans="1:23" ht="13.5" customHeight="1">
       <c r="A296" s="17"/>
       <c r="B296" s="17"/>
-      <c r="C296" s="90"/>
+      <c r="C296" s="89"/>
       <c r="D296" s="2"/>
       <c r="E296" s="2"/>
       <c r="F296" s="2"/>
@@ -13149,7 +13386,7 @@
     <row r="297" spans="1:23" ht="13.5" customHeight="1">
       <c r="A297" s="17"/>
       <c r="B297" s="17"/>
-      <c r="C297" s="90"/>
+      <c r="C297" s="89"/>
       <c r="D297" s="2"/>
       <c r="E297" s="2"/>
       <c r="F297" s="2"/>
@@ -13174,7 +13411,7 @@
     <row r="298" spans="1:23" ht="13.5" customHeight="1">
       <c r="A298" s="17"/>
       <c r="B298" s="17"/>
-      <c r="C298" s="90"/>
+      <c r="C298" s="89"/>
       <c r="D298" s="2"/>
       <c r="E298" s="2"/>
       <c r="F298" s="2"/>
@@ -13199,7 +13436,7 @@
     <row r="299" spans="1:23" ht="13.5" customHeight="1">
       <c r="A299" s="17"/>
       <c r="B299" s="17"/>
-      <c r="C299" s="90"/>
+      <c r="C299" s="89"/>
       <c r="D299" s="2"/>
       <c r="E299" s="2"/>
       <c r="F299" s="2"/>
@@ -13224,7 +13461,7 @@
     <row r="300" spans="1:23" ht="13.5" customHeight="1">
       <c r="A300" s="17"/>
       <c r="B300" s="17"/>
-      <c r="C300" s="90"/>
+      <c r="C300" s="89"/>
       <c r="D300" s="2"/>
       <c r="E300" s="2"/>
       <c r="F300" s="2"/>
@@ -13249,7 +13486,7 @@
     <row r="301" spans="1:23" ht="13.5" customHeight="1">
       <c r="A301" s="17"/>
       <c r="B301" s="17"/>
-      <c r="C301" s="90"/>
+      <c r="C301" s="89"/>
       <c r="D301" s="2"/>
       <c r="E301" s="2"/>
       <c r="F301" s="2"/>
@@ -13274,7 +13511,7 @@
     <row r="302" spans="1:23" ht="13.5" customHeight="1">
       <c r="A302" s="17"/>
       <c r="B302" s="17"/>
-      <c r="C302" s="90"/>
+      <c r="C302" s="89"/>
       <c r="D302" s="2"/>
       <c r="E302" s="2"/>
       <c r="F302" s="2"/>
@@ -13299,7 +13536,7 @@
     <row r="303" spans="1:23" ht="13.5" customHeight="1">
       <c r="A303" s="17"/>
       <c r="B303" s="17"/>
-      <c r="C303" s="90"/>
+      <c r="C303" s="89"/>
       <c r="D303" s="2"/>
       <c r="E303" s="2"/>
       <c r="F303" s="2"/>
@@ -13324,7 +13561,7 @@
     <row r="304" spans="1:23" ht="13.5" customHeight="1">
       <c r="A304" s="17"/>
       <c r="B304" s="17"/>
-      <c r="C304" s="90"/>
+      <c r="C304" s="89"/>
       <c r="D304" s="2"/>
       <c r="E304" s="2"/>
       <c r="F304" s="2"/>
@@ -13349,7 +13586,7 @@
     <row r="305" spans="1:23" ht="13.5" customHeight="1">
       <c r="A305" s="17"/>
       <c r="B305" s="17"/>
-      <c r="C305" s="90"/>
+      <c r="C305" s="89"/>
       <c r="D305" s="2"/>
       <c r="E305" s="2"/>
       <c r="F305" s="2"/>
@@ -13374,7 +13611,7 @@
     <row r="306" spans="1:23" ht="13.5" customHeight="1">
       <c r="A306" s="17"/>
       <c r="B306" s="17"/>
-      <c r="C306" s="90"/>
+      <c r="C306" s="89"/>
       <c r="D306" s="2"/>
       <c r="E306" s="2"/>
       <c r="F306" s="2"/>
@@ -13399,7 +13636,7 @@
     <row r="307" spans="1:23" ht="13.5" customHeight="1">
       <c r="A307" s="17"/>
       <c r="B307" s="17"/>
-      <c r="C307" s="90"/>
+      <c r="C307" s="89"/>
       <c r="D307" s="2"/>
       <c r="E307" s="2"/>
       <c r="F307" s="2"/>
@@ -13424,7 +13661,7 @@
     <row r="308" spans="1:23" ht="13.5" customHeight="1">
       <c r="A308" s="17"/>
       <c r="B308" s="17"/>
-      <c r="C308" s="90"/>
+      <c r="C308" s="89"/>
       <c r="D308" s="2"/>
       <c r="E308" s="2"/>
       <c r="F308" s="2"/>
@@ -13449,7 +13686,7 @@
     <row r="309" spans="1:23" ht="13.5" customHeight="1">
       <c r="A309" s="17"/>
       <c r="B309" s="17"/>
-      <c r="C309" s="90"/>
+      <c r="C309" s="89"/>
       <c r="D309" s="2"/>
       <c r="E309" s="2"/>
       <c r="F309" s="2"/>
@@ -13474,7 +13711,7 @@
     <row r="310" spans="1:23" ht="13.5" customHeight="1">
       <c r="A310" s="17"/>
       <c r="B310" s="17"/>
-      <c r="C310" s="90"/>
+      <c r="C310" s="89"/>
       <c r="D310" s="2"/>
       <c r="E310" s="2"/>
       <c r="F310" s="2"/>
@@ -13499,7 +13736,7 @@
     <row r="311" spans="1:23" ht="13.5" customHeight="1">
       <c r="A311" s="17"/>
       <c r="B311" s="17"/>
-      <c r="C311" s="90"/>
+      <c r="C311" s="89"/>
       <c r="D311" s="2"/>
       <c r="E311" s="2"/>
       <c r="F311" s="2"/>
@@ -13524,7 +13761,7 @@
     <row r="312" spans="1:23" ht="13.5" customHeight="1">
       <c r="A312" s="17"/>
       <c r="B312" s="17"/>
-      <c r="C312" s="90"/>
+      <c r="C312" s="89"/>
       <c r="D312" s="2"/>
       <c r="E312" s="2"/>
       <c r="F312" s="2"/>
@@ -13549,7 +13786,7 @@
     <row r="313" spans="1:23" ht="13.5" customHeight="1">
       <c r="A313" s="17"/>
       <c r="B313" s="17"/>
-      <c r="C313" s="90"/>
+      <c r="C313" s="89"/>
       <c r="D313" s="2"/>
       <c r="E313" s="2"/>
       <c r="F313" s="2"/>
@@ -13574,7 +13811,7 @@
     <row r="314" spans="1:23" ht="13.5" customHeight="1">
       <c r="A314" s="17"/>
       <c r="B314" s="17"/>
-      <c r="C314" s="90"/>
+      <c r="C314" s="89"/>
       <c r="D314" s="2"/>
       <c r="E314" s="2"/>
       <c r="F314" s="2"/>
@@ -13599,7 +13836,7 @@
     <row r="315" spans="1:23" ht="13.5" customHeight="1">
       <c r="A315" s="17"/>
       <c r="B315" s="17"/>
-      <c r="C315" s="90"/>
+      <c r="C315" s="89"/>
       <c r="D315" s="2"/>
       <c r="E315" s="2"/>
       <c r="F315" s="2"/>
@@ -13624,7 +13861,7 @@
     <row r="316" spans="1:23" ht="13.5" customHeight="1">
       <c r="A316" s="17"/>
       <c r="B316" s="17"/>
-      <c r="C316" s="90"/>
+      <c r="C316" s="89"/>
       <c r="D316" s="2"/>
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
@@ -13649,7 +13886,7 @@
     <row r="317" spans="1:23" ht="13.5" customHeight="1">
       <c r="A317" s="17"/>
       <c r="B317" s="17"/>
-      <c r="C317" s="90"/>
+      <c r="C317" s="89"/>
       <c r="D317" s="2"/>
       <c r="E317" s="2"/>
       <c r="F317" s="2"/>
@@ -13674,7 +13911,7 @@
     <row r="318" spans="1:23" ht="13.5" customHeight="1">
       <c r="A318" s="17"/>
       <c r="B318" s="17"/>
-      <c r="C318" s="90"/>
+      <c r="C318" s="89"/>
       <c r="D318" s="2"/>
       <c r="E318" s="2"/>
       <c r="F318" s="2"/>
@@ -13699,7 +13936,7 @@
     <row r="319" spans="1:23" ht="13.5" customHeight="1">
       <c r="A319" s="17"/>
       <c r="B319" s="17"/>
-      <c r="C319" s="90"/>
+      <c r="C319" s="89"/>
       <c r="D319" s="2"/>
       <c r="E319" s="2"/>
       <c r="F319" s="2"/>
@@ -13724,7 +13961,7 @@
     <row r="320" spans="1:23" ht="13.5" customHeight="1">
       <c r="A320" s="17"/>
       <c r="B320" s="17"/>
-      <c r="C320" s="90"/>
+      <c r="C320" s="89"/>
       <c r="D320" s="2"/>
       <c r="E320" s="2"/>
       <c r="F320" s="2"/>
@@ -13749,7 +13986,7 @@
     <row r="321" spans="1:23" ht="13.5" customHeight="1">
       <c r="A321" s="17"/>
       <c r="B321" s="17"/>
-      <c r="C321" s="90"/>
+      <c r="C321" s="89"/>
       <c r="D321" s="2"/>
       <c r="E321" s="2"/>
       <c r="F321" s="2"/>
@@ -13774,7 +14011,7 @@
     <row r="322" spans="1:23" ht="13.5" customHeight="1">
       <c r="A322" s="17"/>
       <c r="B322" s="17"/>
-      <c r="C322" s="90"/>
+      <c r="C322" s="89"/>
       <c r="D322" s="2"/>
       <c r="E322" s="2"/>
       <c r="F322" s="2"/>
@@ -13799,7 +14036,7 @@
     <row r="323" spans="1:23" ht="13.5" customHeight="1">
       <c r="A323" s="17"/>
       <c r="B323" s="17"/>
-      <c r="C323" s="90"/>
+      <c r="C323" s="89"/>
       <c r="D323" s="2"/>
       <c r="E323" s="2"/>
       <c r="F323" s="2"/>
@@ -13824,7 +14061,7 @@
     <row r="324" spans="1:23" ht="13.5" customHeight="1">
       <c r="A324" s="17"/>
       <c r="B324" s="17"/>
-      <c r="C324" s="90"/>
+      <c r="C324" s="89"/>
       <c r="D324" s="2"/>
       <c r="E324" s="2"/>
       <c r="F324" s="2"/>
@@ -13849,7 +14086,7 @@
     <row r="325" spans="1:23" ht="13.5" customHeight="1">
       <c r="A325" s="17"/>
       <c r="B325" s="17"/>
-      <c r="C325" s="90"/>
+      <c r="C325" s="89"/>
       <c r="D325" s="2"/>
       <c r="E325" s="2"/>
       <c r="F325" s="2"/>
@@ -13874,7 +14111,7 @@
     <row r="326" spans="1:23" ht="13.5" customHeight="1">
       <c r="A326" s="17"/>
       <c r="B326" s="17"/>
-      <c r="C326" s="90"/>
+      <c r="C326" s="89"/>
       <c r="D326" s="2"/>
       <c r="E326" s="2"/>
       <c r="F326" s="2"/>
@@ -13899,7 +14136,7 @@
     <row r="327" spans="1:23" ht="13.5" customHeight="1">
       <c r="A327" s="17"/>
       <c r="B327" s="17"/>
-      <c r="C327" s="90"/>
+      <c r="C327" s="89"/>
       <c r="D327" s="2"/>
       <c r="E327" s="2"/>
       <c r="F327" s="2"/>
@@ -13924,7 +14161,7 @@
     <row r="328" spans="1:23" ht="13.5" customHeight="1">
       <c r="A328" s="17"/>
       <c r="B328" s="17"/>
-      <c r="C328" s="90"/>
+      <c r="C328" s="89"/>
       <c r="D328" s="2"/>
       <c r="E328" s="2"/>
       <c r="F328" s="2"/>
@@ -13949,7 +14186,7 @@
     <row r="329" spans="1:23" ht="13.5" customHeight="1">
       <c r="A329" s="17"/>
       <c r="B329" s="17"/>
-      <c r="C329" s="90"/>
+      <c r="C329" s="89"/>
       <c r="D329" s="2"/>
       <c r="E329" s="2"/>
       <c r="F329" s="2"/>
@@ -13974,7 +14211,7 @@
     <row r="330" spans="1:23" ht="13.5" customHeight="1">
       <c r="A330" s="17"/>
       <c r="B330" s="17"/>
-      <c r="C330" s="90"/>
+      <c r="C330" s="89"/>
       <c r="D330" s="2"/>
       <c r="E330" s="2"/>
       <c r="F330" s="2"/>
@@ -13999,7 +14236,7 @@
     <row r="331" spans="1:23" ht="13.5" customHeight="1">
       <c r="A331" s="17"/>
       <c r="B331" s="17"/>
-      <c r="C331" s="90"/>
+      <c r="C331" s="89"/>
       <c r="D331" s="2"/>
       <c r="E331" s="2"/>
       <c r="F331" s="2"/>
@@ -14024,7 +14261,7 @@
     <row r="332" spans="1:23" ht="13.5" customHeight="1">
       <c r="A332" s="17"/>
       <c r="B332" s="17"/>
-      <c r="C332" s="90"/>
+      <c r="C332" s="89"/>
       <c r="D332" s="2"/>
       <c r="E332" s="2"/>
       <c r="F332" s="2"/>
@@ -14049,7 +14286,7 @@
     <row r="333" spans="1:23" ht="13.5" customHeight="1">
       <c r="A333" s="17"/>
       <c r="B333" s="17"/>
-      <c r="C333" s="90"/>
+      <c r="C333" s="89"/>
       <c r="D333" s="2"/>
       <c r="E333" s="2"/>
       <c r="F333" s="2"/>
@@ -14074,7 +14311,7 @@
     <row r="334" spans="1:23" ht="13.5" customHeight="1">
       <c r="A334" s="17"/>
       <c r="B334" s="17"/>
-      <c r="C334" s="90"/>
+      <c r="C334" s="89"/>
       <c r="D334" s="2"/>
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
@@ -14099,7 +14336,7 @@
     <row r="335" spans="1:23" ht="13.5" customHeight="1">
       <c r="A335" s="17"/>
       <c r="B335" s="17"/>
-      <c r="C335" s="90"/>
+      <c r="C335" s="89"/>
       <c r="D335" s="2"/>
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
@@ -14124,7 +14361,7 @@
     <row r="336" spans="1:23" ht="13.5" customHeight="1">
       <c r="A336" s="17"/>
       <c r="B336" s="17"/>
-      <c r="C336" s="90"/>
+      <c r="C336" s="89"/>
       <c r="D336" s="2"/>
       <c r="E336" s="2"/>
       <c r="F336" s="2"/>
@@ -14149,7 +14386,7 @@
     <row r="337" spans="1:23" ht="13.5" customHeight="1">
       <c r="A337" s="17"/>
       <c r="B337" s="17"/>
-      <c r="C337" s="90"/>
+      <c r="C337" s="89"/>
       <c r="D337" s="2"/>
       <c r="E337" s="2"/>
       <c r="F337" s="2"/>
@@ -14174,7 +14411,7 @@
     <row r="338" spans="1:23" ht="13.5" customHeight="1">
       <c r="A338" s="17"/>
       <c r="B338" s="17"/>
-      <c r="C338" s="90"/>
+      <c r="C338" s="89"/>
       <c r="D338" s="2"/>
       <c r="E338" s="2"/>
       <c r="F338" s="2"/>
@@ -14199,7 +14436,7 @@
     <row r="339" spans="1:23" ht="13.5" customHeight="1">
       <c r="A339" s="17"/>
       <c r="B339" s="17"/>
-      <c r="C339" s="90"/>
+      <c r="C339" s="89"/>
       <c r="D339" s="2"/>
       <c r="E339" s="2"/>
       <c r="F339" s="2"/>
@@ -14224,7 +14461,7 @@
     <row r="340" spans="1:23" ht="13.5" customHeight="1">
       <c r="A340" s="17"/>
       <c r="B340" s="17"/>
-      <c r="C340" s="90"/>
+      <c r="C340" s="89"/>
       <c r="D340" s="2"/>
       <c r="E340" s="2"/>
       <c r="F340" s="2"/>
@@ -14249,7 +14486,7 @@
     <row r="341" spans="1:23" ht="13.5" customHeight="1">
       <c r="A341" s="17"/>
       <c r="B341" s="17"/>
-      <c r="C341" s="90"/>
+      <c r="C341" s="89"/>
       <c r="D341" s="2"/>
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
@@ -14274,7 +14511,7 @@
     <row r="342" spans="1:23" ht="13.5" customHeight="1">
       <c r="A342" s="17"/>
       <c r="B342" s="17"/>
-      <c r="C342" s="90"/>
+      <c r="C342" s="89"/>
       <c r="D342" s="2"/>
       <c r="E342" s="2"/>
       <c r="F342" s="2"/>
@@ -14299,7 +14536,7 @@
     <row r="343" spans="1:23" ht="13.5" customHeight="1">
       <c r="A343" s="17"/>
       <c r="B343" s="17"/>
-      <c r="C343" s="90"/>
+      <c r="C343" s="89"/>
       <c r="D343" s="2"/>
       <c r="E343" s="2"/>
       <c r="F343" s="2"/>
@@ -14324,7 +14561,7 @@
     <row r="344" spans="1:23" ht="13.5" customHeight="1">
       <c r="A344" s="17"/>
       <c r="B344" s="17"/>
-      <c r="C344" s="90"/>
+      <c r="C344" s="89"/>
       <c r="D344" s="2"/>
       <c r="E344" s="2"/>
       <c r="F344" s="2"/>
@@ -14349,7 +14586,7 @@
     <row r="345" spans="1:23" ht="13.5" customHeight="1">
       <c r="A345" s="17"/>
       <c r="B345" s="17"/>
-      <c r="C345" s="90"/>
+      <c r="C345" s="89"/>
       <c r="D345" s="2"/>
       <c r="E345" s="2"/>
       <c r="F345" s="2"/>
@@ -14374,7 +14611,7 @@
     <row r="346" spans="1:23" ht="13.5" customHeight="1">
       <c r="A346" s="17"/>
       <c r="B346" s="17"/>
-      <c r="C346" s="90"/>
+      <c r="C346" s="89"/>
       <c r="D346" s="2"/>
       <c r="E346" s="2"/>
       <c r="F346" s="2"/>
@@ -14399,7 +14636,7 @@
     <row r="347" spans="1:23" ht="13.5" customHeight="1">
       <c r="A347" s="17"/>
       <c r="B347" s="17"/>
-      <c r="C347" s="90"/>
+      <c r="C347" s="89"/>
       <c r="D347" s="2"/>
       <c r="E347" s="2"/>
       <c r="F347" s="2"/>
@@ -14424,7 +14661,7 @@
     <row r="348" spans="1:23" ht="13.5" customHeight="1">
       <c r="A348" s="17"/>
       <c r="B348" s="17"/>
-      <c r="C348" s="90"/>
+      <c r="C348" s="89"/>
       <c r="D348" s="2"/>
       <c r="E348" s="2"/>
       <c r="F348" s="2"/>
@@ -14447,9 +14684,9 @@
       <c r="W348" s="2"/>
     </row>
     <row r="349" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A349" s="16"/>
-      <c r="B349" s="16"/>
-      <c r="C349" s="88"/>
+      <c r="A349" s="17"/>
+      <c r="B349" s="17"/>
+      <c r="C349" s="89"/>
       <c r="D349" s="2"/>
       <c r="E349" s="2"/>
       <c r="F349" s="2"/>
@@ -14472,9 +14709,9 @@
       <c r="W349" s="2"/>
     </row>
     <row r="350" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A350" s="16"/>
-      <c r="B350" s="16"/>
-      <c r="C350" s="88"/>
+      <c r="A350" s="17"/>
+      <c r="B350" s="17"/>
+      <c r="C350" s="89"/>
       <c r="D350" s="2"/>
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
@@ -14497,9 +14734,9 @@
       <c r="W350" s="2"/>
     </row>
     <row r="351" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A351" s="16"/>
-      <c r="B351" s="16"/>
-      <c r="C351" s="88"/>
+      <c r="A351" s="17"/>
+      <c r="B351" s="17"/>
+      <c r="C351" s="89"/>
       <c r="D351" s="2"/>
       <c r="E351" s="2"/>
       <c r="F351" s="2"/>
@@ -14522,9 +14759,9 @@
       <c r="W351" s="2"/>
     </row>
     <row r="352" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A352" s="16"/>
-      <c r="B352" s="16"/>
-      <c r="C352" s="88"/>
+      <c r="A352" s="17"/>
+      <c r="B352" s="17"/>
+      <c r="C352" s="89"/>
       <c r="D352" s="2"/>
       <c r="E352" s="2"/>
       <c r="F352" s="2"/>
@@ -14547,9 +14784,9 @@
       <c r="W352" s="2"/>
     </row>
     <row r="353" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A353" s="16"/>
-      <c r="B353" s="16"/>
-      <c r="C353" s="88"/>
+      <c r="A353" s="17"/>
+      <c r="B353" s="17"/>
+      <c r="C353" s="89"/>
       <c r="D353" s="2"/>
       <c r="E353" s="2"/>
       <c r="F353" s="2"/>
@@ -14572,9 +14809,9 @@
       <c r="W353" s="2"/>
     </row>
     <row r="354" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A354" s="16"/>
-      <c r="B354" s="16"/>
-      <c r="C354" s="88"/>
+      <c r="A354" s="17"/>
+      <c r="B354" s="17"/>
+      <c r="C354" s="89"/>
       <c r="D354" s="2"/>
       <c r="E354" s="2"/>
       <c r="F354" s="2"/>
@@ -14597,9 +14834,9 @@
       <c r="W354" s="2"/>
     </row>
     <row r="355" spans="1:23" ht="13.5" customHeight="1">
-      <c r="A355" s="16"/>
-      <c r="B355" s="16"/>
-      <c r="C355" s="88"/>
+      <c r="A355" s="17"/>
+      <c r="B355" s="17"/>
+      <c r="C355" s="89"/>
       <c r="D355" s="2"/>
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
@@ -14621,245 +14858,619 @@
       <c r="V355" s="2"/>
       <c r="W355" s="2"/>
     </row>
-    <row r="356" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A356" s="16"/>
-      <c r="B356" s="16"/>
-      <c r="C356" s="88"/>
-      <c r="D356" s="19"/>
-      <c r="E356" s="19"/>
-      <c r="F356" s="19"/>
-      <c r="G356" s="19"/>
-      <c r="H356" s="19"/>
-      <c r="I356" s="19"/>
-      <c r="J356" s="19"/>
-      <c r="K356" s="19"/>
-      <c r="L356" s="19"/>
-      <c r="M356" s="19"/>
-      <c r="N356" s="19"/>
-      <c r="O356" s="19"/>
-      <c r="P356" s="19"/>
-      <c r="Q356" s="19"/>
-      <c r="R356" s="19"/>
-      <c r="S356" s="19"/>
-      <c r="T356" s="19"/>
-      <c r="U356" s="19"/>
-      <c r="V356" s="19"/>
-      <c r="W356" s="19"/>
-    </row>
-    <row r="357" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A357" s="18"/>
-      <c r="B357" s="18"/>
-      <c r="C357" s="91"/>
-      <c r="D357" s="19"/>
-      <c r="E357" s="19"/>
-      <c r="F357" s="19"/>
-      <c r="G357" s="19"/>
-      <c r="H357" s="19"/>
-      <c r="I357" s="19"/>
-      <c r="J357" s="19"/>
-      <c r="K357" s="19"/>
-      <c r="L357" s="19"/>
-      <c r="M357" s="19"/>
-      <c r="N357" s="19"/>
-      <c r="O357" s="19"/>
-      <c r="P357" s="19"/>
-      <c r="Q357" s="19"/>
-      <c r="R357" s="19"/>
-      <c r="S357" s="19"/>
-      <c r="T357" s="19"/>
-      <c r="U357" s="19"/>
-      <c r="V357" s="19"/>
-      <c r="W357" s="19"/>
-    </row>
-    <row r="358" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A358" s="18"/>
-      <c r="B358" s="18"/>
-      <c r="C358" s="91"/>
-      <c r="D358" s="19"/>
-      <c r="E358" s="19"/>
-      <c r="F358" s="19"/>
-      <c r="G358" s="19"/>
-      <c r="H358" s="19"/>
-      <c r="I358" s="19"/>
-      <c r="J358" s="19"/>
-      <c r="K358" s="19"/>
-      <c r="L358" s="19"/>
-      <c r="M358" s="19"/>
-      <c r="N358" s="19"/>
-      <c r="O358" s="19"/>
-      <c r="P358" s="19"/>
-      <c r="Q358" s="19"/>
-      <c r="R358" s="19"/>
-      <c r="S358" s="19"/>
-      <c r="T358" s="19"/>
-      <c r="U358" s="19"/>
-      <c r="V358" s="19"/>
-      <c r="W358" s="19"/>
-    </row>
-    <row r="359" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A359" s="18"/>
-      <c r="B359" s="18"/>
-      <c r="C359" s="91"/>
-      <c r="D359" s="19"/>
-      <c r="E359" s="19"/>
-      <c r="F359" s="19"/>
-      <c r="G359" s="19"/>
-      <c r="H359" s="19"/>
-      <c r="I359" s="19"/>
-      <c r="J359" s="19"/>
-      <c r="K359" s="19"/>
-      <c r="L359" s="19"/>
-      <c r="M359" s="19"/>
-      <c r="N359" s="19"/>
-      <c r="O359" s="19"/>
-      <c r="P359" s="19"/>
-      <c r="Q359" s="19"/>
-      <c r="R359" s="19"/>
-      <c r="S359" s="19"/>
-      <c r="T359" s="19"/>
-      <c r="U359" s="19"/>
-      <c r="V359" s="19"/>
-      <c r="W359" s="19"/>
-    </row>
-    <row r="360" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A360" s="18"/>
-      <c r="B360" s="18"/>
-      <c r="C360" s="91"/>
-      <c r="D360" s="19"/>
-      <c r="E360" s="19"/>
-      <c r="F360" s="19"/>
-      <c r="G360" s="19"/>
-      <c r="H360" s="19"/>
-      <c r="I360" s="19"/>
-      <c r="J360" s="19"/>
-      <c r="K360" s="19"/>
-      <c r="L360" s="19"/>
-      <c r="M360" s="19"/>
-      <c r="N360" s="19"/>
-      <c r="O360" s="19"/>
-      <c r="P360" s="19"/>
-      <c r="Q360" s="19"/>
-      <c r="R360" s="19"/>
-      <c r="S360" s="19"/>
-      <c r="T360" s="19"/>
-      <c r="U360" s="19"/>
-      <c r="V360" s="19"/>
-      <c r="W360" s="19"/>
-    </row>
-    <row r="361" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A361" s="18"/>
-      <c r="B361" s="18"/>
-      <c r="C361" s="91"/>
-      <c r="D361" s="19"/>
-      <c r="E361" s="19"/>
-      <c r="F361" s="19"/>
-      <c r="G361" s="19"/>
-      <c r="H361" s="19"/>
-      <c r="I361" s="19"/>
-      <c r="J361" s="19"/>
-      <c r="K361" s="19"/>
-      <c r="L361" s="19"/>
-      <c r="M361" s="19"/>
-      <c r="N361" s="19"/>
-      <c r="O361" s="19"/>
-      <c r="P361" s="19"/>
-      <c r="Q361" s="19"/>
-      <c r="R361" s="19"/>
-      <c r="S361" s="19"/>
-      <c r="T361" s="19"/>
-      <c r="U361" s="19"/>
-      <c r="V361" s="19"/>
-      <c r="W361" s="19"/>
-    </row>
-    <row r="362" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A362" s="18"/>
-      <c r="B362" s="18"/>
-      <c r="C362" s="91"/>
-      <c r="D362" s="19"/>
-      <c r="E362" s="19"/>
-      <c r="F362" s="19"/>
-      <c r="G362" s="19"/>
-      <c r="H362" s="19"/>
-      <c r="I362" s="19"/>
-      <c r="J362" s="19"/>
-      <c r="K362" s="19"/>
-      <c r="L362" s="19"/>
-      <c r="M362" s="19"/>
-      <c r="N362" s="19"/>
-      <c r="O362" s="19"/>
-      <c r="P362" s="19"/>
-      <c r="Q362" s="19"/>
-      <c r="R362" s="19"/>
-      <c r="S362" s="19"/>
-      <c r="T362" s="19"/>
-      <c r="U362" s="19"/>
-      <c r="V362" s="19"/>
-      <c r="W362" s="19"/>
-    </row>
-    <row r="363" spans="1:23" ht="15.75" customHeight="1">
-      <c r="C363" s="79"/>
-    </row>
-    <row r="364" spans="1:23" ht="15.75" customHeight="1">
-      <c r="C364" s="79"/>
-    </row>
-    <row r="365" spans="1:23" ht="15.75" customHeight="1">
-      <c r="C365" s="79"/>
-    </row>
-    <row r="366" spans="1:23" ht="15.75" customHeight="1">
-      <c r="C366" s="79"/>
-    </row>
-    <row r="367" spans="1:23" ht="15.75" customHeight="1">
-      <c r="C367" s="79"/>
-    </row>
-    <row r="368" spans="1:23" ht="15.75" customHeight="1">
-      <c r="C368" s="79"/>
-    </row>
-    <row r="369" spans="3:3" ht="15.75" customHeight="1">
-      <c r="C369" s="79"/>
-    </row>
-    <row r="370" spans="3:3" ht="15.75" customHeight="1">
-      <c r="C370" s="79"/>
-    </row>
-    <row r="371" spans="3:3" ht="15.75" customHeight="1">
-      <c r="C371" s="79"/>
-    </row>
-    <row r="372" spans="3:3" ht="15.75" customHeight="1">
-      <c r="C372" s="79"/>
-    </row>
-    <row r="373" spans="3:3" ht="15.75" customHeight="1">
-      <c r="C373" s="79"/>
-    </row>
-    <row r="374" spans="3:3" ht="15.75" customHeight="1">
-      <c r="C374" s="79"/>
-    </row>
-    <row r="375" spans="3:3" ht="15.75" customHeight="1">
-      <c r="C375" s="79"/>
-    </row>
-    <row r="376" spans="3:3" ht="15.75" customHeight="1">
-      <c r="C376" s="79"/>
-    </row>
-    <row r="377" spans="3:3" ht="15.75" customHeight="1">
-      <c r="C377" s="79"/>
-    </row>
-    <row r="378" spans="3:3" ht="15.75" customHeight="1">
-      <c r="C378" s="79"/>
-    </row>
-    <row r="379" spans="3:3" ht="15.75" customHeight="1">
-      <c r="C379" s="79"/>
-    </row>
-    <row r="380" spans="3:3" ht="15.75" customHeight="1">
+    <row r="356" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A356" s="17"/>
+      <c r="B356" s="17"/>
+      <c r="C356" s="89"/>
+      <c r="D356" s="2"/>
+      <c r="E356" s="2"/>
+      <c r="F356" s="2"/>
+      <c r="G356" s="2"/>
+      <c r="H356" s="2"/>
+      <c r="I356" s="2"/>
+      <c r="J356" s="2"/>
+      <c r="K356" s="2"/>
+      <c r="L356" s="2"/>
+      <c r="M356" s="2"/>
+      <c r="N356" s="2"/>
+      <c r="O356" s="2"/>
+      <c r="P356" s="2"/>
+      <c r="Q356" s="2"/>
+      <c r="R356" s="2"/>
+      <c r="S356" s="2"/>
+      <c r="T356" s="2"/>
+      <c r="U356" s="2"/>
+      <c r="V356" s="2"/>
+      <c r="W356" s="2"/>
+    </row>
+    <row r="357" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A357" s="17"/>
+      <c r="B357" s="17"/>
+      <c r="C357" s="89"/>
+      <c r="D357" s="2"/>
+      <c r="E357" s="2"/>
+      <c r="F357" s="2"/>
+      <c r="G357" s="2"/>
+      <c r="H357" s="2"/>
+      <c r="I357" s="2"/>
+      <c r="J357" s="2"/>
+      <c r="K357" s="2"/>
+      <c r="L357" s="2"/>
+      <c r="M357" s="2"/>
+      <c r="N357" s="2"/>
+      <c r="O357" s="2"/>
+      <c r="P357" s="2"/>
+      <c r="Q357" s="2"/>
+      <c r="R357" s="2"/>
+      <c r="S357" s="2"/>
+      <c r="T357" s="2"/>
+      <c r="U357" s="2"/>
+      <c r="V357" s="2"/>
+      <c r="W357" s="2"/>
+    </row>
+    <row r="358" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A358" s="17"/>
+      <c r="B358" s="17"/>
+      <c r="C358" s="89"/>
+      <c r="D358" s="2"/>
+      <c r="E358" s="2"/>
+      <c r="F358" s="2"/>
+      <c r="G358" s="2"/>
+      <c r="H358" s="2"/>
+      <c r="I358" s="2"/>
+      <c r="J358" s="2"/>
+      <c r="K358" s="2"/>
+      <c r="L358" s="2"/>
+      <c r="M358" s="2"/>
+      <c r="N358" s="2"/>
+      <c r="O358" s="2"/>
+      <c r="P358" s="2"/>
+      <c r="Q358" s="2"/>
+      <c r="R358" s="2"/>
+      <c r="S358" s="2"/>
+      <c r="T358" s="2"/>
+      <c r="U358" s="2"/>
+      <c r="V358" s="2"/>
+      <c r="W358" s="2"/>
+    </row>
+    <row r="359" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A359" s="17"/>
+      <c r="B359" s="17"/>
+      <c r="C359" s="89"/>
+      <c r="D359" s="2"/>
+      <c r="E359" s="2"/>
+      <c r="F359" s="2"/>
+      <c r="G359" s="2"/>
+      <c r="H359" s="2"/>
+      <c r="I359" s="2"/>
+      <c r="J359" s="2"/>
+      <c r="K359" s="2"/>
+      <c r="L359" s="2"/>
+      <c r="M359" s="2"/>
+      <c r="N359" s="2"/>
+      <c r="O359" s="2"/>
+      <c r="P359" s="2"/>
+      <c r="Q359" s="2"/>
+      <c r="R359" s="2"/>
+      <c r="S359" s="2"/>
+      <c r="T359" s="2"/>
+      <c r="U359" s="2"/>
+      <c r="V359" s="2"/>
+      <c r="W359" s="2"/>
+    </row>
+    <row r="360" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A360" s="17"/>
+      <c r="B360" s="17"/>
+      <c r="C360" s="89"/>
+      <c r="D360" s="2"/>
+      <c r="E360" s="2"/>
+      <c r="F360" s="2"/>
+      <c r="G360" s="2"/>
+      <c r="H360" s="2"/>
+      <c r="I360" s="2"/>
+      <c r="J360" s="2"/>
+      <c r="K360" s="2"/>
+      <c r="L360" s="2"/>
+      <c r="M360" s="2"/>
+      <c r="N360" s="2"/>
+      <c r="O360" s="2"/>
+      <c r="P360" s="2"/>
+      <c r="Q360" s="2"/>
+      <c r="R360" s="2"/>
+      <c r="S360" s="2"/>
+      <c r="T360" s="2"/>
+      <c r="U360" s="2"/>
+      <c r="V360" s="2"/>
+      <c r="W360" s="2"/>
+    </row>
+    <row r="361" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A361" s="17"/>
+      <c r="B361" s="17"/>
+      <c r="C361" s="89"/>
+      <c r="D361" s="2"/>
+      <c r="E361" s="2"/>
+      <c r="F361" s="2"/>
+      <c r="G361" s="2"/>
+      <c r="H361" s="2"/>
+      <c r="I361" s="2"/>
+      <c r="J361" s="2"/>
+      <c r="K361" s="2"/>
+      <c r="L361" s="2"/>
+      <c r="M361" s="2"/>
+      <c r="N361" s="2"/>
+      <c r="O361" s="2"/>
+      <c r="P361" s="2"/>
+      <c r="Q361" s="2"/>
+      <c r="R361" s="2"/>
+      <c r="S361" s="2"/>
+      <c r="T361" s="2"/>
+      <c r="U361" s="2"/>
+      <c r="V361" s="2"/>
+      <c r="W361" s="2"/>
+    </row>
+    <row r="362" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A362" s="17"/>
+      <c r="B362" s="17"/>
+      <c r="C362" s="89"/>
+      <c r="D362" s="2"/>
+      <c r="E362" s="2"/>
+      <c r="F362" s="2"/>
+      <c r="G362" s="2"/>
+      <c r="H362" s="2"/>
+      <c r="I362" s="2"/>
+      <c r="J362" s="2"/>
+      <c r="K362" s="2"/>
+      <c r="L362" s="2"/>
+      <c r="M362" s="2"/>
+      <c r="N362" s="2"/>
+      <c r="O362" s="2"/>
+      <c r="P362" s="2"/>
+      <c r="Q362" s="2"/>
+      <c r="R362" s="2"/>
+      <c r="S362" s="2"/>
+      <c r="T362" s="2"/>
+      <c r="U362" s="2"/>
+      <c r="V362" s="2"/>
+      <c r="W362" s="2"/>
+    </row>
+    <row r="363" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A363" s="17"/>
+      <c r="B363" s="17"/>
+      <c r="C363" s="89"/>
+      <c r="D363" s="2"/>
+      <c r="E363" s="2"/>
+      <c r="F363" s="2"/>
+      <c r="G363" s="2"/>
+      <c r="H363" s="2"/>
+      <c r="I363" s="2"/>
+      <c r="J363" s="2"/>
+      <c r="K363" s="2"/>
+      <c r="L363" s="2"/>
+      <c r="M363" s="2"/>
+      <c r="N363" s="2"/>
+      <c r="O363" s="2"/>
+      <c r="P363" s="2"/>
+      <c r="Q363" s="2"/>
+      <c r="R363" s="2"/>
+      <c r="S363" s="2"/>
+      <c r="T363" s="2"/>
+      <c r="U363" s="2"/>
+      <c r="V363" s="2"/>
+      <c r="W363" s="2"/>
+    </row>
+    <row r="364" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A364" s="17"/>
+      <c r="B364" s="17"/>
+      <c r="C364" s="89"/>
+      <c r="D364" s="2"/>
+      <c r="E364" s="2"/>
+      <c r="F364" s="2"/>
+      <c r="G364" s="2"/>
+      <c r="H364" s="2"/>
+      <c r="I364" s="2"/>
+      <c r="J364" s="2"/>
+      <c r="K364" s="2"/>
+      <c r="L364" s="2"/>
+      <c r="M364" s="2"/>
+      <c r="N364" s="2"/>
+      <c r="O364" s="2"/>
+      <c r="P364" s="2"/>
+      <c r="Q364" s="2"/>
+      <c r="R364" s="2"/>
+      <c r="S364" s="2"/>
+      <c r="T364" s="2"/>
+      <c r="U364" s="2"/>
+      <c r="V364" s="2"/>
+      <c r="W364" s="2"/>
+    </row>
+    <row r="365" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A365" s="17"/>
+      <c r="B365" s="17"/>
+      <c r="C365" s="89"/>
+      <c r="D365" s="2"/>
+      <c r="E365" s="2"/>
+      <c r="F365" s="2"/>
+      <c r="G365" s="2"/>
+      <c r="H365" s="2"/>
+      <c r="I365" s="2"/>
+      <c r="J365" s="2"/>
+      <c r="K365" s="2"/>
+      <c r="L365" s="2"/>
+      <c r="M365" s="2"/>
+      <c r="N365" s="2"/>
+      <c r="O365" s="2"/>
+      <c r="P365" s="2"/>
+      <c r="Q365" s="2"/>
+      <c r="R365" s="2"/>
+      <c r="S365" s="2"/>
+      <c r="T365" s="2"/>
+      <c r="U365" s="2"/>
+      <c r="V365" s="2"/>
+      <c r="W365" s="2"/>
+    </row>
+    <row r="366" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A366" s="16"/>
+      <c r="B366" s="16"/>
+      <c r="C366" s="88"/>
+      <c r="D366" s="2"/>
+      <c r="E366" s="2"/>
+      <c r="F366" s="2"/>
+      <c r="G366" s="2"/>
+      <c r="H366" s="2"/>
+      <c r="I366" s="2"/>
+      <c r="J366" s="2"/>
+      <c r="K366" s="2"/>
+      <c r="L366" s="2"/>
+      <c r="M366" s="2"/>
+      <c r="N366" s="2"/>
+      <c r="O366" s="2"/>
+      <c r="P366" s="2"/>
+      <c r="Q366" s="2"/>
+      <c r="R366" s="2"/>
+      <c r="S366" s="2"/>
+      <c r="T366" s="2"/>
+      <c r="U366" s="2"/>
+      <c r="V366" s="2"/>
+      <c r="W366" s="2"/>
+    </row>
+    <row r="367" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A367" s="16"/>
+      <c r="B367" s="16"/>
+      <c r="C367" s="88"/>
+      <c r="D367" s="2"/>
+      <c r="E367" s="2"/>
+      <c r="F367" s="2"/>
+      <c r="G367" s="2"/>
+      <c r="H367" s="2"/>
+      <c r="I367" s="2"/>
+      <c r="J367" s="2"/>
+      <c r="K367" s="2"/>
+      <c r="L367" s="2"/>
+      <c r="M367" s="2"/>
+      <c r="N367" s="2"/>
+      <c r="O367" s="2"/>
+      <c r="P367" s="2"/>
+      <c r="Q367" s="2"/>
+      <c r="R367" s="2"/>
+      <c r="S367" s="2"/>
+      <c r="T367" s="2"/>
+      <c r="U367" s="2"/>
+      <c r="V367" s="2"/>
+      <c r="W367" s="2"/>
+    </row>
+    <row r="368" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A368" s="16"/>
+      <c r="B368" s="16"/>
+      <c r="C368" s="88"/>
+      <c r="D368" s="2"/>
+      <c r="E368" s="2"/>
+      <c r="F368" s="2"/>
+      <c r="G368" s="2"/>
+      <c r="H368" s="2"/>
+      <c r="I368" s="2"/>
+      <c r="J368" s="2"/>
+      <c r="K368" s="2"/>
+      <c r="L368" s="2"/>
+      <c r="M368" s="2"/>
+      <c r="N368" s="2"/>
+      <c r="O368" s="2"/>
+      <c r="P368" s="2"/>
+      <c r="Q368" s="2"/>
+      <c r="R368" s="2"/>
+      <c r="S368" s="2"/>
+      <c r="T368" s="2"/>
+      <c r="U368" s="2"/>
+      <c r="V368" s="2"/>
+      <c r="W368" s="2"/>
+    </row>
+    <row r="369" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A369" s="16"/>
+      <c r="B369" s="16"/>
+      <c r="C369" s="88"/>
+      <c r="D369" s="2"/>
+      <c r="E369" s="2"/>
+      <c r="F369" s="2"/>
+      <c r="G369" s="2"/>
+      <c r="H369" s="2"/>
+      <c r="I369" s="2"/>
+      <c r="J369" s="2"/>
+      <c r="K369" s="2"/>
+      <c r="L369" s="2"/>
+      <c r="M369" s="2"/>
+      <c r="N369" s="2"/>
+      <c r="O369" s="2"/>
+      <c r="P369" s="2"/>
+      <c r="Q369" s="2"/>
+      <c r="R369" s="2"/>
+      <c r="S369" s="2"/>
+      <c r="T369" s="2"/>
+      <c r="U369" s="2"/>
+      <c r="V369" s="2"/>
+      <c r="W369" s="2"/>
+    </row>
+    <row r="370" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A370" s="16"/>
+      <c r="B370" s="16"/>
+      <c r="C370" s="88"/>
+      <c r="D370" s="2"/>
+      <c r="E370" s="2"/>
+      <c r="F370" s="2"/>
+      <c r="G370" s="2"/>
+      <c r="H370" s="2"/>
+      <c r="I370" s="2"/>
+      <c r="J370" s="2"/>
+      <c r="K370" s="2"/>
+      <c r="L370" s="2"/>
+      <c r="M370" s="2"/>
+      <c r="N370" s="2"/>
+      <c r="O370" s="2"/>
+      <c r="P370" s="2"/>
+      <c r="Q370" s="2"/>
+      <c r="R370" s="2"/>
+      <c r="S370" s="2"/>
+      <c r="T370" s="2"/>
+      <c r="U370" s="2"/>
+      <c r="V370" s="2"/>
+      <c r="W370" s="2"/>
+    </row>
+    <row r="371" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A371" s="16"/>
+      <c r="B371" s="16"/>
+      <c r="C371" s="88"/>
+      <c r="D371" s="2"/>
+      <c r="E371" s="2"/>
+      <c r="F371" s="2"/>
+      <c r="G371" s="2"/>
+      <c r="H371" s="2"/>
+      <c r="I371" s="2"/>
+      <c r="J371" s="2"/>
+      <c r="K371" s="2"/>
+      <c r="L371" s="2"/>
+      <c r="M371" s="2"/>
+      <c r="N371" s="2"/>
+      <c r="O371" s="2"/>
+      <c r="P371" s="2"/>
+      <c r="Q371" s="2"/>
+      <c r="R371" s="2"/>
+      <c r="S371" s="2"/>
+      <c r="T371" s="2"/>
+      <c r="U371" s="2"/>
+      <c r="V371" s="2"/>
+      <c r="W371" s="2"/>
+    </row>
+    <row r="372" spans="1:23" ht="13.5" customHeight="1">
+      <c r="A372" s="16"/>
+      <c r="B372" s="16"/>
+      <c r="C372" s="88"/>
+      <c r="D372" s="2"/>
+      <c r="E372" s="2"/>
+      <c r="F372" s="2"/>
+      <c r="G372" s="2"/>
+      <c r="H372" s="2"/>
+      <c r="I372" s="2"/>
+      <c r="J372" s="2"/>
+      <c r="K372" s="2"/>
+      <c r="L372" s="2"/>
+      <c r="M372" s="2"/>
+      <c r="N372" s="2"/>
+      <c r="O372" s="2"/>
+      <c r="P372" s="2"/>
+      <c r="Q372" s="2"/>
+      <c r="R372" s="2"/>
+      <c r="S372" s="2"/>
+      <c r="T372" s="2"/>
+      <c r="U372" s="2"/>
+      <c r="V372" s="2"/>
+      <c r="W372" s="2"/>
+    </row>
+    <row r="373" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A373" s="16"/>
+      <c r="B373" s="16"/>
+      <c r="C373" s="88"/>
+      <c r="D373" s="19"/>
+      <c r="E373" s="19"/>
+      <c r="F373" s="19"/>
+      <c r="G373" s="19"/>
+      <c r="H373" s="19"/>
+      <c r="I373" s="19"/>
+      <c r="J373" s="19"/>
+      <c r="K373" s="19"/>
+      <c r="L373" s="19"/>
+      <c r="M373" s="19"/>
+      <c r="N373" s="19"/>
+      <c r="O373" s="19"/>
+      <c r="P373" s="19"/>
+      <c r="Q373" s="19"/>
+      <c r="R373" s="19"/>
+      <c r="S373" s="19"/>
+      <c r="T373" s="19"/>
+      <c r="U373" s="19"/>
+      <c r="V373" s="19"/>
+      <c r="W373" s="19"/>
+    </row>
+    <row r="374" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A374" s="18"/>
+      <c r="B374" s="18"/>
+      <c r="C374" s="90"/>
+      <c r="D374" s="19"/>
+      <c r="E374" s="19"/>
+      <c r="F374" s="19"/>
+      <c r="G374" s="19"/>
+      <c r="H374" s="19"/>
+      <c r="I374" s="19"/>
+      <c r="J374" s="19"/>
+      <c r="K374" s="19"/>
+      <c r="L374" s="19"/>
+      <c r="M374" s="19"/>
+      <c r="N374" s="19"/>
+      <c r="O374" s="19"/>
+      <c r="P374" s="19"/>
+      <c r="Q374" s="19"/>
+      <c r="R374" s="19"/>
+      <c r="S374" s="19"/>
+      <c r="T374" s="19"/>
+      <c r="U374" s="19"/>
+      <c r="V374" s="19"/>
+      <c r="W374" s="19"/>
+    </row>
+    <row r="375" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A375" s="18"/>
+      <c r="B375" s="18"/>
+      <c r="C375" s="90"/>
+      <c r="D375" s="19"/>
+      <c r="E375" s="19"/>
+      <c r="F375" s="19"/>
+      <c r="G375" s="19"/>
+      <c r="H375" s="19"/>
+      <c r="I375" s="19"/>
+      <c r="J375" s="19"/>
+      <c r="K375" s="19"/>
+      <c r="L375" s="19"/>
+      <c r="M375" s="19"/>
+      <c r="N375" s="19"/>
+      <c r="O375" s="19"/>
+      <c r="P375" s="19"/>
+      <c r="Q375" s="19"/>
+      <c r="R375" s="19"/>
+      <c r="S375" s="19"/>
+      <c r="T375" s="19"/>
+      <c r="U375" s="19"/>
+      <c r="V375" s="19"/>
+      <c r="W375" s="19"/>
+    </row>
+    <row r="376" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A376" s="18"/>
+      <c r="B376" s="18"/>
+      <c r="C376" s="90"/>
+      <c r="D376" s="19"/>
+      <c r="E376" s="19"/>
+      <c r="F376" s="19"/>
+      <c r="G376" s="19"/>
+      <c r="H376" s="19"/>
+      <c r="I376" s="19"/>
+      <c r="J376" s="19"/>
+      <c r="K376" s="19"/>
+      <c r="L376" s="19"/>
+      <c r="M376" s="19"/>
+      <c r="N376" s="19"/>
+      <c r="O376" s="19"/>
+      <c r="P376" s="19"/>
+      <c r="Q376" s="19"/>
+      <c r="R376" s="19"/>
+      <c r="S376" s="19"/>
+      <c r="T376" s="19"/>
+      <c r="U376" s="19"/>
+      <c r="V376" s="19"/>
+      <c r="W376" s="19"/>
+    </row>
+    <row r="377" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A377" s="18"/>
+      <c r="B377" s="18"/>
+      <c r="C377" s="90"/>
+      <c r="D377" s="19"/>
+      <c r="E377" s="19"/>
+      <c r="F377" s="19"/>
+      <c r="G377" s="19"/>
+      <c r="H377" s="19"/>
+      <c r="I377" s="19"/>
+      <c r="J377" s="19"/>
+      <c r="K377" s="19"/>
+      <c r="L377" s="19"/>
+      <c r="M377" s="19"/>
+      <c r="N377" s="19"/>
+      <c r="O377" s="19"/>
+      <c r="P377" s="19"/>
+      <c r="Q377" s="19"/>
+      <c r="R377" s="19"/>
+      <c r="S377" s="19"/>
+      <c r="T377" s="19"/>
+      <c r="U377" s="19"/>
+      <c r="V377" s="19"/>
+      <c r="W377" s="19"/>
+    </row>
+    <row r="378" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A378" s="18"/>
+      <c r="B378" s="18"/>
+      <c r="C378" s="90"/>
+      <c r="D378" s="19"/>
+      <c r="E378" s="19"/>
+      <c r="F378" s="19"/>
+      <c r="G378" s="19"/>
+      <c r="H378" s="19"/>
+      <c r="I378" s="19"/>
+      <c r="J378" s="19"/>
+      <c r="K378" s="19"/>
+      <c r="L378" s="19"/>
+      <c r="M378" s="19"/>
+      <c r="N378" s="19"/>
+      <c r="O378" s="19"/>
+      <c r="P378" s="19"/>
+      <c r="Q378" s="19"/>
+      <c r="R378" s="19"/>
+      <c r="S378" s="19"/>
+      <c r="T378" s="19"/>
+      <c r="U378" s="19"/>
+      <c r="V378" s="19"/>
+      <c r="W378" s="19"/>
+    </row>
+    <row r="379" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A379" s="18"/>
+      <c r="B379" s="18"/>
+      <c r="C379" s="90"/>
+      <c r="D379" s="19"/>
+      <c r="E379" s="19"/>
+      <c r="F379" s="19"/>
+      <c r="G379" s="19"/>
+      <c r="H379" s="19"/>
+      <c r="I379" s="19"/>
+      <c r="J379" s="19"/>
+      <c r="K379" s="19"/>
+      <c r="L379" s="19"/>
+      <c r="M379" s="19"/>
+      <c r="N379" s="19"/>
+      <c r="O379" s="19"/>
+      <c r="P379" s="19"/>
+      <c r="Q379" s="19"/>
+      <c r="R379" s="19"/>
+      <c r="S379" s="19"/>
+      <c r="T379" s="19"/>
+      <c r="U379" s="19"/>
+      <c r="V379" s="19"/>
+      <c r="W379" s="19"/>
+    </row>
+    <row r="380" spans="1:23" ht="15.75" customHeight="1">
       <c r="C380" s="79"/>
     </row>
-    <row r="381" spans="3:3" ht="15.75" customHeight="1">
+    <row r="381" spans="1:23" ht="15.75" customHeight="1">
       <c r="C381" s="79"/>
     </row>
-    <row r="382" spans="3:3" ht="15.75" customHeight="1">
+    <row r="382" spans="1:23" ht="15.75" customHeight="1">
       <c r="C382" s="79"/>
     </row>
-    <row r="383" spans="3:3" ht="15.75" customHeight="1">
+    <row r="383" spans="1:23" ht="15.75" customHeight="1">
       <c r="C383" s="79"/>
     </row>
-    <row r="384" spans="3:3" ht="15.75" customHeight="1">
+    <row r="384" spans="1:23" ht="15.75" customHeight="1">
       <c r="C384" s="79"/>
     </row>
     <row r="385" spans="3:3" ht="15.75" customHeight="1">
@@ -15717,25 +16328,59 @@
     <row r="669" spans="3:3" ht="15.75" customHeight="1">
       <c r="C669" s="79"/>
     </row>
-    <row r="670" spans="3:3" ht="15.75" customHeight="1"/>
-    <row r="671" spans="3:3" ht="15.75" customHeight="1"/>
-    <row r="672" spans="3:3" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="670" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C670" s="79"/>
+    </row>
+    <row r="671" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C671" s="79"/>
+    </row>
+    <row r="672" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C672" s="79"/>
+    </row>
+    <row r="673" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C673" s="79"/>
+    </row>
+    <row r="674" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C674" s="79"/>
+    </row>
+    <row r="675" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C675" s="79"/>
+    </row>
+    <row r="676" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C676" s="79"/>
+    </row>
+    <row r="677" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C677" s="79"/>
+    </row>
+    <row r="678" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C678" s="79"/>
+    </row>
+    <row r="679" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C679" s="79"/>
+    </row>
+    <row r="680" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C680" s="79"/>
+    </row>
+    <row r="681" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C681" s="79"/>
+    </row>
+    <row r="682" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C682" s="79"/>
+    </row>
+    <row r="683" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C683" s="79"/>
+    </row>
+    <row r="684" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C684" s="79"/>
+    </row>
+    <row r="685" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C685" s="79"/>
+    </row>
+    <row r="686" spans="3:3" ht="15.75" customHeight="1">
+      <c r="C686" s="79"/>
+    </row>
+    <row r="687" spans="3:3" ht="15.75" customHeight="1"/>
+    <row r="688" spans="3:3" ht="15.75" customHeight="1"/>
     <row r="689" ht="15.75" customHeight="1"/>
     <row r="690" ht="15.75" customHeight="1"/>
     <row r="691" ht="15.75" customHeight="1"/>
@@ -16048,13 +16693,32 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
+    <row r="1015" ht="15.75" customHeight="1"/>
+    <row r="1016" ht="15.75" customHeight="1"/>
+    <row r="1017" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{315649E6-A7C6-4DA7-9C45-C23DCDAE247B}"/>
-    <hyperlink ref="C149" r:id="rId2" xr:uid="{680B6020-A699-43A7-A462-0934E038AD85}"/>
+    <hyperlink ref="C166" r:id="rId2" xr:uid="{680B6020-A699-43A7-A462-0934E038AD85}"/>
     <hyperlink ref="C2" r:id="rId3" xr:uid="{51DC6A58-9863-4BA4-8D62-1794D9D55E09}"/>
     <hyperlink ref="D2" r:id="rId4" xr:uid="{1F6963B5-04E2-4635-B2CC-308E91119C44}"/>
     <hyperlink ref="B2" r:id="rId5" xr:uid="{8629E203-331A-40A5-8963-16BA6F44E7E0}"/>
+    <hyperlink ref="B5" r:id="rId6" tooltip="mailto:autochrisc4@mmh-demo.com" display="mailto:Autochrisc4@mmh-demo.com" xr:uid="{D1666DDB-633D-47C3-AC1F-E8A14BD8B3D3}"/>
+    <hyperlink ref="B4" r:id="rId7" tooltip="mailto:autochrisc4@mmh-demo.com" display="mailto:Autochrisc4@mmh-demo.com" xr:uid="{F7DB5A72-67FE-429D-AD24-95A3552918F2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -16110,8 +16774,8 @@
       <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>1124</v>
+      <c r="B2" s="51" t="s">
+        <v>1261</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1048</v>
@@ -16161,7 +16825,7 @@
         <v>218</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="C12" s="76" t="s">
         <v>1132</v>
@@ -16172,10 +16836,10 @@
         <v>557</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -16186,7 +16850,7 @@
         <v>559</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="30">
@@ -16194,10 +16858,10 @@
         <v>375</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>1235</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -16230,7 +16894,7 @@
         <v>1079</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -16584,7 +17248,7 @@
         <v>571</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>573</v>
@@ -16596,7 +17260,7 @@
         <v>574</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>576</v>
@@ -16607,7 +17271,7 @@
         <v>577</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="C70" s="9" t="s">
         <v>578</v>
@@ -16618,7 +17282,7 @@
         <v>579</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="C71" s="9" t="s">
         <v>581</v>
@@ -16665,7 +17329,7 @@
         <v>589</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>591</v>
@@ -16698,7 +17362,7 @@
         <v>382</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" customHeight="1"/>
@@ -16707,10 +17371,10 @@
         <v>596</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15.75" customHeight="1">
@@ -16859,10 +17523,10 @@
         <v>626</v>
       </c>
       <c r="B110" s="9" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C110" s="9" t="s">
         <v>1242</v>
-      </c>
-      <c r="C110" s="9" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15.75" customHeight="1">
@@ -16870,10 +17534,10 @@
         <v>627</v>
       </c>
       <c r="B111" s="9" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C111" s="9" t="s">
         <v>1243</v>
-      </c>
-      <c r="C111" s="9" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15.75" customHeight="1">
@@ -16881,10 +17545,10 @@
         <v>628</v>
       </c>
       <c r="B112" s="9" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C112" s="9" t="s">
         <v>1244</v>
-      </c>
-      <c r="C112" s="9" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75" customHeight="1"/>
@@ -16893,10 +17557,10 @@
         <v>629</v>
       </c>
       <c r="B114" s="9" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C114" s="9" t="s">
         <v>1250</v>
-      </c>
-      <c r="C114" s="9" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75" customHeight="1">
@@ -16904,10 +17568,10 @@
         <v>630</v>
       </c>
       <c r="B115" s="9" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C115" s="9" t="s">
         <v>1251</v>
-      </c>
-      <c r="C115" s="9" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15.75" customHeight="1">
@@ -16915,10 +17579,10 @@
         <v>631</v>
       </c>
       <c r="B116" s="9" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C116" s="9" t="s">
         <v>1252</v>
-      </c>
-      <c r="C116" s="9" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15.75" customHeight="1"/>
@@ -16964,7 +17628,7 @@
         <v>641</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75" customHeight="1"/>
@@ -16976,7 +17640,7 @@
         <v>643</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15.75" customHeight="1">
@@ -16987,7 +17651,7 @@
         <v>645</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15.75" customHeight="1">
@@ -16998,7 +17662,7 @@
         <v>645</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15.75" customHeight="1"/>
@@ -17906,7 +18570,7 @@
         <v>188</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="C229" s="76" t="s">
         <v>1065</v>
@@ -17940,7 +18604,7 @@
         <v>193</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="C233" s="76" t="s">
         <v>1066</v>
@@ -20632,6 +21296,7 @@
     <hyperlink ref="B466" r:id="rId18" xr:uid="{8CF160AF-E775-46A9-B0E9-8CA08F5C87BE}"/>
     <hyperlink ref="C16" r:id="rId19" xr:uid="{6BAF1573-2EFB-4846-8986-088AD7BBB8AE}"/>
     <hyperlink ref="C3" r:id="rId20" xr:uid="{0014955C-7397-4069-B2DC-1F6C4B21F53F}"/>
+    <hyperlink ref="B2" r:id="rId21" xr:uid="{FDCB0381-0C4A-4281-8093-8D3F723B9334}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -20644,7 +21309,7 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="54.140625" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="90" style="96" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="90" style="95" customWidth="1" collapsed="1"/>
     <col min="3" max="22" width="8.7109375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
@@ -23802,7 +24467,7 @@
       <c r="A117" s="25" t="s">
         <v>335</v>
       </c>
-      <c r="B117" s="93" t="s">
+      <c r="B117" s="92" t="s">
         <v>1198</v>
       </c>
       <c r="C117" s="18"/>
@@ -23930,7 +24595,7 @@
       <c r="A122" s="24" t="s">
         <v>337</v>
       </c>
-      <c r="B122" s="94" t="s">
+      <c r="B122" s="93" t="s">
         <v>310</v>
       </c>
       <c r="C122" s="18"/>
@@ -24730,7 +25395,7 @@
       <c r="A152" s="18" t="s">
         <v>363</v>
       </c>
-      <c r="B152" s="95" t="s">
+      <c r="B152" s="94" t="s">
         <v>364</v>
       </c>
       <c r="C152" s="18"/>
@@ -24758,7 +25423,7 @@
       <c r="A153" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="B153" s="95" t="s">
+      <c r="B153" s="94" t="s">
         <v>355</v>
       </c>
       <c r="C153" s="18"/>
@@ -24786,7 +25451,7 @@
       <c r="A154" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="B154" s="95" t="s">
+      <c r="B154" s="94" t="s">
         <v>367</v>
       </c>
       <c r="C154" s="18"/>
@@ -24814,7 +25479,7 @@
       <c r="A155" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="B155" s="95" t="s">
+      <c r="B155" s="94" t="s">
         <v>369</v>
       </c>
       <c r="C155" s="18"/>
@@ -24840,7 +25505,7 @@
     </row>
     <row r="156" spans="1:22" ht="15.75" customHeight="1">
       <c r="A156" s="18"/>
-      <c r="B156" s="95"/>
+      <c r="B156" s="94"/>
       <c r="C156" s="18"/>
       <c r="D156" s="18"/>
       <c r="E156" s="18"/>
@@ -24866,7 +25531,7 @@
       <c r="A157" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="B157" s="95" t="s">
+      <c r="B157" s="94" t="s">
         <v>1079</v>
       </c>
       <c r="C157" s="18"/>
@@ -24892,7 +25557,7 @@
     </row>
     <row r="158" spans="1:22" ht="15.75" customHeight="1">
       <c r="A158" s="18"/>
-      <c r="B158" s="95"/>
+      <c r="B158" s="94"/>
       <c r="C158" s="18"/>
       <c r="D158" s="18"/>
       <c r="E158" s="18"/>
@@ -24918,7 +25583,7 @@
       <c r="A159" s="18" t="s">
         <v>370</v>
       </c>
-      <c r="B159" s="95" t="s">
+      <c r="B159" s="94" t="s">
         <v>1203</v>
       </c>
       <c r="C159" s="18"/>
@@ -24944,7 +25609,7 @@
     </row>
     <row r="160" spans="1:22" ht="15.75" customHeight="1">
       <c r="A160" s="18"/>
-      <c r="B160" s="95"/>
+      <c r="B160" s="94"/>
       <c r="C160" s="18"/>
       <c r="D160" s="18"/>
       <c r="E160" s="18"/>
@@ -24970,7 +25635,7 @@
       <c r="A161" s="18" t="s">
         <v>371</v>
       </c>
-      <c r="B161" s="95" t="s">
+      <c r="B161" s="94" t="s">
         <v>372</v>
       </c>
       <c r="C161" s="18"/>
@@ -24998,7 +25663,7 @@
       <c r="A162" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="B162" s="95" t="s">
+      <c r="B162" s="94" t="s">
         <v>374</v>
       </c>
       <c r="C162" s="18"/>
@@ -25026,7 +25691,7 @@
       <c r="A163" s="18" t="s">
         <v>375</v>
       </c>
-      <c r="B163" s="95" t="s">
+      <c r="B163" s="94" t="s">
         <v>376</v>
       </c>
       <c r="C163" s="18"/>
@@ -25052,7 +25717,7 @@
     </row>
     <row r="164" spans="1:22" ht="15.75" customHeight="1">
       <c r="A164" s="18"/>
-      <c r="B164" s="95"/>
+      <c r="B164" s="94"/>
       <c r="C164" s="18"/>
       <c r="D164" s="18"/>
       <c r="E164" s="18"/>
@@ -25106,7 +25771,7 @@
       <c r="A166" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="B166" s="95" t="s">
+      <c r="B166" s="94" t="s">
         <v>380</v>
       </c>
       <c r="C166" s="18"/>
@@ -25132,7 +25797,7 @@
     </row>
     <row r="167" spans="1:22" ht="15.75" customHeight="1">
       <c r="A167" s="18"/>
-      <c r="B167" s="95"/>
+      <c r="B167" s="94"/>
       <c r="C167" s="18"/>
       <c r="D167" s="18"/>
       <c r="E167" s="18"/>
@@ -25158,7 +25823,7 @@
       <c r="A168" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B168" s="95" t="s">
+      <c r="B168" s="94" t="s">
         <v>244</v>
       </c>
       <c r="C168" s="18"/>
@@ -25186,7 +25851,7 @@
       <c r="A169" s="18" t="s">
         <v>381</v>
       </c>
-      <c r="B169" s="95" t="s">
+      <c r="B169" s="94" t="s">
         <v>1087</v>
       </c>
       <c r="C169" s="18"/>
@@ -25214,7 +25879,7 @@
       <c r="A170" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="B170" s="95" t="s">
+      <c r="B170" s="94" t="s">
         <v>384</v>
       </c>
       <c r="C170" s="18"/>
@@ -25242,7 +25907,7 @@
       <c r="A171" s="18" t="s">
         <v>385</v>
       </c>
-      <c r="B171" s="95" t="s">
+      <c r="B171" s="94" t="s">
         <v>386</v>
       </c>
       <c r="C171" s="18"/>
@@ -25268,7 +25933,7 @@
     </row>
     <row r="172" spans="1:22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A172" s="18"/>
-      <c r="B172" s="95"/>
+      <c r="B172" s="94"/>
       <c r="C172" s="18"/>
       <c r="D172" s="18"/>
       <c r="E172" s="18"/>
@@ -25320,7 +25985,7 @@
     </row>
     <row r="174" spans="1:22" ht="15.75" customHeight="1">
       <c r="A174" s="18"/>
-      <c r="B174" s="95"/>
+      <c r="B174" s="94"/>
       <c r="C174" s="18"/>
       <c r="D174" s="18"/>
       <c r="E174" s="18"/>
@@ -25343,10 +26008,10 @@
       <c r="V174" s="18"/>
     </row>
     <row r="175" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A175" s="92" t="s">
+      <c r="A175" s="91" t="s">
         <v>1206</v>
       </c>
-      <c r="B175" s="95" t="s">
+      <c r="B175" s="94" t="s">
         <v>1208</v>
       </c>
       <c r="C175" s="18"/>
@@ -25371,10 +26036,10 @@
       <c r="V175" s="18"/>
     </row>
     <row r="176" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A176" s="92" t="s">
+      <c r="A176" s="91" t="s">
         <v>1207</v>
       </c>
-      <c r="B176" s="95" t="s">
+      <c r="B176" s="94" t="s">
         <v>1209</v>
       </c>
       <c r="C176" s="18"/>
@@ -25399,10 +26064,10 @@
       <c r="V176" s="18"/>
     </row>
     <row r="177" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A177" s="92" t="s">
+      <c r="A177" s="91" t="s">
         <v>1210</v>
       </c>
-      <c r="B177" s="95" t="s">
+      <c r="B177" s="94" t="s">
         <v>1208</v>
       </c>
       <c r="C177" s="18"/>
@@ -25427,10 +26092,10 @@
       <c r="V177" s="18"/>
     </row>
     <row r="178" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A178" s="92" t="s">
+      <c r="A178" s="91" t="s">
         <v>1211</v>
       </c>
-      <c r="B178" s="95" t="s">
+      <c r="B178" s="94" t="s">
         <v>1213</v>
       </c>
       <c r="C178" s="18"/>
@@ -25455,10 +26120,10 @@
       <c r="V178" s="18"/>
     </row>
     <row r="179" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A179" s="92" t="s">
+      <c r="A179" s="91" t="s">
         <v>1214</v>
       </c>
-      <c r="B179" s="95" t="s">
+      <c r="B179" s="94" t="s">
         <v>1209</v>
       </c>
       <c r="C179" s="18"/>
@@ -25484,7 +26149,7 @@
     </row>
     <row r="180" spans="1:22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A180" s="18"/>
-      <c r="B180" s="95"/>
+      <c r="B180" s="94"/>
       <c r="C180" s="18"/>
       <c r="D180" s="18"/>
       <c r="E180" s="18"/>
@@ -25567,10 +26232,10 @@
       <c r="V182" s="18"/>
     </row>
     <row r="183" spans="1:22" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A183" s="92" t="s">
+      <c r="A183" s="91" t="s">
         <v>1215</v>
       </c>
-      <c r="B183" s="95" t="s">
+      <c r="B183" s="94" t="s">
         <v>1208</v>
       </c>
       <c r="C183" s="18"/>
@@ -25625,10 +26290,10 @@
       <c r="V184" s="18"/>
     </row>
     <row r="185" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A185" s="92" t="s">
+      <c r="A185" s="91" t="s">
         <v>1216</v>
       </c>
-      <c r="B185" s="95" t="s">
+      <c r="B185" s="94" t="s">
         <v>1212</v>
       </c>
       <c r="C185" s="18"/>
@@ -25654,7 +26319,7 @@
     </row>
     <row r="186" spans="1:22" ht="15.75" customHeight="1">
       <c r="A186" s="18"/>
-      <c r="B186" s="95"/>
+      <c r="B186" s="94"/>
       <c r="C186" s="18"/>
       <c r="D186" s="18"/>
       <c r="E186" s="18"/>
@@ -25677,10 +26342,10 @@
       <c r="V186" s="18"/>
     </row>
     <row r="187" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A187" s="92" t="s">
+      <c r="A187" s="91" t="s">
         <v>1217</v>
       </c>
-      <c r="B187" s="95" t="s">
+      <c r="B187" s="94" t="s">
         <v>1208</v>
       </c>
       <c r="C187" s="18"/>
@@ -25706,7 +26371,7 @@
     </row>
     <row r="188" spans="1:22" ht="15.75" customHeight="1">
       <c r="A188" s="18"/>
-      <c r="B188" s="95"/>
+      <c r="B188" s="94"/>
       <c r="C188" s="18"/>
       <c r="D188" s="18"/>
       <c r="E188" s="18"/>
@@ -25730,7 +26395,7 @@
     </row>
     <row r="189" spans="1:22" ht="15.75" customHeight="1">
       <c r="A189" s="18"/>
-      <c r="B189" s="95"/>
+      <c r="B189" s="94"/>
       <c r="C189" s="18"/>
       <c r="D189" s="18"/>
       <c r="E189" s="18"/>
@@ -25753,8 +26418,8 @@
       <c r="V189" s="18"/>
     </row>
     <row r="190" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A190" s="92"/>
-      <c r="B190" s="95"/>
+      <c r="A190" s="91"/>
+      <c r="B190" s="94"/>
       <c r="C190" s="18"/>
       <c r="D190" s="18"/>
       <c r="E190" s="18"/>
@@ -25778,7 +26443,7 @@
     </row>
     <row r="191" spans="1:22" ht="15.75" customHeight="1">
       <c r="A191" s="18"/>
-      <c r="B191" s="95"/>
+      <c r="B191" s="94"/>
       <c r="C191" s="18"/>
       <c r="D191" s="18"/>
       <c r="E191" s="18"/>
@@ -25802,7 +26467,7 @@
     </row>
     <row r="192" spans="1:22" ht="15.75" customHeight="1">
       <c r="A192" s="18"/>
-      <c r="B192" s="95"/>
+      <c r="B192" s="94"/>
       <c r="C192" s="18"/>
       <c r="D192" s="18"/>
       <c r="E192" s="18"/>
@@ -25826,7 +26491,7 @@
     </row>
     <row r="193" spans="1:22" ht="15.75" customHeight="1">
       <c r="A193" s="18"/>
-      <c r="B193" s="95"/>
+      <c r="B193" s="94"/>
       <c r="C193" s="18"/>
       <c r="D193" s="18"/>
       <c r="E193" s="18"/>
@@ -25850,7 +26515,7 @@
     </row>
     <row r="194" spans="1:22" ht="15.75" customHeight="1">
       <c r="A194" s="18"/>
-      <c r="B194" s="95"/>
+      <c r="B194" s="94"/>
       <c r="C194" s="18"/>
       <c r="D194" s="18"/>
       <c r="E194" s="18"/>
@@ -25874,7 +26539,7 @@
     </row>
     <row r="195" spans="1:22" ht="15.75" customHeight="1">
       <c r="A195" s="18"/>
-      <c r="B195" s="95"/>
+      <c r="B195" s="94"/>
       <c r="C195" s="18"/>
       <c r="D195" s="18"/>
       <c r="E195" s="18"/>
@@ -25898,7 +26563,7 @@
     </row>
     <row r="196" spans="1:22" ht="15.75" customHeight="1">
       <c r="A196" s="18"/>
-      <c r="B196" s="95"/>
+      <c r="B196" s="94"/>
       <c r="C196" s="18"/>
       <c r="D196" s="18"/>
       <c r="E196" s="18"/>
@@ -25922,7 +26587,7 @@
     </row>
     <row r="197" spans="1:22" ht="15.75" customHeight="1">
       <c r="A197" s="18"/>
-      <c r="B197" s="95"/>
+      <c r="B197" s="94"/>
       <c r="C197" s="18"/>
       <c r="D197" s="18"/>
       <c r="E197" s="18"/>
@@ -25946,7 +26611,7 @@
     </row>
     <row r="198" spans="1:22" ht="15.75" customHeight="1">
       <c r="A198" s="18"/>
-      <c r="B198" s="95"/>
+      <c r="B198" s="94"/>
       <c r="C198" s="18"/>
       <c r="D198" s="18"/>
       <c r="E198" s="18"/>
@@ -25970,7 +26635,7 @@
     </row>
     <row r="199" spans="1:22" ht="15.75" customHeight="1">
       <c r="A199" s="18"/>
-      <c r="B199" s="95"/>
+      <c r="B199" s="94"/>
       <c r="C199" s="18"/>
       <c r="D199" s="18"/>
       <c r="E199" s="18"/>
@@ -25994,7 +26659,7 @@
     </row>
     <row r="200" spans="1:22" ht="15.75" customHeight="1">
       <c r="A200" s="18"/>
-      <c r="B200" s="95"/>
+      <c r="B200" s="94"/>
       <c r="C200" s="18"/>
       <c r="D200" s="18"/>
       <c r="E200" s="18"/>
@@ -26018,7 +26683,7 @@
     </row>
     <row r="201" spans="1:22" ht="15.75" customHeight="1">
       <c r="A201" s="18"/>
-      <c r="B201" s="95"/>
+      <c r="B201" s="94"/>
       <c r="C201" s="18"/>
       <c r="D201" s="18"/>
       <c r="E201" s="18"/>
@@ -26042,7 +26707,7 @@
     </row>
     <row r="202" spans="1:22" ht="15.75" customHeight="1">
       <c r="A202" s="18"/>
-      <c r="B202" s="95"/>
+      <c r="B202" s="94"/>
       <c r="C202" s="18"/>
       <c r="D202" s="18"/>
       <c r="E202" s="18"/>
@@ -26066,7 +26731,7 @@
     </row>
     <row r="203" spans="1:22" ht="15.75" customHeight="1">
       <c r="A203" s="18"/>
-      <c r="B203" s="95"/>
+      <c r="B203" s="94"/>
       <c r="C203" s="18"/>
       <c r="D203" s="18"/>
       <c r="E203" s="18"/>
@@ -26090,7 +26755,7 @@
     </row>
     <row r="204" spans="1:22" ht="15.75" customHeight="1">
       <c r="A204" s="18"/>
-      <c r="B204" s="95"/>
+      <c r="B204" s="94"/>
       <c r="C204" s="18"/>
       <c r="D204" s="18"/>
       <c r="E204" s="18"/>
@@ -26114,7 +26779,7 @@
     </row>
     <row r="205" spans="1:22" ht="15.75" customHeight="1">
       <c r="A205" s="18"/>
-      <c r="B205" s="95"/>
+      <c r="B205" s="94"/>
       <c r="C205" s="18"/>
       <c r="D205" s="18"/>
       <c r="E205" s="18"/>
@@ -26138,7 +26803,7 @@
     </row>
     <row r="206" spans="1:22" ht="15.75" customHeight="1">
       <c r="A206" s="18"/>
-      <c r="B206" s="95"/>
+      <c r="B206" s="94"/>
       <c r="C206" s="18"/>
       <c r="D206" s="18"/>
       <c r="E206" s="18"/>
@@ -26162,7 +26827,7 @@
     </row>
     <row r="207" spans="1:22" ht="15.75" customHeight="1">
       <c r="A207" s="18"/>
-      <c r="B207" s="95"/>
+      <c r="B207" s="94"/>
       <c r="C207" s="18"/>
       <c r="D207" s="18"/>
       <c r="E207" s="18"/>
@@ -26186,7 +26851,7 @@
     </row>
     <row r="208" spans="1:22" ht="15.75" customHeight="1">
       <c r="A208" s="18"/>
-      <c r="B208" s="95"/>
+      <c r="B208" s="94"/>
       <c r="C208" s="18"/>
       <c r="D208" s="18"/>
       <c r="E208" s="18"/>
@@ -26210,7 +26875,7 @@
     </row>
     <row r="209" spans="1:22" ht="15.75" customHeight="1">
       <c r="A209" s="18"/>
-      <c r="B209" s="95"/>
+      <c r="B209" s="94"/>
       <c r="C209" s="18"/>
       <c r="D209" s="18"/>
       <c r="E209" s="18"/>
@@ -26234,7 +26899,7 @@
     </row>
     <row r="210" spans="1:22" ht="15.75" customHeight="1">
       <c r="A210" s="18"/>
-      <c r="B210" s="95"/>
+      <c r="B210" s="94"/>
       <c r="C210" s="18"/>
       <c r="D210" s="18"/>
       <c r="E210" s="18"/>
@@ -26258,7 +26923,7 @@
     </row>
     <row r="211" spans="1:22" ht="15.75" customHeight="1">
       <c r="A211" s="18"/>
-      <c r="B211" s="95"/>
+      <c r="B211" s="94"/>
       <c r="C211" s="18"/>
       <c r="D211" s="18"/>
       <c r="E211" s="18"/>
@@ -26282,7 +26947,7 @@
     </row>
     <row r="212" spans="1:22" ht="15.75" customHeight="1">
       <c r="A212" s="18"/>
-      <c r="B212" s="95"/>
+      <c r="B212" s="94"/>
       <c r="C212" s="18"/>
       <c r="D212" s="18"/>
       <c r="E212" s="18"/>
@@ -26306,7 +26971,7 @@
     </row>
     <row r="213" spans="1:22" ht="15.75" customHeight="1">
       <c r="A213" s="18"/>
-      <c r="B213" s="95"/>
+      <c r="B213" s="94"/>
       <c r="C213" s="18"/>
       <c r="D213" s="18"/>
       <c r="E213" s="18"/>
@@ -26330,7 +26995,7 @@
     </row>
     <row r="214" spans="1:22" ht="15.75" customHeight="1">
       <c r="A214" s="18"/>
-      <c r="B214" s="95"/>
+      <c r="B214" s="94"/>
       <c r="C214" s="18"/>
       <c r="D214" s="18"/>
       <c r="E214" s="18"/>
@@ -26354,7 +27019,7 @@
     </row>
     <row r="215" spans="1:22" ht="15.75" customHeight="1">
       <c r="A215" s="18"/>
-      <c r="B215" s="95"/>
+      <c r="B215" s="94"/>
       <c r="C215" s="18"/>
       <c r="D215" s="18"/>
       <c r="E215" s="18"/>
@@ -26378,7 +27043,7 @@
     </row>
     <row r="216" spans="1:22" ht="15.75" customHeight="1">
       <c r="A216" s="18"/>
-      <c r="B216" s="95"/>
+      <c r="B216" s="94"/>
       <c r="C216" s="18"/>
       <c r="D216" s="18"/>
       <c r="E216" s="18"/>
@@ -26402,7 +27067,7 @@
     </row>
     <row r="217" spans="1:22" ht="15.75" customHeight="1">
       <c r="A217" s="18"/>
-      <c r="B217" s="95"/>
+      <c r="B217" s="94"/>
       <c r="C217" s="18"/>
       <c r="D217" s="18"/>
       <c r="E217" s="18"/>
@@ -26426,7 +27091,7 @@
     </row>
     <row r="218" spans="1:22" ht="15.75" customHeight="1">
       <c r="A218" s="18"/>
-      <c r="B218" s="95"/>
+      <c r="B218" s="94"/>
       <c r="C218" s="18"/>
       <c r="D218" s="18"/>
       <c r="E218" s="18"/>
@@ -26450,7 +27115,7 @@
     </row>
     <row r="219" spans="1:22" ht="15.75" customHeight="1">
       <c r="A219" s="18"/>
-      <c r="B219" s="95"/>
+      <c r="B219" s="94"/>
       <c r="C219" s="18"/>
       <c r="D219" s="18"/>
       <c r="E219" s="18"/>
@@ -26474,7 +27139,7 @@
     </row>
     <row r="220" spans="1:22" ht="15.75" customHeight="1">
       <c r="A220" s="18"/>
-      <c r="B220" s="95"/>
+      <c r="B220" s="94"/>
       <c r="C220" s="18"/>
       <c r="D220" s="18"/>
       <c r="E220" s="18"/>
@@ -26498,7 +27163,7 @@
     </row>
     <row r="221" spans="1:22" ht="15.75" customHeight="1">
       <c r="A221" s="18"/>
-      <c r="B221" s="95"/>
+      <c r="B221" s="94"/>
       <c r="C221" s="18"/>
       <c r="D221" s="18"/>
       <c r="E221" s="18"/>
@@ -26522,7 +27187,7 @@
     </row>
     <row r="222" spans="1:22" ht="15.75" customHeight="1">
       <c r="A222" s="18"/>
-      <c r="B222" s="95"/>
+      <c r="B222" s="94"/>
       <c r="C222" s="18"/>
       <c r="D222" s="18"/>
       <c r="E222" s="18"/>
@@ -26546,7 +27211,7 @@
     </row>
     <row r="223" spans="1:22" ht="15.75" customHeight="1">
       <c r="A223" s="18"/>
-      <c r="B223" s="95"/>
+      <c r="B223" s="94"/>
       <c r="C223" s="18"/>
       <c r="D223" s="18"/>
       <c r="E223" s="18"/>
@@ -26570,7 +27235,7 @@
     </row>
     <row r="224" spans="1:22" ht="15.75" customHeight="1">
       <c r="A224" s="18"/>
-      <c r="B224" s="95"/>
+      <c r="B224" s="94"/>
       <c r="C224" s="18"/>
       <c r="D224" s="18"/>
       <c r="E224" s="18"/>
@@ -26594,7 +27259,7 @@
     </row>
     <row r="225" spans="1:22" ht="15.75" customHeight="1">
       <c r="A225" s="18"/>
-      <c r="B225" s="95"/>
+      <c r="B225" s="94"/>
       <c r="C225" s="18"/>
       <c r="D225" s="18"/>
       <c r="E225" s="18"/>
@@ -26618,7 +27283,7 @@
     </row>
     <row r="226" spans="1:22" ht="15.75" customHeight="1">
       <c r="A226" s="18"/>
-      <c r="B226" s="95"/>
+      <c r="B226" s="94"/>
       <c r="C226" s="18"/>
       <c r="D226" s="18"/>
       <c r="E226" s="18"/>
@@ -26642,7 +27307,7 @@
     </row>
     <row r="227" spans="1:22" ht="15.75" customHeight="1">
       <c r="A227" s="18"/>
-      <c r="B227" s="95"/>
+      <c r="B227" s="94"/>
       <c r="C227" s="18"/>
       <c r="D227" s="18"/>
       <c r="E227" s="18"/>
@@ -26666,7 +27331,7 @@
     </row>
     <row r="228" spans="1:22" ht="15.75" customHeight="1">
       <c r="A228" s="18"/>
-      <c r="B228" s="95"/>
+      <c r="B228" s="94"/>
       <c r="C228" s="18"/>
       <c r="D228" s="18"/>
       <c r="E228" s="18"/>
@@ -26690,7 +27355,7 @@
     </row>
     <row r="229" spans="1:22" ht="15.75" customHeight="1">
       <c r="A229" s="18"/>
-      <c r="B229" s="95"/>
+      <c r="B229" s="94"/>
       <c r="C229" s="18"/>
       <c r="D229" s="18"/>
       <c r="E229" s="18"/>
@@ -26714,7 +27379,7 @@
     </row>
     <row r="230" spans="1:22" ht="15.75" customHeight="1">
       <c r="A230" s="18"/>
-      <c r="B230" s="95"/>
+      <c r="B230" s="94"/>
       <c r="C230" s="18"/>
       <c r="D230" s="18"/>
       <c r="E230" s="18"/>
@@ -26738,7 +27403,7 @@
     </row>
     <row r="231" spans="1:22" ht="15.75" customHeight="1">
       <c r="A231" s="18"/>
-      <c r="B231" s="95"/>
+      <c r="B231" s="94"/>
       <c r="C231" s="18"/>
       <c r="D231" s="18"/>
       <c r="E231" s="18"/>
@@ -26762,7 +27427,7 @@
     </row>
     <row r="232" spans="1:22" ht="15.75" customHeight="1">
       <c r="A232" s="18"/>
-      <c r="B232" s="95"/>
+      <c r="B232" s="94"/>
       <c r="C232" s="18"/>
       <c r="D232" s="18"/>
       <c r="E232" s="18"/>
@@ -26786,7 +27451,7 @@
     </row>
     <row r="233" spans="1:22" ht="15.75" customHeight="1">
       <c r="A233" s="18"/>
-      <c r="B233" s="95"/>
+      <c r="B233" s="94"/>
       <c r="C233" s="18"/>
       <c r="D233" s="18"/>
       <c r="E233" s="18"/>
@@ -26810,7 +27475,7 @@
     </row>
     <row r="234" spans="1:22" ht="15.75" customHeight="1">
       <c r="A234" s="18"/>
-      <c r="B234" s="95"/>
+      <c r="B234" s="94"/>
       <c r="C234" s="18"/>
       <c r="D234" s="18"/>
       <c r="E234" s="18"/>
@@ -26834,7 +27499,7 @@
     </row>
     <row r="235" spans="1:22" ht="15.75" customHeight="1">
       <c r="A235" s="18"/>
-      <c r="B235" s="95"/>
+      <c r="B235" s="94"/>
       <c r="C235" s="18"/>
       <c r="D235" s="18"/>
       <c r="E235" s="18"/>
@@ -26858,7 +27523,7 @@
     </row>
     <row r="236" spans="1:22" ht="15.75" customHeight="1">
       <c r="A236" s="18"/>
-      <c r="B236" s="95"/>
+      <c r="B236" s="94"/>
       <c r="C236" s="18"/>
       <c r="D236" s="18"/>
       <c r="E236" s="18"/>
@@ -26882,7 +27547,7 @@
     </row>
     <row r="237" spans="1:22" ht="15.75" customHeight="1">
       <c r="A237" s="18"/>
-      <c r="B237" s="95"/>
+      <c r="B237" s="94"/>
       <c r="C237" s="18"/>
       <c r="D237" s="18"/>
       <c r="E237" s="18"/>
@@ -26906,7 +27571,7 @@
     </row>
     <row r="238" spans="1:22" ht="15.75" customHeight="1">
       <c r="A238" s="18"/>
-      <c r="B238" s="95"/>
+      <c r="B238" s="94"/>
       <c r="C238" s="18"/>
       <c r="D238" s="18"/>
       <c r="E238" s="18"/>
@@ -26930,7 +27595,7 @@
     </row>
     <row r="239" spans="1:22" ht="15.75" customHeight="1">
       <c r="A239" s="18"/>
-      <c r="B239" s="95"/>
+      <c r="B239" s="94"/>
       <c r="C239" s="18"/>
       <c r="D239" s="18"/>
       <c r="E239" s="18"/>
@@ -26954,7 +27619,7 @@
     </row>
     <row r="240" spans="1:22" ht="15.75" customHeight="1">
       <c r="A240" s="18"/>
-      <c r="B240" s="95"/>
+      <c r="B240" s="94"/>
       <c r="C240" s="18"/>
       <c r="D240" s="18"/>
       <c r="E240" s="18"/>
@@ -26978,7 +27643,7 @@
     </row>
     <row r="241" spans="1:22" ht="15.75" customHeight="1">
       <c r="A241" s="18"/>
-      <c r="B241" s="95"/>
+      <c r="B241" s="94"/>
       <c r="C241" s="18"/>
       <c r="D241" s="18"/>
       <c r="E241" s="18"/>
@@ -27002,7 +27667,7 @@
     </row>
     <row r="242" spans="1:22" ht="15.75" customHeight="1">
       <c r="A242" s="18"/>
-      <c r="B242" s="95"/>
+      <c r="B242" s="94"/>
       <c r="C242" s="18"/>
       <c r="D242" s="18"/>
       <c r="E242" s="18"/>
@@ -27026,7 +27691,7 @@
     </row>
     <row r="243" spans="1:22" ht="15.75" customHeight="1">
       <c r="A243" s="18"/>
-      <c r="B243" s="95"/>
+      <c r="B243" s="94"/>
       <c r="C243" s="18"/>
       <c r="D243" s="18"/>
       <c r="E243" s="18"/>
@@ -27050,7 +27715,7 @@
     </row>
     <row r="244" spans="1:22" ht="15.75" customHeight="1">
       <c r="A244" s="18"/>
-      <c r="B244" s="95"/>
+      <c r="B244" s="94"/>
       <c r="C244" s="18"/>
       <c r="D244" s="18"/>
       <c r="E244" s="18"/>
@@ -27074,7 +27739,7 @@
     </row>
     <row r="245" spans="1:22" ht="15.75" customHeight="1">
       <c r="A245" s="18"/>
-      <c r="B245" s="95"/>
+      <c r="B245" s="94"/>
       <c r="C245" s="18"/>
       <c r="D245" s="18"/>
       <c r="E245" s="18"/>
@@ -27098,7 +27763,7 @@
     </row>
     <row r="246" spans="1:22" ht="15.75" customHeight="1">
       <c r="A246" s="18"/>
-      <c r="B246" s="95"/>
+      <c r="B246" s="94"/>
       <c r="C246" s="18"/>
       <c r="D246" s="18"/>
       <c r="E246" s="18"/>
@@ -27122,7 +27787,7 @@
     </row>
     <row r="247" spans="1:22" ht="15.75" customHeight="1">
       <c r="A247" s="18"/>
-      <c r="B247" s="95"/>
+      <c r="B247" s="94"/>
       <c r="C247" s="18"/>
       <c r="D247" s="18"/>
       <c r="E247" s="18"/>
@@ -27146,7 +27811,7 @@
     </row>
     <row r="248" spans="1:22" ht="15.75" customHeight="1">
       <c r="A248" s="18"/>
-      <c r="B248" s="95"/>
+      <c r="B248" s="94"/>
       <c r="C248" s="18"/>
       <c r="D248" s="18"/>
       <c r="E248" s="18"/>
@@ -27170,7 +27835,7 @@
     </row>
     <row r="249" spans="1:22" ht="15.75" customHeight="1">
       <c r="A249" s="18"/>
-      <c r="B249" s="95"/>
+      <c r="B249" s="94"/>
       <c r="C249" s="18"/>
       <c r="D249" s="18"/>
       <c r="E249" s="18"/>
@@ -27194,7 +27859,7 @@
     </row>
     <row r="250" spans="1:22" ht="15.75" customHeight="1">
       <c r="A250" s="18"/>
-      <c r="B250" s="95"/>
+      <c r="B250" s="94"/>
       <c r="C250" s="18"/>
       <c r="D250" s="18"/>
       <c r="E250" s="18"/>
@@ -27218,7 +27883,7 @@
     </row>
     <row r="251" spans="1:22" ht="15.75" customHeight="1">
       <c r="A251" s="18"/>
-      <c r="B251" s="95"/>
+      <c r="B251" s="94"/>
       <c r="C251" s="18"/>
       <c r="D251" s="18"/>
       <c r="E251" s="18"/>
@@ -27242,7 +27907,7 @@
     </row>
     <row r="252" spans="1:22" ht="15.75" customHeight="1">
       <c r="A252" s="18"/>
-      <c r="B252" s="95"/>
+      <c r="B252" s="94"/>
       <c r="C252" s="18"/>
       <c r="D252" s="18"/>
       <c r="E252" s="18"/>
@@ -27266,7 +27931,7 @@
     </row>
     <row r="253" spans="1:22" ht="15.75" customHeight="1">
       <c r="A253" s="18"/>
-      <c r="B253" s="95"/>
+      <c r="B253" s="94"/>
       <c r="C253" s="18"/>
       <c r="D253" s="18"/>
       <c r="E253" s="18"/>
@@ -27290,7 +27955,7 @@
     </row>
     <row r="254" spans="1:22" ht="15.75" customHeight="1">
       <c r="A254" s="18"/>
-      <c r="B254" s="95"/>
+      <c r="B254" s="94"/>
       <c r="C254" s="18"/>
       <c r="D254" s="18"/>
       <c r="E254" s="18"/>
@@ -27314,7 +27979,7 @@
     </row>
     <row r="255" spans="1:22" ht="15.75" customHeight="1">
       <c r="A255" s="18"/>
-      <c r="B255" s="95"/>
+      <c r="B255" s="94"/>
       <c r="C255" s="18"/>
       <c r="D255" s="18"/>
       <c r="E255" s="18"/>
@@ -27338,7 +28003,7 @@
     </row>
     <row r="256" spans="1:22" ht="15.75" customHeight="1">
       <c r="A256" s="18"/>
-      <c r="B256" s="95"/>
+      <c r="B256" s="94"/>
       <c r="C256" s="18"/>
       <c r="D256" s="18"/>
       <c r="E256" s="18"/>
@@ -27362,7 +28027,7 @@
     </row>
     <row r="257" spans="1:22" ht="15.75" customHeight="1">
       <c r="A257" s="18"/>
-      <c r="B257" s="95"/>
+      <c r="B257" s="94"/>
       <c r="C257" s="18"/>
       <c r="D257" s="18"/>
       <c r="E257" s="18"/>
@@ -27386,7 +28051,7 @@
     </row>
     <row r="258" spans="1:22" ht="15.75" customHeight="1">
       <c r="A258" s="18"/>
-      <c r="B258" s="95"/>
+      <c r="B258" s="94"/>
       <c r="C258" s="18"/>
       <c r="D258" s="18"/>
       <c r="E258" s="18"/>
@@ -27410,7 +28075,7 @@
     </row>
     <row r="259" spans="1:22" ht="15.75" customHeight="1">
       <c r="A259" s="18"/>
-      <c r="B259" s="95"/>
+      <c r="B259" s="94"/>
       <c r="C259" s="18"/>
       <c r="D259" s="18"/>
       <c r="E259" s="18"/>
@@ -27434,7 +28099,7 @@
     </row>
     <row r="260" spans="1:22" ht="15.75" customHeight="1">
       <c r="A260" s="18"/>
-      <c r="B260" s="95"/>
+      <c r="B260" s="94"/>
       <c r="C260" s="18"/>
       <c r="D260" s="18"/>
       <c r="E260" s="18"/>
@@ -27458,7 +28123,7 @@
     </row>
     <row r="261" spans="1:22" ht="15.75" customHeight="1">
       <c r="A261" s="18"/>
-      <c r="B261" s="95"/>
+      <c r="B261" s="94"/>
       <c r="C261" s="18"/>
       <c r="D261" s="18"/>
       <c r="E261" s="18"/>
@@ -27482,7 +28147,7 @@
     </row>
     <row r="262" spans="1:22" ht="15.75" customHeight="1">
       <c r="A262" s="18"/>
-      <c r="B262" s="95"/>
+      <c r="B262" s="94"/>
       <c r="C262" s="18"/>
       <c r="D262" s="18"/>
       <c r="E262" s="18"/>
@@ -27506,7 +28171,7 @@
     </row>
     <row r="263" spans="1:22" ht="15.75" customHeight="1">
       <c r="A263" s="18"/>
-      <c r="B263" s="95"/>
+      <c r="B263" s="94"/>
       <c r="C263" s="18"/>
       <c r="D263" s="18"/>
       <c r="E263" s="18"/>
@@ -27530,7 +28195,7 @@
     </row>
     <row r="264" spans="1:22" ht="15.75" customHeight="1">
       <c r="A264" s="18"/>
-      <c r="B264" s="95"/>
+      <c r="B264" s="94"/>
       <c r="C264" s="18"/>
       <c r="D264" s="18"/>
       <c r="E264" s="18"/>
@@ -27554,7 +28219,7 @@
     </row>
     <row r="265" spans="1:22" ht="15.75" customHeight="1">
       <c r="A265" s="18"/>
-      <c r="B265" s="95"/>
+      <c r="B265" s="94"/>
       <c r="C265" s="18"/>
       <c r="D265" s="18"/>
       <c r="E265" s="18"/>
@@ -27578,7 +28243,7 @@
     </row>
     <row r="266" spans="1:22" ht="15.75" customHeight="1">
       <c r="A266" s="18"/>
-      <c r="B266" s="95"/>
+      <c r="B266" s="94"/>
       <c r="C266" s="18"/>
       <c r="D266" s="18"/>
       <c r="E266" s="18"/>
@@ -27602,7 +28267,7 @@
     </row>
     <row r="267" spans="1:22" ht="15.75" customHeight="1">
       <c r="A267" s="18"/>
-      <c r="B267" s="95"/>
+      <c r="B267" s="94"/>
       <c r="C267" s="18"/>
       <c r="D267" s="18"/>
       <c r="E267" s="18"/>
@@ -27626,7 +28291,7 @@
     </row>
     <row r="268" spans="1:22" ht="15.75" customHeight="1">
       <c r="A268" s="18"/>
-      <c r="B268" s="95"/>
+      <c r="B268" s="94"/>
       <c r="C268" s="18"/>
       <c r="D268" s="18"/>
       <c r="E268" s="18"/>
@@ -27650,7 +28315,7 @@
     </row>
     <row r="269" spans="1:22" ht="15.75" customHeight="1">
       <c r="A269" s="18"/>
-      <c r="B269" s="95"/>
+      <c r="B269" s="94"/>
       <c r="C269" s="18"/>
       <c r="D269" s="18"/>
       <c r="E269" s="18"/>
@@ -27674,7 +28339,7 @@
     </row>
     <row r="270" spans="1:22" ht="15.75" customHeight="1">
       <c r="A270" s="18"/>
-      <c r="B270" s="95"/>
+      <c r="B270" s="94"/>
       <c r="C270" s="18"/>
       <c r="D270" s="18"/>
       <c r="E270" s="18"/>
@@ -27698,7 +28363,7 @@
     </row>
     <row r="271" spans="1:22" ht="15.75" customHeight="1">
       <c r="A271" s="18"/>
-      <c r="B271" s="95"/>
+      <c r="B271" s="94"/>
       <c r="C271" s="18"/>
       <c r="D271" s="18"/>
       <c r="E271" s="18"/>
@@ -27722,7 +28387,7 @@
     </row>
     <row r="272" spans="1:22" ht="15.75" customHeight="1">
       <c r="A272" s="18"/>
-      <c r="B272" s="95"/>
+      <c r="B272" s="94"/>
       <c r="C272" s="18"/>
       <c r="D272" s="18"/>
       <c r="E272" s="18"/>
@@ -27746,7 +28411,7 @@
     </row>
     <row r="273" spans="1:22" ht="15.75" customHeight="1">
       <c r="A273" s="18"/>
-      <c r="B273" s="95"/>
+      <c r="B273" s="94"/>
       <c r="C273" s="18"/>
       <c r="D273" s="18"/>
       <c r="E273" s="18"/>
@@ -27770,7 +28435,7 @@
     </row>
     <row r="274" spans="1:22" ht="15.75" customHeight="1">
       <c r="A274" s="18"/>
-      <c r="B274" s="95"/>
+      <c r="B274" s="94"/>
       <c r="C274" s="18"/>
       <c r="D274" s="18"/>
       <c r="E274" s="18"/>
@@ -27794,7 +28459,7 @@
     </row>
     <row r="275" spans="1:22" ht="15.75" customHeight="1">
       <c r="A275" s="18"/>
-      <c r="B275" s="95"/>
+      <c r="B275" s="94"/>
       <c r="C275" s="18"/>
       <c r="D275" s="18"/>
       <c r="E275" s="18"/>
@@ -27818,7 +28483,7 @@
     </row>
     <row r="276" spans="1:22" ht="15.75" customHeight="1">
       <c r="A276" s="18"/>
-      <c r="B276" s="95"/>
+      <c r="B276" s="94"/>
       <c r="C276" s="18"/>
       <c r="D276" s="18"/>
       <c r="E276" s="18"/>
@@ -27842,7 +28507,7 @@
     </row>
     <row r="277" spans="1:22" ht="15.75" customHeight="1">
       <c r="A277" s="18"/>
-      <c r="B277" s="95"/>
+      <c r="B277" s="94"/>
       <c r="C277" s="18"/>
       <c r="D277" s="18"/>
       <c r="E277" s="18"/>
@@ -27866,7 +28531,7 @@
     </row>
     <row r="278" spans="1:22" ht="15.75" customHeight="1">
       <c r="A278" s="18"/>
-      <c r="B278" s="95"/>
+      <c r="B278" s="94"/>
       <c r="C278" s="18"/>
       <c r="D278" s="18"/>
       <c r="E278" s="18"/>
@@ -27890,7 +28555,7 @@
     </row>
     <row r="279" spans="1:22" ht="15.75" customHeight="1">
       <c r="A279" s="18"/>
-      <c r="B279" s="95"/>
+      <c r="B279" s="94"/>
       <c r="C279" s="18"/>
       <c r="D279" s="18"/>
       <c r="E279" s="18"/>
@@ -27914,7 +28579,7 @@
     </row>
     <row r="280" spans="1:22" ht="15.75" customHeight="1">
       <c r="A280" s="18"/>
-      <c r="B280" s="95"/>
+      <c r="B280" s="94"/>
       <c r="C280" s="18"/>
       <c r="D280" s="18"/>
       <c r="E280" s="18"/>
@@ -27938,7 +28603,7 @@
     </row>
     <row r="281" spans="1:22" ht="15.75" customHeight="1">
       <c r="A281" s="18"/>
-      <c r="B281" s="95"/>
+      <c r="B281" s="94"/>
       <c r="C281" s="18"/>
       <c r="D281" s="18"/>
       <c r="E281" s="18"/>
@@ -27962,7 +28627,7 @@
     </row>
     <row r="282" spans="1:22" ht="15.75" customHeight="1">
       <c r="A282" s="18"/>
-      <c r="B282" s="95"/>
+      <c r="B282" s="94"/>
       <c r="C282" s="18"/>
       <c r="D282" s="18"/>
       <c r="E282" s="18"/>
@@ -27986,7 +28651,7 @@
     </row>
     <row r="283" spans="1:22" ht="15.75" customHeight="1">
       <c r="A283" s="18"/>
-      <c r="B283" s="95"/>
+      <c r="B283" s="94"/>
       <c r="C283" s="18"/>
       <c r="D283" s="18"/>
       <c r="E283" s="18"/>
@@ -28010,7 +28675,7 @@
     </row>
     <row r="284" spans="1:22" ht="15.75" customHeight="1">
       <c r="A284" s="18"/>
-      <c r="B284" s="95"/>
+      <c r="B284" s="94"/>
       <c r="C284" s="18"/>
       <c r="D284" s="18"/>
       <c r="E284" s="18"/>
@@ -28034,7 +28699,7 @@
     </row>
     <row r="285" spans="1:22" ht="15.75" customHeight="1">
       <c r="A285" s="18"/>
-      <c r="B285" s="95"/>
+      <c r="B285" s="94"/>
       <c r="C285" s="18"/>
       <c r="D285" s="18"/>
       <c r="E285" s="18"/>
@@ -28058,7 +28723,7 @@
     </row>
     <row r="286" spans="1:22" ht="15.75" customHeight="1">
       <c r="A286" s="18"/>
-      <c r="B286" s="95"/>
+      <c r="B286" s="94"/>
       <c r="C286" s="18"/>
       <c r="D286" s="18"/>
       <c r="E286" s="18"/>
@@ -28082,7 +28747,7 @@
     </row>
     <row r="287" spans="1:22" ht="15.75" customHeight="1">
       <c r="A287" s="18"/>
-      <c r="B287" s="95"/>
+      <c r="B287" s="94"/>
       <c r="C287" s="18"/>
       <c r="D287" s="18"/>
       <c r="E287" s="18"/>
@@ -28106,7 +28771,7 @@
     </row>
     <row r="288" spans="1:22" ht="15.75" customHeight="1">
       <c r="A288" s="18"/>
-      <c r="B288" s="95"/>
+      <c r="B288" s="94"/>
       <c r="C288" s="18"/>
       <c r="D288" s="18"/>
       <c r="E288" s="18"/>
@@ -28130,7 +28795,7 @@
     </row>
     <row r="289" spans="1:22" ht="15.75" customHeight="1">
       <c r="A289" s="18"/>
-      <c r="B289" s="95"/>
+      <c r="B289" s="94"/>
       <c r="C289" s="18"/>
       <c r="D289" s="18"/>
       <c r="E289" s="18"/>
@@ -28154,7 +28819,7 @@
     </row>
     <row r="290" spans="1:22" ht="15.75" customHeight="1">
       <c r="A290" s="18"/>
-      <c r="B290" s="95"/>
+      <c r="B290" s="94"/>
       <c r="C290" s="18"/>
       <c r="D290" s="18"/>
       <c r="E290" s="18"/>
@@ -28178,7 +28843,7 @@
     </row>
     <row r="291" spans="1:22" ht="15.75" customHeight="1">
       <c r="A291" s="18"/>
-      <c r="B291" s="95"/>
+      <c r="B291" s="94"/>
       <c r="C291" s="18"/>
       <c r="D291" s="18"/>
       <c r="E291" s="18"/>
@@ -28202,7 +28867,7 @@
     </row>
     <row r="292" spans="1:22" ht="15.75" customHeight="1">
       <c r="A292" s="18"/>
-      <c r="B292" s="95"/>
+      <c r="B292" s="94"/>
       <c r="C292" s="18"/>
       <c r="D292" s="18"/>
       <c r="E292" s="18"/>
@@ -28226,7 +28891,7 @@
     </row>
     <row r="293" spans="1:22" ht="15.75" customHeight="1">
       <c r="A293" s="18"/>
-      <c r="B293" s="95"/>
+      <c r="B293" s="94"/>
       <c r="C293" s="18"/>
       <c r="D293" s="18"/>
       <c r="E293" s="18"/>
@@ -28250,7 +28915,7 @@
     </row>
     <row r="294" spans="1:22" ht="15.75" customHeight="1">
       <c r="A294" s="18"/>
-      <c r="B294" s="95"/>
+      <c r="B294" s="94"/>
       <c r="C294" s="18"/>
       <c r="D294" s="18"/>
       <c r="E294" s="18"/>
@@ -28274,7 +28939,7 @@
     </row>
     <row r="295" spans="1:22" ht="15.75" customHeight="1">
       <c r="A295" s="18"/>
-      <c r="B295" s="95"/>
+      <c r="B295" s="94"/>
       <c r="C295" s="18"/>
       <c r="D295" s="18"/>
       <c r="E295" s="18"/>
@@ -28298,7 +28963,7 @@
     </row>
     <row r="296" spans="1:22" ht="15.75" customHeight="1">
       <c r="A296" s="18"/>
-      <c r="B296" s="95"/>
+      <c r="B296" s="94"/>
       <c r="C296" s="18"/>
       <c r="D296" s="18"/>
       <c r="E296" s="18"/>
@@ -28322,7 +28987,7 @@
     </row>
     <row r="297" spans="1:22" ht="15.75" customHeight="1">
       <c r="A297" s="18"/>
-      <c r="B297" s="95"/>
+      <c r="B297" s="94"/>
       <c r="C297" s="18"/>
       <c r="D297" s="18"/>
       <c r="E297" s="18"/>
@@ -28346,7 +29011,7 @@
     </row>
     <row r="298" spans="1:22" ht="15.75" customHeight="1">
       <c r="A298" s="18"/>
-      <c r="B298" s="95"/>
+      <c r="B298" s="94"/>
       <c r="C298" s="18"/>
       <c r="D298" s="18"/>
       <c r="E298" s="18"/>
@@ -28370,7 +29035,7 @@
     </row>
     <row r="299" spans="1:22" ht="15.75" customHeight="1">
       <c r="A299" s="18"/>
-      <c r="B299" s="95"/>
+      <c r="B299" s="94"/>
       <c r="C299" s="18"/>
       <c r="D299" s="18"/>
       <c r="E299" s="18"/>
@@ -28394,7 +29059,7 @@
     </row>
     <row r="300" spans="1:22" ht="15.75" customHeight="1">
       <c r="A300" s="18"/>
-      <c r="B300" s="95"/>
+      <c r="B300" s="94"/>
       <c r="C300" s="18"/>
       <c r="D300" s="18"/>
       <c r="E300" s="18"/>
@@ -28418,7 +29083,7 @@
     </row>
     <row r="301" spans="1:22" ht="15.75" customHeight="1">
       <c r="A301" s="18"/>
-      <c r="B301" s="95"/>
+      <c r="B301" s="94"/>
       <c r="C301" s="18"/>
       <c r="D301" s="18"/>
       <c r="E301" s="18"/>
@@ -28442,7 +29107,7 @@
     </row>
     <row r="302" spans="1:22" ht="15.75" customHeight="1">
       <c r="A302" s="18"/>
-      <c r="B302" s="95"/>
+      <c r="B302" s="94"/>
       <c r="C302" s="18"/>
       <c r="D302" s="18"/>
       <c r="E302" s="18"/>
@@ -28466,7 +29131,7 @@
     </row>
     <row r="303" spans="1:22" ht="15.75" customHeight="1">
       <c r="A303" s="18"/>
-      <c r="B303" s="95"/>
+      <c r="B303" s="94"/>
       <c r="C303" s="18"/>
       <c r="D303" s="18"/>
       <c r="E303" s="18"/>
@@ -28490,7 +29155,7 @@
     </row>
     <row r="304" spans="1:22" ht="15.75" customHeight="1">
       <c r="A304" s="18"/>
-      <c r="B304" s="95"/>
+      <c r="B304" s="94"/>
       <c r="C304" s="18"/>
       <c r="D304" s="18"/>
       <c r="E304" s="18"/>
@@ -28514,7 +29179,7 @@
     </row>
     <row r="305" spans="1:22" ht="15.75" customHeight="1">
       <c r="A305" s="18"/>
-      <c r="B305" s="95"/>
+      <c r="B305" s="94"/>
       <c r="C305" s="18"/>
       <c r="D305" s="18"/>
       <c r="E305" s="18"/>
@@ -28538,7 +29203,7 @@
     </row>
     <row r="306" spans="1:22" ht="15.75" customHeight="1">
       <c r="A306" s="18"/>
-      <c r="B306" s="95"/>
+      <c r="B306" s="94"/>
       <c r="C306" s="18"/>
       <c r="D306" s="18"/>
       <c r="E306" s="18"/>
@@ -28562,7 +29227,7 @@
     </row>
     <row r="307" spans="1:22" ht="15.75" customHeight="1">
       <c r="A307" s="18"/>
-      <c r="B307" s="95"/>
+      <c r="B307" s="94"/>
       <c r="C307" s="18"/>
       <c r="D307" s="18"/>
       <c r="E307" s="18"/>
@@ -28586,7 +29251,7 @@
     </row>
     <row r="308" spans="1:22" ht="15.75" customHeight="1">
       <c r="A308" s="18"/>
-      <c r="B308" s="95"/>
+      <c r="B308" s="94"/>
       <c r="C308" s="18"/>
       <c r="D308" s="18"/>
       <c r="E308" s="18"/>
@@ -28610,7 +29275,7 @@
     </row>
     <row r="309" spans="1:22" ht="15.75" customHeight="1">
       <c r="A309" s="18"/>
-      <c r="B309" s="95"/>
+      <c r="B309" s="94"/>
       <c r="C309" s="18"/>
       <c r="D309" s="18"/>
       <c r="E309" s="18"/>
@@ -28634,7 +29299,7 @@
     </row>
     <row r="310" spans="1:22" ht="15.75" customHeight="1">
       <c r="A310" s="18"/>
-      <c r="B310" s="95"/>
+      <c r="B310" s="94"/>
       <c r="C310" s="18"/>
       <c r="D310" s="18"/>
       <c r="E310" s="18"/>
@@ -28658,7 +29323,7 @@
     </row>
     <row r="311" spans="1:22" ht="15.75" customHeight="1">
       <c r="A311" s="18"/>
-      <c r="B311" s="95"/>
+      <c r="B311" s="94"/>
       <c r="C311" s="18"/>
       <c r="D311" s="18"/>
       <c r="E311" s="18"/>
@@ -28682,7 +29347,7 @@
     </row>
     <row r="312" spans="1:22" ht="15.75" customHeight="1">
       <c r="A312" s="18"/>
-      <c r="B312" s="95"/>
+      <c r="B312" s="94"/>
       <c r="C312" s="18"/>
       <c r="D312" s="18"/>
       <c r="E312" s="18"/>
@@ -28706,7 +29371,7 @@
     </row>
     <row r="313" spans="1:22" ht="15.75" customHeight="1">
       <c r="A313" s="18"/>
-      <c r="B313" s="95"/>
+      <c r="B313" s="94"/>
       <c r="C313" s="18"/>
       <c r="D313" s="18"/>
       <c r="E313" s="18"/>
@@ -28730,7 +29395,7 @@
     </row>
     <row r="314" spans="1:22" ht="15.75" customHeight="1">
       <c r="A314" s="18"/>
-      <c r="B314" s="95"/>
+      <c r="B314" s="94"/>
       <c r="C314" s="18"/>
       <c r="D314" s="18"/>
       <c r="E314" s="18"/>
@@ -28754,7 +29419,7 @@
     </row>
     <row r="315" spans="1:22" ht="15.75" customHeight="1">
       <c r="A315" s="18"/>
-      <c r="B315" s="95"/>
+      <c r="B315" s="94"/>
       <c r="C315" s="18"/>
       <c r="D315" s="18"/>
       <c r="E315" s="18"/>
@@ -28778,7 +29443,7 @@
     </row>
     <row r="316" spans="1:22" ht="15.75" customHeight="1">
       <c r="A316" s="18"/>
-      <c r="B316" s="95"/>
+      <c r="B316" s="94"/>
       <c r="C316" s="18"/>
       <c r="D316" s="18"/>
       <c r="E316" s="18"/>
@@ -28802,7 +29467,7 @@
     </row>
     <row r="317" spans="1:22" ht="15.75" customHeight="1">
       <c r="A317" s="18"/>
-      <c r="B317" s="95"/>
+      <c r="B317" s="94"/>
       <c r="C317" s="18"/>
       <c r="D317" s="18"/>
       <c r="E317" s="18"/>
@@ -28826,7 +29491,7 @@
     </row>
     <row r="318" spans="1:22" ht="15.75" customHeight="1">
       <c r="A318" s="18"/>
-      <c r="B318" s="95"/>
+      <c r="B318" s="94"/>
       <c r="C318" s="18"/>
       <c r="D318" s="18"/>
       <c r="E318" s="18"/>
@@ -28850,7 +29515,7 @@
     </row>
     <row r="319" spans="1:22" ht="15.75" customHeight="1">
       <c r="A319" s="18"/>
-      <c r="B319" s="95"/>
+      <c r="B319" s="94"/>
       <c r="C319" s="18"/>
       <c r="D319" s="18"/>
       <c r="E319" s="18"/>
@@ -28874,7 +29539,7 @@
     </row>
     <row r="320" spans="1:22" ht="15.75" customHeight="1">
       <c r="A320" s="18"/>
-      <c r="B320" s="95"/>
+      <c r="B320" s="94"/>
       <c r="C320" s="18"/>
       <c r="D320" s="18"/>
       <c r="E320" s="18"/>
@@ -28898,7 +29563,7 @@
     </row>
     <row r="321" spans="1:22" ht="15.75" customHeight="1">
       <c r="A321" s="18"/>
-      <c r="B321" s="95"/>
+      <c r="B321" s="94"/>
       <c r="C321" s="18"/>
       <c r="D321" s="18"/>
       <c r="E321" s="18"/>
@@ -28922,7 +29587,7 @@
     </row>
     <row r="322" spans="1:22" ht="15.75" customHeight="1">
       <c r="A322" s="18"/>
-      <c r="B322" s="95"/>
+      <c r="B322" s="94"/>
       <c r="C322" s="18"/>
       <c r="D322" s="18"/>
       <c r="E322" s="18"/>
@@ -28946,7 +29611,7 @@
     </row>
     <row r="323" spans="1:22" ht="15.75" customHeight="1">
       <c r="A323" s="18"/>
-      <c r="B323" s="95"/>
+      <c r="B323" s="94"/>
       <c r="C323" s="18"/>
       <c r="D323" s="18"/>
       <c r="E323" s="18"/>
@@ -28970,7 +29635,7 @@
     </row>
     <row r="324" spans="1:22" ht="15.75" customHeight="1">
       <c r="A324" s="18"/>
-      <c r="B324" s="95"/>
+      <c r="B324" s="94"/>
       <c r="C324" s="18"/>
       <c r="D324" s="18"/>
       <c r="E324" s="18"/>
@@ -28994,7 +29659,7 @@
     </row>
     <row r="325" spans="1:22" ht="15.75" customHeight="1">
       <c r="A325" s="18"/>
-      <c r="B325" s="95"/>
+      <c r="B325" s="94"/>
       <c r="C325" s="18"/>
       <c r="D325" s="18"/>
       <c r="E325" s="18"/>
@@ -29018,7 +29683,7 @@
     </row>
     <row r="326" spans="1:22" ht="15.75" customHeight="1">
       <c r="A326" s="18"/>
-      <c r="B326" s="95"/>
+      <c r="B326" s="94"/>
       <c r="C326" s="18"/>
       <c r="D326" s="18"/>
       <c r="E326" s="18"/>
@@ -29042,7 +29707,7 @@
     </row>
     <row r="327" spans="1:22" ht="15.75" customHeight="1">
       <c r="A327" s="18"/>
-      <c r="B327" s="95"/>
+      <c r="B327" s="94"/>
       <c r="C327" s="18"/>
       <c r="D327" s="18"/>
       <c r="E327" s="18"/>
@@ -29066,7 +29731,7 @@
     </row>
     <row r="328" spans="1:22" ht="15.75" customHeight="1">
       <c r="A328" s="18"/>
-      <c r="B328" s="95"/>
+      <c r="B328" s="94"/>
       <c r="C328" s="18"/>
       <c r="D328" s="18"/>
       <c r="E328" s="18"/>
@@ -29090,7 +29755,7 @@
     </row>
     <row r="329" spans="1:22" ht="15.75" customHeight="1">
       <c r="A329" s="18"/>
-      <c r="B329" s="95"/>
+      <c r="B329" s="94"/>
       <c r="C329" s="18"/>
       <c r="D329" s="18"/>
       <c r="E329" s="18"/>
@@ -29114,7 +29779,7 @@
     </row>
     <row r="330" spans="1:22" ht="15.75" customHeight="1">
       <c r="A330" s="18"/>
-      <c r="B330" s="95"/>
+      <c r="B330" s="94"/>
       <c r="C330" s="18"/>
       <c r="D330" s="18"/>
       <c r="E330" s="18"/>
@@ -29138,7 +29803,7 @@
     </row>
     <row r="331" spans="1:22" ht="15.75" customHeight="1">
       <c r="A331" s="18"/>
-      <c r="B331" s="95"/>
+      <c r="B331" s="94"/>
       <c r="C331" s="18"/>
       <c r="D331" s="18"/>
       <c r="E331" s="18"/>
@@ -29162,7 +29827,7 @@
     </row>
     <row r="332" spans="1:22" ht="15.75" customHeight="1">
       <c r="A332" s="18"/>
-      <c r="B332" s="95"/>
+      <c r="B332" s="94"/>
       <c r="C332" s="18"/>
       <c r="D332" s="18"/>
       <c r="E332" s="18"/>
@@ -29186,7 +29851,7 @@
     </row>
     <row r="333" spans="1:22" ht="15.75" customHeight="1">
       <c r="A333" s="18"/>
-      <c r="B333" s="95"/>
+      <c r="B333" s="94"/>
       <c r="C333" s="18"/>
       <c r="D333" s="18"/>
       <c r="E333" s="18"/>
@@ -29210,7 +29875,7 @@
     </row>
     <row r="334" spans="1:22" ht="15.75" customHeight="1">
       <c r="A334" s="18"/>
-      <c r="B334" s="95"/>
+      <c r="B334" s="94"/>
       <c r="C334" s="18"/>
       <c r="D334" s="18"/>
       <c r="E334" s="18"/>
@@ -29234,7 +29899,7 @@
     </row>
     <row r="335" spans="1:22" ht="15.75" customHeight="1">
       <c r="A335" s="18"/>
-      <c r="B335" s="95"/>
+      <c r="B335" s="94"/>
       <c r="C335" s="18"/>
       <c r="D335" s="18"/>
       <c r="E335" s="18"/>
@@ -29258,7 +29923,7 @@
     </row>
     <row r="336" spans="1:22" ht="15.75" customHeight="1">
       <c r="A336" s="18"/>
-      <c r="B336" s="95"/>
+      <c r="B336" s="94"/>
       <c r="C336" s="18"/>
       <c r="D336" s="18"/>
       <c r="E336" s="18"/>
@@ -29282,7 +29947,7 @@
     </row>
     <row r="337" spans="1:22" ht="15.75" customHeight="1">
       <c r="A337" s="18"/>
-      <c r="B337" s="95"/>
+      <c r="B337" s="94"/>
       <c r="C337" s="18"/>
       <c r="D337" s="18"/>
       <c r="E337" s="18"/>
@@ -29306,7 +29971,7 @@
     </row>
     <row r="338" spans="1:22" ht="15.75" customHeight="1">
       <c r="A338" s="18"/>
-      <c r="B338" s="95"/>
+      <c r="B338" s="94"/>
       <c r="C338" s="18"/>
       <c r="D338" s="18"/>
       <c r="E338" s="18"/>
@@ -29330,7 +29995,7 @@
     </row>
     <row r="339" spans="1:22" ht="15.75" customHeight="1">
       <c r="A339" s="18"/>
-      <c r="B339" s="95"/>
+      <c r="B339" s="94"/>
       <c r="C339" s="18"/>
       <c r="D339" s="18"/>
       <c r="E339" s="18"/>
@@ -29354,7 +30019,7 @@
     </row>
     <row r="340" spans="1:22" ht="15.75" customHeight="1">
       <c r="A340" s="18"/>
-      <c r="B340" s="95"/>
+      <c r="B340" s="94"/>
       <c r="C340" s="18"/>
       <c r="D340" s="18"/>
       <c r="E340" s="18"/>
@@ -29378,7 +30043,7 @@
     </row>
     <row r="341" spans="1:22" ht="15.75" customHeight="1">
       <c r="A341" s="18"/>
-      <c r="B341" s="95"/>
+      <c r="B341" s="94"/>
       <c r="C341" s="18"/>
       <c r="D341" s="18"/>
       <c r="E341" s="18"/>
@@ -29402,7 +30067,7 @@
     </row>
     <row r="342" spans="1:22" ht="15.75" customHeight="1">
       <c r="A342" s="18"/>
-      <c r="B342" s="95"/>
+      <c r="B342" s="94"/>
       <c r="C342" s="18"/>
       <c r="D342" s="18"/>
       <c r="E342" s="18"/>
@@ -29426,7 +30091,7 @@
     </row>
     <row r="343" spans="1:22" ht="15.75" customHeight="1">
       <c r="A343" s="18"/>
-      <c r="B343" s="95"/>
+      <c r="B343" s="94"/>
       <c r="C343" s="18"/>
       <c r="D343" s="18"/>
       <c r="E343" s="18"/>
@@ -29450,7 +30115,7 @@
     </row>
     <row r="344" spans="1:22" ht="15.75" customHeight="1">
       <c r="A344" s="18"/>
-      <c r="B344" s="95"/>
+      <c r="B344" s="94"/>
       <c r="C344" s="18"/>
       <c r="D344" s="18"/>
       <c r="E344" s="18"/>
@@ -29474,7 +30139,7 @@
     </row>
     <row r="345" spans="1:22" ht="15.75" customHeight="1">
       <c r="A345" s="18"/>
-      <c r="B345" s="95"/>
+      <c r="B345" s="94"/>
       <c r="C345" s="18"/>
       <c r="D345" s="18"/>
       <c r="E345" s="18"/>
@@ -29498,7 +30163,7 @@
     </row>
     <row r="346" spans="1:22" ht="15.75" customHeight="1">
       <c r="A346" s="18"/>
-      <c r="B346" s="95"/>
+      <c r="B346" s="94"/>
       <c r="C346" s="18"/>
       <c r="D346" s="18"/>
       <c r="E346" s="18"/>
@@ -32072,7 +32737,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="C2" s="51" t="s">
         <v>1048</v>
@@ -34068,7 +34733,7 @@
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A171" s="92" t="s">
+      <c r="A171" s="91" t="s">
         <v>1166</v>
       </c>
       <c r="B171" s="9" t="s">
@@ -34111,7 +34776,7 @@
         <v>1225</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>1229</v>
+        <v>1284</v>
       </c>
       <c r="C175" s="62" t="s">
         <v>1228</v>
@@ -34122,25 +34787,29 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A176" s="9" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B176" s="9" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C176" s="9"/>
+    </row>
+    <row r="177" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A177" s="91" t="s">
         <v>1230</v>
       </c>
-      <c r="B176" s="9" t="s">
-        <v>1231</v>
-      </c>
-      <c r="C176" s="9"/>
-    </row>
-    <row r="177" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A177" s="92" t="s">
-        <v>1232</v>
-      </c>
       <c r="B177" s="9" t="s">
-        <v>1233</v>
+        <v>1283</v>
       </c>
       <c r="C177" s="9"/>
     </row>
     <row r="178" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A178" s="9"/>
-      <c r="B178" s="9"/>
+      <c r="A178" s="9" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B178" s="9" t="s">
+        <v>1286</v>
+      </c>
       <c r="C178" s="9"/>
     </row>
     <row r="179" spans="1:3" ht="15.75" customHeight="1">

--- a/config/testdata/testdata.xlsx
+++ b/config/testdata/testdata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MMHNZ_V2_AUTOMATION\config\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0C8326-C362-4610-AC69-4FCF85F670DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA572738-7A69-4413-B516-BCC5322A0949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2632" uniqueCount="1299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2632" uniqueCount="1302">
   <si>
     <t>KEY</t>
   </si>
@@ -3951,7 +3951,16 @@
     <t>VISIT_APPOINTMENT_DETAILS_UHC_USING_CARD_PAYMENT</t>
   </si>
   <si>
-    <t>Automation1_HC1;Automation1_Loc1;Myself (AUTO AUTOCHRISC4);A new issue;Visit;9:00 AM;GP2WHITE;AFTER_THREE_DAYS</t>
+    <t>https://v2webprdfeature.mmh-demo.com/home</t>
+  </si>
+  <si>
+    <t>Automation1_HC1;Automation1_Loc1;Myself (CHRISC4 AUTOCHRISC4);A new issue;Visit;9:00 AM;GP2WHITE;AFTER_THREE_DAYS</t>
+  </si>
+  <si>
+    <t>https://v2portal.mmhnz.cloud/home</t>
+  </si>
+  <si>
+    <t>31 Jan 2025;03 Apr 2025;Prod Test 31 jan 25;VM07 Loc1 Evo Prod;</t>
   </si>
 </sst>
 </file>
@@ -4032,6 +4041,7 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Quattrocento Sans"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -4925,7 +4935,7 @@
         <v>1261</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>1048</v>
+        <v>1300</v>
       </c>
       <c r="D2" s="57" t="s">
         <v>1124</v>
@@ -9299,7 +9309,7 @@
         <v>1258</v>
       </c>
       <c r="C146" s="76" t="s">
-        <v>1065</v>
+        <v>1301</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>1125</v>
@@ -10953,7 +10963,7 @@
         <v>1296</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C200" s="76" t="s">
         <v>1127</v>
@@ -16717,7 +16727,7 @@
     <hyperlink ref="C2" r:id="rId3" xr:uid="{51DC6A58-9863-4BA4-8D62-1794D9D55E09}"/>
     <hyperlink ref="D2" r:id="rId4" xr:uid="{1F6963B5-04E2-4635-B2CC-308E91119C44}"/>
     <hyperlink ref="B2" r:id="rId5" xr:uid="{8629E203-331A-40A5-8963-16BA6F44E7E0}"/>
-    <hyperlink ref="B5" r:id="rId6" tooltip="mailto:autochrisc4@mmh-demo.com" display="mailto:Autochrisc4@mmh-demo.com" xr:uid="{D1666DDB-633D-47C3-AC1F-E8A14BD8B3D3}"/>
+    <hyperlink ref="B5" r:id="rId6" xr:uid="{D1666DDB-633D-47C3-AC1F-E8A14BD8B3D3}"/>
     <hyperlink ref="B4" r:id="rId7" tooltip="mailto:autochrisc4@mmh-demo.com" display="mailto:Autochrisc4@mmh-demo.com" xr:uid="{F7DB5A72-67FE-429D-AD24-95A3552918F2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -16777,7 +16787,7 @@
       <c r="B2" s="51" t="s">
         <v>1261</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="51" t="s">
         <v>1048</v>
       </c>
     </row>
@@ -21297,6 +21307,7 @@
     <hyperlink ref="C16" r:id="rId19" xr:uid="{6BAF1573-2EFB-4846-8986-088AD7BBB8AE}"/>
     <hyperlink ref="C3" r:id="rId20" xr:uid="{0014955C-7397-4069-B2DC-1F6C4B21F53F}"/>
     <hyperlink ref="B2" r:id="rId21" xr:uid="{FDCB0381-0C4A-4281-8093-8D3F723B9334}"/>
+    <hyperlink ref="C2" r:id="rId22" xr:uid="{A07F2944-7E15-41CA-AD10-4E6BD1E11282}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -32737,7 +32748,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>1261</v>
+        <v>1298</v>
       </c>
       <c r="C2" s="51" t="s">
         <v>1048</v>
@@ -36392,8 +36403,8 @@
     <hyperlink ref="B3" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{3EFD36B0-2228-45CC-AC19-2290C035AA1A}"/>
     <hyperlink ref="C145" r:id="rId3" xr:uid="{D585080A-FC84-4C4E-BBDD-A485B5C6854A}"/>
-    <hyperlink ref="B2" r:id="rId4" xr:uid="{AE460962-5ECE-43B9-8307-F9744D2F7A7C}"/>
-    <hyperlink ref="C2" r:id="rId5" xr:uid="{A4DEE308-051E-4F9C-9C85-8307AF9E1ACB}"/>
+    <hyperlink ref="C2" r:id="rId4" xr:uid="{A4DEE308-051E-4F9C-9C85-8307AF9E1ACB}"/>
+    <hyperlink ref="B2" r:id="rId5" xr:uid="{6B02F5FD-321A-4EC6-B083-48F8A4F10673}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId6"/>

--- a/config/testdata/testdata.xlsx
+++ b/config/testdata/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MMHNZ_V2_AUTOMATION\config\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA572738-7A69-4413-B516-BCC5322A0949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57015136-9C9D-4DB4-9347-531F3B407720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3957,10 +3957,10 @@
     <t>Automation1_HC1;Automation1_Loc1;Myself (CHRISC4 AUTOCHRISC4);A new issue;Visit;9:00 AM;GP2WHITE;AFTER_THREE_DAYS</t>
   </si>
   <si>
-    <t>https://v2portal.mmhnz.cloud/home</t>
-  </si>
-  <si>
-    <t>31 Jan 2025;03 Apr 2025;Prod Test 31 jan 25;VM07 Loc1 Evo Prod;</t>
+    <t>https://app.managemyhealth.co.nz/home</t>
+  </si>
+  <si>
+    <t>31 Jan 2025;16 May 2025;Prod Test 31 jan 25;VM07 Loc1 Evo Prod;</t>
   </si>
 </sst>
 </file>

--- a/config/testdata/testdata.xlsx
+++ b/config/testdata/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MMHNZ_V2_AUTOMATION\config\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57015136-9C9D-4DB4-9347-531F3B407720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB49A04-3DCF-441B-BC98-4A0B83DE31C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2632" uniqueCount="1302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="1316">
   <si>
     <t>KEY</t>
   </si>
@@ -3324,9 +3324,6 @@
     <t>Automation1_HC1;Automation1_Loc1;AFTER_FIVE_DAYS;15;AUTO AUTOCHRISC1;GP2WHITE;A new issue;Pay at Health Centre;TODAY</t>
   </si>
   <si>
-    <t>Automation1_HC1;Automation1_Loc2;Myself (AUTO AUTOCHRISC1);A new issue;Video;9:00 AM;Book Video Appointment;GP3 White;AFTER_THREE_DAYS</t>
-  </si>
-  <si>
     <t>Automation1_HC1;Automation1_Loc2;Myself (AUTO AUTOCHRISC1);A new issue;Visit;9:00 AM;GP3 White;AFTER_THREE_DAYS;Automation1_Loc1;Automation1_Loc2</t>
   </si>
   <si>
@@ -3522,9 +3519,6 @@
     <t>VM07 HC Evo Prod;2;Hour(s);Day(s);12:00 AM - 01:00 AM;1</t>
   </si>
   <si>
-    <t>Dr B Beta;Dr Percival Chapman;GP1 Vm07 Loc1</t>
-  </si>
-  <si>
     <t>UAT</t>
   </si>
   <si>
@@ -3711,9 +3705,6 @@
     <t>BOOK_VISIT_APPOINTMENT_RULE_C</t>
   </si>
   <si>
-    <t>Automation1_HC1;Repeat Prescription;Gp2White;Gp1 A1 L1</t>
-  </si>
-  <si>
     <t>VM07 HC Evo Prod;Repeat Prescription;Dr B Beta</t>
   </si>
   <si>
@@ -3951,16 +3942,67 @@
     <t>VISIT_APPOINTMENT_DETAILS_UHC_USING_CARD_PAYMENT</t>
   </si>
   <si>
-    <t>https://v2webprdfeature.mmh-demo.com/home</t>
-  </si>
-  <si>
     <t>Automation1_HC1;Automation1_Loc1;Myself (CHRISC4 AUTOCHRISC4);A new issue;Visit;9:00 AM;GP2WHITE;AFTER_THREE_DAYS</t>
   </si>
   <si>
-    <t>https://app.managemyhealth.co.nz/home</t>
-  </si>
-  <si>
     <t>31 Jan 2025;16 May 2025;Prod Test 31 jan 25;VM07 Loc1 Evo Prod;</t>
+  </si>
+  <si>
+    <t>PATIENT_REPEAT_SCRIPT_SETTINGS_DATA</t>
+  </si>
+  <si>
+    <t>VM07 Loc1 Evo Prod;Repeat Prescription;Dr B Beta;Gp2 Vm07 Loc2</t>
+  </si>
+  <si>
+    <t>Automation1_HC1;Repeat Prescription;Gp1 A1 L1;Gp3 White</t>
+  </si>
+  <si>
+    <t>Automation1_Loc1;Gp1 A1 L1;Deliver Meds by Pharmacy</t>
+  </si>
+  <si>
+    <t>Automation1_Loc1;Pacifen 10mg Tab;pending;48 Hours;GP2WHITE</t>
+  </si>
+  <si>
+    <t>Automation1_HC1;Automation1_Loc1;Lab Result enquiry;Clinical Staff;Gp2White;Compose Msg Testing_RANDOM;Compose Message Testing_RANDOM;MMHtest.jpg</t>
+  </si>
+  <si>
+    <t>SETUP_SERVICE_RECEIVED_MESSAGE_DETAILS</t>
+  </si>
+  <si>
+    <t>Automation1_HC1;Automation1_Loc1;TestAutomation;Patient;Auto;Received Msg Testing_RANDOM;Body : Received Message Testing_RANDOM;MMHtest.jpg;Compose Message_RANDOM;Body : Reply Message Testing_RANDOM;Compose Message Testing_RANDOM;TestAutomation</t>
+  </si>
+  <si>
+    <t>VM07 HC Evo Prod;VM07 Loc1 Evo Prod;TestAutomation;Patient;peter;Received Msg Testing_RANDOM;Body : Received Message Testing_RANDOM;MMHtest.jpg</t>
+  </si>
+  <si>
+    <t>Dr Percival Chapman;Dr B Beta;GP1 Vm07 Loc1</t>
+  </si>
+  <si>
+    <t>AUTO_PRA_LOC1_PHONE_APPOINTMENT_DETAILS</t>
+  </si>
+  <si>
+    <t>Phone;VM07 Loc2 Evo Prod;GP2 VM07 Loc2</t>
+  </si>
+  <si>
+    <t>AUTO_PRA_LOC1_PHONE_APPOINTMENT_SUMMARY</t>
+  </si>
+  <si>
+    <t>AUTO_PRA_LOC1_APPOINTMENT_DETAILS_FOR_CANCEL</t>
+  </si>
+  <si>
+    <t>AUTO_PRA_LOC1_APPOINTMENT_DETAILS_AFTER_CANCELLED</t>
+  </si>
+  <si>
+    <t>Bruce Wayne;GP1 A1 L1;GP2WHITE;GP3 White;Gp4 White;Gp5white;Gp6 White</t>
+  </si>
+  <si>
+    <t>Bruce Wayne;GP1 A1 L1;GP2WHITE;Gp5white</t>
+  </si>
+  <si>
+    <t>VM07 Loc1 Evo Prod;2 g, Twice Daily, 1 week;Dr B Beta</t>
+  </si>
+  <si>
+    <t>2 time per day</t>
   </si>
 </sst>
 </file>
@@ -4417,7 +4459,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4666,6 +4708,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="3"/>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="3" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4899,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C1" s="73" t="s">
         <v>1</v>
@@ -4932,13 +4978,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>1300</v>
+        <v>1048</v>
       </c>
       <c r="D2" s="57" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -4995,10 +5041,10 @@
     </row>
     <row r="4" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A4" s="1" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="C4" s="75"/>
       <c r="D4" s="4"/>
@@ -5024,10 +5070,10 @@
     </row>
     <row r="5" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A5" s="1" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="C5" s="75"/>
       <c r="D5" s="4"/>
@@ -5177,7 +5223,7 @@
         <v>1072</v>
       </c>
       <c r="C10" s="76" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>1072</v>
@@ -5334,7 +5380,7 @@
         <v>1073</v>
       </c>
       <c r="C15" s="76" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>1073</v>
@@ -5483,7 +5529,7 @@
         <v>1074</v>
       </c>
       <c r="C20" s="76" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>1074</v>
@@ -5632,7 +5678,7 @@
         <v>1075</v>
       </c>
       <c r="C25" s="76" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>1075</v>
@@ -5781,7 +5827,7 @@
         <v>1072</v>
       </c>
       <c r="C30" s="76" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>1072</v>
@@ -6169,7 +6215,7 @@
     </row>
     <row r="43" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="B43" s="8" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="C43"/>
       <c r="E43" s="2"/>
@@ -6194,13 +6240,13 @@
     </row>
     <row r="44" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A44" s="1" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="C44" s="76" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>1072</v>
@@ -6227,10 +6273,10 @@
     </row>
     <row r="45" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A45" s="1" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="C45" s="76" t="s">
         <v>13</v>
@@ -6260,10 +6306,10 @@
     </row>
     <row r="46" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A46" s="1" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="C46" s="76" t="s">
         <v>16</v>
@@ -6326,10 +6372,10 @@
     </row>
     <row r="48" spans="1:23" ht="13.5" customHeight="1">
       <c r="A48" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="B48" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="C48"/>
       <c r="E48" s="2"/>
@@ -6398,13 +6444,13 @@
     </row>
     <row r="51" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A51" s="1" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="C51" s="76" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -6428,10 +6474,10 @@
     </row>
     <row r="52" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A52" s="1" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="C52" s="76" t="s">
         <v>13</v>
@@ -6458,10 +6504,10 @@
     </row>
     <row r="53" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A53" s="1" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="C53" s="76" t="s">
         <v>16</v>
@@ -6518,10 +6564,10 @@
     </row>
     <row r="55" spans="1:23" ht="13.5" customHeight="1">
       <c r="A55" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B55" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="C55"/>
       <c r="E55" s="2"/>
@@ -7707,7 +7753,7 @@
         <v>106</v>
       </c>
       <c r="C94" s="76" t="s">
-        <v>1050</v>
+        <v>1314</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>106</v>
@@ -8040,10 +8086,18 @@
       <c r="W104" s="2"/>
     </row>
     <row r="105" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A105" s="9"/>
-      <c r="B105" s="9"/>
-      <c r="C105" s="77"/>
-      <c r="D105" s="9"/>
+      <c r="A105" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C105" s="76" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
@@ -8060,6 +8114,9 @@
       <c r="R105" s="2"/>
       <c r="S105" s="2"/>
       <c r="T105" s="2"/>
+      <c r="U105" s="2"/>
+      <c r="V105" s="2"/>
+      <c r="W105" s="2"/>
     </row>
     <row r="106" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A106" s="1" t="s">
@@ -9306,13 +9363,13 @@
         <v>188</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="C146" s="76" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
@@ -9339,7 +9396,7 @@
         <v>189</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C147" s="85" t="s">
         <v>976</v>
@@ -9372,7 +9429,7 @@
         <v>190</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C148" s="76" t="s">
         <v>192</v>
@@ -9430,7 +9487,7 @@
         <v>193</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="C150" s="76" t="s">
         <v>1066</v>
@@ -9499,7 +9556,7 @@
         <v>1033</v>
       </c>
       <c r="C152" s="76" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>1033</v>
@@ -9999,7 +10056,7 @@
         <v>1076</v>
       </c>
       <c r="C168" s="76" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>1076</v>
@@ -10032,7 +10089,7 @@
         <v>1076</v>
       </c>
       <c r="C169" s="76" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>1076</v>
@@ -10230,7 +10287,7 @@
         <v>1077</v>
       </c>
       <c r="C175" s="87" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D175" s="15" t="s">
         <v>1077</v>
@@ -10263,7 +10320,7 @@
         <v>1078</v>
       </c>
       <c r="C176" s="76" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>1078</v>
@@ -10296,7 +10353,7 @@
         <v>1079</v>
       </c>
       <c r="C177" s="76" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>1079</v>
@@ -10362,7 +10419,7 @@
         <v>1080</v>
       </c>
       <c r="C179" s="76" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>1080</v>
@@ -10648,10 +10705,10 @@
     </row>
     <row r="189" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A189" s="1" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="C189" s="55"/>
       <c r="D189" s="2"/>
@@ -10677,10 +10734,10 @@
     </row>
     <row r="190" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A190" s="1" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="C190" s="55"/>
       <c r="D190" s="2"/>
@@ -10730,10 +10787,10 @@
     </row>
     <row r="192" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A192" s="1" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="C192"/>
       <c r="D192" s="2"/>
@@ -10759,10 +10816,10 @@
     </row>
     <row r="193" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A193" s="1" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="C193" s="55"/>
       <c r="D193" s="2"/>
@@ -10812,13 +10869,13 @@
     </row>
     <row r="195" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A195" s="1" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="C195" s="76" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" s="2"/>
@@ -10843,7 +10900,7 @@
     </row>
     <row r="196" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A196" s="1" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>12</v>
@@ -10960,13 +11017,13 @@
     </row>
     <row r="200" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A200" s="1" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="C200" s="76" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
@@ -10991,7 +11048,7 @@
     </row>
     <row r="201" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A201" s="1" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>12</v>
@@ -16754,7 +16811,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>1</v>
@@ -16785,7 +16842,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="C2" s="51" t="s">
         <v>1048</v>
@@ -16827,7 +16884,7 @@
         <v>1076</v>
       </c>
       <c r="C11" s="76" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="30" thickBot="1">
@@ -16835,10 +16892,10 @@
         <v>218</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="C12" s="76" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="30.75" thickBot="1">
@@ -16846,10 +16903,10 @@
         <v>557</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -16860,7 +16917,7 @@
         <v>559</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="30">
@@ -16868,10 +16925,10 @@
         <v>375</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>1232</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -16904,7 +16961,7 @@
         <v>1079</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -16978,7 +17035,7 @@
         <v>1072</v>
       </c>
       <c r="C28" s="76" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -17023,7 +17080,7 @@
         <v>1073</v>
       </c>
       <c r="C33" s="76" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="13.5" customHeight="1" thickBot="1">
@@ -17058,7 +17115,7 @@
         <v>1074</v>
       </c>
       <c r="C38" s="76" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="13.5" customHeight="1" thickBot="1">
@@ -17093,7 +17150,7 @@
         <v>1075</v>
       </c>
       <c r="C43" s="76" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.5" customHeight="1" thickBot="1">
@@ -17128,7 +17185,7 @@
         <v>1072</v>
       </c>
       <c r="C48" s="76" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" thickBot="1">
@@ -17258,7 +17315,7 @@
         <v>571</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>573</v>
@@ -17270,7 +17327,7 @@
         <v>574</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>576</v>
@@ -17281,7 +17338,7 @@
         <v>577</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="C70" s="9" t="s">
         <v>578</v>
@@ -17292,7 +17349,7 @@
         <v>579</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="C71" s="9" t="s">
         <v>581</v>
@@ -17339,7 +17396,7 @@
         <v>589</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>591</v>
@@ -17372,7 +17429,7 @@
         <v>382</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" customHeight="1"/>
@@ -17381,10 +17438,10 @@
         <v>596</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15.75" customHeight="1">
@@ -17533,10 +17590,10 @@
         <v>626</v>
       </c>
       <c r="B110" s="9" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C110" s="9" t="s">
         <v>1239</v>
-      </c>
-      <c r="C110" s="9" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15.75" customHeight="1">
@@ -17544,10 +17601,10 @@
         <v>627</v>
       </c>
       <c r="B111" s="9" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C111" s="9" t="s">
         <v>1240</v>
-      </c>
-      <c r="C111" s="9" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15.75" customHeight="1">
@@ -17555,10 +17612,10 @@
         <v>628</v>
       </c>
       <c r="B112" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C112" s="9" t="s">
         <v>1241</v>
-      </c>
-      <c r="C112" s="9" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75" customHeight="1"/>
@@ -17567,10 +17624,10 @@
         <v>629</v>
       </c>
       <c r="B114" s="9" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C114" s="9" t="s">
         <v>1247</v>
-      </c>
-      <c r="C114" s="9" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75" customHeight="1">
@@ -17578,10 +17635,10 @@
         <v>630</v>
       </c>
       <c r="B115" s="9" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C115" s="9" t="s">
         <v>1248</v>
-      </c>
-      <c r="C115" s="9" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15.75" customHeight="1">
@@ -17589,10 +17646,10 @@
         <v>631</v>
       </c>
       <c r="B116" s="9" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C116" s="9" t="s">
         <v>1249</v>
-      </c>
-      <c r="C116" s="9" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15.75" customHeight="1"/>
@@ -17638,7 +17695,7 @@
         <v>641</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75" customHeight="1"/>
@@ -17650,7 +17707,7 @@
         <v>643</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15.75" customHeight="1">
@@ -17661,7 +17718,7 @@
         <v>645</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15.75" customHeight="1">
@@ -17672,7 +17729,7 @@
         <v>645</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15.75" customHeight="1"/>
@@ -18580,7 +18637,7 @@
         <v>188</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="C229" s="76" t="s">
         <v>1065</v>
@@ -18591,7 +18648,7 @@
         <v>189</v>
       </c>
       <c r="B230" s="10" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C230" s="85" t="s">
         <v>976</v>
@@ -18602,7 +18659,7 @@
         <v>190</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C231" s="76" t="s">
         <v>192</v>
@@ -18614,7 +18671,7 @@
         <v>193</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="C233" s="76" t="s">
         <v>1066</v>
@@ -18639,7 +18696,7 @@
         <v>1033</v>
       </c>
       <c r="C235" s="76" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
@@ -21329,7 +21386,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>1</v>
@@ -21359,7 +21416,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -21963,7 +22020,7 @@
         <v>39</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
@@ -22779,7 +22836,7 @@
         <v>281</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C54" s="18"/>
       <c r="D54" s="18"/>
@@ -22807,7 +22864,7 @@
         <v>282</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C55" s="18"/>
       <c r="D55" s="18"/>
@@ -22835,7 +22892,7 @@
         <v>283</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C56" s="18"/>
       <c r="D56" s="18"/>
@@ -22863,7 +22920,7 @@
         <v>284</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C57" s="18"/>
       <c r="D57" s="18"/>
@@ -22891,7 +22948,7 @@
         <v>285</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C58" s="18"/>
       <c r="D58" s="18"/>
@@ -22919,7 +22976,7 @@
         <v>286</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C59" s="18"/>
       <c r="D59" s="18"/>
@@ -22947,7 +23004,7 @@
         <v>287</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C60" s="18"/>
       <c r="D60" s="18"/>
@@ -22975,7 +23032,7 @@
         <v>288</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C61" s="18"/>
       <c r="D61" s="18"/>
@@ -23003,7 +23060,7 @@
         <v>289</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C62" s="18"/>
       <c r="D62" s="18"/>
@@ -23031,7 +23088,7 @@
         <v>290</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C63" s="18"/>
       <c r="D63" s="18"/>
@@ -23059,7 +23116,7 @@
         <v>291</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C64" s="18"/>
       <c r="D64" s="18"/>
@@ -23087,7 +23144,7 @@
         <v>292</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C65" s="18"/>
       <c r="D65" s="18"/>
@@ -23115,7 +23172,7 @@
         <v>293</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C66" s="18"/>
       <c r="D66" s="18"/>
@@ -23143,7 +23200,7 @@
         <v>294</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C67" s="18"/>
       <c r="D67" s="18"/>
@@ -23195,7 +23252,7 @@
         <v>295</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C69" s="18"/>
       <c r="D69" s="18"/>
@@ -23251,7 +23308,7 @@
         <v>298</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C71" s="18"/>
       <c r="D71" s="18"/>
@@ -23303,7 +23360,7 @@
         <v>299</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="C73" s="18"/>
       <c r="D73" s="18"/>
@@ -23331,7 +23388,7 @@
         <v>300</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="C74" s="18"/>
       <c r="D74" s="18"/>
@@ -23815,7 +23872,7 @@
         <v>319</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C92" s="18"/>
       <c r="D92" s="18"/>
@@ -23843,7 +23900,7 @@
         <v>320</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C93" s="18"/>
       <c r="D93" s="18"/>
@@ -23951,7 +24008,7 @@
         <v>323</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C97" s="18"/>
       <c r="D97" s="18"/>
@@ -23979,7 +24036,7 @@
         <v>324</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C98" s="18"/>
       <c r="D98" s="18"/>
@@ -24007,7 +24064,7 @@
         <v>325</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C99" s="18"/>
       <c r="D99" s="18"/>
@@ -24059,7 +24116,7 @@
         <v>326</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C101" s="18"/>
       <c r="D101" s="18"/>
@@ -24115,7 +24172,7 @@
         <v>327</v>
       </c>
       <c r="B103" s="22" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C103" s="18"/>
       <c r="D103" s="18"/>
@@ -24195,7 +24252,7 @@
         <v>330</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="C106" s="18"/>
       <c r="D106" s="18"/>
@@ -24223,7 +24280,7 @@
         <v>331</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C107" s="18"/>
       <c r="D107" s="18"/>
@@ -24375,7 +24432,7 @@
         <v>333</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C113" s="18"/>
       <c r="D113" s="18"/>
@@ -24427,7 +24484,7 @@
         <v>334</v>
       </c>
       <c r="B115" s="24" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C115" s="18"/>
       <c r="D115" s="18"/>
@@ -24479,7 +24536,7 @@
         <v>335</v>
       </c>
       <c r="B117" s="92" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C117" s="18"/>
       <c r="D117" s="18"/>
@@ -24787,7 +24844,7 @@
         <v>340</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C129" s="18"/>
       <c r="D129" s="18"/>
@@ -24843,7 +24900,7 @@
         <v>341</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C131" s="18"/>
       <c r="D131" s="18"/>
@@ -25595,7 +25652,7 @@
         <v>370</v>
       </c>
       <c r="B159" s="94" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C159" s="18"/>
       <c r="D159" s="18"/>
@@ -25971,7 +26028,7 @@
         <v>441</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C173" s="18"/>
       <c r="D173" s="18"/>
@@ -26020,10 +26077,10 @@
     </row>
     <row r="175" spans="1:22" ht="15.75" customHeight="1">
       <c r="A175" s="91" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B175" s="94" t="s">
         <v>1206</v>
-      </c>
-      <c r="B175" s="94" t="s">
-        <v>1208</v>
       </c>
       <c r="C175" s="18"/>
       <c r="D175" s="18"/>
@@ -26048,10 +26105,10 @@
     </row>
     <row r="176" spans="1:22" ht="15.75" customHeight="1">
       <c r="A176" s="91" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B176" s="94" t="s">
         <v>1207</v>
-      </c>
-      <c r="B176" s="94" t="s">
-        <v>1209</v>
       </c>
       <c r="C176" s="18"/>
       <c r="D176" s="18"/>
@@ -26076,10 +26133,10 @@
     </row>
     <row r="177" spans="1:22" ht="15.75" customHeight="1">
       <c r="A177" s="91" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B177" s="94" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C177" s="18"/>
       <c r="D177" s="18"/>
@@ -26104,10 +26161,10 @@
     </row>
     <row r="178" spans="1:22" ht="15.75" customHeight="1">
       <c r="A178" s="91" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B178" s="94" t="s">
         <v>1211</v>
-      </c>
-      <c r="B178" s="94" t="s">
-        <v>1213</v>
       </c>
       <c r="C178" s="18"/>
       <c r="D178" s="18"/>
@@ -26132,10 +26189,10 @@
     </row>
     <row r="179" spans="1:22" ht="15.75" customHeight="1">
       <c r="A179" s="91" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="B179" s="94" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C179" s="18"/>
       <c r="D179" s="18"/>
@@ -26190,7 +26247,7 @@
         <v>1087</v>
       </c>
       <c r="C181" s="62" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D181" s="18"/>
       <c r="E181" s="18"/>
@@ -26244,10 +26301,10 @@
     </row>
     <row r="183" spans="1:22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A183" s="91" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B183" s="94" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C183" s="18"/>
       <c r="D183" s="18"/>
@@ -26278,7 +26335,7 @@
         <v>505</v>
       </c>
       <c r="C184" s="62" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D184" s="18"/>
       <c r="E184" s="18"/>
@@ -26302,10 +26359,10 @@
     </row>
     <row r="185" spans="1:22" ht="15.75" customHeight="1">
       <c r="A185" s="91" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B185" s="94" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C185" s="18"/>
       <c r="D185" s="18"/>
@@ -26354,10 +26411,10 @@
     </row>
     <row r="187" spans="1:22" ht="15.75" customHeight="1">
       <c r="A187" s="91" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B187" s="94" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C187" s="18"/>
       <c r="D187" s="18"/>
@@ -30872,7 +30929,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C1" s="26" t="s">
         <v>1</v>
@@ -32734,7 +32791,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C1" s="65" t="s">
         <v>1</v>
@@ -32747,10 +32804,10 @@
       <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="57" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C2" s="51" t="s">
+      <c r="B2" s="96" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" s="72" t="s">
         <v>1048</v>
       </c>
       <c r="D2" t="s">
@@ -32823,7 +32880,7 @@
         <v>1082</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>417</v>
@@ -32837,7 +32894,7 @@
         <v>1083</v>
       </c>
       <c r="C9" s="62" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>420</v>
@@ -32848,10 +32905,10 @@
         <v>422</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C10" s="62" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>423</v>
@@ -32862,10 +32919,10 @@
         <v>425</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C11" s="62" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>426</v>
@@ -32876,10 +32933,10 @@
         <v>428</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>429</v>
@@ -32890,10 +32947,10 @@
         <v>431</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C13" s="62" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>432</v>
@@ -32904,10 +32961,10 @@
         <v>434</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C14" s="62" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>435</v>
@@ -32942,94 +32999,100 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A17" s="9" t="s">
-        <v>441</v>
+      <c r="A17" s="91" t="s">
+        <v>1297</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1218</v>
+        <v>442</v>
       </c>
       <c r="C17" s="62" t="s">
-        <v>1219</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>442</v>
-      </c>
+        <v>1298</v>
+      </c>
+      <c r="D17" s="9"/>
     </row>
     <row r="18" spans="1:4" ht="15.75" thickBot="1">
       <c r="A18" s="9" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>98</v>
+        <v>1299</v>
       </c>
       <c r="C18" s="62" t="s">
-        <v>976</v>
+        <v>1216</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>98</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" thickBot="1">
       <c r="A19" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C19" s="62" t="s">
+        <v>976</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A20" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B20" s="31" t="s">
         <v>447</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C20" s="62" t="s">
         <v>448</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D20" s="31" t="s">
         <v>447</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="30.75" thickBot="1">
-      <c r="A20" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="C20" s="62" t="s">
-        <v>451</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C21" s="62" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="C22" s="62" t="s">
+        <v>454</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A23" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B23" s="9" t="s">
         <v>456</v>
       </c>
-      <c r="C22" s="62" t="s">
+      <c r="C23" s="62" t="s">
         <v>457</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D23" s="9" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="9"/>
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="9"/>
@@ -33068,261 +33131,253 @@
       <c r="D29" s="9"/>
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A30" s="29"/>
-      <c r="B30" s="29" t="s">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="9"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A31" s="29"/>
+      <c r="B31" s="29" t="s">
         <v>458</v>
       </c>
-      <c r="C30" s="66"/>
-      <c r="D30" s="29" t="s">
+      <c r="C31" s="66"/>
+      <c r="D31" s="29" t="s">
         <v>458</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A31" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="C31" s="61" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A32" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="67" t="s">
-        <v>968</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>5</v>
+        <v>459</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="C32" s="61" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A33" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>56</v>
+        <v>462</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="67" t="s">
+        <v>968</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A34" s="9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C34" s="60" t="s">
-        <v>966</v>
+        <v>57</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A35" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="C35" s="62" t="s">
-        <v>469</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>469</v>
+        <v>58</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="60" t="s">
+        <v>966</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A36" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="C36" s="62" t="s">
+        <v>469</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A37" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C36" s="59" t="s">
+      <c r="C37" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="62"/>
-      <c r="D37" s="9"/>
-    </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="9"/>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A39" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="C38" s="60" t="s">
+      <c r="C39" s="60" t="s">
         <v>989</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>1068</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A39" s="33" t="s">
+    <row r="40" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A40" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="C39" s="60" t="s">
+      <c r="C40" s="60" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>1069</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="62"/>
-      <c r="D40" s="9"/>
-    </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="62"/>
+      <c r="D41" s="9"/>
+    </row>
+    <row r="42" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A42" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="60" t="s">
+      <c r="C42" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A42" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C42" s="60" t="s">
-        <v>1220</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="60" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A44" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="76" t="s">
+      <c r="C44" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="76"/>
-      <c r="D44" s="1"/>
-    </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A45" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C45" s="60" t="s">
-        <v>1222</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>1070</v>
-      </c>
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="1"/>
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A46" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C46" s="60" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A47" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B46" s="9" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C46" s="60" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A47" s="9"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="59"/>
-      <c r="D47" s="1"/>
+      <c r="B47" s="9" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C47" s="60" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>1220</v>
+      </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="9"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="59"/>
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A49" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C48" s="60" t="s">
+      <c r="C49" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>480</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A49" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="C49" s="60" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="50" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A50" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C50" s="76" t="s">
-        <v>77</v>
+        <v>482</v>
+      </c>
+      <c r="C50" s="60" t="s">
+        <v>1218</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1047</v>
+        <v>482</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
@@ -33345,224 +33400,238 @@
       <c r="W50" s="2"/>
     </row>
     <row r="51" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A51" s="34"/>
-      <c r="B51" s="34" t="s">
+      <c r="A51" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C51" s="76" t="s">
+        <v>77</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A52" s="34"/>
+      <c r="B52" s="34" t="s">
         <v>484</v>
       </c>
-      <c r="C51" s="68"/>
-      <c r="D51" s="34" t="s">
+      <c r="C52" s="68"/>
+      <c r="D52" s="34" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="62"/>
-      <c r="D52" s="9"/>
-    </row>
     <row r="53" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A53" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C53" s="59" t="s">
-        <v>1131</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>217</v>
-      </c>
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="62"/>
+      <c r="D53" s="9"/>
     </row>
     <row r="54" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A54" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C54" s="59" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A55" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B55" s="15" t="s">
         <v>1084</v>
       </c>
-      <c r="C54" s="64" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D54" s="15" t="s">
+      <c r="C55" s="64" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D55" s="15" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="59"/>
-      <c r="D55" s="1"/>
-    </row>
     <row r="56" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A56" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C56" s="60" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>232</v>
-      </c>
+      <c r="A56" s="91" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C56" s="64" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D56" s="1"/>
     </row>
     <row r="57" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A57" s="1" t="s">
-        <v>486</v>
+        <v>231</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C57" s="59" t="s">
-        <v>222</v>
+        <v>1079</v>
+      </c>
+      <c r="C57" s="60" t="s">
+        <v>1134</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="58" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A58" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C58" s="59" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A59" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C59" s="59" t="s">
+        <v>224</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A60" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C59" s="59" t="s">
+      <c r="C60" s="59" t="s">
         <v>226</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A60" s="28" t="s">
+    <row r="61" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A61" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C60" s="59" t="s">
+      <c r="C61" s="59" t="s">
         <v>980</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>228</v>
-      </c>
-    </row>
-    <row r="61" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A61" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C61" s="60" t="s">
-        <v>1131</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="62" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A62" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C62" s="60" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A63" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C62" s="60" t="s">
+      <c r="C63" s="60" t="s">
         <v>966</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="63" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A63" s="34"/>
-      <c r="B63" s="34" t="s">
+    <row r="64" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A64" s="34"/>
+      <c r="B64" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="C63" s="68"/>
-      <c r="D63" s="34" t="s">
+      <c r="C64" s="68"/>
+      <c r="D64" s="34" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="64" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A64" s="1" t="s">
+    <row r="65" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A65" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="C64" s="60" t="s">
+      <c r="C65" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>492</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A65" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C65" s="62" t="s">
-        <v>18</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A66" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C66" s="59" t="s">
-        <v>94</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>1044</v>
+        <v>17</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A67" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C67" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A68" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C67" s="59" t="s">
+      <c r="C68" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A68" s="9"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="62"/>
-      <c r="D68" s="9"/>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A69" s="9"/>
@@ -33589,190 +33658,190 @@
       <c r="D72" s="9"/>
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A73" s="34"/>
-      <c r="B73" s="34" t="s">
+      <c r="A73" s="9"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="62"/>
+      <c r="D73" s="9"/>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A74" s="34"/>
+      <c r="B74" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="C73" s="68"/>
-      <c r="D73" s="34" t="s">
+      <c r="C74" s="68"/>
+      <c r="D74" s="34" t="s">
         <v>493</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A74" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C74" s="62" t="s">
-        <v>1144</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A75" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C75" s="62" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A76" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B76" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="C75" s="62" t="s">
+      <c r="C76" s="62" t="s">
         <v>497</v>
       </c>
-      <c r="D75" s="9" t="s">
+      <c r="D76" s="9" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A76" s="9"/>
-      <c r="B76" s="9" t="s">
+    <row r="77" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A77" s="9"/>
+      <c r="B77" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="C76" s="62" t="s">
+      <c r="C77" s="62" t="s">
         <v>498</v>
       </c>
-      <c r="D76" s="9" t="s">
+      <c r="D77" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A77" s="9" t="s">
+    <row r="78" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A78" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>1086</v>
       </c>
-      <c r="C77" s="60" t="s">
-        <v>1131</v>
-      </c>
-      <c r="D77" s="1" t="s">
+      <c r="C78" s="60" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
-      <c r="C78" s="62"/>
-      <c r="D78" s="1"/>
-    </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A79" s="9" t="s">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="62"/>
+      <c r="D79" s="1"/>
+    </row>
+    <row r="80" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A80" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B80" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="C79" s="62" t="s">
+      <c r="C80" s="62" t="s">
         <v>498</v>
       </c>
-      <c r="D79" s="9" t="s">
+      <c r="D80" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A80" s="34"/>
-      <c r="B80" s="34" t="s">
+    <row r="81" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A81" s="34"/>
+      <c r="B81" s="34" t="s">
         <v>502</v>
       </c>
-      <c r="C80" s="68"/>
-      <c r="D80" s="34" t="s">
+      <c r="C81" s="68"/>
+      <c r="D81" s="34" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="62"/>
-      <c r="D81" s="9"/>
-    </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A82" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C82" s="62" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>382</v>
-      </c>
+      <c r="A82" s="9"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="62"/>
+      <c r="D82" s="9"/>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A83" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>384</v>
+        <v>1087</v>
       </c>
       <c r="C83" s="62" t="s">
-        <v>503</v>
+        <v>1144</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A84" s="9" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C84" s="62" t="s">
-        <v>386</v>
+        <v>503</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A85" s="9" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="C85" s="62" t="s">
-        <v>1104</v>
+        <v>386</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>412</v>
+        <v>386</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A86" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="C86" s="62" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A87" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B87" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="C86" s="62" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D86" s="9" t="s">
+      <c r="C87" s="62" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D87" s="9" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A87" s="34"/>
-      <c r="B87" s="34" t="s">
+    <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A88" s="34"/>
+      <c r="B88" s="34" t="s">
         <v>506</v>
       </c>
-      <c r="C87" s="68"/>
-      <c r="D87" s="34" t="s">
+      <c r="C88" s="68"/>
+      <c r="D88" s="34" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A88" s="9"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="62"/>
-      <c r="D88" s="9"/>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A89" s="9"/>
@@ -33787,290 +33856,274 @@
       <c r="D90" s="9"/>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A91" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C91" s="60" t="s">
-        <v>1127</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>10</v>
-      </c>
+      <c r="A91" s="9"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="62"/>
+      <c r="D91" s="9"/>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A92" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>12</v>
+        <v>1072</v>
       </c>
       <c r="C92" s="60" t="s">
-        <v>13</v>
+        <v>1126</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A93" s="9" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C93" s="62" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="C93" s="60" t="s">
+        <v>13</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A94" s="9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C94" s="60" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C94" s="62" t="s">
+        <v>18</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A95" s="9" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C95" s="60" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A96" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C96" s="60" t="s">
+        <v>46</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A97" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B97" s="9" t="s">
         <v>1088</v>
       </c>
-      <c r="C96" s="62" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D96" s="9" t="s">
+      <c r="C97" s="62" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D97" s="9" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A97" s="9"/>
-      <c r="B97" s="9"/>
-      <c r="C97" s="62"/>
-      <c r="D97" s="9"/>
-    </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A98" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C98" s="60" t="s">
-        <v>1128</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>20</v>
-      </c>
+      <c r="A98" s="9"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="62"/>
+      <c r="D98" s="9"/>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A99" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>22</v>
+        <v>1101</v>
       </c>
       <c r="C99" s="60" t="s">
-        <v>23</v>
+        <v>1127</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A100" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="C100" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A101" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B100" s="9" t="s">
+      <c r="B101" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="D101" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C100" s="60" t="s">
-        <v>16</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A101" s="9"/>
-      <c r="B101" s="9"/>
-      <c r="C101" s="62"/>
-      <c r="D101" s="9"/>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A102" s="29"/>
-      <c r="B102" s="35" t="s">
+      <c r="A102" s="9"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="62"/>
+      <c r="D102" s="9"/>
+    </row>
+    <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A103" s="29"/>
+      <c r="B103" s="35" t="s">
         <v>509</v>
       </c>
-      <c r="C102" s="66"/>
-      <c r="D102" s="35" t="s">
+      <c r="C103" s="66"/>
+      <c r="D103" s="35" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A103" s="28" t="s">
+    <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A104" s="28" t="s">
         <v>391</v>
       </c>
-      <c r="B103" s="9" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C103" s="63" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D103" s="9" t="s">
+      <c r="B104" s="9" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C104" s="63" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D104" s="9" t="s">
         <v>392</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A104" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="C104" s="62" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A105" s="9" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>396</v>
+        <v>1313</v>
       </c>
       <c r="C105" s="62" t="s">
-        <v>1106</v>
+        <v>1306</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A106" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C106" s="62" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A107" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B106" s="9" t="s">
+      <c r="B107" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="C106" s="62" t="s">
+      <c r="C107" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="D106" s="9" t="s">
+      <c r="D107" s="9" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A107" s="9"/>
-      <c r="B107" s="9"/>
-      <c r="C107" s="62"/>
-      <c r="D107" s="9"/>
-    </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A108" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="C108" s="62" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D108" s="9" t="s">
-        <v>511</v>
-      </c>
+      <c r="A108" s="9"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="62"/>
+      <c r="D108" s="9"/>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A109" s="9" t="s">
-        <v>403</v>
+        <v>1307</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C109" s="62" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>25</v>
-      </c>
+        <v>1308</v>
+      </c>
+      <c r="D109" s="9"/>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A110" s="9" t="s">
-        <v>512</v>
+      <c r="A110" s="91" t="s">
+        <v>1309</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C110" s="62" t="s">
-        <v>1109</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>53</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D110" s="9"/>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A111" s="9"/>
-      <c r="B111" s="9"/>
-      <c r="C111" s="62"/>
+      <c r="A111" s="9" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="D111" s="9"/>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A112" s="9" t="s">
-        <v>513</v>
+        <v>1311</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C112" s="63" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>400</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D112" s="9"/>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A113" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C113" s="63" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>400</v>
-      </c>
+      <c r="A113" s="9"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="62"/>
+      <c r="D113" s="9"/>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A114" s="9"/>
@@ -34080,44 +34133,44 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A115" s="9" t="s">
-        <v>515</v>
+        <v>402</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C115" s="63" t="s">
-        <v>1148</v>
+        <v>511</v>
+      </c>
+      <c r="C115" s="62" t="s">
+        <v>1106</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A116" s="9" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C116" s="63" t="s">
-        <v>1148</v>
+        <v>25</v>
+      </c>
+      <c r="C116" s="62" t="s">
+        <v>1107</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>398</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A117" s="9" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C117" s="63" t="s">
-        <v>1148</v>
+        <v>53</v>
+      </c>
+      <c r="C117" s="62" t="s">
+        <v>1108</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>398</v>
+        <v>53</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
@@ -34128,222 +34181,222 @@
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A119" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C119" s="59" t="s">
-        <v>1149</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>519</v>
+        <v>513</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C119" s="63" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A120" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C120" s="59" t="s">
-        <v>1149</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>521</v>
+        <v>514</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C120" s="63" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A121" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="B121" s="9" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C121" s="63" t="s">
-        <v>1149</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>521</v>
-      </c>
+      <c r="A121" s="9"/>
+      <c r="B121" s="9"/>
+      <c r="C121" s="62"/>
+      <c r="D121" s="9"/>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A122" s="9"/>
-      <c r="B122" s="9"/>
-      <c r="C122" s="62"/>
-      <c r="D122" s="9"/>
+      <c r="A122" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C122" s="63" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A123" s="9" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C123" s="63" t="s">
         <v>1147</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A124" s="9" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C124" s="63" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D124" s="9" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A125" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C125" s="59" t="s">
-        <v>1149</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>525</v>
-      </c>
+      <c r="A125" s="9"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="62"/>
+      <c r="D125" s="9"/>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A126" s="9"/>
-      <c r="B126" s="9"/>
-      <c r="C126" s="62"/>
-      <c r="D126" s="9"/>
+      <c r="A126" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C126" s="59" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A127" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="B127" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="C127" s="62" t="s">
-        <v>1110</v>
-      </c>
-      <c r="D127" s="9" t="s">
-        <v>527</v>
+        <v>520</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C127" s="59" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A128" s="9" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C128" s="62" t="s">
-        <v>530</v>
+        <v>1094</v>
+      </c>
+      <c r="C128" s="63" t="s">
+        <v>1148</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A129" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="B129" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="C129" s="62" t="s">
-        <v>530</v>
-      </c>
-      <c r="D129" s="9" t="s">
-        <v>394</v>
-      </c>
+      <c r="A129" s="9"/>
+      <c r="B129" s="9"/>
+      <c r="C129" s="62"/>
+      <c r="D129" s="9"/>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A130" s="9"/>
-      <c r="B130" s="9"/>
-      <c r="C130" s="62"/>
-      <c r="D130" s="9"/>
+      <c r="A130" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="B130" s="9" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C130" s="63" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A131" s="9" t="s">
-        <v>406</v>
+        <v>523</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="C131" s="62" t="s">
-        <v>1111</v>
+        <v>1092</v>
+      </c>
+      <c r="C131" s="63" t="s">
+        <v>1147</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A132" s="9"/>
-      <c r="B132" s="9"/>
-      <c r="C132" s="62"/>
-      <c r="D132" s="9"/>
+      <c r="A132" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C132" s="59" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A133" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="B133" s="9" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C133" s="62" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D133" s="9" t="s">
-        <v>1023</v>
-      </c>
+      <c r="A133" s="9"/>
+      <c r="B133" s="9"/>
+      <c r="C133" s="62"/>
+      <c r="D133" s="9"/>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A134" s="9" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>12</v>
+        <v>527</v>
       </c>
       <c r="C134" s="62" t="s">
-        <v>13</v>
+        <v>1109</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>12</v>
+        <v>527</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A135" s="9" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>380</v>
+        <v>1312</v>
       </c>
       <c r="C135" s="62" t="s">
-        <v>380</v>
+        <v>530</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>380</v>
+        <v>529</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A136" s="9" t="s">
-        <v>534</v>
+        <v>401</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>535</v>
+        <v>1312</v>
       </c>
       <c r="C136" s="62" t="s">
-        <v>1112</v>
+        <v>530</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>535</v>
+        <v>394</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
@@ -34354,158 +34407,154 @@
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A138" s="9" t="s">
-        <v>536</v>
+        <v>406</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>537</v>
+        <v>407</v>
       </c>
       <c r="C138" s="62" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>537</v>
+        <v>407</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A139" s="36" t="s">
-        <v>538</v>
-      </c>
-      <c r="B139" s="9" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C139" s="62" t="s">
-        <v>1151</v>
-      </c>
-      <c r="D139" s="9" t="s">
-        <v>539</v>
-      </c>
+      <c r="A139" s="9"/>
+      <c r="B139" s="9"/>
+      <c r="C139" s="62"/>
+      <c r="D139" s="9"/>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A140" s="9" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="C140" s="62" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>541</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A141" s="9" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>543</v>
+        <v>12</v>
       </c>
       <c r="C141" s="62" t="s">
-        <v>1114</v>
+        <v>13</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>543</v>
+        <v>12</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A142" s="9" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>545</v>
+        <v>380</v>
       </c>
       <c r="C142" s="62" t="s">
-        <v>1115</v>
+        <v>380</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>545</v>
+        <v>380</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A143" s="9"/>
-      <c r="B143" s="9"/>
-      <c r="C143" s="62"/>
-      <c r="D143" s="9"/>
+      <c r="A143" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="C143" s="62" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D143" s="9" t="s">
+        <v>535</v>
+      </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A144" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="B144" s="9" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C144" s="62" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D144" s="9" t="s">
-        <v>382</v>
-      </c>
+      <c r="A144" s="9"/>
+      <c r="B144" s="9"/>
+      <c r="C144" s="62"/>
+      <c r="D144" s="9"/>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A145" s="9" t="s">
-        <v>404</v>
+        <v>536</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="C145" s="72" t="s">
-        <v>1116</v>
+        <v>537</v>
+      </c>
+      <c r="C145" s="62" t="s">
+        <v>1112</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>405</v>
+        <v>537</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A146" s="34"/>
-      <c r="B146" s="34" t="s">
-        <v>547</v>
-      </c>
-      <c r="C146" s="68"/>
-      <c r="D146" s="34" t="s">
-        <v>547</v>
+      <c r="A146" s="36" t="s">
+        <v>538</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C146" s="62" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D146" s="9" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A147" s="9" t="s">
-        <v>408</v>
+        <v>540</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>1118</v>
+        <v>1098</v>
       </c>
       <c r="C147" s="62" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>409</v>
+        <v>541</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A148" s="9" t="s">
-        <v>30</v>
+        <v>542</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C148" s="60" t="s">
-        <v>1130</v>
+        <v>543</v>
+      </c>
+      <c r="C148" s="62" t="s">
+        <v>1113</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>410</v>
+        <v>543</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A149" s="9" t="s">
-        <v>31</v>
+        <v>544</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C149" s="60" t="s">
-        <v>33</v>
+        <v>545</v>
+      </c>
+      <c r="C149" s="62" t="s">
+        <v>1114</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>32</v>
+        <v>545</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
@@ -34516,404 +34565,487 @@
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A151" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C151" s="62" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D151" s="9" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A152" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="B152" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="C152" s="72" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D152" s="9" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A153" s="34"/>
+      <c r="B153" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="C153" s="68"/>
+      <c r="D153" s="34" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A154" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="B154" s="9" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C154" s="62" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D154" s="9" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A155" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C155" s="60" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D155" s="9" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A156" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B156" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C156" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="D156" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A157" s="9"/>
+      <c r="B157" s="9"/>
+      <c r="C157" s="62"/>
+      <c r="D157" s="9"/>
+    </row>
+    <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A158" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B151" s="9" t="s">
+      <c r="B158" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C151" s="60" t="s">
+      <c r="C158" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="D151" s="9" t="s">
+      <c r="D158" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A152" s="37"/>
-      <c r="B152" s="37"/>
-      <c r="C152" s="69"/>
-      <c r="D152" s="37"/>
-    </row>
-    <row r="153" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A153" s="6"/>
-      <c r="B153" s="38"/>
-      <c r="C153" s="70"/>
-      <c r="D153" s="38"/>
-    </row>
-    <row r="154" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A154" s="39"/>
-      <c r="B154" s="40" t="s">
+    <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A159" s="37"/>
+      <c r="B159" s="37"/>
+      <c r="C159" s="69"/>
+      <c r="D159" s="37"/>
+    </row>
+    <row r="160" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A160" s="6"/>
+      <c r="B160" s="38"/>
+      <c r="C160" s="70"/>
+      <c r="D160" s="38"/>
+    </row>
+    <row r="161" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A161" s="39"/>
+      <c r="B161" s="40" t="s">
         <v>493</v>
       </c>
-      <c r="C154" s="71"/>
-      <c r="D154" s="40" t="s">
+      <c r="C161" s="71"/>
+      <c r="D161" s="40" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A155" s="6" t="s">
+    <row r="162" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A162" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="B155" s="38" t="s">
+      <c r="B162" s="38" t="s">
         <v>1085</v>
       </c>
-      <c r="C155" s="38" t="s">
-        <v>1144</v>
-      </c>
-      <c r="D155" s="38" t="s">
+      <c r="C162" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D162" s="38" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A156" s="6" t="s">
+    <row r="163" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A163" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="B156" s="38" t="s">
+      <c r="B163" s="38" t="s">
         <v>497</v>
       </c>
-      <c r="C156" s="38" t="s">
+      <c r="C163" s="38" t="s">
         <v>497</v>
       </c>
-      <c r="D156" s="38" t="s">
+      <c r="D163" s="38" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A157" s="6"/>
-      <c r="B157" s="38" t="s">
+    <row r="164" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A164" s="6"/>
+      <c r="B164" s="38" t="s">
         <v>498</v>
       </c>
-      <c r="C157" s="38" t="s">
+      <c r="C164" s="38" t="s">
         <v>498</v>
       </c>
-      <c r="D157" s="38" t="s">
+      <c r="D164" s="38" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A158" s="9"/>
-      <c r="B158" s="9"/>
-      <c r="C158" s="62"/>
-      <c r="D158" s="9"/>
-    </row>
-    <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A159" s="29"/>
-      <c r="B159" s="35" t="s">
+    <row r="165" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A165" s="9"/>
+      <c r="B165" s="9"/>
+      <c r="C165" s="62"/>
+      <c r="D165" s="9"/>
+    </row>
+    <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A166" s="29"/>
+      <c r="B166" s="35" t="s">
         <v>548</v>
       </c>
-      <c r="C159" s="66"/>
-      <c r="D159" s="35" t="s">
+      <c r="C166" s="66"/>
+      <c r="D166" s="35" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A160" s="9" t="s">
+    <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A167" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="B160" s="9" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C160" s="62" t="s">
-        <v>1154</v>
-      </c>
-      <c r="D160" s="9" t="s">
+      <c r="B167" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C167" s="62" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D167" s="9" t="s">
         <v>1071</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A161" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="B161" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="C161" s="62" t="s">
-        <v>1117</v>
-      </c>
-      <c r="D161" s="9" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A162" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="B162" s="9" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C162" s="62" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D162" s="9" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A163" s="9"/>
-      <c r="B163" s="9"/>
-      <c r="C163" s="62"/>
-      <c r="D163" s="9"/>
-    </row>
-    <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A164" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="B164" s="12" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C164" s="63" t="s">
-        <v>1128</v>
-      </c>
-      <c r="D164" s="12" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A165" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="B165" s="9" t="s">
-        <v>555</v>
-      </c>
-      <c r="C165" s="62" t="s">
-        <v>23</v>
-      </c>
-      <c r="D165" s="9" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A166" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="B166" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C166" s="62" t="s">
-        <v>16</v>
-      </c>
-      <c r="D166" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A167" s="9"/>
-      <c r="B167" s="9"/>
-      <c r="C167" s="62"/>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A168" s="9" t="s">
-        <v>1059</v>
+        <v>550</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>1087</v>
+        <v>551</v>
       </c>
       <c r="C168" s="62" t="s">
-        <v>1145</v>
+        <v>1116</v>
       </c>
       <c r="D168" s="9" t="s">
-        <v>1087</v>
+        <v>551</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A169" s="9" t="s">
-        <v>1161</v>
+        <v>413</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="C169" s="62" t="s">
-        <v>1163</v>
+        <v>1155</v>
       </c>
       <c r="D169" s="9" t="s">
-        <v>1162</v>
+        <v>414</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A170" s="9" t="s">
-        <v>1164</v>
-      </c>
-      <c r="B170" s="9" t="s">
-        <v>1165</v>
-      </c>
-      <c r="C170" s="9" t="s">
-        <v>1165</v>
-      </c>
-      <c r="D170" s="9" t="s">
-        <v>1165</v>
-      </c>
+      <c r="A170" s="9"/>
+      <c r="B170" s="9"/>
+      <c r="C170" s="62"/>
+      <c r="D170" s="9"/>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A171" s="91" t="s">
-        <v>1166</v>
-      </c>
-      <c r="B171" s="9" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C171" s="9" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D171" s="9" t="s">
-        <v>1167</v>
+      <c r="A171" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B171" s="12" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C171" s="63" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D171" s="12" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A172" s="9" t="s">
-        <v>1170</v>
+      <c r="A172" s="1" t="s">
+        <v>554</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C172" s="9" t="s">
-        <v>1169</v>
+        <v>555</v>
+      </c>
+      <c r="C172" s="62" t="s">
+        <v>23</v>
       </c>
       <c r="D172" s="9" t="s">
-        <v>1168</v>
+        <v>555</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B173" s="9"/>
-      <c r="C173" s="9"/>
+      <c r="A173" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B173" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C173" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="D173" s="9" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A174" s="29"/>
-      <c r="B174" s="35" t="s">
-        <v>1226</v>
-      </c>
-      <c r="C174" s="66"/>
+      <c r="A174" s="9"/>
+      <c r="B174" s="9"/>
+      <c r="C174" s="62"/>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A175" s="9" t="s">
-        <v>1225</v>
+        <v>1059</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>1284</v>
+        <v>1087</v>
       </c>
       <c r="C175" s="62" t="s">
-        <v>1228</v>
+        <v>1144</v>
       </c>
       <c r="D175" s="9" t="s">
-        <v>1227</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A176" s="9" t="s">
-        <v>1229</v>
+        <v>1159</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C176" s="9"/>
-    </row>
-    <row r="177" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A177" s="91" t="s">
-        <v>1230</v>
+        <v>1160</v>
+      </c>
+      <c r="C176" s="62" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D176" s="9" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A177" s="9" t="s">
+        <v>1162</v>
       </c>
       <c r="B177" s="9" t="s">
-        <v>1283</v>
-      </c>
-      <c r="C177" s="9"/>
-    </row>
-    <row r="178" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A178" s="9" t="s">
-        <v>1285</v>
+        <v>1163</v>
+      </c>
+      <c r="C177" s="9" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D177" s="9" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A178" s="91" t="s">
+        <v>1164</v>
       </c>
       <c r="B178" s="9" t="s">
-        <v>1286</v>
-      </c>
-      <c r="C178" s="9"/>
-    </row>
-    <row r="179" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A179" s="9"/>
-      <c r="B179" s="9"/>
-      <c r="C179" s="9"/>
-    </row>
-    <row r="180" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A180" s="9"/>
+        <v>1165</v>
+      </c>
+      <c r="C178" s="9" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D178" s="9" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A179" s="9" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C179" s="9" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D179" s="9" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="B180" s="9"/>
       <c r="C180" s="9"/>
     </row>
-    <row r="181" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A181" s="9"/>
-      <c r="B181" s="9"/>
-      <c r="C181" s="9"/>
-    </row>
-    <row r="182" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A182" s="9"/>
-      <c r="B182" s="9"/>
-      <c r="C182" s="9"/>
-    </row>
-    <row r="183" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A183" s="9"/>
-      <c r="B183" s="9"/>
-      <c r="C183" s="9"/>
-    </row>
-    <row r="184" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A184" s="9"/>
-      <c r="B184" s="9"/>
+    <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A181" s="29"/>
+      <c r="B181" s="35" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C181" s="66"/>
+    </row>
+    <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A182" s="9" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B182" s="9" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C182" s="62" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D182" s="9" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A183" s="9" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B183" s="9" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C183" s="62" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A184" s="91" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B184" s="9" t="s">
+        <v>1280</v>
+      </c>
       <c r="C184" s="9"/>
     </row>
-    <row r="185" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A185" s="9"/>
-      <c r="B185" s="9"/>
+    <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A185" s="9" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>1283</v>
+      </c>
       <c r="C185" s="9"/>
     </row>
-    <row r="186" spans="1:3" ht="15.75" customHeight="1">
+    <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A186" s="9"/>
       <c r="B186" s="9"/>
       <c r="C186" s="9"/>
     </row>
-    <row r="187" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A187" s="9"/>
-      <c r="B187" s="9"/>
-      <c r="C187" s="9"/>
-    </row>
-    <row r="188" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A188" s="9"/>
-      <c r="B188" s="9"/>
-      <c r="C188" s="9"/>
-    </row>
-    <row r="189" spans="1:3" ht="15.75" customHeight="1">
+    <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A187" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C187" s="97" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A188" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C188" s="76" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A189" s="9"/>
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
     </row>
-    <row r="190" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A190" s="9"/>
-      <c r="B190" s="9"/>
-      <c r="C190" s="9"/>
-    </row>
-    <row r="191" spans="1:3" ht="15.75" customHeight="1">
+    <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A190" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C190" s="76" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A191" s="9"/>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
     </row>
-    <row r="192" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A192" s="9"/>
-      <c r="B192" s="9"/>
-      <c r="C192" s="9"/>
-    </row>
-    <row r="193" spans="1:3" ht="15.75" customHeight="1">
+    <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A192" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C192" s="76" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A193" s="9"/>
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
     </row>
-    <row r="194" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A194" s="9"/>
-      <c r="B194" s="9"/>
-      <c r="C194" s="9"/>
-    </row>
-    <row r="195" spans="1:3" ht="15.75" customHeight="1">
+    <row r="194" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A194" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C194" s="76" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A195" s="9"/>
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
     </row>
-    <row r="196" spans="1:3" ht="15.75" customHeight="1">
+    <row r="196" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A196" s="9"/>
       <c r="B196" s="9"/>
       <c r="C196" s="9"/>
     </row>
-    <row r="197" spans="1:3" ht="15.75" customHeight="1">
+    <row r="197" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A197" s="9"/>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
@@ -36400,13 +36532,14 @@
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{3EFD36B0-2228-45CC-AC19-2290C035AA1A}"/>
-    <hyperlink ref="C145" r:id="rId3" xr:uid="{D585080A-FC84-4C4E-BBDD-A485B5C6854A}"/>
-    <hyperlink ref="C2" r:id="rId4" xr:uid="{A4DEE308-051E-4F9C-9C85-8307AF9E1ACB}"/>
-    <hyperlink ref="B2" r:id="rId5" xr:uid="{6B02F5FD-321A-4EC6-B083-48F8A4F10673}"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{51CF91D8-7A2D-4C64-827B-6C41EEA7AE41}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{40CD9620-87B1-4D27-9D9D-9B54D2D36C19}"/>
+    <hyperlink ref="C152" r:id="rId3" xr:uid="{25FAC99D-B272-4C71-9B4D-364D57432552}"/>
+    <hyperlink ref="B2" r:id="rId4" xr:uid="{A5D45DE0-52B9-458D-A530-797F4FB8B49C}"/>
+    <hyperlink ref="C2" r:id="rId5" xr:uid="{10A69855-CD62-4F1A-BCBC-DBB64A29B7CA}"/>
+    <hyperlink ref="C187" r:id="rId6" xr:uid="{15BB9E58-3CD9-4309-9710-BEFD670B22CD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId6"/>
+  <pageSetup orientation="landscape" r:id="rId7"/>
 </worksheet>
 </file>
--- a/config/testdata/testdata.xlsx
+++ b/config/testdata/testdata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MMHNZ_V2_AUTOMATION\config\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB49A04-3DCF-441B-BC98-4A0B83DE31C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E3AEF5-69EA-4ACF-97C2-1C6DB9EA01FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="1316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="1322">
   <si>
     <t>KEY</t>
   </si>
@@ -3456,9 +3456,6 @@
     <t>VM07 HC Evo Prod;VM07 Loc1 Evo Prod;Patient Communication;Patient;peter;Received Msg Testing_RANDOM;Body : Received Message Testing_RANDOM;MMHtest.jpg</t>
   </si>
   <si>
-    <t>VM07 HC Evo Prod;Internal Communication;Patient;peter;Manual Test for Message;Body : Manual Test for Message;MMHtest.jpg</t>
-  </si>
-  <si>
     <t>VM07 HC Evo Prod;Any provider;No Preference;All Patients (Registered and Activated) to Patient Portal;Group MessageTesting_RANDOM;Group Message Test_RANDOM</t>
   </si>
   <si>
@@ -4003,6 +4000,27 @@
   </si>
   <si>
     <t>2 time per day</t>
+  </si>
+  <si>
+    <t>VM07 HC Evo Prod;Patient Communication;Patient;peter;Manual Test for Message;Body : Manual Test for Message;MMHtest.jpg</t>
+  </si>
+  <si>
+    <t>VM07 Loc1 Evo Prod ; Dr B Beta ; Patient to Collect Script ; Next Day;Praluent Prefilled Pen 150mg/1mL Soln for injection;Repeat Medication Testing for PATIENT TO COLLECT</t>
+  </si>
+  <si>
+    <t>VM07 Loc1 Evo Prod;praluent prefilled pen 150mg/1ml soln for injection(alirocumab);pending;Next Day - Fee: NZ$;Dr B Beta</t>
+  </si>
+  <si>
+    <t>Dr B Beta ( VM07 Loc1 Evo Prod );VM07 Loc1 Evo Prod;Patient to Collect Script;Next Day - Fee: NZ$;praluent prefilled pen 150mg/1ml soln for injection(alirocumab);Pending</t>
+  </si>
+  <si>
+    <t>VM07 Loc1 Evo Prod;GP1 Vm07 Loc1;Send Script by Post;Next Day;Panadol (Optizorb) 500mg Caplets;Repeat Medication Testing for PATIENT TO COLLECT</t>
+  </si>
+  <si>
+    <t>https://app.managemyhealth.co.nz/home</t>
+  </si>
+  <si>
+    <t>Pacifen 10mg Tab;1 tabs, Twice Daily, 1 week;14;GP2WHITE;Automation1_Loc1</t>
   </si>
 </sst>
 </file>
@@ -4945,7 +4963,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C1" s="73" t="s">
         <v>1</v>
@@ -4978,10 +4996,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>1048</v>
+        <v>1320</v>
       </c>
       <c r="D2" s="57" t="s">
         <v>1123</v>
@@ -5041,10 +5059,10 @@
     </row>
     <row r="4" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A4" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C4" s="75"/>
       <c r="D4" s="4"/>
@@ -5070,10 +5088,10 @@
     </row>
     <row r="5" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A5" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C5" s="75"/>
       <c r="D5" s="4"/>
@@ -6215,7 +6233,7 @@
     </row>
     <row r="43" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="B43" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C43"/>
       <c r="E43" s="2"/>
@@ -6240,10 +6258,10 @@
     </row>
     <row r="44" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A44" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C44" s="76" t="s">
         <v>1126</v>
@@ -6273,10 +6291,10 @@
     </row>
     <row r="45" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A45" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C45" s="76" t="s">
         <v>13</v>
@@ -6306,10 +6324,10 @@
     </row>
     <row r="46" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A46" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C46" s="76" t="s">
         <v>16</v>
@@ -6372,10 +6390,10 @@
     </row>
     <row r="48" spans="1:23" ht="13.5" customHeight="1">
       <c r="A48" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B48" t="s">
         <v>1270</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1271</v>
       </c>
       <c r="C48"/>
       <c r="E48" s="2"/>
@@ -6444,10 +6462,10 @@
     </row>
     <row r="51" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A51" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C51" s="76" t="s">
         <v>1126</v>
@@ -6474,10 +6492,10 @@
     </row>
     <row r="52" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A52" s="1" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C52" s="76" t="s">
         <v>13</v>
@@ -6504,10 +6522,10 @@
     </row>
     <row r="53" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A53" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C53" s="76" t="s">
         <v>16</v>
@@ -6564,10 +6582,10 @@
     </row>
     <row r="55" spans="1:23" ht="13.5" customHeight="1">
       <c r="A55" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B55" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C55"/>
       <c r="E55" s="2"/>
@@ -6674,7 +6692,7 @@
         <v>56</v>
       </c>
       <c r="C59" s="76" t="s">
-        <v>57</v>
+        <v>1316</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>56</v>
@@ -6707,7 +6725,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="76" t="s">
-        <v>966</v>
+        <v>1317</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>59</v>
@@ -6740,7 +6758,7 @@
         <v>61</v>
       </c>
       <c r="C61" s="76" t="s">
-        <v>62</v>
+        <v>1318</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>61</v>
@@ -6831,7 +6849,7 @@
         <v>67</v>
       </c>
       <c r="C64" s="76" t="s">
-        <v>68</v>
+        <v>1319</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>67</v>
@@ -7717,7 +7735,7 @@
         <v>104</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>1028</v>
+        <v>1321</v>
       </c>
       <c r="C93" s="76" t="s">
         <v>1049</v>
@@ -7753,7 +7771,7 @@
         <v>106</v>
       </c>
       <c r="C94" s="76" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>106</v>
@@ -8093,7 +8111,7 @@
         <v>112</v>
       </c>
       <c r="C105" s="76" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>112</v>
@@ -9363,10 +9381,10 @@
         <v>188</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C146" s="76" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>1124</v>
@@ -9396,7 +9414,7 @@
         <v>189</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C147" s="85" t="s">
         <v>976</v>
@@ -9429,7 +9447,7 @@
         <v>190</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C148" s="76" t="s">
         <v>192</v>
@@ -9487,7 +9505,7 @@
         <v>193</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C150" s="76" t="s">
         <v>1066</v>
@@ -10320,7 +10338,7 @@
         <v>1078</v>
       </c>
       <c r="C176" s="76" t="s">
-        <v>1133</v>
+        <v>1315</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>1078</v>
@@ -10353,7 +10371,7 @@
         <v>1079</v>
       </c>
       <c r="C177" s="76" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>1079</v>
@@ -10419,7 +10437,7 @@
         <v>1080</v>
       </c>
       <c r="C179" s="76" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>1080</v>
@@ -10705,10 +10723,10 @@
     </row>
     <row r="189" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A189" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C189" s="55"/>
       <c r="D189" s="2"/>
@@ -10734,10 +10752,10 @@
     </row>
     <row r="190" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A190" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C190" s="55"/>
       <c r="D190" s="2"/>
@@ -10787,10 +10805,10 @@
     </row>
     <row r="192" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A192" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C192"/>
       <c r="D192" s="2"/>
@@ -10816,10 +10834,10 @@
     </row>
     <row r="193" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A193" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C193" s="55"/>
       <c r="D193" s="2"/>
@@ -10869,10 +10887,10 @@
     </row>
     <row r="195" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A195" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C195" s="76" t="s">
         <v>1126</v>
@@ -10900,7 +10918,7 @@
     </row>
     <row r="196" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A196" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>12</v>
@@ -11017,10 +11035,10 @@
     </row>
     <row r="200" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A200" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C200" s="76" t="s">
         <v>1126</v>
@@ -11048,7 +11066,7 @@
     </row>
     <row r="201" spans="1:23" ht="13.5" customHeight="1" thickBot="1">
       <c r="A201" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>12</v>
@@ -16811,7 +16829,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>1</v>
@@ -16842,7 +16860,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C2" s="51" t="s">
         <v>1048</v>
@@ -16892,7 +16910,7 @@
         <v>218</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C12" s="76" t="s">
         <v>1131</v>
@@ -16903,10 +16921,10 @@
         <v>557</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -16917,7 +16935,7 @@
         <v>559</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="30">
@@ -16925,10 +16943,10 @@
         <v>375</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -16961,7 +16979,7 @@
         <v>1079</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -17315,7 +17333,7 @@
         <v>571</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>573</v>
@@ -17327,7 +17345,7 @@
         <v>574</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>576</v>
@@ -17338,7 +17356,7 @@
         <v>577</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C70" s="9" t="s">
         <v>578</v>
@@ -17349,7 +17367,7 @@
         <v>579</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C71" s="9" t="s">
         <v>581</v>
@@ -17396,7 +17414,7 @@
         <v>589</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>591</v>
@@ -17429,7 +17447,7 @@
         <v>382</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" customHeight="1"/>
@@ -17438,10 +17456,10 @@
         <v>596</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15.75" customHeight="1">
@@ -17590,10 +17608,10 @@
         <v>626</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15.75" customHeight="1">
@@ -17601,10 +17619,10 @@
         <v>627</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15.75" customHeight="1">
@@ -17612,10 +17630,10 @@
         <v>628</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75" customHeight="1"/>
@@ -17624,10 +17642,10 @@
         <v>629</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75" customHeight="1">
@@ -17635,10 +17653,10 @@
         <v>630</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15.75" customHeight="1">
@@ -17646,10 +17664,10 @@
         <v>631</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15.75" customHeight="1"/>
@@ -17695,7 +17713,7 @@
         <v>641</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75" customHeight="1"/>
@@ -17707,7 +17725,7 @@
         <v>643</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15.75" customHeight="1">
@@ -17718,7 +17736,7 @@
         <v>645</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15.75" customHeight="1">
@@ -17729,7 +17747,7 @@
         <v>645</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15.75" customHeight="1"/>
@@ -18637,7 +18655,7 @@
         <v>188</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C229" s="76" t="s">
         <v>1065</v>
@@ -18648,7 +18666,7 @@
         <v>189</v>
       </c>
       <c r="B230" s="10" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C230" s="85" t="s">
         <v>976</v>
@@ -18659,7 +18677,7 @@
         <v>190</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C231" s="76" t="s">
         <v>192</v>
@@ -18671,7 +18689,7 @@
         <v>193</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C233" s="76" t="s">
         <v>1066</v>
@@ -21386,7 +21404,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>1</v>
@@ -22020,7 +22038,7 @@
         <v>39</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
@@ -22836,7 +22854,7 @@
         <v>281</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C54" s="18"/>
       <c r="D54" s="18"/>
@@ -22864,7 +22882,7 @@
         <v>282</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C55" s="18"/>
       <c r="D55" s="18"/>
@@ -22892,7 +22910,7 @@
         <v>283</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C56" s="18"/>
       <c r="D56" s="18"/>
@@ -22920,7 +22938,7 @@
         <v>284</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C57" s="18"/>
       <c r="D57" s="18"/>
@@ -22948,7 +22966,7 @@
         <v>285</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C58" s="18"/>
       <c r="D58" s="18"/>
@@ -22976,7 +22994,7 @@
         <v>286</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C59" s="18"/>
       <c r="D59" s="18"/>
@@ -23004,7 +23022,7 @@
         <v>287</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C60" s="18"/>
       <c r="D60" s="18"/>
@@ -23032,7 +23050,7 @@
         <v>288</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C61" s="18"/>
       <c r="D61" s="18"/>
@@ -23060,7 +23078,7 @@
         <v>289</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C62" s="18"/>
       <c r="D62" s="18"/>
@@ -23088,7 +23106,7 @@
         <v>290</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C63" s="18"/>
       <c r="D63" s="18"/>
@@ -23116,7 +23134,7 @@
         <v>291</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C64" s="18"/>
       <c r="D64" s="18"/>
@@ -23144,7 +23162,7 @@
         <v>292</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C65" s="18"/>
       <c r="D65" s="18"/>
@@ -23172,7 +23190,7 @@
         <v>293</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C66" s="18"/>
       <c r="D66" s="18"/>
@@ -23200,7 +23218,7 @@
         <v>294</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C67" s="18"/>
       <c r="D67" s="18"/>
@@ -23252,7 +23270,7 @@
         <v>295</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C69" s="18"/>
       <c r="D69" s="18"/>
@@ -23308,7 +23326,7 @@
         <v>298</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C71" s="18"/>
       <c r="D71" s="18"/>
@@ -23360,7 +23378,7 @@
         <v>299</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C73" s="18"/>
       <c r="D73" s="18"/>
@@ -23388,7 +23406,7 @@
         <v>300</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C74" s="18"/>
       <c r="D74" s="18"/>
@@ -23872,7 +23890,7 @@
         <v>319</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C92" s="18"/>
       <c r="D92" s="18"/>
@@ -23900,7 +23918,7 @@
         <v>320</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C93" s="18"/>
       <c r="D93" s="18"/>
@@ -24008,7 +24026,7 @@
         <v>323</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C97" s="18"/>
       <c r="D97" s="18"/>
@@ -24036,7 +24054,7 @@
         <v>324</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C98" s="18"/>
       <c r="D98" s="18"/>
@@ -24064,7 +24082,7 @@
         <v>325</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C99" s="18"/>
       <c r="D99" s="18"/>
@@ -24116,7 +24134,7 @@
         <v>326</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C101" s="18"/>
       <c r="D101" s="18"/>
@@ -24172,7 +24190,7 @@
         <v>327</v>
       </c>
       <c r="B103" s="22" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C103" s="18"/>
       <c r="D103" s="18"/>
@@ -24252,7 +24270,7 @@
         <v>330</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C106" s="18"/>
       <c r="D106" s="18"/>
@@ -24280,7 +24298,7 @@
         <v>331</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C107" s="18"/>
       <c r="D107" s="18"/>
@@ -24432,7 +24450,7 @@
         <v>333</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C113" s="18"/>
       <c r="D113" s="18"/>
@@ -24484,7 +24502,7 @@
         <v>334</v>
       </c>
       <c r="B115" s="24" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C115" s="18"/>
       <c r="D115" s="18"/>
@@ -24536,7 +24554,7 @@
         <v>335</v>
       </c>
       <c r="B117" s="92" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C117" s="18"/>
       <c r="D117" s="18"/>
@@ -24844,7 +24862,7 @@
         <v>340</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C129" s="18"/>
       <c r="D129" s="18"/>
@@ -24900,7 +24918,7 @@
         <v>341</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C131" s="18"/>
       <c r="D131" s="18"/>
@@ -25652,7 +25670,7 @@
         <v>370</v>
       </c>
       <c r="B159" s="94" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C159" s="18"/>
       <c r="D159" s="18"/>
@@ -26028,7 +26046,7 @@
         <v>441</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C173" s="18"/>
       <c r="D173" s="18"/>
@@ -26077,10 +26095,10 @@
     </row>
     <row r="175" spans="1:22" ht="15.75" customHeight="1">
       <c r="A175" s="91" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B175" s="94" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C175" s="18"/>
       <c r="D175" s="18"/>
@@ -26105,10 +26123,10 @@
     </row>
     <row r="176" spans="1:22" ht="15.75" customHeight="1">
       <c r="A176" s="91" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B176" s="94" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C176" s="18"/>
       <c r="D176" s="18"/>
@@ -26133,10 +26151,10 @@
     </row>
     <row r="177" spans="1:22" ht="15.75" customHeight="1">
       <c r="A177" s="91" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B177" s="94" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C177" s="18"/>
       <c r="D177" s="18"/>
@@ -26161,10 +26179,10 @@
     </row>
     <row r="178" spans="1:22" ht="15.75" customHeight="1">
       <c r="A178" s="91" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B178" s="94" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="C178" s="18"/>
       <c r="D178" s="18"/>
@@ -26189,10 +26207,10 @@
     </row>
     <row r="179" spans="1:22" ht="15.75" customHeight="1">
       <c r="A179" s="91" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B179" s="94" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C179" s="18"/>
       <c r="D179" s="18"/>
@@ -26247,7 +26265,7 @@
         <v>1087</v>
       </c>
       <c r="C181" s="62" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D181" s="18"/>
       <c r="E181" s="18"/>
@@ -26301,10 +26319,10 @@
     </row>
     <row r="183" spans="1:22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A183" s="91" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B183" s="94" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C183" s="18"/>
       <c r="D183" s="18"/>
@@ -26359,10 +26377,10 @@
     </row>
     <row r="185" spans="1:22" ht="15.75" customHeight="1">
       <c r="A185" s="91" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B185" s="94" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C185" s="18"/>
       <c r="D185" s="18"/>
@@ -26411,10 +26429,10 @@
     </row>
     <row r="187" spans="1:22" ht="15.75" customHeight="1">
       <c r="A187" s="91" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B187" s="94" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C187" s="18"/>
       <c r="D187" s="18"/>
@@ -30929,7 +30947,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C1" s="26" t="s">
         <v>1</v>
@@ -32791,7 +32809,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C1" s="65" t="s">
         <v>1</v>
@@ -32805,7 +32823,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="96" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C2" s="72" t="s">
         <v>1048</v>
@@ -32880,7 +32898,7 @@
         <v>1082</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>417</v>
@@ -32894,7 +32912,7 @@
         <v>1083</v>
       </c>
       <c r="C9" s="62" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>420</v>
@@ -32908,7 +32926,7 @@
         <v>1118</v>
       </c>
       <c r="C10" s="62" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>423</v>
@@ -32922,7 +32940,7 @@
         <v>1119</v>
       </c>
       <c r="C11" s="62" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>426</v>
@@ -32936,7 +32954,7 @@
         <v>1120</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>429</v>
@@ -32950,7 +32968,7 @@
         <v>1121</v>
       </c>
       <c r="C13" s="62" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>432</v>
@@ -32964,7 +32982,7 @@
         <v>1122</v>
       </c>
       <c r="C14" s="62" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>435</v>
@@ -33000,13 +33018,13 @@
     </row>
     <row r="17" spans="1:4" ht="15.75" thickBot="1">
       <c r="A17" s="91" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>442</v>
       </c>
       <c r="C17" s="62" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D17" s="9"/>
     </row>
@@ -33015,10 +33033,10 @@
         <v>441</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C18" s="62" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>442</v>
@@ -33029,7 +33047,7 @@
         <v>444</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C19" s="62" t="s">
         <v>976</v>
@@ -33292,7 +33310,7 @@
         <v>67</v>
       </c>
       <c r="C43" s="60" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>67</v>
@@ -33326,7 +33344,7 @@
         <v>1070</v>
       </c>
       <c r="C46" s="60" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1070</v>
@@ -33337,13 +33355,13 @@
         <v>89</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C47" s="60" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
@@ -33374,7 +33392,7 @@
         <v>482</v>
       </c>
       <c r="C50" s="60" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>482</v>
@@ -33434,7 +33452,7 @@
         <v>485</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C54" s="59" t="s">
         <v>1130</v>
@@ -33459,13 +33477,13 @@
     </row>
     <row r="56" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A56" s="91" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B56" s="15" t="s">
         <v>1303</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="C56" s="64" t="s">
         <v>1304</v>
-      </c>
-      <c r="C56" s="64" t="s">
-        <v>1305</v>
       </c>
       <c r="D56" s="1"/>
     </row>
@@ -33477,7 +33495,7 @@
         <v>1079</v>
       </c>
       <c r="C57" s="60" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>232</v>
@@ -33681,7 +33699,7 @@
         <v>1085</v>
       </c>
       <c r="C75" s="62" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>495</v>
@@ -33771,7 +33789,7 @@
         <v>1087</v>
       </c>
       <c r="C83" s="62" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D83" s="9" t="s">
         <v>382</v>
@@ -33939,7 +33957,7 @@
         <v>1088</v>
       </c>
       <c r="C97" s="62" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D97" s="9" t="s">
         <v>508</v>
@@ -34017,7 +34035,7 @@
         <v>1089</v>
       </c>
       <c r="C104" s="63" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>392</v>
@@ -34028,10 +34046,10 @@
         <v>393</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C105" s="62" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>394</v>
@@ -34073,19 +34091,19 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A109" s="9" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B109" s="9" t="s">
         <v>32</v>
       </c>
       <c r="C109" s="62" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D109" s="9"/>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A110" s="91" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B110" s="9" t="s">
         <v>15</v>
@@ -34097,7 +34115,7 @@
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A111" s="9" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="B111" s="9" t="s">
         <v>45</v>
@@ -34109,7 +34127,7 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A112" s="9" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B112" s="9" t="s">
         <v>48</v>
@@ -34187,7 +34205,7 @@
         <v>1090</v>
       </c>
       <c r="C119" s="63" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D119" s="9" t="s">
         <v>400</v>
@@ -34201,7 +34219,7 @@
         <v>1090</v>
       </c>
       <c r="C120" s="63" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D120" s="9" t="s">
         <v>400</v>
@@ -34221,7 +34239,7 @@
         <v>1091</v>
       </c>
       <c r="C122" s="63" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D122" s="9" t="s">
         <v>516</v>
@@ -34235,7 +34253,7 @@
         <v>1092</v>
       </c>
       <c r="C123" s="63" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D123" s="9" t="s">
         <v>398</v>
@@ -34249,7 +34267,7 @@
         <v>1092</v>
       </c>
       <c r="C124" s="63" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D124" s="9" t="s">
         <v>398</v>
@@ -34269,7 +34287,7 @@
         <v>1093</v>
       </c>
       <c r="C126" s="59" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>519</v>
@@ -34283,7 +34301,7 @@
         <v>1094</v>
       </c>
       <c r="C127" s="59" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>521</v>
@@ -34297,7 +34315,7 @@
         <v>1094</v>
       </c>
       <c r="C128" s="63" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D128" s="9" t="s">
         <v>521</v>
@@ -34317,7 +34335,7 @@
         <v>1090</v>
       </c>
       <c r="C130" s="63" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D130" s="9" t="s">
         <v>400</v>
@@ -34331,7 +34349,7 @@
         <v>1092</v>
       </c>
       <c r="C131" s="63" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D131" s="9" t="s">
         <v>398</v>
@@ -34345,7 +34363,7 @@
         <v>1095</v>
       </c>
       <c r="C132" s="59" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>525</v>
@@ -34376,7 +34394,7 @@
         <v>528</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C135" s="62" t="s">
         <v>530</v>
@@ -34390,7 +34408,7 @@
         <v>401</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C136" s="62" t="s">
         <v>530</v>
@@ -34433,7 +34451,7 @@
         <v>1096</v>
       </c>
       <c r="C140" s="62" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D140" s="9" t="s">
         <v>1023</v>
@@ -34509,7 +34527,7 @@
         <v>1097</v>
       </c>
       <c r="C146" s="62" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D146" s="9" t="s">
         <v>539</v>
@@ -34523,7 +34541,7 @@
         <v>1098</v>
       </c>
       <c r="C147" s="62" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D147" s="9" t="s">
         <v>541</v>
@@ -34571,7 +34589,7 @@
         <v>1087</v>
       </c>
       <c r="C151" s="62" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D151" s="9" t="s">
         <v>382</v>
@@ -34609,7 +34627,7 @@
         <v>1117</v>
       </c>
       <c r="C154" s="62" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="D154" s="9" t="s">
         <v>409</v>
@@ -34693,7 +34711,7 @@
         <v>1085</v>
       </c>
       <c r="C162" s="38" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D162" s="38" t="s">
         <v>495</v>
@@ -34749,7 +34767,7 @@
         <v>1100</v>
       </c>
       <c r="C167" s="62" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D167" s="9" t="s">
         <v>1071</v>
@@ -34774,10 +34792,10 @@
         <v>413</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C169" s="62" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D169" s="9" t="s">
         <v>414</v>
@@ -34844,7 +34862,7 @@
         <v>1087</v>
       </c>
       <c r="C175" s="62" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D175" s="9" t="s">
         <v>1087</v>
@@ -34852,58 +34870,58 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A176" s="9" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B176" s="9" t="s">
         <v>1159</v>
       </c>
-      <c r="B176" s="9" t="s">
+      <c r="C176" s="62" t="s">
         <v>1160</v>
       </c>
-      <c r="C176" s="62" t="s">
-        <v>1161</v>
-      </c>
       <c r="D176" s="9" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A177" s="9" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B177" s="9" t="s">
         <v>1162</v>
       </c>
-      <c r="B177" s="9" t="s">
-        <v>1163</v>
-      </c>
       <c r="C177" s="9" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D177" s="9" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A178" s="91" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B178" s="9" t="s">
         <v>1164</v>
       </c>
-      <c r="B178" s="9" t="s">
-        <v>1165</v>
-      </c>
       <c r="C178" s="9" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D178" s="9" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A179" s="9" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B179" s="9" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C179" s="9" t="s">
         <v>1166</v>
       </c>
-      <c r="C179" s="9" t="s">
-        <v>1167</v>
-      </c>
       <c r="D179" s="9" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
@@ -34913,50 +34931,50 @@
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A181" s="29"/>
       <c r="B181" s="35" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C181" s="66"/>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A182" s="9" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B182" s="9" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C182" s="62" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="D182" s="9" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A183" s="9" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B183" s="9" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C183" s="62" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A184" s="91" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C184" s="9"/>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A185" s="9" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B185" s="9" t="s">
         <v>1282</v>
-      </c>
-      <c r="B185" s="9" t="s">
-        <v>1283</v>
       </c>
       <c r="C185" s="9"/>
     </row>

--- a/config/testdata/testdata.xlsx
+++ b/config/testdata/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MMHNZ_V2_AUTOMATION\config\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E3AEF5-69EA-4ACF-97C2-1C6DB9EA01FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3345DA54-5B04-442A-8A75-AD344F7C26C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Happy_Path_Patient_Web_and_MR" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="1322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="1333">
   <si>
     <t>KEY</t>
   </si>
@@ -4017,10 +4017,43 @@
     <t>VM07 Loc1 Evo Prod;GP1 Vm07 Loc1;Send Script by Post;Next Day;Panadol (Optizorb) 500mg Caplets;Repeat Medication Testing for PATIENT TO COLLECT</t>
   </si>
   <si>
-    <t>https://app.managemyhealth.co.nz/home</t>
-  </si>
-  <si>
     <t>Pacifen 10mg Tab;1 tabs, Twice Daily, 1 week;14;GP2WHITE;Automation1_Loc1</t>
+  </si>
+  <si>
+    <t>https://v2portal.mmhnz.cloud/home</t>
+  </si>
+  <si>
+    <t>VM07 HC Evo Prod;VM07 Loc1 Evo Prod;Patient Communication;Patient;peter;Received Msg Testing_RANDOM;Body : Received Message Testing_RANDOM;MMHtest.jpg;Compose Message_RANDOM;Body : Reply Message Testing_RANDOM;Compose Message</t>
+  </si>
+  <si>
+    <t>NON_CLINICAL_MESSAGE_DETAILS</t>
+  </si>
+  <si>
+    <t>Automation1_HC1;Automation1_Loc1;Internal Communication;Patient;Auto;Non Clinical Msg Testing_RANDOM;Body : Received Message Testing_RANDOM;MMHtest.jpg;Compose Message_RANDOM;Body : Reply Message Testing_RANDOM;Compose Message Testing_RANDOM;TestAutomation</t>
+  </si>
+  <si>
+    <t>ALLOW_PATIENT_MESSAGE_DETAILS</t>
+  </si>
+  <si>
+    <t>Automation1_HC1;Automation1_Loc1;Internal Communication;Patient;Auto;Allow Patient Msg Testing_RANDOM;Body : Received Message Testing_RANDOM;MMHtest.jpg;Compose Message_RANDOM;Body : Reply Message Testing_RANDOM;Compose Message Testing_RANDOM;TestAutomation</t>
+  </si>
+  <si>
+    <t>VM07 HC Evo Prod;VM07 Loc1 Evo Prod;Patient Communication;Patient;peter;Allow Patient Msg Testing_RANDOM;Body : Received Message Testing_RANDOM;MMHtest.jpg;Compose Message_RANDOM;Body : Reply Message Testing_RANDOM;Compose Message</t>
+  </si>
+  <si>
+    <t>VM07 HC Evo Prod;VM07 Loc1 Evo Prod;Patient Communication;Patient;peter;Non Clinical Msg Testing_RANDOM;Body : Received Message Testing_RANDOM;MMHtest.jpg;Compose Message_RANDOM;Body : Reply Message Testing_RANDOM;Compose Message</t>
+  </si>
+  <si>
+    <t>NONCLINICAL_MESSAGE_DETAILS</t>
+  </si>
+  <si>
+    <t>ALLOWPATIENT_MESSAGE_DETAILS</t>
+  </si>
+  <si>
+    <t>Allow Patient Msg Testing_RANDOM</t>
+  </si>
+  <si>
+    <t>Non Clinical Msg Testing_RANDOM</t>
   </si>
 </sst>
 </file>
@@ -4264,7 +4297,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -4470,6 +4503,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -4477,7 +4519,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4730,6 +4772,9 @@
     <xf numFmtId="0" fontId="24" fillId="11" borderId="3" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4999,7 +5044,7 @@
         <v>1257</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D2" s="57" t="s">
         <v>1123</v>
@@ -7735,7 +7780,7 @@
         <v>104</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C93" s="76" t="s">
         <v>1049</v>
@@ -32794,7 +32839,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W1001"/>
+  <dimension ref="A1:W1004"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1" collapsed="1"/>
@@ -33469,7 +33514,7 @@
         <v>1084</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>1132</v>
+        <v>1322</v>
       </c>
       <c r="D55" s="15" t="s">
         <v>1020</v>
@@ -33720,509 +33765,519 @@
       </c>
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A77" s="9"/>
+      <c r="A77" s="9" t="s">
+        <v>1330</v>
+      </c>
       <c r="B77" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="C77" s="62" t="s">
-        <v>498</v>
+        <v>1331</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>1331</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>498</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A78" s="9" t="s">
+      <c r="A78" s="9"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="98"/>
+      <c r="D78" s="9"/>
+    </row>
+    <row r="79" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A79" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>1086</v>
       </c>
-      <c r="C78" s="60" t="s">
+      <c r="C79" s="60" t="s">
         <v>1130</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="62"/>
-      <c r="D79" s="1"/>
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A80" s="9" t="s">
-        <v>501</v>
+        <v>1329</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="C80" s="62" t="s">
-        <v>498</v>
+        <v>1332</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>1332</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>498</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A81" s="34"/>
-      <c r="B81" s="34" t="s">
-        <v>502</v>
-      </c>
-      <c r="C81" s="68"/>
-      <c r="D81" s="34" t="s">
-        <v>502</v>
+      <c r="A81" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C81" s="64" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>1326</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A82" s="9"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="62"/>
-      <c r="D82" s="9"/>
+      <c r="A82" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C82" s="64" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>1324</v>
+      </c>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A83" s="9" t="s">
-        <v>381</v>
+        <v>501</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>1087</v>
+        <v>498</v>
       </c>
       <c r="C83" s="62" t="s">
-        <v>1143</v>
+        <v>498</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>382</v>
+        <v>498</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A84" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="C84" s="62" t="s">
-        <v>503</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>384</v>
+      <c r="A84" s="34"/>
+      <c r="B84" s="34" t="s">
+        <v>502</v>
+      </c>
+      <c r="C84" s="68"/>
+      <c r="D84" s="34" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A85" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="B85" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="C85" s="62" t="s">
-        <v>386</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>386</v>
-      </c>
+      <c r="A85" s="9"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="62"/>
+      <c r="D85" s="9"/>
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A86" s="9" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>412</v>
+        <v>1087</v>
       </c>
       <c r="C86" s="62" t="s">
-        <v>1103</v>
+        <v>1143</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A87" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="C87" s="62" t="s">
+        <v>503</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A88" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="C88" s="62" t="s">
+        <v>386</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A89" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="C89" s="62" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A90" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B90" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="C87" s="62" t="s">
+      <c r="C90" s="62" t="s">
         <v>1104</v>
       </c>
-      <c r="D87" s="9" t="s">
+      <c r="D90" s="9" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A88" s="34"/>
-      <c r="B88" s="34" t="s">
+    <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A91" s="34"/>
+      <c r="B91" s="34" t="s">
         <v>506</v>
       </c>
-      <c r="C88" s="68"/>
-      <c r="D88" s="34" t="s">
+      <c r="C91" s="68"/>
+      <c r="D91" s="34" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A89" s="9"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="62"/>
-      <c r="D89" s="9"/>
-    </row>
-    <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A90" s="9"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="62"/>
-      <c r="D90" s="9"/>
-    </row>
-    <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A91" s="9"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="62"/>
-      <c r="D91" s="9"/>
-    </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A92" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C92" s="60" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>10</v>
-      </c>
+      <c r="A92" s="9"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="62"/>
+      <c r="D92" s="9"/>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A93" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C93" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>12</v>
-      </c>
+      <c r="A93" s="9"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="62"/>
+      <c r="D93" s="9"/>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A94" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C94" s="62" t="s">
-        <v>18</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>18</v>
-      </c>
+      <c r="A94" s="9"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="62"/>
+      <c r="D94" s="9"/>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A95" s="9" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>15</v>
+        <v>1072</v>
       </c>
       <c r="C95" s="60" t="s">
-        <v>16</v>
+        <v>1126</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A96" s="9" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C96" s="60" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A97" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A98" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A99" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C99" s="60" t="s">
+        <v>46</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A100" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B100" s="9" t="s">
         <v>1088</v>
       </c>
-      <c r="C97" s="62" t="s">
+      <c r="C100" s="62" t="s">
         <v>1144</v>
       </c>
-      <c r="D97" s="9" t="s">
+      <c r="D100" s="9" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A98" s="9"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="62"/>
-      <c r="D98" s="9"/>
-    </row>
-    <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A99" s="1" t="s">
+    <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A101" s="9"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="62"/>
+      <c r="D101" s="9"/>
+    </row>
+    <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A102" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B99" s="9" t="s">
+      <c r="B102" s="9" t="s">
         <v>1101</v>
       </c>
-      <c r="C99" s="60" t="s">
+      <c r="C102" s="60" t="s">
         <v>1127</v>
       </c>
-      <c r="D99" s="9" t="s">
+      <c r="D102" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A100" s="1" t="s">
+    <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A103" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B100" s="9" t="s">
+      <c r="B103" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="C100" s="60" t="s">
+      <c r="C103" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D100" s="9" t="s">
+      <c r="D103" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A101" s="1" t="s">
+    <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A104" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B101" s="9" t="s">
+      <c r="B104" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C101" s="60" t="s">
+      <c r="C104" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="D101" s="9" t="s">
+      <c r="D104" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A102" s="9"/>
-      <c r="B102" s="9"/>
-      <c r="C102" s="62"/>
-      <c r="D102" s="9"/>
-    </row>
-    <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A103" s="29"/>
-      <c r="B103" s="35" t="s">
+    <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A105" s="9"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="62"/>
+      <c r="D105" s="9"/>
+    </row>
+    <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A106" s="29"/>
+      <c r="B106" s="35" t="s">
         <v>509</v>
       </c>
-      <c r="C103" s="66"/>
-      <c r="D103" s="35" t="s">
+      <c r="C106" s="66"/>
+      <c r="D106" s="35" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A104" s="28" t="s">
+    <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A107" s="28" t="s">
         <v>391</v>
       </c>
-      <c r="B104" s="9" t="s">
+      <c r="B107" s="9" t="s">
         <v>1089</v>
       </c>
-      <c r="C104" s="63" t="s">
+      <c r="C107" s="63" t="s">
         <v>1145</v>
       </c>
-      <c r="D104" s="9" t="s">
+      <c r="D107" s="9" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A105" s="9" t="s">
+    <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A108" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="B105" s="9" t="s">
+      <c r="B108" s="9" t="s">
         <v>1312</v>
       </c>
-      <c r="C105" s="62" t="s">
+      <c r="C108" s="62" t="s">
         <v>1305</v>
       </c>
-      <c r="D105" s="9" t="s">
+      <c r="D108" s="9" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A106" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="C106" s="62" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A107" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="C107" s="62" t="s">
-        <v>49</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A108" s="9"/>
-      <c r="B108" s="9"/>
-      <c r="C108" s="62"/>
-      <c r="D108" s="9"/>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A109" s="9" t="s">
-        <v>1306</v>
+        <v>395</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>32</v>
+        <v>396</v>
       </c>
       <c r="C109" s="62" t="s">
-        <v>1307</v>
-      </c>
-      <c r="D109" s="9"/>
+        <v>1105</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A110" s="91" t="s">
-        <v>1308</v>
+      <c r="A110" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C110" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D110" s="9"/>
+        <v>510</v>
+      </c>
+      <c r="C110" s="62" t="s">
+        <v>49</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A111" s="9" t="s">
-        <v>1309</v>
-      </c>
-      <c r="B111" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C111" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A111" s="9"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="62"/>
       <c r="D111" s="9"/>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A112" s="9" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C112" s="9" t="s">
-        <v>49</v>
+        <v>32</v>
+      </c>
+      <c r="C112" s="62" t="s">
+        <v>1307</v>
       </c>
       <c r="D112" s="9"/>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A113" s="9"/>
-      <c r="B113" s="9"/>
-      <c r="C113" s="62"/>
+      <c r="A113" s="91" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="D113" s="9"/>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A114" s="9"/>
-      <c r="B114" s="9"/>
-      <c r="C114" s="62"/>
+      <c r="A114" s="9" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="D114" s="9"/>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A115" s="9" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D115" s="9"/>
+    </row>
+    <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A116" s="9"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="62"/>
+      <c r="D116" s="9"/>
+    </row>
+    <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A117" s="9"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="62"/>
+      <c r="D117" s="9"/>
+    </row>
+    <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A118" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="B115" s="9" t="s">
+      <c r="B118" s="9" t="s">
         <v>511</v>
       </c>
-      <c r="C115" s="62" t="s">
+      <c r="C118" s="62" t="s">
         <v>1106</v>
       </c>
-      <c r="D115" s="9" t="s">
+      <c r="D118" s="9" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A116" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="B116" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C116" s="62" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D116" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A117" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="B117" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C117" s="62" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A118" s="9"/>
-      <c r="B118" s="9"/>
-      <c r="C118" s="62"/>
-      <c r="D118" s="9"/>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A119" s="9" t="s">
-        <v>513</v>
+        <v>403</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C119" s="63" t="s">
-        <v>1145</v>
+        <v>25</v>
+      </c>
+      <c r="C119" s="62" t="s">
+        <v>1107</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>400</v>
+        <v>25</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A120" s="9" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C120" s="63" t="s">
-        <v>1145</v>
+        <v>53</v>
+      </c>
+      <c r="C120" s="62" t="s">
+        <v>1108</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>400</v>
+        <v>53</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
@@ -34233,777 +34288,784 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A122" s="9" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C122" s="63" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>516</v>
+        <v>400</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A123" s="9" t="s">
-        <v>397</v>
+        <v>514</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C123" s="63" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A124" s="9"/>
+      <c r="B124" s="9"/>
+      <c r="C124" s="62"/>
+      <c r="D124" s="9"/>
+    </row>
+    <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A125" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C125" s="63" t="s">
         <v>1146</v>
       </c>
-      <c r="D123" s="9" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A124" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="B124" s="9" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C124" s="63" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D124" s="9" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A125" s="9"/>
-      <c r="B125" s="9"/>
-      <c r="C125" s="62"/>
-      <c r="D125" s="9"/>
+      <c r="D125" s="9" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A126" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C126" s="59" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>519</v>
+        <v>397</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C126" s="63" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A127" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C127" s="59" t="s">
+        <v>517</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C127" s="63" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A128" s="9"/>
+      <c r="B128" s="9"/>
+      <c r="C128" s="62"/>
+      <c r="D128" s="9"/>
+    </row>
+    <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A129" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C129" s="59" t="s">
         <v>1147</v>
       </c>
-      <c r="D127" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A128" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="B128" s="9" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C128" s="63" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D128" s="9" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A129" s="9"/>
-      <c r="B129" s="9"/>
-      <c r="C129" s="62"/>
-      <c r="D129" s="9"/>
+      <c r="D129" s="1" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A130" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="B130" s="9" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C130" s="63" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D130" s="9" t="s">
-        <v>400</v>
+        <v>520</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C130" s="59" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A131" s="9" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C131" s="63" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>398</v>
+        <v>521</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A132" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C132" s="59" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>525</v>
-      </c>
+      <c r="A132" s="9"/>
+      <c r="B132" s="9"/>
+      <c r="C132" s="62"/>
+      <c r="D132" s="9"/>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A133" s="9"/>
-      <c r="B133" s="9"/>
-      <c r="C133" s="62"/>
-      <c r="D133" s="9"/>
+      <c r="A133" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C133" s="63" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D133" s="9" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A134" s="9" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="C134" s="62" t="s">
-        <v>1109</v>
+        <v>1092</v>
+      </c>
+      <c r="C134" s="63" t="s">
+        <v>1146</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>527</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A135" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="B135" s="9" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C135" s="62" t="s">
-        <v>530</v>
-      </c>
-      <c r="D135" s="9" t="s">
-        <v>529</v>
+        <v>524</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C135" s="59" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A136" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="B136" s="9" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C136" s="62" t="s">
-        <v>530</v>
-      </c>
-      <c r="D136" s="9" t="s">
-        <v>394</v>
-      </c>
+      <c r="A136" s="9"/>
+      <c r="B136" s="9"/>
+      <c r="C136" s="62"/>
+      <c r="D136" s="9"/>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A137" s="9"/>
-      <c r="B137" s="9"/>
-      <c r="C137" s="62"/>
-      <c r="D137" s="9"/>
+      <c r="A137" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="C137" s="62" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D137" s="9" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A138" s="9" t="s">
-        <v>406</v>
+        <v>528</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>407</v>
+        <v>1311</v>
       </c>
       <c r="C138" s="62" t="s">
-        <v>1110</v>
+        <v>530</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>407</v>
+        <v>529</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A139" s="9"/>
-      <c r="B139" s="9"/>
-      <c r="C139" s="62"/>
-      <c r="D139" s="9"/>
+      <c r="A139" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C139" s="62" t="s">
+        <v>530</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A140" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="B140" s="9" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C140" s="62" t="s">
-        <v>1148</v>
-      </c>
-      <c r="D140" s="9" t="s">
-        <v>1023</v>
-      </c>
+      <c r="A140" s="9"/>
+      <c r="B140" s="9"/>
+      <c r="C140" s="62"/>
+      <c r="D140" s="9"/>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A141" s="9" t="s">
-        <v>532</v>
+        <v>406</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>12</v>
+        <v>407</v>
       </c>
       <c r="C141" s="62" t="s">
-        <v>13</v>
+        <v>1110</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>12</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A142" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="B142" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="C142" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="D142" s="9" t="s">
-        <v>380</v>
-      </c>
+      <c r="A142" s="9"/>
+      <c r="B142" s="9"/>
+      <c r="C142" s="62"/>
+      <c r="D142" s="9"/>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A143" s="9" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>535</v>
+        <v>1096</v>
       </c>
       <c r="C143" s="62" t="s">
-        <v>1111</v>
+        <v>1148</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>535</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A144" s="9"/>
-      <c r="B144" s="9"/>
-      <c r="C144" s="62"/>
-      <c r="D144" s="9"/>
+      <c r="A144" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C144" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D144" s="9" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A145" s="9" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>537</v>
+        <v>380</v>
       </c>
       <c r="C145" s="62" t="s">
-        <v>1112</v>
+        <v>380</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>537</v>
+        <v>380</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A146" s="36" t="s">
-        <v>538</v>
+      <c r="A146" s="9" t="s">
+        <v>534</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>1097</v>
+        <v>535</v>
       </c>
       <c r="C146" s="62" t="s">
-        <v>1149</v>
+        <v>1111</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A147" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="B147" s="9" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C147" s="62" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D147" s="9" t="s">
-        <v>541</v>
-      </c>
+      <c r="A147" s="9"/>
+      <c r="B147" s="9"/>
+      <c r="C147" s="62"/>
+      <c r="D147" s="9"/>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A148" s="9" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C148" s="62" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A149" s="9" t="s">
-        <v>544</v>
+      <c r="A149" s="36" t="s">
+        <v>538</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>545</v>
+        <v>1097</v>
       </c>
       <c r="C149" s="62" t="s">
-        <v>1114</v>
+        <v>1149</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A150" s="9"/>
-      <c r="B150" s="9"/>
-      <c r="C150" s="62"/>
-      <c r="D150" s="9"/>
+      <c r="A150" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="B150" s="9" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C150" s="62" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A151" s="9" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>1087</v>
+        <v>543</v>
       </c>
       <c r="C151" s="62" t="s">
-        <v>1143</v>
+        <v>1113</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>382</v>
+        <v>543</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A152" s="9" t="s">
-        <v>404</v>
+        <v>544</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="C152" s="72" t="s">
-        <v>1115</v>
+        <v>545</v>
+      </c>
+      <c r="C152" s="62" t="s">
+        <v>1114</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>405</v>
+        <v>545</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A153" s="34"/>
-      <c r="B153" s="34" t="s">
-        <v>547</v>
-      </c>
-      <c r="C153" s="68"/>
-      <c r="D153" s="34" t="s">
-        <v>547</v>
-      </c>
+      <c r="A153" s="9"/>
+      <c r="B153" s="9"/>
+      <c r="C153" s="62"/>
+      <c r="D153" s="9"/>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A154" s="9" t="s">
-        <v>408</v>
+        <v>546</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>1117</v>
+        <v>1087</v>
       </c>
       <c r="C154" s="62" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A155" s="9" t="s">
-        <v>30</v>
+        <v>404</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C155" s="60" t="s">
-        <v>1129</v>
+        <v>405</v>
+      </c>
+      <c r="C155" s="72" t="s">
+        <v>1115</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A156" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B156" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C156" s="60" t="s">
-        <v>33</v>
-      </c>
-      <c r="D156" s="9" t="s">
-        <v>32</v>
+      <c r="A156" s="34"/>
+      <c r="B156" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="C156" s="68"/>
+      <c r="D156" s="34" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A157" s="9"/>
-      <c r="B157" s="9"/>
-      <c r="C157" s="62"/>
-      <c r="D157" s="9"/>
+      <c r="A157" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C157" s="62" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A158" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C158" s="60" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D158" s="9" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A159" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C159" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="D159" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A160" s="9"/>
+      <c r="B160" s="9"/>
+      <c r="C160" s="62"/>
+      <c r="D160" s="9"/>
+    </row>
+    <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A161" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B158" s="9" t="s">
+      <c r="B161" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C158" s="60" t="s">
+      <c r="C161" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="D158" s="9" t="s">
+      <c r="D161" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A159" s="37"/>
-      <c r="B159" s="37"/>
-      <c r="C159" s="69"/>
-      <c r="D159" s="37"/>
-    </row>
-    <row r="160" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A160" s="6"/>
-      <c r="B160" s="38"/>
-      <c r="C160" s="70"/>
-      <c r="D160" s="38"/>
-    </row>
-    <row r="161" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A161" s="39"/>
-      <c r="B161" s="40" t="s">
+    <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A162" s="37"/>
+      <c r="B162" s="37"/>
+      <c r="C162" s="69"/>
+      <c r="D162" s="37"/>
+    </row>
+    <row r="163" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A163" s="6"/>
+      <c r="B163" s="38"/>
+      <c r="C163" s="70"/>
+      <c r="D163" s="38"/>
+    </row>
+    <row r="164" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A164" s="39"/>
+      <c r="B164" s="40" t="s">
         <v>493</v>
       </c>
-      <c r="C161" s="71"/>
-      <c r="D161" s="40" t="s">
+      <c r="C164" s="71"/>
+      <c r="D164" s="40" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A162" s="6" t="s">
+    <row r="165" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A165" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="B162" s="38" t="s">
+      <c r="B165" s="38" t="s">
         <v>1085</v>
       </c>
-      <c r="C162" s="38" t="s">
+      <c r="C165" s="38" t="s">
         <v>1142</v>
       </c>
-      <c r="D162" s="38" t="s">
+      <c r="D165" s="38" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A163" s="6" t="s">
+    <row r="166" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A166" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="B163" s="38" t="s">
+      <c r="B166" s="38" t="s">
         <v>497</v>
       </c>
-      <c r="C163" s="38" t="s">
+      <c r="C166" s="38" t="s">
         <v>497</v>
       </c>
-      <c r="D163" s="38" t="s">
+      <c r="D166" s="38" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A164" s="6"/>
-      <c r="B164" s="38" t="s">
+    <row r="167" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A167" s="6"/>
+      <c r="B167" s="38" t="s">
         <v>498</v>
       </c>
-      <c r="C164" s="38" t="s">
+      <c r="C167" s="38" t="s">
         <v>498</v>
       </c>
-      <c r="D164" s="38" t="s">
+      <c r="D167" s="38" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A165" s="9"/>
-      <c r="B165" s="9"/>
-      <c r="C165" s="62"/>
-      <c r="D165" s="9"/>
-    </row>
-    <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A166" s="29"/>
-      <c r="B166" s="35" t="s">
+    <row r="168" spans="1:4" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A168" s="9"/>
+      <c r="B168" s="9"/>
+      <c r="C168" s="62"/>
+      <c r="D168" s="9"/>
+    </row>
+    <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A169" s="29"/>
+      <c r="B169" s="35" t="s">
         <v>548</v>
       </c>
-      <c r="C166" s="66"/>
-      <c r="D166" s="35" t="s">
+      <c r="C169" s="66"/>
+      <c r="D169" s="35" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A167" s="9" t="s">
+    <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A170" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="B167" s="9" t="s">
+      <c r="B170" s="9" t="s">
         <v>1100</v>
       </c>
-      <c r="C167" s="62" t="s">
+      <c r="C170" s="62" t="s">
         <v>1152</v>
       </c>
-      <c r="D167" s="9" t="s">
+      <c r="D170" s="9" t="s">
         <v>1071</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A168" s="9" t="s">
+    <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A171" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="B168" s="9" t="s">
+      <c r="B171" s="9" t="s">
         <v>551</v>
       </c>
-      <c r="C168" s="62" t="s">
+      <c r="C171" s="62" t="s">
         <v>1116</v>
       </c>
-      <c r="D168" s="9" t="s">
+      <c r="D171" s="9" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A169" s="9" t="s">
+    <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A172" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="B169" s="9" t="s">
+      <c r="B172" s="9" t="s">
         <v>1155</v>
       </c>
-      <c r="C169" s="62" t="s">
+      <c r="C172" s="62" t="s">
         <v>1154</v>
       </c>
-      <c r="D169" s="9" t="s">
+      <c r="D172" s="9" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A170" s="9"/>
-      <c r="B170" s="9"/>
-      <c r="C170" s="62"/>
-      <c r="D170" s="9"/>
-    </row>
-    <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A171" s="1" t="s">
+    <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A173" s="9"/>
+      <c r="B173" s="9"/>
+      <c r="C173" s="62"/>
+      <c r="D173" s="9"/>
+    </row>
+    <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A174" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B171" s="12" t="s">
+      <c r="B174" s="12" t="s">
         <v>1101</v>
       </c>
-      <c r="C171" s="63" t="s">
+      <c r="C174" s="63" t="s">
         <v>1127</v>
       </c>
-      <c r="D171" s="12" t="s">
+      <c r="D174" s="12" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A172" s="1" t="s">
+    <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A175" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B172" s="9" t="s">
+      <c r="B175" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="C172" s="62" t="s">
+      <c r="C175" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D172" s="9" t="s">
+      <c r="D175" s="9" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A173" s="1" t="s">
+    <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A176" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="B173" s="9" t="s">
+      <c r="B176" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C173" s="62" t="s">
+      <c r="C176" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="D173" s="9" t="s">
+      <c r="D176" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A174" s="9"/>
-      <c r="B174" s="9"/>
-      <c r="C174" s="62"/>
-    </row>
-    <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A175" s="9" t="s">
+    <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A177" s="9"/>
+      <c r="B177" s="9"/>
+      <c r="C177" s="62"/>
+    </row>
+    <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A178" s="9" t="s">
         <v>1059</v>
       </c>
-      <c r="B175" s="9" t="s">
+      <c r="B178" s="9" t="s">
         <v>1087</v>
       </c>
-      <c r="C175" s="62" t="s">
+      <c r="C178" s="62" t="s">
         <v>1143</v>
       </c>
-      <c r="D175" s="9" t="s">
+      <c r="D178" s="9" t="s">
         <v>1087</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A176" s="9" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B176" s="9" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C176" s="62" t="s">
-        <v>1160</v>
-      </c>
-      <c r="D176" s="9" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A177" s="9" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B177" s="9" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C177" s="9" t="s">
-        <v>1162</v>
-      </c>
-      <c r="D177" s="9" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A178" s="91" t="s">
-        <v>1163</v>
-      </c>
-      <c r="B178" s="9" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C178" s="9" t="s">
-        <v>1164</v>
-      </c>
-      <c r="D178" s="9" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A179" s="9" t="s">
-        <v>1167</v>
+        <v>1158</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>1165</v>
-      </c>
-      <c r="C179" s="9" t="s">
-        <v>1166</v>
+        <v>1159</v>
+      </c>
+      <c r="C179" s="62" t="s">
+        <v>1160</v>
       </c>
       <c r="D179" s="9" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B180" s="9"/>
-      <c r="C180" s="9"/>
+      <c r="A180" s="9" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B180" s="9" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C180" s="9" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D180" s="9" t="s">
+        <v>1162</v>
+      </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A181" s="29"/>
-      <c r="B181" s="35" t="s">
-        <v>1222</v>
-      </c>
-      <c r="C181" s="66"/>
+      <c r="A181" s="91" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C181" s="9" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D181" s="9" t="s">
+        <v>1164</v>
+      </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A182" s="9" t="s">
-        <v>1221</v>
+        <v>1167</v>
       </c>
       <c r="B182" s="9" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C182" s="62" t="s">
-        <v>1224</v>
+        <v>1165</v>
+      </c>
+      <c r="C182" s="9" t="s">
+        <v>1166</v>
       </c>
       <c r="D182" s="9" t="s">
-        <v>1223</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A183" s="9" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B183" s="9" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C183" s="62" t="s">
-        <v>1224</v>
-      </c>
+      <c r="B183" s="9"/>
+      <c r="C183" s="9"/>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A184" s="91" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B184" s="9" t="s">
-        <v>1279</v>
-      </c>
-      <c r="C184" s="9"/>
+      <c r="A184" s="29"/>
+      <c r="B184" s="35" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C184" s="66"/>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A185" s="9" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C185" s="62" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D185" s="9" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A186" s="9" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B186" s="9" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C186" s="62" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A187" s="91" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B187" s="9" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C187" s="9"/>
+    </row>
+    <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A188" s="9" t="s">
         <v>1281</v>
       </c>
-      <c r="B185" s="9" t="s">
+      <c r="B188" s="9" t="s">
         <v>1282</v>
       </c>
-      <c r="C185" s="9"/>
-    </row>
-    <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A186" s="9"/>
-      <c r="B186" s="9"/>
-      <c r="C186" s="9"/>
-    </row>
-    <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A187" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B187" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C187" s="97" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A188" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C188" s="76" t="s">
-        <v>7</v>
-      </c>
+      <c r="C188" s="9"/>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A189" s="9"/>
@@ -35012,51 +35074,57 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A190" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C190" s="97" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A191" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C191" s="76" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A192" s="9"/>
+      <c r="B192" s="9"/>
+      <c r="C192" s="9"/>
+    </row>
+    <row r="193" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A193" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="B193" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C190" s="76" t="s">
+      <c r="C193" s="76" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A191" s="9"/>
-      <c r="B191" s="9"/>
-      <c r="C191" s="9"/>
-    </row>
-    <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A192" s="1" t="s">
+    <row r="194" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A194" s="9"/>
+      <c r="B194" s="9"/>
+      <c r="C194" s="9"/>
+    </row>
+    <row r="195" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A195" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="B195" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C192" s="76" t="s">
+      <c r="C195" s="76" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A193" s="9"/>
-      <c r="B193" s="9"/>
-      <c r="C193" s="9"/>
-    </row>
-    <row r="194" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A194" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C194" s="76" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A195" s="9"/>
-      <c r="B195" s="9"/>
-      <c r="C195" s="9"/>
     </row>
     <row r="196" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A196" s="9"/>
@@ -35064,21 +35132,27 @@
       <c r="C196" s="9"/>
     </row>
     <row r="197" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A197" s="9"/>
-      <c r="B197" s="9"/>
-      <c r="C197" s="9"/>
-    </row>
-    <row r="198" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A197" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C197" s="76" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A198" s="9"/>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
     </row>
-    <row r="199" spans="1:3" ht="15.75" customHeight="1">
+    <row r="199" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A199" s="9"/>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
     </row>
-    <row r="200" spans="1:3" ht="15.75" customHeight="1">
+    <row r="200" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A200" s="9"/>
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
@@ -35913,24 +35987,36 @@
       <c r="B366" s="9"/>
       <c r="C366" s="9"/>
     </row>
-    <row r="367" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="368" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="367" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A367" s="9"/>
+      <c r="B367" s="9"/>
+      <c r="C367" s="9"/>
+    </row>
+    <row r="368" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A368" s="9"/>
+      <c r="B368" s="9"/>
+      <c r="C368" s="9"/>
+    </row>
+    <row r="369" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A369" s="9"/>
+      <c r="B369" s="9"/>
+      <c r="C369" s="9"/>
+    </row>
+    <row r="370" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="371" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="372" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="373" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="374" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="375" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="376" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="377" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="378" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="379" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="380" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="381" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="382" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="383" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="384" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="385" ht="15.75" customHeight="1"/>
     <row r="386" ht="15.75" customHeight="1"/>
     <row r="387" ht="15.75" customHeight="1"/>
@@ -36548,14 +36634,17 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{51CF91D8-7A2D-4C64-827B-6C41EEA7AE41}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{40CD9620-87B1-4D27-9D9D-9B54D2D36C19}"/>
-    <hyperlink ref="C152" r:id="rId3" xr:uid="{25FAC99D-B272-4C71-9B4D-364D57432552}"/>
+    <hyperlink ref="C155" r:id="rId3" xr:uid="{25FAC99D-B272-4C71-9B4D-364D57432552}"/>
     <hyperlink ref="B2" r:id="rId4" xr:uid="{A5D45DE0-52B9-458D-A530-797F4FB8B49C}"/>
     <hyperlink ref="C2" r:id="rId5" xr:uid="{10A69855-CD62-4F1A-BCBC-DBB64A29B7CA}"/>
-    <hyperlink ref="C187" r:id="rId6" xr:uid="{15BB9E58-3CD9-4309-9710-BEFD670B22CD}"/>
+    <hyperlink ref="C190" r:id="rId6" xr:uid="{15BB9E58-3CD9-4309-9710-BEFD670B22CD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId7"/>

--- a/config/testdata/testdata.xlsx
+++ b/config/testdata/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MMHNZ_V2_AUTOMATION\config\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3030F9DA-20C6-462D-B0E5-1AC4BCEFEEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2797BFE-4FB0-44A7-9F0E-A562D4E06B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="1369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="1365">
   <si>
     <t>KEY</t>
   </si>
@@ -4096,24 +4096,9 @@
     <t>Automation1_HC1;Repeat Prescription;Urgent/Same day;10;Patient to Collect Script - 24 Hours -22;Next Day;33;Patient to Collect Script - 36 Hours - 33;48 Hours;44;Patient to Collect Script - 48 Hours - 44;72 Hours;55;Patient to Collect Script - 72 Hours - 55;</t>
   </si>
   <si>
-    <t>Automation1_Loc3;prostin vr 500mcg/1ml inj(alprostadil);Pending;Next Day;Gp6 White</t>
-  </si>
-  <si>
     <t>Automation1_Loc1;Trasylol 500,000KIU/50ml Inj;Pending;Next Day;GP2WHITE</t>
   </si>
   <si>
-    <t>Automation1_Loc1;Trasylol 500,000KIU/50ml Inj;Pending;Urgent/Same day;GP1 A1 L1</t>
-  </si>
-  <si>
-    <t>Automation1_Loc1;Trasylol 500,000KIU/50ml Inj;Pending;48 Hours;GP3 White</t>
-  </si>
-  <si>
-    <t>Automation1_Loc1;Trasylol 500,000KIU/50ml Inj;Pending;ZOOM Pharmacy home delivery;48 Hours;GP2WHITE</t>
-  </si>
-  <si>
-    <t>Automation1_Loc2;Trasylol 500,000KIU/50ml Inj;Pending;48 Hours;GP3 White</t>
-  </si>
-  <si>
     <t>GP1 Vm07 Loc1 ( VM07 Loc1 Evo Prod );VM07 Loc1 Evo Prod;Send Script by Post;Urgent/Same day;panadol (optizorb) 500mg caplets(paracetamol);pending</t>
   </si>
   <si>
@@ -4136,6 +4121,9 @@
   </si>
   <si>
     <t>https://app.managemyhealth.co.nz/home</t>
+  </si>
+  <si>
+    <t>Automation1_Loc3;prostin vr 500mcg/1ml inj(alprostadil);pending;Next Day;Gp6 White</t>
   </si>
 </sst>
 </file>
@@ -5130,7 +5118,7 @@
         <v>1113</v>
       </c>
       <c r="C2" s="73" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>1113</v>
@@ -6857,13 +6845,13 @@
         <v>1351</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C60" s="75" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>1355</v>
-      </c>
-      <c r="C60" s="75" t="s">
-        <v>1367</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>1356</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
@@ -6981,10 +6969,10 @@
         <v>58</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1356</v>
+        <v>59</v>
       </c>
       <c r="C64" s="75" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>59</v>
@@ -7105,7 +7093,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1357</v>
+        <v>67</v>
       </c>
       <c r="C68" s="75" t="s">
         <v>1302</v>
@@ -7229,7 +7217,7 @@
         <v>74</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>1358</v>
+        <v>1039</v>
       </c>
       <c r="C72" s="75" t="s">
         <v>75</v>
@@ -7353,7 +7341,7 @@
         <v>79</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>1359</v>
+        <v>1034</v>
       </c>
       <c r="C76" s="75" t="s">
         <v>80</v>
@@ -7477,7 +7465,7 @@
         <v>84</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>1359</v>
+        <v>1034</v>
       </c>
       <c r="C80" s="75" t="s">
         <v>80</v>
@@ -7568,7 +7556,7 @@
         <v>86</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>1359</v>
+        <v>1034</v>
       </c>
       <c r="C83" s="75" t="s">
         <v>80</v>
@@ -7659,7 +7647,7 @@
         <v>89</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>1360</v>
+        <v>1035</v>
       </c>
       <c r="C86" s="76" t="s">
         <v>90</v>
@@ -9643,7 +9631,7 @@
         <v>1240</v>
       </c>
       <c r="C150" s="75" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>1114</v>
@@ -33732,10 +33720,10 @@
         <v>70</v>
       </c>
       <c r="C49" s="75" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="50" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
@@ -33830,13 +33818,13 @@
         <v>76</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="C56" s="75" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="57" spans="1:23" ht="15.75" customHeight="1" thickBot="1">
@@ -33998,13 +33986,13 @@
         <v>60</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="C69" s="59" t="s">
         <v>959</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" thickBot="1">

--- a/config/testdata/testdata.xlsx
+++ b/config/testdata/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MMHNZ_V2_AUTOMATION\config\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2797BFE-4FB0-44A7-9F0E-A562D4E06B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C48EB8CD-2A86-4884-AAA2-D50656FFD597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
